--- a/data/historico/semana_320.xlsx
+++ b/data/historico/semana_320.xlsx
@@ -30,10 +30,10 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Visitas Acima de 15min'!$A$2:$J$40</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Fora do Expediente'!$A$2:$K$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Visitas no Almoço'!$A$2:$I$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Ausências'!$A$2:$G$68</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Ausências'!$A$2:$G$63</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Cronograma'!$A$2:$D$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Ponto Estratégico'!$A$2:$AE$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Ranking'!$A$2:$G$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Ranking'!$A$2:$H$39</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1332,25 +1332,25 @@
         </is>
       </c>
       <c r="D6" s="5" t="n">
-        <v>123</v>
+        <v>179</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>41</v>
+        <v>44.75</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>3.78</v>
+        <v>3.68</v>
       </c>
       <c r="H6" s="5" t="n">
         <v>3</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>35.77</v>
+        <v>34.08</v>
       </c>
       <c r="K6" s="5" t="n">
         <v>1</v>
@@ -1359,7 +1359,7 @@
         <v>3</v>
       </c>
       <c r="M6" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N6" s="5" t="n">
         <v>3</v>
@@ -1374,49 +1374,49 @@
         <v>0</v>
       </c>
       <c r="R6" s="5" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="S6" s="5" t="n">
         <v>0</v>
       </c>
       <c r="T6" s="5" t="n">
-        <v>137</v>
+        <v>202</v>
       </c>
       <c r="U6" s="5" t="n">
-        <v>10.22</v>
+        <v>11.39</v>
       </c>
       <c r="V6" s="5" t="n">
-        <v>5.57</v>
+        <v>5.64</v>
       </c>
       <c r="W6" s="5" t="n">
-        <v>16.7</v>
+        <v>22.55</v>
       </c>
       <c r="X6" s="5" t="n">
-        <v>2.52</v>
+        <v>2.7</v>
       </c>
       <c r="Y6" s="5" t="inlineStr">
         <is>
-          <t>R$ 87,64</t>
+          <t>R$ 82,00</t>
         </is>
       </c>
       <c r="Z6" s="5" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AA6" s="5" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AB6" s="5" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AC6" s="5" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>16:03</t>
         </is>
       </c>
     </row>
@@ -1437,16 +1437,16 @@
         </is>
       </c>
       <c r="D7" s="4" t="n">
-        <v>90</v>
+        <v>114</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>30</v>
+        <v>28.5</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>5.42</v>
+        <v>5.54</v>
       </c>
       <c r="H7" s="4" t="n">
         <v>5</v>
@@ -1455,7 +1455,7 @@
         <v>2</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>2.22</v>
+        <v>1.75</v>
       </c>
       <c r="K7" s="4" t="n">
         <v>0</v>
@@ -1464,7 +1464,7 @@
         <v>0</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N7" s="4" t="n">
         <v>25</v>
@@ -1479,49 +1479,49 @@
         <v>0</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="S7" s="4" t="n">
         <v>0</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>20.35</v>
+        <v>23.49</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>4.99</v>
+        <v>4.89</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>14.98</v>
+        <v>19.55</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>2.71</v>
+        <v>2.63</v>
       </c>
       <c r="Y7" s="4" t="inlineStr">
         <is>
-          <t>R$ 81,53</t>
+          <t>R$ 84,07</t>
         </is>
       </c>
       <c r="Z7" s="4" t="inlineStr">
         <is>
-          <t>08:27</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AA7" s="4" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AB7" s="4" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AC7" s="4" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:16</t>
         </is>
       </c>
     </row>
@@ -3949,25 +3949,25 @@
         </is>
       </c>
       <c r="D31" s="4" t="n">
-        <v>87</v>
+        <v>119</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>29</v>
+        <v>29.75</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>6.56</v>
+        <v>6.24</v>
       </c>
       <c r="H31" s="4" t="n">
         <v>6</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>5.75</v>
+        <v>5.04</v>
       </c>
       <c r="K31" s="4" t="n">
         <v>0</v>
@@ -3976,7 +3976,7 @@
         <v>0</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N31" s="4" t="n">
         <v>0</v>
@@ -3991,29 +3991,29 @@
         <v>0</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="S31" s="4" t="n">
         <v>0</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>119</v>
+        <v>174</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>26.89</v>
+        <v>31.61</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>6.54</v>
+        <v>5.78</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>19.62</v>
+        <v>23.1</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>3.17</v>
+        <v>3.09</v>
       </c>
       <c r="Y31" s="4" t="inlineStr">
         <is>
-          <t>R$ 69,68</t>
+          <t>R$ 71,50</t>
         </is>
       </c>
       <c r="Z31" s="4" t="inlineStr">
@@ -4028,12 +4028,12 @@
       </c>
       <c r="AB31" s="4" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AC31" s="4" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>16:15</t>
         </is>
       </c>
     </row>
@@ -5331,19 +5331,19 @@
         </is>
       </c>
       <c r="C6" s="29" t="n">
-        <v>123</v>
+        <v>179</v>
       </c>
       <c r="D6" s="29" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="E6" s="29" t="n">
         <v>0</v>
       </c>
       <c r="F6" s="29" t="n">
-        <v>137</v>
+        <v>202</v>
       </c>
       <c r="G6" s="29" t="n">
-        <v>10.22</v>
+        <v>11.39</v>
       </c>
       <c r="H6" s="2" t="n"/>
       <c r="I6" s="2" t="n"/>
@@ -5360,19 +5360,19 @@
         </is>
       </c>
       <c r="C7" s="29" t="n">
-        <v>90</v>
+        <v>114</v>
       </c>
       <c r="D7" s="29" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="E7" s="29" t="n">
         <v>0</v>
       </c>
       <c r="F7" s="29" t="n">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="G7" s="29" t="n">
-        <v>20.35</v>
+        <v>23.49</v>
       </c>
       <c r="H7" s="2" t="n"/>
       <c r="I7" s="2" t="n"/>
@@ -6056,19 +6056,19 @@
         </is>
       </c>
       <c r="C31" s="29" t="n">
-        <v>87</v>
+        <v>119</v>
       </c>
       <c r="D31" s="29" t="n">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="E31" s="29" t="n">
         <v>0</v>
       </c>
       <c r="F31" s="29" t="n">
-        <v>119</v>
+        <v>174</v>
       </c>
       <c r="G31" s="29" t="n">
-        <v>26.89</v>
+        <v>31.61</v>
       </c>
       <c r="H31" s="2" t="n"/>
       <c r="I31" s="2" t="n"/>
@@ -6317,19 +6317,19 @@
         </is>
       </c>
       <c r="C40" s="26" t="n">
-        <v>3407</v>
+        <v>3519</v>
       </c>
       <c r="D40" s="26" t="n">
-        <v>1407</v>
+        <v>1451</v>
       </c>
       <c r="E40" s="26" t="n">
         <v>5</v>
       </c>
       <c r="F40" s="26" t="n">
-        <v>4819</v>
+        <v>4975</v>
       </c>
       <c r="G40" s="26" t="n">
-        <v>29.3</v>
+        <v>29.27</v>
       </c>
       <c r="H40" s="2" t="n"/>
       <c r="I40" s="2" t="n"/>
@@ -7139,16 +7139,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G278"/>
+  <dimension ref="A1:H278"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
     <col width="35" customWidth="1" min="2" max="2"/>
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="29" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="36" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="6" max="6"/>
+    <col width="32" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -7163,6 +7164,7 @@
       <c r="E1" s="2" t="n"/>
       <c r="F1" s="2" t="n"/>
       <c r="G1" s="2" t="n"/>
+      <c r="H1" s="2" t="n"/>
     </row>
     <row r="2" ht="28" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
@@ -7192,10 +7194,15 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
+          <t>Turnos Sem Trabalhar</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
           <t>Pontuação Final</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>Classificação</t>
         </is>
@@ -7219,12 +7226,15 @@
         <v>4</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="F3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
@@ -7248,12 +7258,15 @@
         <v>4</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="F4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
@@ -7277,12 +7290,15 @@
         <v>4</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="F5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
@@ -7306,12 +7322,15 @@
         <v>4</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="F6" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="H6" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
@@ -7335,12 +7354,15 @@
         <v>4</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="F7" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
@@ -7364,12 +7386,15 @@
         <v>4</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="F8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="H8" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
@@ -7393,12 +7418,15 @@
         <v>3</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="F9" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G9" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="G9" s="4" t="inlineStr">
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
@@ -7422,12 +7450,15 @@
         <v>4</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="F10" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="G10" s="4" t="inlineStr">
+      <c r="H10" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
@@ -7451,12 +7482,15 @@
         <v>4</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="F11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="G11" s="4" t="inlineStr">
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
@@ -7480,12 +7514,15 @@
         <v>3</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="F12" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G12" s="4" t="n">
         <v>99.90000000000001</v>
       </c>
-      <c r="G12" s="4" t="inlineStr">
+      <c r="H12" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
@@ -7509,12 +7546,15 @@
         <v>4</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>98.59999999999999</v>
-      </c>
-      <c r="G13" s="4" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="G13" s="4" t="n">
+        <v>98.8</v>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
@@ -7526,7 +7566,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Alana Amanda Fernandes Ovelar</t>
+          <t>Miglidiane Maciel Ajala</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -7535,15 +7575,18 @@
         </is>
       </c>
       <c r="D14" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>95.90000000000001</v>
-      </c>
-      <c r="G14" s="4" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="G14" s="4" t="n">
+        <v>97.8</v>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
@@ -7555,7 +7598,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Silvina Regina de Souza Valiente</t>
+          <t>Gisele Lopes Justiniano</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -7567,12 +7610,15 @@
         <v>4</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>94.90000000000001</v>
-      </c>
-      <c r="G15" s="4" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="G15" s="4" t="n">
+        <v>96.8</v>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
@@ -7584,7 +7630,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Miglidiane Maciel Ajala</t>
+          <t>Alana Amanda Fernandes Ovelar</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -7593,15 +7639,18 @@
         </is>
       </c>
       <c r="D16" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>94.59999999999999</v>
-      </c>
-      <c r="G16" s="4" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="G16" s="4" t="n">
+        <v>95.90000000000001</v>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
@@ -7625,12 +7674,15 @@
         <v>4</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>94.09999999999999</v>
-      </c>
-      <c r="G17" s="4" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="G17" s="4" t="n">
+        <v>95.09999999999999</v>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
@@ -7642,24 +7694,27 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Gilmar Bitencourt Luiz</t>
+          <t>Silvina Regina de Souza Valiente</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="D18" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>92.90000000000001</v>
-      </c>
-      <c r="G18" s="4" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="G18" s="4" t="n">
+        <v>95.09999999999999</v>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
@@ -7683,12 +7738,15 @@
         <v>4</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>92.3</v>
-      </c>
-      <c r="G19" s="4" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="G19" s="4" t="n">
+        <v>94.5</v>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
@@ -7700,7 +7758,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>Gisele Lopes Justiniano</t>
+          <t>Juliana Patricia Goncalves</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -7709,15 +7767,18 @@
         </is>
       </c>
       <c r="D20" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>92.2</v>
-      </c>
-      <c r="G20" s="4" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="G20" s="4" t="n">
+        <v>93.09999999999999</v>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
@@ -7729,24 +7790,27 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Juliana Patricia Goncalves</t>
+          <t>Gilmar Bitencourt Luiz</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>Equipe 4</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="D21" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>91.7</v>
-      </c>
-      <c r="G21" s="4" t="inlineStr">
+        <v>4</v>
+      </c>
+      <c r="G21" s="4" t="n">
+        <v>92.90000000000001</v>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
@@ -7770,12 +7834,15 @@
         <v>3</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>91</v>
-      </c>
-      <c r="G22" s="4" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="G22" s="4" t="n">
+        <v>92.2</v>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
@@ -7799,43 +7866,49 @@
         <v>3</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>90.7</v>
-      </c>
-      <c r="G23" s="4" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="G23" s="4" t="n">
+        <v>90.90000000000001</v>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="6" t="n">
+      <c r="A24" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="B24" s="6" t="inlineStr">
+      <c r="B24" s="4" t="inlineStr">
         <is>
           <t>Teonilda Florentino Vieira</t>
         </is>
       </c>
-      <c r="C24" s="6" t="inlineStr">
+      <c r="C24" s="4" t="inlineStr">
         <is>
           <t>Equipe 2</t>
         </is>
       </c>
-      <c r="D24" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E24" s="6" t="n">
-        <v>21</v>
-      </c>
-      <c r="F24" s="6" t="n">
-        <v>89.90000000000001</v>
-      </c>
-      <c r="G24" s="6" t="inlineStr">
-        <is>
-          <t>🟡 BOM</t>
+      <c r="D24" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="F24" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G24" s="4" t="n">
+        <v>90.90000000000001</v>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>🟢 EXCELENTE</t>
         </is>
       </c>
     </row>
@@ -7857,12 +7930,15 @@
         <v>4</v>
       </c>
       <c r="E25" s="6" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>88.59999999999999</v>
-      </c>
-      <c r="G25" s="6" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>88.8</v>
+      </c>
+      <c r="H25" s="6" t="inlineStr">
         <is>
           <t>🟡 BOM</t>
         </is>
@@ -7886,12 +7962,15 @@
         <v>2</v>
       </c>
       <c r="E26" s="6" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>87</v>
-      </c>
-      <c r="G26" s="6" t="inlineStr">
+        <v>4</v>
+      </c>
+      <c r="G26" s="6" t="n">
+        <v>87.8</v>
+      </c>
+      <c r="H26" s="6" t="inlineStr">
         <is>
           <t>🟡 BOM</t>
         </is>
@@ -7903,7 +7982,7 @@
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>Brauher Luiz Alvarenga Gonzalez</t>
+          <t>Gisele Olimpia Torres</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
@@ -7912,15 +7991,18 @@
         </is>
       </c>
       <c r="D27" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="E27" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="F27" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="E27" s="6" t="n">
-        <v>21</v>
-      </c>
-      <c r="F27" s="6" t="n">
-        <v>82.7</v>
-      </c>
-      <c r="G27" s="6" t="inlineStr">
+      <c r="G27" s="6" t="n">
+        <v>85.5</v>
+      </c>
+      <c r="H27" s="6" t="inlineStr">
         <is>
           <t>🟡 BOM</t>
         </is>
@@ -7932,7 +8014,7 @@
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>Gisele Olimpia Torres</t>
+          <t>Brauher Luiz Alvarenga Gonzalez</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
@@ -7941,15 +8023,18 @@
         </is>
       </c>
       <c r="D28" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E28" s="6" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>82.7</v>
-      </c>
-      <c r="G28" s="6" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="G28" s="6" t="n">
+        <v>84.5</v>
+      </c>
+      <c r="H28" s="6" t="inlineStr">
         <is>
           <t>🟡 BOM</t>
         </is>
@@ -7973,12 +8058,15 @@
         <v>3</v>
       </c>
       <c r="E29" s="6" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>81.3</v>
-      </c>
-      <c r="G29" s="6" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="G29" s="6" t="n">
+        <v>81.5</v>
+      </c>
+      <c r="H29" s="6" t="inlineStr">
         <is>
           <t>🟡 BOM</t>
         </is>
@@ -8002,12 +8090,15 @@
         <v>4</v>
       </c>
       <c r="E30" s="6" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>78.09999999999999</v>
-      </c>
-      <c r="G30" s="6" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="G30" s="6" t="n">
+        <v>80.90000000000001</v>
+      </c>
+      <c r="H30" s="6" t="inlineStr">
         <is>
           <t>🟡 BOM</t>
         </is>
@@ -8031,12 +8122,15 @@
         <v>1</v>
       </c>
       <c r="E31" s="6" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>75.8</v>
-      </c>
-      <c r="G31" s="6" t="inlineStr">
+        <v>6</v>
+      </c>
+      <c r="G31" s="6" t="n">
+        <v>78</v>
+      </c>
+      <c r="H31" s="6" t="inlineStr">
         <is>
           <t>🟡 BOM</t>
         </is>
@@ -8060,12 +8154,15 @@
         <v>4</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>75.40000000000001</v>
-      </c>
-      <c r="G32" s="6" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="G32" s="6" t="n">
+        <v>77.59999999999999</v>
+      </c>
+      <c r="H32" s="6" t="inlineStr">
         <is>
           <t>🟡 BOM</t>
         </is>
@@ -8089,101 +8186,113 @@
         <v>4</v>
       </c>
       <c r="E33" s="47" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="F33" s="47" t="n">
-        <v>62.6</v>
-      </c>
-      <c r="G33" s="47" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="G33" s="47" t="n">
+        <v>74.2</v>
+      </c>
+      <c r="H33" s="47" t="inlineStr">
         <is>
           <t>🟠 ATENÇÃO</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="5" t="n">
+      <c r="A34" s="47" t="n">
         <v>32</v>
       </c>
-      <c r="B34" s="5" t="inlineStr">
+      <c r="B34" s="47" t="inlineStr">
         <is>
           <t>Rafael Ramos Recalde</t>
         </is>
       </c>
-      <c r="C34" s="5" t="inlineStr">
+      <c r="C34" s="47" t="inlineStr">
         <is>
           <t>Equipe 4</t>
         </is>
       </c>
-      <c r="D34" s="5" t="n">
+      <c r="D34" s="47" t="n">
         <v>4</v>
       </c>
-      <c r="E34" s="5" t="n">
-        <v>19</v>
-      </c>
-      <c r="F34" s="5" t="n">
-        <v>59.6</v>
-      </c>
-      <c r="G34" s="5" t="inlineStr">
-        <is>
-          <t>🔴 CRÍTICO</t>
+      <c r="E34" s="47" t="n">
+        <v>12</v>
+      </c>
+      <c r="F34" s="47" t="n">
+        <v>1</v>
+      </c>
+      <c r="G34" s="47" t="n">
+        <v>72.59999999999999</v>
+      </c>
+      <c r="H34" s="47" t="inlineStr">
+        <is>
+          <t>🟠 ATENÇÃO</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="5" t="n">
+      <c r="A35" s="47" t="n">
         <v>33</v>
       </c>
-      <c r="B35" s="5" t="inlineStr">
+      <c r="B35" s="47" t="inlineStr">
         <is>
           <t>Anderson Jose de Santana</t>
         </is>
       </c>
-      <c r="C35" s="5" t="inlineStr">
+      <c r="C35" s="47" t="inlineStr">
         <is>
           <t>Equipe 4</t>
         </is>
       </c>
-      <c r="D35" s="5" t="n">
+      <c r="D35" s="47" t="n">
         <v>3</v>
       </c>
-      <c r="E35" s="5" t="n">
-        <v>19</v>
-      </c>
-      <c r="F35" s="5" t="n">
-        <v>57.9</v>
-      </c>
-      <c r="G35" s="5" t="inlineStr">
-        <is>
-          <t>🔴 CRÍTICO</t>
+      <c r="E35" s="47" t="n">
+        <v>12</v>
+      </c>
+      <c r="F35" s="47" t="n">
+        <v>1</v>
+      </c>
+      <c r="G35" s="47" t="n">
+        <v>68.7</v>
+      </c>
+      <c r="H35" s="47" t="inlineStr">
+        <is>
+          <t>🟠 ATENÇÃO</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="5" t="n">
+      <c r="A36" s="47" t="n">
         <v>34</v>
       </c>
-      <c r="B36" s="5" t="inlineStr">
+      <c r="B36" s="47" t="inlineStr">
         <is>
           <t>Carlos Alberto Albiero</t>
         </is>
       </c>
-      <c r="C36" s="5" t="inlineStr">
+      <c r="C36" s="47" t="inlineStr">
         <is>
           <t>Equipe 1</t>
         </is>
       </c>
-      <c r="D36" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="E36" s="5" t="n">
-        <v>21</v>
-      </c>
-      <c r="F36" s="5" t="n">
-        <v>55</v>
-      </c>
-      <c r="G36" s="5" t="inlineStr">
-        <is>
-          <t>🔴 CRÍTICO</t>
+      <c r="D36" s="47" t="n">
+        <v>4</v>
+      </c>
+      <c r="E36" s="47" t="n">
+        <v>14</v>
+      </c>
+      <c r="F36" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" s="47" t="n">
+        <v>68.40000000000001</v>
+      </c>
+      <c r="H36" s="47" t="inlineStr">
+        <is>
+          <t>🟠 ATENÇÃO</t>
         </is>
       </c>
     </row>
@@ -8205,12 +8314,15 @@
         <v>3</v>
       </c>
       <c r="E37" s="5" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="F37" s="5" t="n">
-        <v>48.2</v>
-      </c>
-      <c r="G37" s="5" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="G37" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="H37" s="5" t="inlineStr">
         <is>
           <t>🔴 CRÍTICO</t>
         </is>
@@ -8234,12 +8346,15 @@
         <v>4</v>
       </c>
       <c r="E38" s="5" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="F38" s="5" t="n">
-        <v>38.1</v>
-      </c>
-      <c r="G38" s="5" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="G38" s="5" t="n">
+        <v>49.9</v>
+      </c>
+      <c r="H38" s="5" t="inlineStr">
         <is>
           <t>🔴 CRÍTICO</t>
         </is>
@@ -8260,15 +8375,18 @@
         </is>
       </c>
       <c r="D39" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E39" s="5" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="F39" s="5" t="n">
-        <v>25.7</v>
-      </c>
-      <c r="G39" s="5" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="G39" s="5" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="H39" s="5" t="inlineStr">
         <is>
           <t>🔴 CRÍTICO</t>
         </is>
@@ -8282,6 +8400,7 @@
       <c r="E40" s="2" t="n"/>
       <c r="F40" s="2" t="n"/>
       <c r="G40" s="2" t="n"/>
+      <c r="H40" s="2" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n"/>
@@ -8291,6 +8410,7 @@
       <c r="E41" s="2" t="n"/>
       <c r="F41" s="2" t="n"/>
       <c r="G41" s="2" t="n"/>
+      <c r="H41" s="2" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="48" t="inlineStr">
@@ -8304,6 +8424,7 @@
       <c r="E42" s="2" t="n"/>
       <c r="F42" s="2" t="n"/>
       <c r="G42" s="2" t="n"/>
+      <c r="H42" s="2" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
@@ -8328,15 +8449,24 @@
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>Peso (pontos/ocorrência)</t>
+          <t>Peso Nominal (tabela de critérios)</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
+          <t>Fator de Normalização</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t>Peso Efetivo (nominal × fator)</t>
+        </is>
+      </c>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
           <t>Pontos Aplicados</t>
         </is>
       </c>
-      <c r="G43" s="2" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="49" t="inlineStr">
@@ -8361,9 +8491,14 @@
         <v>1</v>
       </c>
       <c r="F44" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="G44" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="H44" s="49" t="n">
         <v>4</v>
       </c>
-      <c r="G44" s="2" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="50" t="inlineStr">
@@ -8385,12 +8520,17 @@
         <v>1</v>
       </c>
       <c r="E45" s="50" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F45" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G45" s="50" t="n">
         <v>0.6</v>
       </c>
-      <c r="F45" s="50" t="n">
+      <c r="H45" s="50" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G45" s="2" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="50" t="inlineStr">
@@ -8412,12 +8552,17 @@
         <v>2</v>
       </c>
       <c r="E46" s="50" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F46" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G46" s="50" t="n">
         <v>0.6</v>
       </c>
-      <c r="F46" s="50" t="n">
+      <c r="H46" s="50" t="n">
         <v>-1.2</v>
       </c>
-      <c r="G46" s="2" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="50" t="inlineStr">
@@ -8439,12 +8584,17 @@
         <v>1</v>
       </c>
       <c r="E47" s="50" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F47" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G47" s="50" t="n">
         <v>3</v>
       </c>
-      <c r="F47" s="50" t="n">
+      <c r="H47" s="50" t="n">
         <v>-3</v>
       </c>
-      <c r="G47" s="2" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="50" t="inlineStr">
@@ -8466,12 +8616,17 @@
         <v>1</v>
       </c>
       <c r="E48" s="50" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="F48" s="50" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="G48" s="2" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="G48" s="50" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H48" s="50" t="n">
+        <v>-0.4</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="49" t="inlineStr">
@@ -8496,9 +8651,14 @@
         <v>1</v>
       </c>
       <c r="F49" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="G49" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="H49" s="49" t="n">
         <v>3</v>
       </c>
-      <c r="G49" s="2" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="50" t="inlineStr">
@@ -8523,9 +8683,14 @@
         <v>0.5</v>
       </c>
       <c r="F50" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="G50" s="50" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H50" s="50" t="n">
         <v>-0.5</v>
       </c>
-      <c r="G50" s="2" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="50" t="inlineStr">
@@ -8547,12 +8712,17 @@
         <v>3</v>
       </c>
       <c r="E51" s="50" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F51" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G51" s="50" t="n">
         <v>0.6</v>
       </c>
-      <c r="F51" s="50" t="n">
+      <c r="H51" s="50" t="n">
         <v>-1.8</v>
       </c>
-      <c r="G51" s="2" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="50" t="inlineStr">
@@ -8574,12 +8744,17 @@
         <v>1</v>
       </c>
       <c r="E52" s="50" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F52" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G52" s="50" t="n">
         <v>0.6</v>
       </c>
-      <c r="F52" s="50" t="n">
+      <c r="H52" s="50" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G52" s="2" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="50" t="inlineStr">
@@ -8601,12 +8776,17 @@
         <v>1</v>
       </c>
       <c r="E53" s="50" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F53" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G53" s="50" t="n">
         <v>3</v>
       </c>
-      <c r="F53" s="50" t="n">
+      <c r="H53" s="50" t="n">
         <v>-3</v>
       </c>
-      <c r="G53" s="2" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="50" t="inlineStr">
@@ -8628,12 +8808,17 @@
         <v>5</v>
       </c>
       <c r="E54" s="50" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="F54" s="50" t="n">
-        <v>-3</v>
-      </c>
-      <c r="G54" s="2" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="G54" s="50" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H54" s="50" t="n">
+        <v>-2</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="49" t="inlineStr">
@@ -8658,9 +8843,14 @@
         <v>5</v>
       </c>
       <c r="F55" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="G55" s="49" t="n">
         <v>5</v>
       </c>
-      <c r="G55" s="2" t="n"/>
+      <c r="H55" s="49" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="49" t="inlineStr">
@@ -8687,7 +8877,12 @@
       <c r="F56" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="G56" s="2" t="n"/>
+      <c r="G56" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="H56" s="49" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="50" t="inlineStr">
@@ -8712,9 +8907,14 @@
         <v>0.5</v>
       </c>
       <c r="F57" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="G57" s="50" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H57" s="50" t="n">
         <v>-0.5</v>
       </c>
-      <c r="G57" s="2" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="50" t="inlineStr">
@@ -8736,12 +8936,17 @@
         <v>1</v>
       </c>
       <c r="E58" s="50" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F58" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G58" s="50" t="n">
         <v>0.6</v>
       </c>
-      <c r="F58" s="50" t="n">
+      <c r="H58" s="50" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G58" s="2" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="50" t="inlineStr">
@@ -8763,12 +8968,17 @@
         <v>3</v>
       </c>
       <c r="E59" s="50" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F59" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G59" s="50" t="n">
         <v>3</v>
       </c>
-      <c r="F59" s="50" t="n">
+      <c r="H59" s="50" t="n">
         <v>-9</v>
       </c>
-      <c r="G59" s="2" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="49" t="inlineStr">
@@ -8793,9 +9003,14 @@
         <v>1</v>
       </c>
       <c r="F60" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="G60" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="H60" s="49" t="n">
         <v>2</v>
       </c>
-      <c r="G60" s="2" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="50" t="inlineStr">
@@ -8820,9 +9035,14 @@
         <v>0.5</v>
       </c>
       <c r="F61" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="G61" s="50" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H61" s="50" t="n">
         <v>-0.5</v>
       </c>
-      <c r="G61" s="2" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="50" t="inlineStr">
@@ -8844,12 +9064,17 @@
         <v>1</v>
       </c>
       <c r="E62" s="50" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F62" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G62" s="50" t="n">
         <v>0.6</v>
       </c>
-      <c r="F62" s="50" t="n">
+      <c r="H62" s="50" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G62" s="2" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="50" t="inlineStr">
@@ -8871,12 +9096,17 @@
         <v>1</v>
       </c>
       <c r="E63" s="50" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F63" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G63" s="50" t="n">
         <v>0.6</v>
       </c>
-      <c r="F63" s="50" t="n">
+      <c r="H63" s="50" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G63" s="2" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="50" t="inlineStr">
@@ -8898,12 +9128,17 @@
         <v>3</v>
       </c>
       <c r="E64" s="50" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F64" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G64" s="50" t="n">
         <v>3</v>
       </c>
-      <c r="F64" s="50" t="n">
+      <c r="H64" s="50" t="n">
         <v>-9</v>
       </c>
-      <c r="G64" s="2" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="50" t="inlineStr">
@@ -8925,12 +9160,17 @@
         <v>1</v>
       </c>
       <c r="E65" s="50" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="F65" s="50" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="G65" s="2" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="G65" s="50" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H65" s="50" t="n">
+        <v>-0.4</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="49" t="inlineStr">
@@ -8955,9 +9195,14 @@
         <v>1</v>
       </c>
       <c r="F66" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="G66" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="H66" s="49" t="n">
         <v>2</v>
       </c>
-      <c r="G66" s="2" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="50" t="inlineStr">
@@ -8982,9 +9227,14 @@
         <v>0.5</v>
       </c>
       <c r="F67" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="G67" s="50" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H67" s="50" t="n">
         <v>-0.5</v>
       </c>
-      <c r="G67" s="2" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="50" t="inlineStr">
@@ -9006,12 +9256,17 @@
         <v>1</v>
       </c>
       <c r="E68" s="50" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F68" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G68" s="50" t="n">
         <v>0.6</v>
       </c>
-      <c r="F68" s="50" t="n">
+      <c r="H68" s="50" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G68" s="2" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="50" t="inlineStr">
@@ -9033,12 +9288,17 @@
         <v>2</v>
       </c>
       <c r="E69" s="50" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F69" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G69" s="50" t="n">
         <v>0.6</v>
       </c>
-      <c r="F69" s="50" t="n">
+      <c r="H69" s="50" t="n">
         <v>-1.2</v>
       </c>
-      <c r="G69" s="2" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="50" t="inlineStr">
@@ -9060,12 +9320,17 @@
         <v>2</v>
       </c>
       <c r="E70" s="50" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F70" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G70" s="50" t="n">
         <v>0.6</v>
       </c>
-      <c r="F70" s="50" t="n">
+      <c r="H70" s="50" t="n">
         <v>-1.2</v>
       </c>
-      <c r="G70" s="2" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="50" t="inlineStr">
@@ -9087,12 +9352,17 @@
         <v>1</v>
       </c>
       <c r="E71" s="50" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F71" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G71" s="50" t="n">
         <v>3</v>
       </c>
-      <c r="F71" s="50" t="n">
+      <c r="H71" s="50" t="n">
         <v>-3</v>
       </c>
-      <c r="G71" s="2" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="50" t="inlineStr">
@@ -9114,12 +9384,17 @@
         <v>2</v>
       </c>
       <c r="E72" s="50" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F72" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G72" s="50" t="n">
         <v>0.6</v>
       </c>
-      <c r="F72" s="50" t="n">
+      <c r="H72" s="50" t="n">
         <v>-1.2</v>
       </c>
-      <c r="G72" s="2" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="50" t="inlineStr">
@@ -9141,12 +9416,17 @@
         <v>2</v>
       </c>
       <c r="E73" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="F73" s="50" t="n">
         <v>2</v>
       </c>
-      <c r="F73" s="50" t="n">
+      <c r="G73" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="H73" s="50" t="n">
         <v>-4</v>
       </c>
-      <c r="G73" s="2" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="50" t="inlineStr">
@@ -9168,12 +9448,17 @@
         <v>54</v>
       </c>
       <c r="E74" s="50" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="F74" s="50" t="n">
-        <v>-32.4</v>
-      </c>
-      <c r="G74" s="2" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="G74" s="50" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H74" s="50" t="n">
+        <v>-21.6</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="49" t="inlineStr">
@@ -9198,9 +9483,14 @@
         <v>5</v>
       </c>
       <c r="F75" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="G75" s="49" t="n">
         <v>5</v>
       </c>
-      <c r="G75" s="2" t="n"/>
+      <c r="H75" s="49" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="49" t="inlineStr">
@@ -9225,9 +9515,14 @@
         <v>1</v>
       </c>
       <c r="F76" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="G76" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="H76" s="49" t="n">
         <v>3</v>
       </c>
-      <c r="G76" s="2" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="50" t="inlineStr">
@@ -9252,9 +9547,14 @@
         <v>0.5</v>
       </c>
       <c r="F77" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="G77" s="50" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H77" s="50" t="n">
         <v>-0.5</v>
       </c>
-      <c r="G77" s="2" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="50" t="inlineStr">
@@ -9276,12 +9576,17 @@
         <v>1</v>
       </c>
       <c r="E78" s="50" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F78" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G78" s="50" t="n">
         <v>0.6</v>
       </c>
-      <c r="F78" s="50" t="n">
+      <c r="H78" s="50" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G78" s="2" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="50" t="inlineStr">
@@ -9303,12 +9608,17 @@
         <v>1</v>
       </c>
       <c r="E79" s="50" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F79" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G79" s="50" t="n">
         <v>0.6</v>
       </c>
-      <c r="F79" s="50" t="n">
+      <c r="H79" s="50" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G79" s="2" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="50" t="inlineStr">
@@ -9330,12 +9640,17 @@
         <v>2</v>
       </c>
       <c r="E80" s="50" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F80" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G80" s="50" t="n">
         <v>0.6</v>
       </c>
-      <c r="F80" s="50" t="n">
+      <c r="H80" s="50" t="n">
         <v>-1.2</v>
       </c>
-      <c r="G80" s="2" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="50" t="inlineStr">
@@ -9357,12 +9672,17 @@
         <v>1</v>
       </c>
       <c r="E81" s="50" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F81" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G81" s="50" t="n">
         <v>3</v>
       </c>
-      <c r="F81" s="50" t="n">
+      <c r="H81" s="50" t="n">
         <v>-3</v>
       </c>
-      <c r="G81" s="2" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="49" t="inlineStr">
@@ -9387,9 +9707,14 @@
         <v>1</v>
       </c>
       <c r="F82" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="G82" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="H82" s="49" t="n">
         <v>2</v>
       </c>
-      <c r="G82" s="2" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="50" t="inlineStr">
@@ -9414,9 +9739,14 @@
         <v>0.5</v>
       </c>
       <c r="F83" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="G83" s="50" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H83" s="50" t="n">
         <v>-0.5</v>
       </c>
-      <c r="G83" s="2" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="50" t="inlineStr">
@@ -9438,12 +9768,17 @@
         <v>3</v>
       </c>
       <c r="E84" s="50" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F84" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G84" s="50" t="n">
         <v>0.6</v>
       </c>
-      <c r="F84" s="50" t="n">
+      <c r="H84" s="50" t="n">
         <v>-1.8</v>
       </c>
-      <c r="G84" s="2" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="50" t="inlineStr">
@@ -9465,12 +9800,17 @@
         <v>1</v>
       </c>
       <c r="E85" s="50" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F85" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G85" s="50" t="n">
         <v>0.6</v>
       </c>
-      <c r="F85" s="50" t="n">
+      <c r="H85" s="50" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G85" s="2" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="50" t="inlineStr">
@@ -9492,12 +9832,17 @@
         <v>3</v>
       </c>
       <c r="E86" s="50" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F86" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G86" s="50" t="n">
         <v>3</v>
       </c>
-      <c r="F86" s="50" t="n">
+      <c r="H86" s="50" t="n">
         <v>-9</v>
       </c>
-      <c r="G86" s="2" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="50" t="inlineStr">
@@ -9519,12 +9864,17 @@
         <v>2</v>
       </c>
       <c r="E87" s="50" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F87" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G87" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="H87" s="50" t="n">
         <v>-2</v>
       </c>
-      <c r="G87" s="2" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="50" t="inlineStr">
@@ -9546,12 +9896,17 @@
         <v>9</v>
       </c>
       <c r="E88" s="50" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="F88" s="50" t="n">
-        <v>-5.4</v>
-      </c>
-      <c r="G88" s="2" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="G88" s="50" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H88" s="50" t="n">
+        <v>-3.6</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="49" t="inlineStr">
@@ -9566,46 +9921,56 @@
       </c>
       <c r="C89" s="49" t="inlineStr">
         <is>
+          <t>Bônus: nenhum turno sem lançamento no período</t>
+        </is>
+      </c>
+      <c r="D89" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="E89" s="49" t="n">
+        <v>5</v>
+      </c>
+      <c r="F89" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="G89" s="49" t="n">
+        <v>5</v>
+      </c>
+      <c r="H89" s="49" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="49" t="inlineStr">
+        <is>
+          <t>Carlos Alberto Albiero</t>
+        </is>
+      </c>
+      <c r="B90" s="49" t="inlineStr">
+        <is>
+          <t>Equipe 1</t>
+        </is>
+      </c>
+      <c r="C90" s="49" t="inlineStr">
+        <is>
           <t>Dia com meta diária batida</t>
         </is>
       </c>
-      <c r="D89" s="49" t="n">
-        <v>3</v>
-      </c>
-      <c r="E89" s="49" t="n">
-        <v>1</v>
-      </c>
-      <c r="F89" s="49" t="n">
-        <v>3</v>
-      </c>
-      <c r="G89" s="2" t="n"/>
-    </row>
-    <row r="90">
-      <c r="A90" s="50" t="inlineStr">
-        <is>
-          <t>Carlos Alberto Albiero</t>
-        </is>
-      </c>
-      <c r="B90" s="50" t="inlineStr">
-        <is>
-          <t>Equipe 1</t>
-        </is>
-      </c>
-      <c r="C90" s="50" t="inlineStr">
-        <is>
-          <t>Fim tarde antes de 16h00</t>
-        </is>
-      </c>
-      <c r="D90" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="E90" s="50" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="F90" s="50" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="G90" s="2" t="n"/>
+      <c r="D90" s="49" t="n">
+        <v>4</v>
+      </c>
+      <c r="E90" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="F90" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="G90" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="H90" s="49" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="50" t="inlineStr">
@@ -9620,19 +9985,24 @@
       </c>
       <c r="C91" s="50" t="inlineStr">
         <is>
-          <t>Início manhã após 08h30</t>
+          <t>Fim tarde antes de 16h00</t>
         </is>
       </c>
       <c r="D91" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="E91" s="50" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F91" s="50" t="n">
         <v>2</v>
       </c>
-      <c r="E91" s="50" t="n">
+      <c r="G91" s="50" t="n">
         <v>0.6</v>
       </c>
-      <c r="F91" s="50" t="n">
-        <v>-1.2</v>
-      </c>
-      <c r="G91" s="2" t="n"/>
+      <c r="H91" s="50" t="n">
+        <v>-0.6</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="50" t="inlineStr">
@@ -9647,19 +10017,24 @@
       </c>
       <c r="C92" s="50" t="inlineStr">
         <is>
-          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
+          <t>Início manhã após 08h30</t>
         </is>
       </c>
       <c r="D92" s="50" t="n">
+        <v>3</v>
+      </c>
+      <c r="E92" s="50" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F92" s="50" t="n">
         <v>2</v>
       </c>
-      <c r="E92" s="50" t="n">
-        <v>3</v>
-      </c>
-      <c r="F92" s="50" t="n">
-        <v>-6</v>
-      </c>
-      <c r="G92" s="2" t="n"/>
+      <c r="G92" s="50" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H92" s="50" t="n">
+        <v>-1.8</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="50" t="inlineStr">
@@ -9681,12 +10056,17 @@
         <v>3</v>
       </c>
       <c r="E93" s="50" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F93" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G93" s="50" t="n">
         <v>0.6</v>
       </c>
-      <c r="F93" s="50" t="n">
+      <c r="H93" s="50" t="n">
         <v>-1.8</v>
       </c>
-      <c r="G93" s="2" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="50" t="inlineStr">
@@ -9708,12 +10088,17 @@
         <v>6</v>
       </c>
       <c r="E94" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="F94" s="50" t="n">
         <v>2</v>
       </c>
-      <c r="F94" s="50" t="n">
+      <c r="G94" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="H94" s="50" t="n">
         <v>-12</v>
       </c>
-      <c r="G94" s="2" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="50" t="inlineStr">
@@ -9732,15 +10117,20 @@
         </is>
       </c>
       <c r="D95" s="50" t="n">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="E95" s="50" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="F95" s="50" t="n">
-        <v>-26.4</v>
-      </c>
-      <c r="G95" s="2" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="G95" s="50" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H95" s="50" t="n">
+        <v>-24.4</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="49" t="inlineStr">
@@ -9765,9 +10155,14 @@
         <v>1</v>
       </c>
       <c r="F96" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="G96" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="H96" s="49" t="n">
         <v>3</v>
       </c>
-      <c r="G96" s="2" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="50" t="inlineStr">
@@ -9789,12 +10184,17 @@
         <v>3</v>
       </c>
       <c r="E97" s="50" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F97" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G97" s="50" t="n">
         <v>0.6</v>
       </c>
-      <c r="F97" s="50" t="n">
+      <c r="H97" s="50" t="n">
         <v>-1.8</v>
       </c>
-      <c r="G97" s="2" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="50" t="inlineStr">
@@ -9816,12 +10216,17 @@
         <v>2</v>
       </c>
       <c r="E98" s="50" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F98" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G98" s="50" t="n">
         <v>3</v>
       </c>
-      <c r="F98" s="50" t="n">
+      <c r="H98" s="50" t="n">
         <v>-6</v>
       </c>
-      <c r="G98" s="2" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="50" t="inlineStr">
@@ -9843,12 +10248,17 @@
         <v>16</v>
       </c>
       <c r="E99" s="50" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F99" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G99" s="50" t="n">
         <v>0.6</v>
       </c>
-      <c r="F99" s="50" t="n">
+      <c r="H99" s="50" t="n">
         <v>-9.6</v>
       </c>
-      <c r="G99" s="2" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="50" t="inlineStr">
@@ -9870,12 +10280,17 @@
         <v>16</v>
       </c>
       <c r="E100" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="F100" s="50" t="n">
         <v>2</v>
       </c>
-      <c r="F100" s="50" t="n">
+      <c r="G100" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="H100" s="50" t="n">
         <v>-32</v>
       </c>
-      <c r="G100" s="2" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="50" t="inlineStr">
@@ -9897,12 +10312,17 @@
         <v>9</v>
       </c>
       <c r="E101" s="50" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="F101" s="50" t="n">
-        <v>-5.4</v>
-      </c>
-      <c r="G101" s="2" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="G101" s="50" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H101" s="50" t="n">
+        <v>-3.6</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="49" t="inlineStr">
@@ -9921,15 +10341,20 @@
         </is>
       </c>
       <c r="D102" s="49" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E102" s="49" t="n">
         <v>1</v>
       </c>
       <c r="F102" s="49" t="n">
-        <v>2</v>
-      </c>
-      <c r="G102" s="2" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G102" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="H102" s="49" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="50" t="inlineStr">
@@ -9954,9 +10379,14 @@
         <v>0.5</v>
       </c>
       <c r="F103" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="G103" s="50" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H103" s="50" t="n">
         <v>-0.5</v>
       </c>
-      <c r="G103" s="2" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="50" t="inlineStr">
@@ -9975,15 +10405,20 @@
         </is>
       </c>
       <c r="D104" s="50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E104" s="50" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F104" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G104" s="50" t="n">
         <v>0.6</v>
       </c>
-      <c r="F104" s="50" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="G104" s="2" t="n"/>
+      <c r="H104" s="50" t="n">
+        <v>-1.2</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="50" t="inlineStr">
@@ -10002,15 +10437,20 @@
         </is>
       </c>
       <c r="D105" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="E105" s="50" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F105" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G105" s="50" t="n">
         <v>3</v>
       </c>
-      <c r="E105" s="50" t="n">
-        <v>3</v>
-      </c>
-      <c r="F105" s="50" t="n">
-        <v>-9</v>
-      </c>
-      <c r="G105" s="2" t="n"/>
+      <c r="H105" s="50" t="n">
+        <v>-3</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="50" t="inlineStr">
@@ -10032,12 +10472,17 @@
         <v>25</v>
       </c>
       <c r="E106" s="50" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F106" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G106" s="50" t="n">
         <v>0.6</v>
       </c>
-      <c r="F106" s="50" t="n">
+      <c r="H106" s="50" t="n">
         <v>-15</v>
       </c>
-      <c r="G106" s="2" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="50" t="inlineStr">
@@ -10059,12 +10504,17 @@
         <v>25</v>
       </c>
       <c r="E107" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="F107" s="50" t="n">
         <v>2</v>
       </c>
-      <c r="F107" s="50" t="n">
+      <c r="G107" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="H107" s="50" t="n">
         <v>-50</v>
       </c>
-      <c r="G107" s="2" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="50" t="inlineStr">
@@ -10086,12 +10536,17 @@
         <v>2</v>
       </c>
       <c r="E108" s="50" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="F108" s="50" t="n">
-        <v>-1.2</v>
-      </c>
-      <c r="G108" s="2" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="G108" s="50" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H108" s="50" t="n">
+        <v>-0.8</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="49" t="inlineStr">
@@ -10118,7 +10573,12 @@
       <c r="F109" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="G109" s="2" t="n"/>
+      <c r="G109" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="H109" s="49" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="50" t="inlineStr">
@@ -10143,9 +10603,14 @@
         <v>0.5</v>
       </c>
       <c r="F110" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="G110" s="50" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H110" s="50" t="n">
         <v>-1.5</v>
       </c>
-      <c r="G110" s="2" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="50" t="inlineStr">
@@ -10167,12 +10632,17 @@
         <v>2</v>
       </c>
       <c r="E111" s="50" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F111" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G111" s="50" t="n">
         <v>0.6</v>
       </c>
-      <c r="F111" s="50" t="n">
+      <c r="H111" s="50" t="n">
         <v>-1.2</v>
       </c>
-      <c r="G111" s="2" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="50" t="inlineStr">
@@ -10194,12 +10664,17 @@
         <v>2</v>
       </c>
       <c r="E112" s="50" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F112" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G112" s="50" t="n">
         <v>0.6</v>
       </c>
-      <c r="F112" s="50" t="n">
+      <c r="H112" s="50" t="n">
         <v>-1.2</v>
       </c>
-      <c r="G112" s="2" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="50" t="inlineStr">
@@ -10221,12 +10696,17 @@
         <v>1</v>
       </c>
       <c r="E113" s="50" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F113" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G113" s="50" t="n">
         <v>0.6</v>
       </c>
-      <c r="F113" s="50" t="n">
+      <c r="H113" s="50" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G113" s="2" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="50" t="inlineStr">
@@ -10248,12 +10728,17 @@
         <v>2</v>
       </c>
       <c r="E114" s="50" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F114" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G114" s="50" t="n">
         <v>3</v>
       </c>
-      <c r="F114" s="50" t="n">
+      <c r="H114" s="50" t="n">
         <v>-6</v>
       </c>
-      <c r="G114" s="2" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="50" t="inlineStr">
@@ -10275,12 +10760,17 @@
         <v>2</v>
       </c>
       <c r="E115" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="F115" s="50" t="n">
         <v>2</v>
       </c>
-      <c r="F115" s="50" t="n">
+      <c r="G115" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="H115" s="50" t="n">
         <v>-4</v>
       </c>
-      <c r="G115" s="2" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="50" t="inlineStr">
@@ -10302,12 +10792,17 @@
         <v>14</v>
       </c>
       <c r="E116" s="50" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="F116" s="50" t="n">
-        <v>-8.4</v>
-      </c>
-      <c r="G116" s="2" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="G116" s="50" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H116" s="50" t="n">
+        <v>-5.6</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="49" t="inlineStr">
@@ -10332,9 +10827,14 @@
         <v>1</v>
       </c>
       <c r="F117" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="G117" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="H117" s="49" t="n">
         <v>2</v>
       </c>
-      <c r="G117" s="2" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="50" t="inlineStr">
@@ -10359,9 +10859,14 @@
         <v>0.5</v>
       </c>
       <c r="F118" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="G118" s="50" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H118" s="50" t="n">
         <v>-1</v>
       </c>
-      <c r="G118" s="2" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="50" t="inlineStr">
@@ -10383,12 +10888,17 @@
         <v>1</v>
       </c>
       <c r="E119" s="50" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F119" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G119" s="50" t="n">
         <v>0.6</v>
       </c>
-      <c r="F119" s="50" t="n">
+      <c r="H119" s="50" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G119" s="2" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="50" t="inlineStr">
@@ -10410,12 +10920,17 @@
         <v>1</v>
       </c>
       <c r="E120" s="50" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F120" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G120" s="50" t="n">
         <v>0.6</v>
       </c>
-      <c r="F120" s="50" t="n">
+      <c r="H120" s="50" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G120" s="2" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="50" t="inlineStr">
@@ -10437,12 +10952,17 @@
         <v>1</v>
       </c>
       <c r="E121" s="50" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F121" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G121" s="50" t="n">
         <v>0.6</v>
       </c>
-      <c r="F121" s="50" t="n">
+      <c r="H121" s="50" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G121" s="2" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="50" t="inlineStr">
@@ -10464,12 +10984,17 @@
         <v>2</v>
       </c>
       <c r="E122" s="50" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F122" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G122" s="50" t="n">
         <v>3</v>
       </c>
-      <c r="F122" s="50" t="n">
+      <c r="H122" s="50" t="n">
         <v>-6</v>
       </c>
-      <c r="G122" s="2" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="50" t="inlineStr">
@@ -10491,12 +11016,17 @@
         <v>2</v>
       </c>
       <c r="E123" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="F123" s="50" t="n">
         <v>2</v>
       </c>
-      <c r="F123" s="50" t="n">
+      <c r="G123" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="H123" s="50" t="n">
         <v>-4</v>
       </c>
-      <c r="G123" s="2" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="50" t="inlineStr">
@@ -10518,12 +11048,17 @@
         <v>1</v>
       </c>
       <c r="E124" s="50" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="F124" s="50" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="G124" s="2" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="G124" s="50" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H124" s="50" t="n">
+        <v>-0.4</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="49" t="inlineStr">
@@ -10548,9 +11083,14 @@
         <v>5</v>
       </c>
       <c r="F125" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="G125" s="49" t="n">
         <v>5</v>
       </c>
-      <c r="G125" s="2" t="n"/>
+      <c r="H125" s="49" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="49" t="inlineStr">
@@ -10575,9 +11115,14 @@
         <v>1</v>
       </c>
       <c r="F126" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="G126" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="H126" s="49" t="n">
         <v>3</v>
       </c>
-      <c r="G126" s="2" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="50" t="inlineStr">
@@ -10602,9 +11147,14 @@
         <v>0.5</v>
       </c>
       <c r="F127" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="G127" s="50" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H127" s="50" t="n">
         <v>-0.5</v>
       </c>
-      <c r="G127" s="2" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="50" t="inlineStr">
@@ -10626,12 +11176,17 @@
         <v>1</v>
       </c>
       <c r="E128" s="50" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F128" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G128" s="50" t="n">
         <v>0.6</v>
       </c>
-      <c r="F128" s="50" t="n">
+      <c r="H128" s="50" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G128" s="2" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="50" t="inlineStr">
@@ -10653,12 +11208,17 @@
         <v>3</v>
       </c>
       <c r="E129" s="50" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F129" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G129" s="50" t="n">
         <v>0.6</v>
       </c>
-      <c r="F129" s="50" t="n">
+      <c r="H129" s="50" t="n">
         <v>-1.8</v>
       </c>
-      <c r="G129" s="2" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="50" t="inlineStr">
@@ -10680,12 +11240,17 @@
         <v>1</v>
       </c>
       <c r="E130" s="50" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F130" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G130" s="50" t="n">
         <v>3</v>
       </c>
-      <c r="F130" s="50" t="n">
+      <c r="H130" s="50" t="n">
         <v>-3</v>
       </c>
-      <c r="G130" s="2" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="49" t="inlineStr">
@@ -10710,9 +11275,14 @@
         <v>1</v>
       </c>
       <c r="F131" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="G131" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="H131" s="49" t="n">
         <v>2</v>
       </c>
-      <c r="G131" s="2" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="50" t="inlineStr">
@@ -10737,9 +11307,14 @@
         <v>0.5</v>
       </c>
       <c r="F132" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="G132" s="50" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H132" s="50" t="n">
         <v>-0.5</v>
       </c>
-      <c r="G132" s="2" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="50" t="inlineStr">
@@ -10761,12 +11336,17 @@
         <v>1</v>
       </c>
       <c r="E133" s="50" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F133" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G133" s="50" t="n">
         <v>0.6</v>
       </c>
-      <c r="F133" s="50" t="n">
+      <c r="H133" s="50" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G133" s="2" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="50" t="inlineStr">
@@ -10788,12 +11368,17 @@
         <v>2</v>
       </c>
       <c r="E134" s="50" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F134" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G134" s="50" t="n">
         <v>0.6</v>
       </c>
-      <c r="F134" s="50" t="n">
+      <c r="H134" s="50" t="n">
         <v>-1.2</v>
       </c>
-      <c r="G134" s="2" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="50" t="inlineStr">
@@ -10815,12 +11400,17 @@
         <v>1</v>
       </c>
       <c r="E135" s="50" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F135" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G135" s="50" t="n">
         <v>0.6</v>
       </c>
-      <c r="F135" s="50" t="n">
+      <c r="H135" s="50" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G135" s="2" t="n"/>
     </row>
     <row r="136">
       <c r="A136" s="50" t="inlineStr">
@@ -10842,12 +11432,17 @@
         <v>3</v>
       </c>
       <c r="E136" s="50" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F136" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G136" s="50" t="n">
         <v>3</v>
       </c>
-      <c r="F136" s="50" t="n">
+      <c r="H136" s="50" t="n">
         <v>-9</v>
       </c>
-      <c r="G136" s="2" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="50" t="inlineStr">
@@ -10869,12 +11464,17 @@
         <v>2</v>
       </c>
       <c r="E137" s="50" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F137" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G137" s="50" t="n">
         <v>0.6</v>
       </c>
-      <c r="F137" s="50" t="n">
+      <c r="H137" s="50" t="n">
         <v>-1.2</v>
       </c>
-      <c r="G137" s="2" t="n"/>
     </row>
     <row r="138">
       <c r="A138" s="50" t="inlineStr">
@@ -10896,12 +11496,17 @@
         <v>2</v>
       </c>
       <c r="E138" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="F138" s="50" t="n">
         <v>2</v>
       </c>
-      <c r="F138" s="50" t="n">
+      <c r="G138" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="H138" s="50" t="n">
         <v>-4</v>
       </c>
-      <c r="G138" s="2" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="50" t="inlineStr">
@@ -10923,12 +11528,17 @@
         <v>3</v>
       </c>
       <c r="E139" s="50" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F139" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G139" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="H139" s="50" t="n">
         <v>-3</v>
       </c>
-      <c r="G139" s="2" t="n"/>
     </row>
     <row r="140">
       <c r="A140" s="50" t="inlineStr">
@@ -10950,12 +11560,17 @@
         <v>1</v>
       </c>
       <c r="E140" s="50" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="F140" s="50" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="G140" s="2" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="G140" s="50" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H140" s="50" t="n">
+        <v>-0.4</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="49" t="inlineStr">
@@ -10980,9 +11595,14 @@
         <v>5</v>
       </c>
       <c r="F141" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="G141" s="49" t="n">
         <v>5</v>
       </c>
-      <c r="G141" s="2" t="n"/>
+      <c r="H141" s="49" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="49" t="inlineStr">
@@ -11007,9 +11627,14 @@
         <v>5</v>
       </c>
       <c r="F142" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="G142" s="49" t="n">
         <v>5</v>
       </c>
-      <c r="G142" s="2" t="n"/>
+      <c r="H142" s="49" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="49" t="inlineStr">
@@ -11034,9 +11659,14 @@
         <v>1</v>
       </c>
       <c r="F143" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="G143" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="H143" s="49" t="n">
         <v>4</v>
       </c>
-      <c r="G143" s="2" t="n"/>
     </row>
     <row r="144">
       <c r="A144" s="50" t="inlineStr">
@@ -11058,12 +11688,17 @@
         <v>1</v>
       </c>
       <c r="E144" s="50" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F144" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G144" s="50" t="n">
         <v>0.6</v>
       </c>
-      <c r="F144" s="50" t="n">
+      <c r="H144" s="50" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G144" s="2" t="n"/>
     </row>
     <row r="145">
       <c r="A145" s="50" t="inlineStr">
@@ -11085,12 +11720,17 @@
         <v>2</v>
       </c>
       <c r="E145" s="50" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F145" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G145" s="50" t="n">
         <v>0.6</v>
       </c>
-      <c r="F145" s="50" t="n">
+      <c r="H145" s="50" t="n">
         <v>-1.2</v>
       </c>
-      <c r="G145" s="2" t="n"/>
     </row>
     <row r="146">
       <c r="A146" s="50" t="inlineStr">
@@ -11112,12 +11752,17 @@
         <v>3</v>
       </c>
       <c r="E146" s="50" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F146" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G146" s="50" t="n">
         <v>0.6</v>
       </c>
-      <c r="F146" s="50" t="n">
+      <c r="H146" s="50" t="n">
         <v>-1.8</v>
       </c>
-      <c r="G146" s="2" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="50" t="inlineStr">
@@ -11139,12 +11784,17 @@
         <v>1</v>
       </c>
       <c r="E147" s="50" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F147" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G147" s="50" t="n">
         <v>0.6</v>
       </c>
-      <c r="F147" s="50" t="n">
+      <c r="H147" s="50" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G147" s="2" t="n"/>
     </row>
     <row r="148">
       <c r="A148" s="49" t="inlineStr">
@@ -11169,9 +11819,14 @@
         <v>5</v>
       </c>
       <c r="F148" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="G148" s="49" t="n">
         <v>5</v>
       </c>
-      <c r="G148" s="2" t="n"/>
+      <c r="H148" s="49" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="49" t="inlineStr">
@@ -11198,7 +11853,12 @@
       <c r="F149" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="G149" s="2" t="n"/>
+      <c r="G149" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="H149" s="49" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="50" t="inlineStr">
@@ -11223,9 +11883,14 @@
         <v>0.5</v>
       </c>
       <c r="F150" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="G150" s="50" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H150" s="50" t="n">
         <v>-0.5</v>
       </c>
-      <c r="G150" s="2" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="50" t="inlineStr">
@@ -11247,12 +11912,17 @@
         <v>1</v>
       </c>
       <c r="E151" s="50" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F151" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G151" s="50" t="n">
         <v>0.6</v>
       </c>
-      <c r="F151" s="50" t="n">
+      <c r="H151" s="50" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G151" s="2" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="50" t="inlineStr">
@@ -11274,12 +11944,17 @@
         <v>4</v>
       </c>
       <c r="E152" s="50" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F152" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G152" s="50" t="n">
         <v>3</v>
       </c>
-      <c r="F152" s="50" t="n">
+      <c r="H152" s="50" t="n">
         <v>-12</v>
       </c>
-      <c r="G152" s="2" t="n"/>
     </row>
     <row r="153">
       <c r="A153" s="49" t="inlineStr">
@@ -11298,15 +11973,20 @@
         </is>
       </c>
       <c r="D153" s="49" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E153" s="49" t="n">
         <v>1</v>
       </c>
       <c r="F153" s="49" t="n">
-        <v>3</v>
-      </c>
-      <c r="G153" s="2" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G153" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="H153" s="49" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="50" t="inlineStr">
@@ -11328,12 +12008,17 @@
         <v>1</v>
       </c>
       <c r="E154" s="50" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F154" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G154" s="50" t="n">
         <v>0.6</v>
       </c>
-      <c r="F154" s="50" t="n">
+      <c r="H154" s="50" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G154" s="2" t="n"/>
     </row>
     <row r="155">
       <c r="A155" s="50" t="inlineStr">
@@ -11355,12 +12040,17 @@
         <v>1</v>
       </c>
       <c r="E155" s="50" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F155" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G155" s="50" t="n">
         <v>0.6</v>
       </c>
-      <c r="F155" s="50" t="n">
+      <c r="H155" s="50" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G155" s="2" t="n"/>
     </row>
     <row r="156">
       <c r="A156" s="50" t="inlineStr">
@@ -11382,12 +12072,17 @@
         <v>1</v>
       </c>
       <c r="E156" s="50" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F156" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G156" s="50" t="n">
         <v>0.6</v>
       </c>
-      <c r="F156" s="50" t="n">
+      <c r="H156" s="50" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G156" s="2" t="n"/>
     </row>
     <row r="157">
       <c r="A157" s="50" t="inlineStr">
@@ -11406,15 +12101,20 @@
         </is>
       </c>
       <c r="D157" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="E157" s="50" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F157" s="50" t="n">
         <v>2</v>
       </c>
-      <c r="E157" s="50" t="n">
+      <c r="G157" s="50" t="n">
         <v>3</v>
       </c>
-      <c r="F157" s="50" t="n">
-        <v>-6</v>
-      </c>
-      <c r="G157" s="2" t="n"/>
+      <c r="H157" s="50" t="n">
+        <v>-3</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="50" t="inlineStr">
@@ -11433,15 +12133,20 @@
         </is>
       </c>
       <c r="D158" s="50" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E158" s="50" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="F158" s="50" t="n">
-        <v>-3</v>
-      </c>
-      <c r="G158" s="2" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="G158" s="50" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H158" s="50" t="n">
+        <v>-2.4</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="49" t="inlineStr">
@@ -11466,9 +12171,14 @@
         <v>1</v>
       </c>
       <c r="F159" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="G159" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="H159" s="49" t="n">
         <v>3</v>
       </c>
-      <c r="G159" s="2" t="n"/>
     </row>
     <row r="160">
       <c r="A160" s="50" t="inlineStr">
@@ -11493,9 +12203,14 @@
         <v>0.5</v>
       </c>
       <c r="F160" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="G160" s="50" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H160" s="50" t="n">
         <v>-0.5</v>
       </c>
-      <c r="G160" s="2" t="n"/>
     </row>
     <row r="161">
       <c r="A161" s="50" t="inlineStr">
@@ -11517,12 +12232,17 @@
         <v>1</v>
       </c>
       <c r="E161" s="50" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F161" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G161" s="50" t="n">
         <v>0.6</v>
       </c>
-      <c r="F161" s="50" t="n">
+      <c r="H161" s="50" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G161" s="2" t="n"/>
     </row>
     <row r="162">
       <c r="A162" s="50" t="inlineStr">
@@ -11544,12 +12264,17 @@
         <v>2</v>
       </c>
       <c r="E162" s="50" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F162" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G162" s="50" t="n">
         <v>0.6</v>
       </c>
-      <c r="F162" s="50" t="n">
+      <c r="H162" s="50" t="n">
         <v>-1.2</v>
       </c>
-      <c r="G162" s="2" t="n"/>
     </row>
     <row r="163">
       <c r="A163" s="50" t="inlineStr">
@@ -11571,12 +12296,17 @@
         <v>1</v>
       </c>
       <c r="E163" s="50" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F163" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G163" s="50" t="n">
         <v>0.6</v>
       </c>
-      <c r="F163" s="50" t="n">
+      <c r="H163" s="50" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G163" s="2" t="n"/>
     </row>
     <row r="164">
       <c r="A164" s="50" t="inlineStr">
@@ -11598,12 +12328,17 @@
         <v>3</v>
       </c>
       <c r="E164" s="50" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F164" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G164" s="50" t="n">
         <v>3</v>
       </c>
-      <c r="F164" s="50" t="n">
+      <c r="H164" s="50" t="n">
         <v>-9</v>
       </c>
-      <c r="G164" s="2" t="n"/>
     </row>
     <row r="165">
       <c r="A165" s="50" t="inlineStr">
@@ -11625,12 +12360,17 @@
         <v>14</v>
       </c>
       <c r="E165" s="50" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="F165" s="50" t="n">
-        <v>-8.4</v>
-      </c>
-      <c r="G165" s="2" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="G165" s="50" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H165" s="50" t="n">
+        <v>-5.6</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="50" t="inlineStr">
@@ -11655,9 +12395,14 @@
         <v>0.5</v>
       </c>
       <c r="F166" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="G166" s="50" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H166" s="50" t="n">
         <v>-0.5</v>
       </c>
-      <c r="G166" s="2" t="n"/>
     </row>
     <row r="167">
       <c r="A167" s="50" t="inlineStr">
@@ -11679,12 +12424,17 @@
         <v>1</v>
       </c>
       <c r="E167" s="50" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F167" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G167" s="50" t="n">
         <v>0.6</v>
       </c>
-      <c r="F167" s="50" t="n">
+      <c r="H167" s="50" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G167" s="2" t="n"/>
     </row>
     <row r="168">
       <c r="A168" s="50" t="inlineStr">
@@ -11706,12 +12456,17 @@
         <v>1</v>
       </c>
       <c r="E168" s="50" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F168" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G168" s="50" t="n">
         <v>3</v>
       </c>
-      <c r="F168" s="50" t="n">
+      <c r="H168" s="50" t="n">
         <v>-3</v>
       </c>
-      <c r="G168" s="2" t="n"/>
     </row>
     <row r="169">
       <c r="A169" s="50" t="inlineStr">
@@ -11733,12 +12488,17 @@
         <v>7</v>
       </c>
       <c r="E169" s="50" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="F169" s="50" t="n">
-        <v>-4.2</v>
-      </c>
-      <c r="G169" s="2" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="G169" s="50" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H169" s="50" t="n">
+        <v>-2.8</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="49" t="inlineStr">
@@ -11763,9 +12523,14 @@
         <v>1</v>
       </c>
       <c r="F170" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="G170" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="H170" s="49" t="n">
         <v>4</v>
       </c>
-      <c r="G170" s="2" t="n"/>
     </row>
     <row r="171">
       <c r="A171" s="50" t="inlineStr">
@@ -11787,12 +12552,17 @@
         <v>3</v>
       </c>
       <c r="E171" s="50" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F171" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G171" s="50" t="n">
         <v>0.6</v>
       </c>
-      <c r="F171" s="50" t="n">
+      <c r="H171" s="50" t="n">
         <v>-1.8</v>
       </c>
-      <c r="G171" s="2" t="n"/>
     </row>
     <row r="172">
       <c r="A172" s="50" t="inlineStr">
@@ -11814,12 +12584,17 @@
         <v>3</v>
       </c>
       <c r="E172" s="50" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F172" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G172" s="50" t="n">
         <v>0.6</v>
       </c>
-      <c r="F172" s="50" t="n">
+      <c r="H172" s="50" t="n">
         <v>-1.8</v>
       </c>
-      <c r="G172" s="2" t="n"/>
     </row>
     <row r="173">
       <c r="A173" s="50" t="inlineStr">
@@ -11841,12 +12616,17 @@
         <v>1</v>
       </c>
       <c r="E173" s="50" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F173" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G173" s="50" t="n">
         <v>3</v>
       </c>
-      <c r="F173" s="50" t="n">
+      <c r="H173" s="50" t="n">
         <v>-3</v>
       </c>
-      <c r="G173" s="2" t="n"/>
     </row>
     <row r="174">
       <c r="A174" s="50" t="inlineStr">
@@ -11868,12 +12648,17 @@
         <v>58</v>
       </c>
       <c r="E174" s="50" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="F174" s="50" t="n">
-        <v>-34.8</v>
-      </c>
-      <c r="G174" s="2" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="G174" s="50" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H174" s="50" t="n">
+        <v>-23.2</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="50" t="inlineStr">
@@ -11898,9 +12683,14 @@
         <v>0.5</v>
       </c>
       <c r="F175" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="G175" s="50" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H175" s="50" t="n">
         <v>-2</v>
       </c>
-      <c r="G175" s="2" t="n"/>
     </row>
     <row r="176">
       <c r="A176" s="50" t="inlineStr">
@@ -11922,12 +12712,17 @@
         <v>1</v>
       </c>
       <c r="E176" s="50" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F176" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G176" s="50" t="n">
         <v>0.6</v>
       </c>
-      <c r="F176" s="50" t="n">
+      <c r="H176" s="50" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G176" s="2" t="n"/>
     </row>
     <row r="177">
       <c r="A177" s="50" t="inlineStr">
@@ -11949,12 +12744,17 @@
         <v>2</v>
       </c>
       <c r="E177" s="50" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F177" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G177" s="50" t="n">
         <v>0.6</v>
       </c>
-      <c r="F177" s="50" t="n">
+      <c r="H177" s="50" t="n">
         <v>-1.2</v>
       </c>
-      <c r="G177" s="2" t="n"/>
     </row>
     <row r="178">
       <c r="A178" s="50" t="inlineStr">
@@ -11976,12 +12776,17 @@
         <v>2</v>
       </c>
       <c r="E178" s="50" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F178" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G178" s="50" t="n">
         <v>0.6</v>
       </c>
-      <c r="F178" s="50" t="n">
+      <c r="H178" s="50" t="n">
         <v>-1.2</v>
       </c>
-      <c r="G178" s="2" t="n"/>
     </row>
     <row r="179">
       <c r="A179" s="50" t="inlineStr">
@@ -12003,12 +12808,17 @@
         <v>2</v>
       </c>
       <c r="E179" s="50" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F179" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G179" s="50" t="n">
         <v>3</v>
       </c>
-      <c r="F179" s="50" t="n">
+      <c r="H179" s="50" t="n">
         <v>-6</v>
       </c>
-      <c r="G179" s="2" t="n"/>
     </row>
     <row r="180">
       <c r="A180" s="50" t="inlineStr">
@@ -12030,12 +12840,17 @@
         <v>5</v>
       </c>
       <c r="E180" s="50" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F180" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G180" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="H180" s="50" t="n">
         <v>-5</v>
       </c>
-      <c r="G180" s="2" t="n"/>
     </row>
     <row r="181">
       <c r="A181" s="50" t="inlineStr">
@@ -12057,12 +12872,17 @@
         <v>2</v>
       </c>
       <c r="E181" s="50" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F181" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G181" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="H181" s="50" t="n">
         <v>-2</v>
       </c>
-      <c r="G181" s="2" t="n"/>
     </row>
     <row r="182">
       <c r="A182" s="50" t="inlineStr">
@@ -12084,12 +12904,17 @@
         <v>11</v>
       </c>
       <c r="E182" s="50" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="F182" s="50" t="n">
-        <v>-6.6</v>
-      </c>
-      <c r="G182" s="2" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="G182" s="50" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H182" s="50" t="n">
+        <v>-4.4</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" s="49" t="inlineStr">
@@ -12114,9 +12939,14 @@
         <v>5</v>
       </c>
       <c r="F183" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="G183" s="49" t="n">
         <v>5</v>
       </c>
-      <c r="G183" s="2" t="n"/>
+      <c r="H183" s="49" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" s="49" t="inlineStr">
@@ -12141,9 +12971,14 @@
         <v>1</v>
       </c>
       <c r="F184" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="G184" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="H184" s="49" t="n">
         <v>4</v>
       </c>
-      <c r="G184" s="2" t="n"/>
     </row>
     <row r="185">
       <c r="A185" s="50" t="inlineStr">
@@ -12165,12 +13000,17 @@
         <v>1</v>
       </c>
       <c r="E185" s="50" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F185" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G185" s="50" t="n">
         <v>0.6</v>
       </c>
-      <c r="F185" s="50" t="n">
+      <c r="H185" s="50" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G185" s="2" t="n"/>
     </row>
     <row r="186">
       <c r="A186" s="50" t="inlineStr">
@@ -12192,12 +13032,17 @@
         <v>2</v>
       </c>
       <c r="E186" s="50" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F186" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G186" s="50" t="n">
         <v>0.6</v>
       </c>
-      <c r="F186" s="50" t="n">
+      <c r="H186" s="50" t="n">
         <v>-1.2</v>
       </c>
-      <c r="G186" s="2" t="n"/>
     </row>
     <row r="187">
       <c r="A187" s="50" t="inlineStr">
@@ -12219,12 +13064,17 @@
         <v>4</v>
       </c>
       <c r="E187" s="50" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F187" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G187" s="50" t="n">
         <v>0.6</v>
       </c>
-      <c r="F187" s="50" t="n">
+      <c r="H187" s="50" t="n">
         <v>-2.4</v>
       </c>
-      <c r="G187" s="2" t="n"/>
     </row>
     <row r="188">
       <c r="A188" s="50" t="inlineStr">
@@ -12246,12 +13096,17 @@
         <v>1</v>
       </c>
       <c r="E188" s="50" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F188" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G188" s="50" t="n">
         <v>0.6</v>
       </c>
-      <c r="F188" s="50" t="n">
+      <c r="H188" s="50" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G188" s="2" t="n"/>
     </row>
     <row r="189">
       <c r="A189" s="50" t="inlineStr">
@@ -12273,12 +13128,17 @@
         <v>16</v>
       </c>
       <c r="E189" s="50" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="F189" s="50" t="n">
-        <v>-9.6</v>
-      </c>
-      <c r="G189" s="2" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="G189" s="50" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H189" s="50" t="n">
+        <v>-6.4</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" s="49" t="inlineStr">
@@ -12303,9 +13163,14 @@
         <v>5</v>
       </c>
       <c r="F190" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="G190" s="49" t="n">
         <v>5</v>
       </c>
-      <c r="G190" s="2" t="n"/>
+      <c r="H190" s="49" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" s="49" t="inlineStr">
@@ -12330,9 +13195,14 @@
         <v>1</v>
       </c>
       <c r="F191" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="G191" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="H191" s="49" t="n">
         <v>3</v>
       </c>
-      <c r="G191" s="2" t="n"/>
     </row>
     <row r="192">
       <c r="A192" s="50" t="inlineStr">
@@ -12354,12 +13224,17 @@
         <v>1</v>
       </c>
       <c r="E192" s="50" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F192" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G192" s="50" t="n">
         <v>0.6</v>
       </c>
-      <c r="F192" s="50" t="n">
+      <c r="H192" s="50" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G192" s="2" t="n"/>
     </row>
     <row r="193">
       <c r="A193" s="50" t="inlineStr">
@@ -12381,12 +13256,17 @@
         <v>2</v>
       </c>
       <c r="E193" s="50" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F193" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G193" s="50" t="n">
         <v>3</v>
       </c>
-      <c r="F193" s="50" t="n">
+      <c r="H193" s="50" t="n">
         <v>-6</v>
       </c>
-      <c r="G193" s="2" t="n"/>
     </row>
     <row r="194">
       <c r="A194" s="49" t="inlineStr">
@@ -12411,9 +13291,14 @@
         <v>1</v>
       </c>
       <c r="F194" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="G194" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="H194" s="49" t="n">
         <v>4</v>
       </c>
-      <c r="G194" s="2" t="n"/>
     </row>
     <row r="195">
       <c r="A195" s="50" t="inlineStr">
@@ -12435,12 +13320,17 @@
         <v>2</v>
       </c>
       <c r="E195" s="50" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F195" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G195" s="50" t="n">
         <v>0.6</v>
       </c>
-      <c r="F195" s="50" t="n">
+      <c r="H195" s="50" t="n">
         <v>-1.2</v>
       </c>
-      <c r="G195" s="2" t="n"/>
     </row>
     <row r="196">
       <c r="A196" s="50" t="inlineStr">
@@ -12462,12 +13352,17 @@
         <v>2</v>
       </c>
       <c r="E196" s="50" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F196" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G196" s="50" t="n">
         <v>0.6</v>
       </c>
-      <c r="F196" s="50" t="n">
+      <c r="H196" s="50" t="n">
         <v>-1.2</v>
       </c>
-      <c r="G196" s="2" t="n"/>
     </row>
     <row r="197">
       <c r="A197" s="50" t="inlineStr">
@@ -12489,12 +13384,17 @@
         <v>1</v>
       </c>
       <c r="E197" s="50" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F197" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G197" s="50" t="n">
         <v>3</v>
       </c>
-      <c r="F197" s="50" t="n">
+      <c r="H197" s="50" t="n">
         <v>-3</v>
       </c>
-      <c r="G197" s="2" t="n"/>
     </row>
     <row r="198">
       <c r="A198" s="50" t="inlineStr">
@@ -12516,12 +13416,17 @@
         <v>65</v>
       </c>
       <c r="E198" s="50" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="F198" s="50" t="n">
-        <v>-39</v>
-      </c>
-      <c r="G198" s="2" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="G198" s="50" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H198" s="50" t="n">
+        <v>-26</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" s="49" t="inlineStr">
@@ -12546,9 +13451,14 @@
         <v>1</v>
       </c>
       <c r="F199" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="G199" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="H199" s="49" t="n">
         <v>3</v>
       </c>
-      <c r="G199" s="2" t="n"/>
     </row>
     <row r="200">
       <c r="A200" s="50" t="inlineStr">
@@ -12573,9 +13483,14 @@
         <v>0.5</v>
       </c>
       <c r="F200" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="G200" s="50" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H200" s="50" t="n">
         <v>-0.5</v>
       </c>
-      <c r="G200" s="2" t="n"/>
     </row>
     <row r="201">
       <c r="A201" s="50" t="inlineStr">
@@ -12597,12 +13512,17 @@
         <v>2</v>
       </c>
       <c r="E201" s="50" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F201" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G201" s="50" t="n">
         <v>0.6</v>
       </c>
-      <c r="F201" s="50" t="n">
+      <c r="H201" s="50" t="n">
         <v>-1.2</v>
       </c>
-      <c r="G201" s="2" t="n"/>
     </row>
     <row r="202">
       <c r="A202" s="50" t="inlineStr">
@@ -12624,12 +13544,17 @@
         <v>3</v>
       </c>
       <c r="E202" s="50" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F202" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G202" s="50" t="n">
         <v>0.6</v>
       </c>
-      <c r="F202" s="50" t="n">
+      <c r="H202" s="50" t="n">
         <v>-1.8</v>
       </c>
-      <c r="G202" s="2" t="n"/>
     </row>
     <row r="203">
       <c r="A203" s="50" t="inlineStr">
@@ -12651,12 +13576,17 @@
         <v>2</v>
       </c>
       <c r="E203" s="50" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F203" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G203" s="50" t="n">
         <v>3</v>
       </c>
-      <c r="F203" s="50" t="n">
+      <c r="H203" s="50" t="n">
         <v>-6</v>
       </c>
-      <c r="G203" s="2" t="n"/>
     </row>
     <row r="204">
       <c r="A204" s="50" t="inlineStr">
@@ -12678,12 +13608,17 @@
         <v>9</v>
       </c>
       <c r="E204" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="F204" s="50" t="n">
         <v>2</v>
       </c>
-      <c r="F204" s="50" t="n">
+      <c r="G204" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="H204" s="50" t="n">
         <v>-18</v>
       </c>
-      <c r="G204" s="2" t="n"/>
     </row>
     <row r="205">
       <c r="A205" s="50" t="inlineStr">
@@ -12705,12 +13640,17 @@
         <v>2</v>
       </c>
       <c r="E205" s="50" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F205" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G205" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="H205" s="50" t="n">
         <v>-2</v>
       </c>
-      <c r="G205" s="2" t="n"/>
     </row>
     <row r="206">
       <c r="A206" s="50" t="inlineStr">
@@ -12732,12 +13672,17 @@
         <v>59</v>
       </c>
       <c r="E206" s="50" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="F206" s="50" t="n">
-        <v>-35.4</v>
-      </c>
-      <c r="G206" s="2" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="G206" s="50" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H206" s="50" t="n">
+        <v>-23.6</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" s="49" t="inlineStr">
@@ -12762,9 +13707,14 @@
         <v>5</v>
       </c>
       <c r="F207" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="G207" s="49" t="n">
         <v>5</v>
       </c>
-      <c r="G207" s="2" t="n"/>
+      <c r="H207" s="49" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208" s="49" t="inlineStr">
@@ -12789,9 +13739,14 @@
         <v>1</v>
       </c>
       <c r="F208" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="G208" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="H208" s="49" t="n">
         <v>2</v>
       </c>
-      <c r="G208" s="2" t="n"/>
     </row>
     <row r="209">
       <c r="A209" s="50" t="inlineStr">
@@ -12816,9 +13771,14 @@
         <v>0.5</v>
       </c>
       <c r="F209" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="G209" s="50" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H209" s="50" t="n">
         <v>-1</v>
       </c>
-      <c r="G209" s="2" t="n"/>
     </row>
     <row r="210">
       <c r="A210" s="50" t="inlineStr">
@@ -12840,12 +13800,17 @@
         <v>1</v>
       </c>
       <c r="E210" s="50" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F210" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G210" s="50" t="n">
         <v>0.6</v>
       </c>
-      <c r="F210" s="50" t="n">
+      <c r="H210" s="50" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G210" s="2" t="n"/>
     </row>
     <row r="211">
       <c r="A211" s="50" t="inlineStr">
@@ -12867,12 +13832,17 @@
         <v>1</v>
       </c>
       <c r="E211" s="50" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F211" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G211" s="50" t="n">
         <v>0.6</v>
       </c>
-      <c r="F211" s="50" t="n">
+      <c r="H211" s="50" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G211" s="2" t="n"/>
     </row>
     <row r="212">
       <c r="A212" s="50" t="inlineStr">
@@ -12894,12 +13864,17 @@
         <v>1</v>
       </c>
       <c r="E212" s="50" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F212" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G212" s="50" t="n">
         <v>0.6</v>
       </c>
-      <c r="F212" s="50" t="n">
+      <c r="H212" s="50" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G212" s="2" t="n"/>
     </row>
     <row r="213">
       <c r="A213" s="50" t="inlineStr">
@@ -12921,12 +13896,17 @@
         <v>1</v>
       </c>
       <c r="E213" s="50" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F213" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G213" s="50" t="n">
         <v>0.6</v>
       </c>
-      <c r="F213" s="50" t="n">
+      <c r="H213" s="50" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G213" s="2" t="n"/>
     </row>
     <row r="214">
       <c r="A214" s="50" t="inlineStr">
@@ -12948,12 +13928,17 @@
         <v>1</v>
       </c>
       <c r="E214" s="50" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F214" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G214" s="50" t="n">
         <v>3</v>
       </c>
-      <c r="F214" s="50" t="n">
+      <c r="H214" s="50" t="n">
         <v>-3</v>
       </c>
-      <c r="G214" s="2" t="n"/>
     </row>
     <row r="215">
       <c r="A215" s="49" t="inlineStr">
@@ -12978,9 +13963,14 @@
         <v>5</v>
       </c>
       <c r="F215" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="G215" s="49" t="n">
         <v>5</v>
       </c>
-      <c r="G215" s="2" t="n"/>
+      <c r="H215" s="49" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" s="49" t="inlineStr">
@@ -13005,9 +13995,14 @@
         <v>1</v>
       </c>
       <c r="F216" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="G216" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="H216" s="49" t="n">
         <v>3</v>
       </c>
-      <c r="G216" s="2" t="n"/>
     </row>
     <row r="217">
       <c r="A217" s="50" t="inlineStr">
@@ -13032,9 +14027,14 @@
         <v>0.5</v>
       </c>
       <c r="F217" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="G217" s="50" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H217" s="50" t="n">
         <v>-0.5</v>
       </c>
-      <c r="G217" s="2" t="n"/>
     </row>
     <row r="218">
       <c r="A218" s="50" t="inlineStr">
@@ -13056,12 +14056,17 @@
         <v>3</v>
       </c>
       <c r="E218" s="50" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F218" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G218" s="50" t="n">
         <v>0.6</v>
       </c>
-      <c r="F218" s="50" t="n">
+      <c r="H218" s="50" t="n">
         <v>-1.8</v>
       </c>
-      <c r="G218" s="2" t="n"/>
     </row>
     <row r="219">
       <c r="A219" s="50" t="inlineStr">
@@ -13083,12 +14088,17 @@
         <v>4</v>
       </c>
       <c r="E219" s="50" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F219" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G219" s="50" t="n">
         <v>0.6</v>
       </c>
-      <c r="F219" s="50" t="n">
+      <c r="H219" s="50" t="n">
         <v>-2.4</v>
       </c>
-      <c r="G219" s="2" t="n"/>
     </row>
     <row r="220">
       <c r="A220" s="50" t="inlineStr">
@@ -13110,12 +14120,17 @@
         <v>4</v>
       </c>
       <c r="E220" s="50" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F220" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G220" s="50" t="n">
         <v>0.6</v>
       </c>
-      <c r="F220" s="50" t="n">
+      <c r="H220" s="50" t="n">
         <v>-2.4</v>
       </c>
-      <c r="G220" s="2" t="n"/>
     </row>
     <row r="221">
       <c r="A221" s="50" t="inlineStr">
@@ -13137,12 +14152,17 @@
         <v>2</v>
       </c>
       <c r="E221" s="50" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F221" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G221" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="H221" s="50" t="n">
         <v>-2</v>
       </c>
-      <c r="G221" s="2" t="n"/>
     </row>
     <row r="222">
       <c r="A222" s="50" t="inlineStr">
@@ -13164,12 +14184,17 @@
         <v>11</v>
       </c>
       <c r="E222" s="50" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="F222" s="50" t="n">
-        <v>-6.6</v>
-      </c>
-      <c r="G222" s="2" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="G222" s="50" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H222" s="50" t="n">
+        <v>-4.4</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223" s="49" t="inlineStr">
@@ -13194,9 +14219,14 @@
         <v>5</v>
       </c>
       <c r="F223" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="G223" s="49" t="n">
         <v>5</v>
       </c>
-      <c r="G223" s="2" t="n"/>
+      <c r="H223" s="49" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" s="49" t="inlineStr">
@@ -13221,9 +14251,14 @@
         <v>1</v>
       </c>
       <c r="F224" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="G224" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="H224" s="49" t="n">
         <v>3</v>
       </c>
-      <c r="G224" s="2" t="n"/>
     </row>
     <row r="225">
       <c r="A225" s="50" t="inlineStr">
@@ -13248,9 +14283,14 @@
         <v>0.5</v>
       </c>
       <c r="F225" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="G225" s="50" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H225" s="50" t="n">
         <v>-0.5</v>
       </c>
-      <c r="G225" s="2" t="n"/>
     </row>
     <row r="226">
       <c r="A226" s="50" t="inlineStr">
@@ -13272,12 +14312,17 @@
         <v>1</v>
       </c>
       <c r="E226" s="50" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F226" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G226" s="50" t="n">
         <v>0.6</v>
       </c>
-      <c r="F226" s="50" t="n">
+      <c r="H226" s="50" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G226" s="2" t="n"/>
     </row>
     <row r="227">
       <c r="A227" s="50" t="inlineStr">
@@ -13299,12 +14344,17 @@
         <v>3</v>
       </c>
       <c r="E227" s="50" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F227" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G227" s="50" t="n">
         <v>0.6</v>
       </c>
-      <c r="F227" s="50" t="n">
+      <c r="H227" s="50" t="n">
         <v>-1.8</v>
       </c>
-      <c r="G227" s="2" t="n"/>
     </row>
     <row r="228">
       <c r="A228" s="50" t="inlineStr">
@@ -13326,12 +14376,17 @@
         <v>3</v>
       </c>
       <c r="E228" s="50" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F228" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G228" s="50" t="n">
         <v>0.6</v>
       </c>
-      <c r="F228" s="50" t="n">
+      <c r="H228" s="50" t="n">
         <v>-1.8</v>
       </c>
-      <c r="G228" s="2" t="n"/>
     </row>
     <row r="229">
       <c r="A229" s="50" t="inlineStr">
@@ -13353,12 +14408,17 @@
         <v>1</v>
       </c>
       <c r="E229" s="50" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F229" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G229" s="50" t="n">
         <v>0.6</v>
       </c>
-      <c r="F229" s="50" t="n">
+      <c r="H229" s="50" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G229" s="2" t="n"/>
     </row>
     <row r="230">
       <c r="A230" s="50" t="inlineStr">
@@ -13380,12 +14440,17 @@
         <v>2</v>
       </c>
       <c r="E230" s="50" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="F230" s="50" t="n">
-        <v>-1.2</v>
-      </c>
-      <c r="G230" s="2" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="G230" s="50" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H230" s="50" t="n">
+        <v>-0.8</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231" s="49" t="inlineStr">
@@ -13410,9 +14475,14 @@
         <v>1</v>
       </c>
       <c r="F231" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="G231" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="H231" s="49" t="n">
         <v>3</v>
       </c>
-      <c r="G231" s="2" t="n"/>
     </row>
     <row r="232">
       <c r="A232" s="50" t="inlineStr">
@@ -13434,12 +14504,17 @@
         <v>2</v>
       </c>
       <c r="E232" s="50" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F232" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G232" s="50" t="n">
         <v>0.6</v>
       </c>
-      <c r="F232" s="50" t="n">
+      <c r="H232" s="50" t="n">
         <v>-1.2</v>
       </c>
-      <c r="G232" s="2" t="n"/>
     </row>
     <row r="233">
       <c r="A233" s="50" t="inlineStr">
@@ -13461,12 +14536,17 @@
         <v>2</v>
       </c>
       <c r="E233" s="50" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F233" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G233" s="50" t="n">
         <v>0.6</v>
       </c>
-      <c r="F233" s="50" t="n">
+      <c r="H233" s="50" t="n">
         <v>-1.2</v>
       </c>
-      <c r="G233" s="2" t="n"/>
     </row>
     <row r="234">
       <c r="A234" s="50" t="inlineStr">
@@ -13488,12 +14568,17 @@
         <v>2</v>
       </c>
       <c r="E234" s="50" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F234" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G234" s="50" t="n">
         <v>3</v>
       </c>
-      <c r="F234" s="50" t="n">
+      <c r="H234" s="50" t="n">
         <v>-6</v>
       </c>
-      <c r="G234" s="2" t="n"/>
     </row>
     <row r="235">
       <c r="A235" s="50" t="inlineStr">
@@ -13515,12 +14600,17 @@
         <v>6</v>
       </c>
       <c r="E235" s="50" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="F235" s="50" t="n">
-        <v>-3.6</v>
-      </c>
-      <c r="G235" s="2" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="G235" s="50" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H235" s="50" t="n">
+        <v>-2.4</v>
+      </c>
     </row>
     <row r="236">
       <c r="A236" s="49" t="inlineStr">
@@ -13545,9 +14635,14 @@
         <v>5</v>
       </c>
       <c r="F236" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="G236" s="49" t="n">
         <v>5</v>
       </c>
-      <c r="G236" s="2" t="n"/>
+      <c r="H236" s="49" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237" s="49" t="inlineStr">
@@ -13572,9 +14667,14 @@
         <v>5</v>
       </c>
       <c r="F237" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="G237" s="49" t="n">
         <v>5</v>
       </c>
-      <c r="G237" s="2" t="n"/>
+      <c r="H237" s="49" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238" s="49" t="inlineStr">
@@ -13599,9 +14699,14 @@
         <v>1</v>
       </c>
       <c r="F238" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="G238" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="H238" s="49" t="n">
         <v>4</v>
       </c>
-      <c r="G238" s="2" t="n"/>
     </row>
     <row r="239">
       <c r="A239" s="50" t="inlineStr">
@@ -13623,12 +14728,17 @@
         <v>1</v>
       </c>
       <c r="E239" s="50" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F239" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G239" s="50" t="n">
         <v>0.6</v>
       </c>
-      <c r="F239" s="50" t="n">
+      <c r="H239" s="50" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G239" s="2" t="n"/>
     </row>
     <row r="240">
       <c r="A240" s="50" t="inlineStr">
@@ -13650,12 +14760,17 @@
         <v>1</v>
       </c>
       <c r="E240" s="50" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F240" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G240" s="50" t="n">
         <v>0.6</v>
       </c>
-      <c r="F240" s="50" t="n">
+      <c r="H240" s="50" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G240" s="2" t="n"/>
     </row>
     <row r="241">
       <c r="A241" s="50" t="inlineStr">
@@ -13677,12 +14792,17 @@
         <v>2</v>
       </c>
       <c r="E241" s="50" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F241" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G241" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="H241" s="50" t="n">
         <v>-2</v>
       </c>
-      <c r="G241" s="2" t="n"/>
     </row>
     <row r="242">
       <c r="A242" s="50" t="inlineStr">
@@ -13704,12 +14824,17 @@
         <v>1</v>
       </c>
       <c r="E242" s="50" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F242" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G242" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="H242" s="50" t="n">
         <v>-1</v>
       </c>
-      <c r="G242" s="2" t="n"/>
     </row>
     <row r="243">
       <c r="A243" s="49" t="inlineStr">
@@ -13734,9 +14859,14 @@
         <v>1</v>
       </c>
       <c r="F243" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="G243" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="H243" s="49" t="n">
         <v>3</v>
       </c>
-      <c r="G243" s="2" t="n"/>
     </row>
     <row r="244">
       <c r="A244" s="50" t="inlineStr">
@@ -13761,9 +14891,14 @@
         <v>0.5</v>
       </c>
       <c r="F244" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="G244" s="50" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H244" s="50" t="n">
         <v>-0.5</v>
       </c>
-      <c r="G244" s="2" t="n"/>
     </row>
     <row r="245">
       <c r="A245" s="50" t="inlineStr">
@@ -13785,12 +14920,17 @@
         <v>1</v>
       </c>
       <c r="E245" s="50" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F245" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G245" s="50" t="n">
         <v>0.6</v>
       </c>
-      <c r="F245" s="50" t="n">
+      <c r="H245" s="50" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G245" s="2" t="n"/>
     </row>
     <row r="246">
       <c r="A246" s="50" t="inlineStr">
@@ -13812,12 +14952,17 @@
         <v>3</v>
       </c>
       <c r="E246" s="50" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F246" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G246" s="50" t="n">
         <v>0.6</v>
       </c>
-      <c r="F246" s="50" t="n">
+      <c r="H246" s="50" t="n">
         <v>-1.8</v>
       </c>
-      <c r="G246" s="2" t="n"/>
     </row>
     <row r="247">
       <c r="A247" s="50" t="inlineStr">
@@ -13839,12 +14984,17 @@
         <v>1</v>
       </c>
       <c r="E247" s="50" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F247" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G247" s="50" t="n">
         <v>0.6</v>
       </c>
-      <c r="F247" s="50" t="n">
+      <c r="H247" s="50" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G247" s="2" t="n"/>
     </row>
     <row r="248">
       <c r="A248" s="50" t="inlineStr">
@@ -13866,12 +15016,17 @@
         <v>1</v>
       </c>
       <c r="E248" s="50" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F248" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G248" s="50" t="n">
         <v>3</v>
       </c>
-      <c r="F248" s="50" t="n">
+      <c r="H248" s="50" t="n">
         <v>-3</v>
       </c>
-      <c r="G248" s="2" t="n"/>
     </row>
     <row r="249">
       <c r="A249" s="50" t="inlineStr">
@@ -13893,12 +15048,17 @@
         <v>1</v>
       </c>
       <c r="E249" s="50" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F249" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G249" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="H249" s="50" t="n">
         <v>-1</v>
       </c>
-      <c r="G249" s="2" t="n"/>
     </row>
     <row r="250">
       <c r="A250" s="50" t="inlineStr">
@@ -13920,12 +15080,17 @@
         <v>1</v>
       </c>
       <c r="E250" s="50" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="F250" s="50" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="G250" s="2" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="G250" s="50" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H250" s="50" t="n">
+        <v>-0.4</v>
+      </c>
     </row>
     <row r="251">
       <c r="A251" s="49" t="inlineStr">
@@ -13950,9 +15115,14 @@
         <v>5</v>
       </c>
       <c r="F251" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="G251" s="49" t="n">
         <v>5</v>
       </c>
-      <c r="G251" s="2" t="n"/>
+      <c r="H251" s="49" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="252">
       <c r="A252" s="49" t="inlineStr">
@@ -13977,9 +15147,14 @@
         <v>1</v>
       </c>
       <c r="F252" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="G252" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="H252" s="49" t="n">
         <v>2</v>
       </c>
-      <c r="G252" s="2" t="n"/>
     </row>
     <row r="253">
       <c r="A253" s="50" t="inlineStr">
@@ -14004,9 +15179,14 @@
         <v>0.5</v>
       </c>
       <c r="F253" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="G253" s="50" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H253" s="50" t="n">
         <v>-0.5</v>
       </c>
-      <c r="G253" s="2" t="n"/>
     </row>
     <row r="254">
       <c r="A254" s="50" t="inlineStr">
@@ -14028,12 +15208,17 @@
         <v>1</v>
       </c>
       <c r="E254" s="50" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F254" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G254" s="50" t="n">
         <v>0.6</v>
       </c>
-      <c r="F254" s="50" t="n">
+      <c r="H254" s="50" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G254" s="2" t="n"/>
     </row>
     <row r="255">
       <c r="A255" s="50" t="inlineStr">
@@ -14055,12 +15240,17 @@
         <v>2</v>
       </c>
       <c r="E255" s="50" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F255" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G255" s="50" t="n">
         <v>3</v>
       </c>
-      <c r="F255" s="50" t="n">
+      <c r="H255" s="50" t="n">
         <v>-6</v>
       </c>
-      <c r="G255" s="2" t="n"/>
     </row>
     <row r="256">
       <c r="A256" s="50" t="inlineStr">
@@ -14085,9 +15275,14 @@
         <v>0.5</v>
       </c>
       <c r="F256" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="G256" s="50" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H256" s="50" t="n">
         <v>-0.5</v>
       </c>
-      <c r="G256" s="2" t="n"/>
     </row>
     <row r="257">
       <c r="A257" s="50" t="inlineStr">
@@ -14109,12 +15304,17 @@
         <v>1</v>
       </c>
       <c r="E257" s="50" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F257" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G257" s="50" t="n">
         <v>0.6</v>
       </c>
-      <c r="F257" s="50" t="n">
+      <c r="H257" s="50" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G257" s="2" t="n"/>
     </row>
     <row r="258">
       <c r="A258" s="50" t="inlineStr">
@@ -14136,12 +15336,17 @@
         <v>2</v>
       </c>
       <c r="E258" s="50" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F258" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G258" s="50" t="n">
         <v>3</v>
       </c>
-      <c r="F258" s="50" t="n">
+      <c r="H258" s="50" t="n">
         <v>-6</v>
       </c>
-      <c r="G258" s="2" t="n"/>
     </row>
     <row r="259">
       <c r="A259" s="50" t="inlineStr">
@@ -14163,12 +15368,17 @@
         <v>5</v>
       </c>
       <c r="E259" s="50" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="F259" s="50" t="n">
-        <v>-3</v>
-      </c>
-      <c r="G259" s="2" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="G259" s="50" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H259" s="50" t="n">
+        <v>-2</v>
+      </c>
     </row>
     <row r="260">
       <c r="A260" s="49" t="inlineStr">
@@ -14195,7 +15405,12 @@
       <c r="F260" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="G260" s="2" t="n"/>
+      <c r="G260" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="H260" s="49" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="261">
       <c r="A261" s="50" t="inlineStr">
@@ -14217,12 +15432,17 @@
         <v>1</v>
       </c>
       <c r="E261" s="50" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F261" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G261" s="50" t="n">
         <v>0.6</v>
       </c>
-      <c r="F261" s="50" t="n">
+      <c r="H261" s="50" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G261" s="2" t="n"/>
     </row>
     <row r="262">
       <c r="A262" s="50" t="inlineStr">
@@ -14244,12 +15464,17 @@
         <v>6</v>
       </c>
       <c r="E262" s="50" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F262" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G262" s="50" t="n">
         <v>3</v>
       </c>
-      <c r="F262" s="50" t="n">
+      <c r="H262" s="50" t="n">
         <v>-18</v>
       </c>
-      <c r="G262" s="2" t="n"/>
     </row>
     <row r="263">
       <c r="A263" s="50" t="inlineStr">
@@ -14271,12 +15496,17 @@
         <v>11</v>
       </c>
       <c r="E263" s="50" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="F263" s="50" t="n">
-        <v>-6.6</v>
-      </c>
-      <c r="G263" s="2" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="G263" s="50" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H263" s="50" t="n">
+        <v>-4.4</v>
+      </c>
     </row>
     <row r="264">
       <c r="A264" s="49" t="inlineStr">
@@ -14301,9 +15531,14 @@
         <v>1</v>
       </c>
       <c r="F264" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="G264" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="H264" s="49" t="n">
         <v>2</v>
       </c>
-      <c r="G264" s="2" t="n"/>
     </row>
     <row r="265">
       <c r="A265" s="50" t="inlineStr">
@@ -14325,12 +15560,17 @@
         <v>1</v>
       </c>
       <c r="E265" s="50" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F265" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G265" s="50" t="n">
         <v>0.6</v>
       </c>
-      <c r="F265" s="50" t="n">
+      <c r="H265" s="50" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G265" s="2" t="n"/>
     </row>
     <row r="266">
       <c r="A266" s="50" t="inlineStr">
@@ -14352,12 +15592,17 @@
         <v>4</v>
       </c>
       <c r="E266" s="50" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F266" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G266" s="50" t="n">
         <v>3</v>
       </c>
-      <c r="F266" s="50" t="n">
+      <c r="H266" s="50" t="n">
         <v>-12</v>
       </c>
-      <c r="G266" s="2" t="n"/>
     </row>
     <row r="267">
       <c r="A267" s="50" t="inlineStr">
@@ -14379,12 +15624,17 @@
         <v>4</v>
       </c>
       <c r="E267" s="50" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="F267" s="50" t="n">
-        <v>-2.4</v>
-      </c>
-      <c r="G267" s="2" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="G267" s="50" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H267" s="50" t="n">
+        <v>-1.6</v>
+      </c>
     </row>
     <row r="268">
       <c r="A268" s="49" t="inlineStr">
@@ -14409,9 +15659,14 @@
         <v>5</v>
       </c>
       <c r="F268" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="G268" s="49" t="n">
         <v>5</v>
       </c>
-      <c r="G268" s="2" t="n"/>
+      <c r="H268" s="49" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="269">
       <c r="A269" s="49" t="inlineStr">
@@ -14436,9 +15691,14 @@
         <v>1</v>
       </c>
       <c r="F269" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="G269" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="H269" s="49" t="n">
         <v>3</v>
       </c>
-      <c r="G269" s="2" t="n"/>
     </row>
     <row r="270">
       <c r="A270" s="50" t="inlineStr">
@@ -14463,9 +15723,14 @@
         <v>0.5</v>
       </c>
       <c r="F270" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="G270" s="50" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H270" s="50" t="n">
         <v>-0.5</v>
       </c>
-      <c r="G270" s="2" t="n"/>
     </row>
     <row r="271">
       <c r="A271" s="50" t="inlineStr">
@@ -14487,12 +15752,17 @@
         <v>1</v>
       </c>
       <c r="E271" s="50" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F271" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G271" s="50" t="n">
         <v>0.6</v>
       </c>
-      <c r="F271" s="50" t="n">
+      <c r="H271" s="50" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G271" s="2" t="n"/>
     </row>
     <row r="272">
       <c r="A272" s="50" t="inlineStr">
@@ -14514,12 +15784,17 @@
         <v>2</v>
       </c>
       <c r="E272" s="50" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F272" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G272" s="50" t="n">
         <v>0.6</v>
       </c>
-      <c r="F272" s="50" t="n">
+      <c r="H272" s="50" t="n">
         <v>-1.2</v>
       </c>
-      <c r="G272" s="2" t="n"/>
     </row>
     <row r="273">
       <c r="A273" s="50" t="inlineStr">
@@ -14541,12 +15816,17 @@
         <v>1</v>
       </c>
       <c r="E273" s="50" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F273" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G273" s="50" t="n">
         <v>3</v>
       </c>
-      <c r="F273" s="50" t="n">
+      <c r="H273" s="50" t="n">
         <v>-3</v>
       </c>
-      <c r="G273" s="2" t="n"/>
     </row>
     <row r="274">
       <c r="A274" s="49" t="inlineStr">
@@ -14571,9 +15851,14 @@
         <v>5</v>
       </c>
       <c r="F274" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="G274" s="49" t="n">
         <v>5</v>
       </c>
-      <c r="G274" s="2" t="n"/>
+      <c r="H274" s="49" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="275">
       <c r="A275" s="49" t="inlineStr">
@@ -14598,9 +15883,14 @@
         <v>1</v>
       </c>
       <c r="F275" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="G275" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="H275" s="49" t="n">
         <v>3</v>
       </c>
-      <c r="G275" s="2" t="n"/>
     </row>
     <row r="276">
       <c r="A276" s="50" t="inlineStr">
@@ -14625,9 +15915,14 @@
         <v>0.5</v>
       </c>
       <c r="F276" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="G276" s="50" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H276" s="50" t="n">
         <v>-0.5</v>
       </c>
-      <c r="G276" s="2" t="n"/>
     </row>
     <row r="277">
       <c r="A277" s="50" t="inlineStr">
@@ -14649,12 +15944,17 @@
         <v>3</v>
       </c>
       <c r="E277" s="50" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F277" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G277" s="50" t="n">
         <v>0.6</v>
       </c>
-      <c r="F277" s="50" t="n">
+      <c r="H277" s="50" t="n">
         <v>-1.8</v>
       </c>
-      <c r="G277" s="2" t="n"/>
     </row>
     <row r="278">
       <c r="A278" s="50" t="inlineStr">
@@ -14676,18 +15976,23 @@
         <v>1</v>
       </c>
       <c r="E278" s="50" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F278" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G278" s="50" t="n">
         <v>3</v>
       </c>
-      <c r="F278" s="50" t="n">
+      <c r="H278" s="50" t="n">
         <v>-3</v>
       </c>
-      <c r="G278" s="2" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:G39"/>
+  <autoFilter ref="A2:H39"/>
   <mergeCells count="2">
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A42:F42"/>
+    <mergeCell ref="A42:H42"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -15259,36 +16564,36 @@
         </is>
       </c>
       <c r="D11" s="5" t="n">
-        <v>96</v>
+        <v>152</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>3.39</v>
+        <v>3.41</v>
       </c>
       <c r="F11" s="5" t="n">
         <v>3</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H11" s="5" t="inlineStr">
         <is>
-          <t>Q030, Q031, Q032, Q033, Q034, Q035, Q038, Q039</t>
+          <t>Q030, Q031, Q032, Q033, Q034, Q035, Q036, Q037, Q038, Q039</t>
         </is>
       </c>
       <c r="I11" s="5" t="n">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>39.58</v>
+        <v>36.18</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="L11" s="5" t="n">
         <v>0</v>
       </c>
       <c r="M11" s="5" t="n">
-        <v>11.93</v>
+        <v>12.64</v>
       </c>
       <c r="N11" s="5" t="inlineStr">
         <is>
@@ -15421,20 +16726,20 @@
         </is>
       </c>
       <c r="D14" s="4" t="n">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>5.75</v>
+        <v>5.88</v>
       </c>
       <c r="F14" s="4" t="n">
         <v>5</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>Q016, Q037</t>
+          <t>Q001, Q016, Q026, Q037</t>
         </is>
       </c>
       <c r="I14" s="4" t="n">
@@ -15444,13 +16749,13 @@
         <v>0</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="L14" s="4" t="n">
         <v>0</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>40.74</v>
+        <v>36.51</v>
       </c>
       <c r="N14" s="4" t="inlineStr">
         <is>
@@ -17943,110 +19248,110 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="6" t="inlineStr">
+      <c r="A61" s="4" t="inlineStr">
         <is>
           <t>Gisele Lopes Justiniano</t>
         </is>
       </c>
-      <c r="B61" s="6" t="inlineStr">
+      <c r="B61" s="4" t="inlineStr">
         <is>
           <t>Equipe 4</t>
         </is>
       </c>
-      <c r="C61" s="6" t="inlineStr">
+      <c r="C61" s="4" t="inlineStr">
+        <is>
+          <t>441 - PARQUE DOS IPES</t>
+        </is>
+      </c>
+      <c r="D61" s="4" t="n">
+        <v>83</v>
+      </c>
+      <c r="E61" s="4" t="n">
+        <v>6.13</v>
+      </c>
+      <c r="F61" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="G61" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="H61" s="4" t="inlineStr">
+        <is>
+          <t>Q001, Q002, Q019, Q024, Q039, Q040, Q041</t>
+        </is>
+      </c>
+      <c r="I61" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J61" s="4" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="K61" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="L61" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M61" s="4" t="n">
+        <v>32.52</v>
+      </c>
+      <c r="N61" s="4" t="inlineStr">
+        <is>
+          <t>🟢 NORMAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="6" t="inlineStr">
+        <is>
+          <t>Gisele Lopes Justiniano</t>
+        </is>
+      </c>
+      <c r="B62" s="6" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="C62" s="6" t="inlineStr">
         <is>
           <t>435 - JARDIM PRIMOR</t>
         </is>
       </c>
-      <c r="D61" s="6" t="n">
+      <c r="D62" s="6" t="n">
         <v>36</v>
       </c>
-      <c r="E61" s="6" t="n">
+      <c r="E62" s="6" t="n">
         <v>6.47</v>
       </c>
-      <c r="F61" s="6" t="n">
+      <c r="F62" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="G61" s="6" t="n">
+      <c r="G62" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="H61" s="6" t="inlineStr">
+      <c r="H62" s="6" t="inlineStr">
         <is>
           <t>Q019, Q021, Q022, Q023</t>
         </is>
       </c>
-      <c r="I61" s="6" t="n">
+      <c r="I62" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="J61" s="6" t="n">
+      <c r="J62" s="6" t="n">
         <v>11.11</v>
       </c>
-      <c r="K61" s="6" t="n">
+      <c r="K62" s="6" t="n">
         <v>15</v>
       </c>
-      <c r="L61" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M61" s="6" t="n">
+      <c r="L62" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M62" s="6" t="n">
         <v>29.41</v>
       </c>
-      <c r="N61" s="6" t="inlineStr">
+      <c r="N62" s="6" t="inlineStr">
         <is>
           <t>🟡 ATENÇÃO</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="4" t="inlineStr">
-        <is>
-          <t>Gisele Lopes Justiniano</t>
-        </is>
-      </c>
-      <c r="B62" s="4" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="C62" s="4" t="inlineStr">
-        <is>
-          <t>441 - PARQUE DOS IPES</t>
-        </is>
-      </c>
-      <c r="D62" s="4" t="n">
-        <v>51</v>
-      </c>
-      <c r="E62" s="4" t="n">
-        <v>6.63</v>
-      </c>
-      <c r="F62" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="G62" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="H62" s="4" t="inlineStr">
-        <is>
-          <t>Q001, Q002, Q024, Q041</t>
-        </is>
-      </c>
-      <c r="I62" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J62" s="4" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="K62" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="L62" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M62" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="N62" s="4" t="inlineStr">
-        <is>
-          <t>🟢 NORMAL</t>
         </is>
       </c>
     </row>
@@ -19081,7 +20386,7 @@
       </c>
       <c r="C5" s="21" t="inlineStr">
         <is>
-          <t>16975299</t>
+          <t>16975301</t>
         </is>
       </c>
       <c r="D5" s="20" t="inlineStr">
@@ -19185,7 +20490,7 @@
       </c>
       <c r="C7" s="21" t="inlineStr">
         <is>
-          <t>16975301</t>
+          <t>16975299</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr">
@@ -20069,7 +21374,7 @@
       </c>
       <c r="C24" s="21" t="inlineStr">
         <is>
-          <t>17023120</t>
+          <t>17023116</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
@@ -20121,7 +21426,7 @@
       </c>
       <c r="C25" s="21" t="inlineStr">
         <is>
-          <t>17023119</t>
+          <t>17023117</t>
         </is>
       </c>
       <c r="D25" s="20" t="inlineStr">
@@ -20225,7 +21530,7 @@
       </c>
       <c r="C27" s="21" t="inlineStr">
         <is>
-          <t>17023117</t>
+          <t>17023119</t>
         </is>
       </c>
       <c r="D27" s="20" t="inlineStr">
@@ -20277,7 +21582,7 @@
       </c>
       <c r="C28" s="21" t="inlineStr">
         <is>
-          <t>17023116</t>
+          <t>17023120</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
@@ -20329,7 +21634,7 @@
       </c>
       <c r="C29" s="21" t="inlineStr">
         <is>
-          <t>17022602</t>
+          <t>17022604</t>
         </is>
       </c>
       <c r="D29" s="20" t="inlineStr">
@@ -20433,7 +21738,7 @@
       </c>
       <c r="C31" s="21" t="inlineStr">
         <is>
-          <t>17022604</t>
+          <t>17022602</t>
         </is>
       </c>
       <c r="D31" s="20" t="inlineStr">
@@ -20485,7 +21790,7 @@
       </c>
       <c r="C32" s="21" t="inlineStr">
         <is>
-          <t>17022612</t>
+          <t>17022605</t>
         </is>
       </c>
       <c r="D32" s="20" t="inlineStr">
@@ -20537,7 +21842,7 @@
       </c>
       <c r="C33" s="21" t="inlineStr">
         <is>
-          <t>17022611</t>
+          <t>17022606</t>
         </is>
       </c>
       <c r="D33" s="20" t="inlineStr">
@@ -20589,7 +21894,7 @@
       </c>
       <c r="C34" s="21" t="inlineStr">
         <is>
-          <t>17022610</t>
+          <t>17022607</t>
         </is>
       </c>
       <c r="D34" s="20" t="inlineStr">
@@ -20641,7 +21946,7 @@
       </c>
       <c r="C35" s="21" t="inlineStr">
         <is>
-          <t>17022609</t>
+          <t>17022608</t>
         </is>
       </c>
       <c r="D35" s="20" t="inlineStr">
@@ -20693,7 +21998,7 @@
       </c>
       <c r="C36" s="21" t="inlineStr">
         <is>
-          <t>17022605</t>
+          <t>17022609</t>
         </is>
       </c>
       <c r="D36" s="20" t="inlineStr">
@@ -20745,7 +22050,7 @@
       </c>
       <c r="C37" s="21" t="inlineStr">
         <is>
-          <t>17022607</t>
+          <t>17022610</t>
         </is>
       </c>
       <c r="D37" s="20" t="inlineStr">
@@ -20797,7 +22102,7 @@
       </c>
       <c r="C38" s="21" t="inlineStr">
         <is>
-          <t>17022606</t>
+          <t>17022611</t>
         </is>
       </c>
       <c r="D38" s="20" t="inlineStr">
@@ -20849,7 +22154,7 @@
       </c>
       <c r="C39" s="21" t="inlineStr">
         <is>
-          <t>17022608</t>
+          <t>17022612</t>
         </is>
       </c>
       <c r="D39" s="20" t="inlineStr">
@@ -21005,7 +22310,7 @@
       </c>
       <c r="C42" s="21" t="inlineStr">
         <is>
-          <t>17022802</t>
+          <t>17022803</t>
         </is>
       </c>
       <c r="D42" s="20" t="inlineStr">
@@ -21057,7 +22362,7 @@
       </c>
       <c r="C43" s="21" t="inlineStr">
         <is>
-          <t>17022803</t>
+          <t>17022802</t>
         </is>
       </c>
       <c r="D43" s="20" t="inlineStr">
@@ -21109,7 +22414,7 @@
       </c>
       <c r="C44" s="21" t="inlineStr">
         <is>
-          <t>17022907</t>
+          <t>17022908</t>
         </is>
       </c>
       <c r="D44" s="20" t="inlineStr">
@@ -21161,7 +22466,7 @@
       </c>
       <c r="C45" s="21" t="inlineStr">
         <is>
-          <t>17022908</t>
+          <t>17022907</t>
         </is>
       </c>
       <c r="D45" s="20" t="inlineStr">
@@ -21213,7 +22518,7 @@
       </c>
       <c r="C46" s="21" t="inlineStr">
         <is>
-          <t>17023793</t>
+          <t>17023792</t>
         </is>
       </c>
       <c r="D46" s="20" t="inlineStr">
@@ -21265,7 +22570,7 @@
       </c>
       <c r="C47" s="21" t="inlineStr">
         <is>
-          <t>17023792</t>
+          <t>17023793</t>
         </is>
       </c>
       <c r="D47" s="20" t="inlineStr">
@@ -21735,7 +23040,7 @@
       </c>
       <c r="D5" s="24" t="inlineStr">
         <is>
-          <t>16975299</t>
+          <t>16975303</t>
         </is>
       </c>
       <c r="E5" s="23" t="inlineStr">
@@ -21755,7 +23060,7 @@
       </c>
       <c r="H5" s="23" t="inlineStr">
         <is>
-          <t>325 - R</t>
+          <t>325 - 1 - R</t>
         </is>
       </c>
       <c r="I5" s="23" t="inlineStr">
@@ -21765,7 +23070,7 @@
       </c>
       <c r="J5" s="23" t="inlineStr">
         <is>
-          <t>18/08/2026 08:27</t>
+          <t>18/08/2026 08:35</t>
         </is>
       </c>
       <c r="K5" s="23" t="inlineStr"/>
@@ -21786,7 +23091,7 @@
       </c>
       <c r="D6" s="24" t="inlineStr">
         <is>
-          <t>16975300</t>
+          <t>16975301</t>
         </is>
       </c>
       <c r="E6" s="23" t="inlineStr">
@@ -21839,7 +23144,7 @@
       </c>
       <c r="D7" s="24" t="inlineStr">
         <is>
-          <t>16975301</t>
+          <t>16975300</t>
         </is>
       </c>
       <c r="E7" s="23" t="inlineStr">
@@ -21892,7 +23197,7 @@
       </c>
       <c r="D8" s="24" t="inlineStr">
         <is>
-          <t>16975303</t>
+          <t>16975299</t>
         </is>
       </c>
       <c r="E8" s="23" t="inlineStr">
@@ -21912,7 +23217,7 @@
       </c>
       <c r="H8" s="23" t="inlineStr">
         <is>
-          <t>325 - 1 - R</t>
+          <t>325 - R</t>
         </is>
       </c>
       <c r="I8" s="23" t="inlineStr">
@@ -21922,7 +23227,7 @@
       </c>
       <c r="J8" s="23" t="inlineStr">
         <is>
-          <t>18/08/2026 08:35</t>
+          <t>18/08/2026 08:27</t>
         </is>
       </c>
       <c r="K8" s="23" t="n">
@@ -22881,7 +24186,7 @@
       </c>
       <c r="D27" s="24" t="inlineStr">
         <is>
-          <t>17023120</t>
+          <t>17023116</t>
         </is>
       </c>
       <c r="E27" s="23" t="inlineStr">
@@ -22932,7 +24237,7 @@
       </c>
       <c r="D28" s="24" t="inlineStr">
         <is>
-          <t>17023119</t>
+          <t>17023117</t>
         </is>
       </c>
       <c r="E28" s="23" t="inlineStr">
@@ -23038,7 +24343,7 @@
       </c>
       <c r="D30" s="24" t="inlineStr">
         <is>
-          <t>17023117</t>
+          <t>17023119</t>
         </is>
       </c>
       <c r="E30" s="23" t="inlineStr">
@@ -23091,7 +24396,7 @@
       </c>
       <c r="D31" s="24" t="inlineStr">
         <is>
-          <t>17023116</t>
+          <t>17023120</t>
         </is>
       </c>
       <c r="E31" s="23" t="inlineStr">
@@ -23144,7 +24449,7 @@
       </c>
       <c r="D32" s="24" t="inlineStr">
         <is>
-          <t>17023793</t>
+          <t>17023792</t>
         </is>
       </c>
       <c r="E32" s="23" t="inlineStr">
@@ -23195,7 +24500,7 @@
       </c>
       <c r="D33" s="24" t="inlineStr">
         <is>
-          <t>17023792</t>
+          <t>17023793</t>
         </is>
       </c>
       <c r="E33" s="23" t="inlineStr">
@@ -23301,7 +24606,7 @@
       </c>
       <c r="D35" s="24" t="inlineStr">
         <is>
-          <t>17022602</t>
+          <t>17022604</t>
         </is>
       </c>
       <c r="E35" s="23" t="inlineStr">
@@ -23405,7 +24710,7 @@
       </c>
       <c r="D37" s="24" t="inlineStr">
         <is>
-          <t>17022604</t>
+          <t>17022602</t>
         </is>
       </c>
       <c r="E37" s="23" t="inlineStr">
@@ -23458,7 +24763,7 @@
       </c>
       <c r="D38" s="24" t="inlineStr">
         <is>
-          <t>17022612</t>
+          <t>17022605</t>
         </is>
       </c>
       <c r="E38" s="23" t="inlineStr">
@@ -23509,7 +24814,7 @@
       </c>
       <c r="D39" s="24" t="inlineStr">
         <is>
-          <t>17022611</t>
+          <t>17022606</t>
         </is>
       </c>
       <c r="E39" s="23" t="inlineStr">
@@ -23562,7 +24867,7 @@
       </c>
       <c r="D40" s="24" t="inlineStr">
         <is>
-          <t>17022610</t>
+          <t>17022607</t>
         </is>
       </c>
       <c r="E40" s="23" t="inlineStr">
@@ -23615,7 +24920,7 @@
       </c>
       <c r="D41" s="24" t="inlineStr">
         <is>
-          <t>17022609</t>
+          <t>17022608</t>
         </is>
       </c>
       <c r="E41" s="23" t="inlineStr">
@@ -23668,7 +24973,7 @@
       </c>
       <c r="D42" s="24" t="inlineStr">
         <is>
-          <t>17022605</t>
+          <t>17022609</t>
         </is>
       </c>
       <c r="E42" s="23" t="inlineStr">
@@ -23721,7 +25026,7 @@
       </c>
       <c r="D43" s="24" t="inlineStr">
         <is>
-          <t>17022607</t>
+          <t>17022610</t>
         </is>
       </c>
       <c r="E43" s="23" t="inlineStr">
@@ -23774,7 +25079,7 @@
       </c>
       <c r="D44" s="24" t="inlineStr">
         <is>
-          <t>17022606</t>
+          <t>17022611</t>
         </is>
       </c>
       <c r="E44" s="23" t="inlineStr">
@@ -23827,7 +25132,7 @@
       </c>
       <c r="D45" s="24" t="inlineStr">
         <is>
-          <t>17022608</t>
+          <t>17022612</t>
         </is>
       </c>
       <c r="E45" s="23" t="inlineStr">
@@ -23984,7 +25289,7 @@
       </c>
       <c r="D48" s="24" t="inlineStr">
         <is>
-          <t>17022802</t>
+          <t>17022803</t>
         </is>
       </c>
       <c r="E48" s="23" t="inlineStr">
@@ -24035,7 +25340,7 @@
       </c>
       <c r="D49" s="24" t="inlineStr">
         <is>
-          <t>17022803</t>
+          <t>17022802</t>
         </is>
       </c>
       <c r="E49" s="23" t="inlineStr">
@@ -24088,7 +25393,7 @@
       </c>
       <c r="D50" s="24" t="inlineStr">
         <is>
-          <t>17022907</t>
+          <t>17022908</t>
         </is>
       </c>
       <c r="E50" s="23" t="inlineStr">
@@ -24139,7 +25444,7 @@
       </c>
       <c r="D51" s="24" t="inlineStr">
         <is>
-          <t>17022908</t>
+          <t>17022907</t>
         </is>
       </c>
       <c r="E51" s="23" t="inlineStr">
@@ -25261,7 +26566,7 @@
       </c>
       <c r="C3" s="27" t="inlineStr">
         <is>
-          <t>16975299</t>
+          <t>16975301</t>
         </is>
       </c>
       <c r="D3" s="26" t="inlineStr">
@@ -25371,7 +26676,7 @@
       </c>
       <c r="C5" s="27" t="inlineStr">
         <is>
-          <t>16975301</t>
+          <t>16975299</t>
         </is>
       </c>
       <c r="D5" s="26" t="inlineStr">
@@ -28971,7 +30276,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G68"/>
+  <dimension ref="A1:G63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -28986,7 +30291,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>POSSÍVEIS AUSÊNCIAS POR DIA/TURNO (66 registros) — CONFIRMAR COM A ESCALA (FOLGA/ATESTADO/FALTA)</t>
+          <t>POSSÍVEIS AUSÊNCIAS POR DIA/TURNO (61 registros) — CONFIRMAR COM A ESCALA (FOLGA/ATESTADO/FALTA)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -29420,11 +30725,11 @@
     </row>
     <row r="14">
       <c r="A14" s="38" t="n">
-        <v>3101</v>
+        <v>3037</v>
       </c>
       <c r="B14" s="38" t="inlineStr">
         <is>
-          <t>Carlos Alberto Albiero</t>
+          <t>Evelyn Santana Santos Oliveira</t>
         </is>
       </c>
       <c r="C14" s="38" t="inlineStr">
@@ -29455,11 +30760,11 @@
     </row>
     <row r="15">
       <c r="A15" s="38" t="n">
-        <v>470</v>
+        <v>1935</v>
       </c>
       <c r="B15" s="38" t="inlineStr">
         <is>
-          <t>Cris Milene Cardenas da Silva</t>
+          <t>Gabriel Alan de Oliveira Martins</t>
         </is>
       </c>
       <c r="C15" s="38" t="inlineStr">
@@ -29490,11 +30795,11 @@
     </row>
     <row r="16">
       <c r="A16" s="38" t="n">
-        <v>3037</v>
+        <v>79</v>
       </c>
       <c r="B16" s="38" t="inlineStr">
         <is>
-          <t>Evelyn Santana Santos Oliveira</t>
+          <t>Raquel Ortiz dos Santos</t>
         </is>
       </c>
       <c r="C16" s="38" t="inlineStr">
@@ -29525,11 +30830,11 @@
     </row>
     <row r="17">
       <c r="A17" s="38" t="n">
-        <v>1935</v>
+        <v>116</v>
       </c>
       <c r="B17" s="38" t="inlineStr">
         <is>
-          <t>Gabriel Alan de Oliveira Martins</t>
+          <t>Wagner Tarlei Gomes</t>
         </is>
       </c>
       <c r="C17" s="38" t="inlineStr">
@@ -29560,11 +30865,11 @@
     </row>
     <row r="18">
       <c r="A18" s="38" t="n">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="B18" s="38" t="inlineStr">
         <is>
-          <t>Raquel Ortiz dos Santos</t>
+          <t>Adriano Ricardo Thiel</t>
         </is>
       </c>
       <c r="C18" s="38" t="inlineStr">
@@ -29584,7 +30889,7 @@
       </c>
       <c r="F18" s="38" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G18" s="38" t="inlineStr">
@@ -29595,11 +30900,11 @@
     </row>
     <row r="19">
       <c r="A19" s="38" t="n">
-        <v>116</v>
+        <v>73</v>
       </c>
       <c r="B19" s="38" t="inlineStr">
         <is>
-          <t>Wagner Tarlei Gomes</t>
+          <t>Ana Gabriela Silva Garcete</t>
         </is>
       </c>
       <c r="C19" s="38" t="inlineStr">
@@ -29619,7 +30924,7 @@
       </c>
       <c r="F19" s="38" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G19" s="38" t="inlineStr">
@@ -29630,11 +30935,11 @@
     </row>
     <row r="20">
       <c r="A20" s="38" t="n">
-        <v>85</v>
+        <v>1935</v>
       </c>
       <c r="B20" s="38" t="inlineStr">
         <is>
-          <t>Adriano Ricardo Thiel</t>
+          <t>Gabriel Alan de Oliveira Martins</t>
         </is>
       </c>
       <c r="C20" s="38" t="inlineStr">
@@ -29665,11 +30970,11 @@
     </row>
     <row r="21">
       <c r="A21" s="38" t="n">
-        <v>73</v>
+        <v>116</v>
       </c>
       <c r="B21" s="38" t="inlineStr">
         <is>
-          <t>Ana Gabriela Silva Garcete</t>
+          <t>Wagner Tarlei Gomes</t>
         </is>
       </c>
       <c r="C21" s="38" t="inlineStr">
@@ -29700,26 +31005,26 @@
     </row>
     <row r="22">
       <c r="A22" s="38" t="n">
-        <v>3101</v>
+        <v>3127</v>
       </c>
       <c r="B22" s="38" t="inlineStr">
         <is>
-          <t>Carlos Alberto Albiero</t>
+          <t>Gisele Olimpia Torres</t>
         </is>
       </c>
       <c r="C22" s="38" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="D22" s="38" t="inlineStr">
         <is>
-          <t>20/08/2026</t>
+          <t>17/08/2026</t>
         </is>
       </c>
       <c r="E22" s="38" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="F22" s="38" t="inlineStr">
@@ -29735,31 +31040,31 @@
     </row>
     <row r="23">
       <c r="A23" s="38" t="n">
-        <v>470</v>
+        <v>125</v>
       </c>
       <c r="B23" s="38" t="inlineStr">
         <is>
-          <t>Cris Milene Cardenas da Silva</t>
+          <t>Brauher Luiz Alvarenga Gonzalez</t>
         </is>
       </c>
       <c r="C23" s="38" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="D23" s="38" t="inlineStr">
         <is>
-          <t>20/08/2026</t>
+          <t>18/08/2026</t>
         </is>
       </c>
       <c r="E23" s="38" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="F23" s="38" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G23" s="38" t="inlineStr">
@@ -29770,26 +31075,26 @@
     </row>
     <row r="24">
       <c r="A24" s="38" t="n">
-        <v>1935</v>
+        <v>125</v>
       </c>
       <c r="B24" s="38" t="inlineStr">
         <is>
-          <t>Gabriel Alan de Oliveira Martins</t>
+          <t>Brauher Luiz Alvarenga Gonzalez</t>
         </is>
       </c>
       <c r="C24" s="38" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="D24" s="38" t="inlineStr">
         <is>
-          <t>20/08/2026</t>
+          <t>18/08/2026</t>
         </is>
       </c>
       <c r="E24" s="38" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="F24" s="38" t="inlineStr">
@@ -29805,31 +31110,31 @@
     </row>
     <row r="25">
       <c r="A25" s="38" t="n">
-        <v>116</v>
+        <v>151</v>
       </c>
       <c r="B25" s="38" t="inlineStr">
         <is>
-          <t>Wagner Tarlei Gomes</t>
+          <t>Gilmar Bitencourt Luiz</t>
         </is>
       </c>
       <c r="C25" s="38" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="D25" s="38" t="inlineStr">
         <is>
-          <t>20/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
       <c r="E25" s="38" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="F25" s="38" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G25" s="38" t="inlineStr">
@@ -29854,17 +31159,17 @@
       </c>
       <c r="D26" s="38" t="inlineStr">
         <is>
-          <t>17/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
       <c r="E26" s="38" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="F26" s="38" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G26" s="38" t="inlineStr">
@@ -29875,11 +31180,11 @@
     </row>
     <row r="27">
       <c r="A27" s="38" t="n">
-        <v>125</v>
+        <v>151</v>
       </c>
       <c r="B27" s="38" t="inlineStr">
         <is>
-          <t>Brauher Luiz Alvarenga Gonzalez</t>
+          <t>Gilmar Bitencourt Luiz</t>
         </is>
       </c>
       <c r="C27" s="38" t="inlineStr">
@@ -29889,17 +31194,17 @@
       </c>
       <c r="D27" s="38" t="inlineStr">
         <is>
-          <t>18/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
       <c r="E27" s="38" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="F27" s="38" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G27" s="38" t="inlineStr">
@@ -29910,11 +31215,11 @@
     </row>
     <row r="28">
       <c r="A28" s="38" t="n">
-        <v>125</v>
+        <v>142</v>
       </c>
       <c r="B28" s="38" t="inlineStr">
         <is>
-          <t>Brauher Luiz Alvarenga Gonzalez</t>
+          <t>William Anderson Chamorro Tavares</t>
         </is>
       </c>
       <c r="C28" s="38" t="inlineStr">
@@ -29924,12 +31229,12 @@
       </c>
       <c r="D28" s="38" t="inlineStr">
         <is>
-          <t>18/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
       <c r="E28" s="38" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="F28" s="38" t="inlineStr">
@@ -29945,11 +31250,11 @@
     </row>
     <row r="29">
       <c r="A29" s="38" t="n">
-        <v>151</v>
+        <v>2917</v>
       </c>
       <c r="B29" s="38" t="inlineStr">
         <is>
-          <t>Gilmar Bitencourt Luiz</t>
+          <t>Bianca Afonso Narbaez</t>
         </is>
       </c>
       <c r="C29" s="38" t="inlineStr">
@@ -29959,12 +31264,12 @@
       </c>
       <c r="D29" s="38" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>20/08/2026</t>
         </is>
       </c>
       <c r="E29" s="38" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="F29" s="38" t="inlineStr">
@@ -29980,11 +31285,11 @@
     </row>
     <row r="30">
       <c r="A30" s="38" t="n">
-        <v>3127</v>
+        <v>125</v>
       </c>
       <c r="B30" s="38" t="inlineStr">
         <is>
-          <t>Gisele Olimpia Torres</t>
+          <t>Brauher Luiz Alvarenga Gonzalez</t>
         </is>
       </c>
       <c r="C30" s="38" t="inlineStr">
@@ -29994,12 +31299,12 @@
       </c>
       <c r="D30" s="38" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>20/08/2026</t>
         </is>
       </c>
       <c r="E30" s="38" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="F30" s="38" t="inlineStr">
@@ -30029,17 +31334,17 @@
       </c>
       <c r="D31" s="38" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>20/08/2026</t>
         </is>
       </c>
       <c r="E31" s="38" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="F31" s="38" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G31" s="38" t="inlineStr">
@@ -30050,11 +31355,11 @@
     </row>
     <row r="32">
       <c r="A32" s="38" t="n">
-        <v>142</v>
+        <v>3127</v>
       </c>
       <c r="B32" s="38" t="inlineStr">
         <is>
-          <t>William Anderson Chamorro Tavares</t>
+          <t>Gisele Olimpia Torres</t>
         </is>
       </c>
       <c r="C32" s="38" t="inlineStr">
@@ -30064,17 +31369,17 @@
       </c>
       <c r="D32" s="38" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>20/08/2026</t>
         </is>
       </c>
       <c r="E32" s="38" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="F32" s="38" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G32" s="38" t="inlineStr">
@@ -30085,11 +31390,11 @@
     </row>
     <row r="33">
       <c r="A33" s="38" t="n">
-        <v>2917</v>
+        <v>465</v>
       </c>
       <c r="B33" s="38" t="inlineStr">
         <is>
-          <t>Bianca Afonso Narbaez</t>
+          <t>Suely Aguiar Alves Luiz</t>
         </is>
       </c>
       <c r="C33" s="38" t="inlineStr">
@@ -30120,11 +31425,11 @@
     </row>
     <row r="34">
       <c r="A34" s="38" t="n">
-        <v>125</v>
+        <v>3035</v>
       </c>
       <c r="B34" s="38" t="inlineStr">
         <is>
-          <t>Brauher Luiz Alvarenga Gonzalez</t>
+          <t>Teonilda Florentino Vieira</t>
         </is>
       </c>
       <c r="C34" s="38" t="inlineStr">
@@ -30155,11 +31460,11 @@
     </row>
     <row r="35">
       <c r="A35" s="38" t="n">
-        <v>151</v>
+        <v>81</v>
       </c>
       <c r="B35" s="38" t="inlineStr">
         <is>
-          <t>Gilmar Bitencourt Luiz</t>
+          <t>Wesley de Souza Leal</t>
         </is>
       </c>
       <c r="C35" s="38" t="inlineStr">
@@ -30190,11 +31495,11 @@
     </row>
     <row r="36">
       <c r="A36" s="38" t="n">
-        <v>3127</v>
+        <v>99</v>
       </c>
       <c r="B36" s="38" t="inlineStr">
         <is>
-          <t>Gisele Olimpia Torres</t>
+          <t>Fabiana de Figueredo Vieira</t>
         </is>
       </c>
       <c r="C36" s="38" t="inlineStr">
@@ -30214,7 +31519,7 @@
       </c>
       <c r="F36" s="38" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G36" s="38" t="inlineStr">
@@ -30225,11 +31530,11 @@
     </row>
     <row r="37">
       <c r="A37" s="38" t="n">
-        <v>465</v>
+        <v>151</v>
       </c>
       <c r="B37" s="38" t="inlineStr">
         <is>
-          <t>Suely Aguiar Alves Luiz</t>
+          <t>Gilmar Bitencourt Luiz</t>
         </is>
       </c>
       <c r="C37" s="38" t="inlineStr">
@@ -30249,7 +31554,7 @@
       </c>
       <c r="F37" s="38" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G37" s="38" t="inlineStr">
@@ -30260,11 +31565,11 @@
     </row>
     <row r="38">
       <c r="A38" s="38" t="n">
-        <v>3035</v>
+        <v>465</v>
       </c>
       <c r="B38" s="38" t="inlineStr">
         <is>
-          <t>Teonilda Florentino Vieira</t>
+          <t>Suely Aguiar Alves Luiz</t>
         </is>
       </c>
       <c r="C38" s="38" t="inlineStr">
@@ -30284,7 +31589,7 @@
       </c>
       <c r="F38" s="38" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G38" s="38" t="inlineStr">
@@ -30295,11 +31600,11 @@
     </row>
     <row r="39">
       <c r="A39" s="38" t="n">
-        <v>81</v>
+        <v>3035</v>
       </c>
       <c r="B39" s="38" t="inlineStr">
         <is>
-          <t>Wesley de Souza Leal</t>
+          <t>Teonilda Florentino Vieira</t>
         </is>
       </c>
       <c r="C39" s="38" t="inlineStr">
@@ -30319,7 +31624,7 @@
       </c>
       <c r="F39" s="38" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G39" s="38" t="inlineStr">
@@ -30330,31 +31635,31 @@
     </row>
     <row r="40">
       <c r="A40" s="38" t="n">
-        <v>99</v>
+        <v>2951</v>
       </c>
       <c r="B40" s="38" t="inlineStr">
         <is>
-          <t>Fabiana de Figueredo Vieira</t>
+          <t>Alana Amanda Fernandes Ovelar</t>
         </is>
       </c>
       <c r="C40" s="38" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 3</t>
         </is>
       </c>
       <c r="D40" s="38" t="inlineStr">
         <is>
-          <t>20/08/2026</t>
+          <t>18/08/2026</t>
         </is>
       </c>
       <c r="E40" s="38" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="F40" s="38" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G40" s="38" t="inlineStr">
@@ -30365,26 +31670,26 @@
     </row>
     <row r="41">
       <c r="A41" s="38" t="n">
-        <v>151</v>
+        <v>120</v>
       </c>
       <c r="B41" s="38" t="inlineStr">
         <is>
-          <t>Gilmar Bitencourt Luiz</t>
+          <t>Emidio Rainer Vilhalba</t>
         </is>
       </c>
       <c r="C41" s="38" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 3</t>
         </is>
       </c>
       <c r="D41" s="38" t="inlineStr">
         <is>
-          <t>20/08/2026</t>
+          <t>18/08/2026</t>
         </is>
       </c>
       <c r="E41" s="38" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="F41" s="38" t="inlineStr">
@@ -30400,31 +31705,31 @@
     </row>
     <row r="42">
       <c r="A42" s="38" t="n">
-        <v>465</v>
+        <v>120</v>
       </c>
       <c r="B42" s="38" t="inlineStr">
         <is>
-          <t>Suely Aguiar Alves Luiz</t>
+          <t>Emidio Rainer Vilhalba</t>
         </is>
       </c>
       <c r="C42" s="38" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 3</t>
         </is>
       </c>
       <c r="D42" s="38" t="inlineStr">
         <is>
-          <t>20/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
       <c r="E42" s="38" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="F42" s="38" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G42" s="38" t="inlineStr">
@@ -30435,16 +31740,16 @@
     </row>
     <row r="43">
       <c r="A43" s="38" t="n">
-        <v>3035</v>
+        <v>2951</v>
       </c>
       <c r="B43" s="38" t="inlineStr">
         <is>
-          <t>Teonilda Florentino Vieira</t>
+          <t>Alana Amanda Fernandes Ovelar</t>
         </is>
       </c>
       <c r="C43" s="38" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 3</t>
         </is>
       </c>
       <c r="D43" s="38" t="inlineStr">
@@ -30459,7 +31764,7 @@
       </c>
       <c r="F43" s="38" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G43" s="38" t="inlineStr">
@@ -30470,11 +31775,11 @@
     </row>
     <row r="44">
       <c r="A44" s="38" t="n">
-        <v>2951</v>
+        <v>2918</v>
       </c>
       <c r="B44" s="38" t="inlineStr">
         <is>
-          <t>Alana Amanda Fernandes Ovelar</t>
+          <t>Claine Luisa Figueiredo Torraca</t>
         </is>
       </c>
       <c r="C44" s="38" t="inlineStr">
@@ -30484,12 +31789,12 @@
       </c>
       <c r="D44" s="38" t="inlineStr">
         <is>
-          <t>18/08/2026</t>
+          <t>20/08/2026</t>
         </is>
       </c>
       <c r="E44" s="38" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="F44" s="38" t="inlineStr">
@@ -30505,11 +31810,11 @@
     </row>
     <row r="45">
       <c r="A45" s="38" t="n">
-        <v>120</v>
+        <v>3038</v>
       </c>
       <c r="B45" s="38" t="inlineStr">
         <is>
-          <t>Emidio Rainer Vilhalba</t>
+          <t>Naime Cristina Freitas</t>
         </is>
       </c>
       <c r="C45" s="38" t="inlineStr">
@@ -30519,17 +31824,17 @@
       </c>
       <c r="D45" s="38" t="inlineStr">
         <is>
-          <t>18/08/2026</t>
+          <t>20/08/2026</t>
         </is>
       </c>
       <c r="E45" s="38" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="F45" s="38" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G45" s="38" t="inlineStr">
@@ -30540,11 +31845,11 @@
     </row>
     <row r="46">
       <c r="A46" s="38" t="n">
-        <v>120</v>
+        <v>3128</v>
       </c>
       <c r="B46" s="38" t="inlineStr">
         <is>
-          <t>Emidio Rainer Vilhalba</t>
+          <t>Rosalina Beniel Vargas</t>
         </is>
       </c>
       <c r="C46" s="38" t="inlineStr">
@@ -30554,12 +31859,12 @@
       </c>
       <c r="D46" s="38" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>20/08/2026</t>
         </is>
       </c>
       <c r="E46" s="38" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="F46" s="38" t="inlineStr">
@@ -30599,7 +31904,7 @@
       </c>
       <c r="F47" s="38" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G47" s="38" t="inlineStr">
@@ -30634,7 +31939,7 @@
       </c>
       <c r="F48" s="38" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G48" s="38" t="inlineStr">
@@ -30669,7 +31974,7 @@
       </c>
       <c r="F49" s="38" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G49" s="38" t="inlineStr">
@@ -30680,26 +31985,26 @@
     </row>
     <row r="50">
       <c r="A50" s="38" t="n">
-        <v>3128</v>
+        <v>157</v>
       </c>
       <c r="B50" s="38" t="inlineStr">
         <is>
-          <t>Rosalina Beniel Vargas</t>
+          <t>Walquiria Araujo Flores</t>
         </is>
       </c>
       <c r="C50" s="38" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="D50" s="38" t="inlineStr">
         <is>
-          <t>20/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
       <c r="E50" s="38" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="F50" s="38" t="inlineStr">
@@ -30715,26 +32020,26 @@
     </row>
     <row r="51">
       <c r="A51" s="38" t="n">
-        <v>2951</v>
+        <v>110</v>
       </c>
       <c r="B51" s="38" t="inlineStr">
         <is>
-          <t>Alana Amanda Fernandes Ovelar</t>
+          <t>Anderson Jose de Santana</t>
         </is>
       </c>
       <c r="C51" s="38" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="D51" s="38" t="inlineStr">
         <is>
-          <t>20/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
       <c r="E51" s="38" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="F51" s="38" t="inlineStr">
@@ -30750,26 +32055,26 @@
     </row>
     <row r="52">
       <c r="A52" s="38" t="n">
-        <v>2918</v>
+        <v>149</v>
       </c>
       <c r="B52" s="38" t="inlineStr">
         <is>
-          <t>Claine Luisa Figueiredo Torraca</t>
+          <t>Kátia Cilene Silveira Machado</t>
         </is>
       </c>
       <c r="C52" s="38" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="D52" s="38" t="inlineStr">
         <is>
-          <t>20/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
       <c r="E52" s="38" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="F52" s="38" t="inlineStr">
@@ -30785,26 +32090,26 @@
     </row>
     <row r="53">
       <c r="A53" s="38" t="n">
-        <v>3038</v>
+        <v>157</v>
       </c>
       <c r="B53" s="38" t="inlineStr">
         <is>
-          <t>Naime Cristina Freitas</t>
+          <t>Walquiria Araujo Flores</t>
         </is>
       </c>
       <c r="C53" s="38" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="D53" s="38" t="inlineStr">
         <is>
-          <t>20/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
       <c r="E53" s="38" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="F53" s="38" t="inlineStr">
@@ -30820,11 +32125,11 @@
     </row>
     <row r="54">
       <c r="A54" s="38" t="n">
-        <v>157</v>
+        <v>80</v>
       </c>
       <c r="B54" s="38" t="inlineStr">
         <is>
-          <t>Walquiria Araujo Flores</t>
+          <t>Gisele Lopes Justiniano</t>
         </is>
       </c>
       <c r="C54" s="38" t="inlineStr">
@@ -30834,12 +32139,12 @@
       </c>
       <c r="D54" s="38" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>20/08/2026</t>
         </is>
       </c>
       <c r="E54" s="38" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="F54" s="38" t="inlineStr">
@@ -30855,11 +32160,11 @@
     </row>
     <row r="55">
       <c r="A55" s="38" t="n">
-        <v>110</v>
+        <v>1943</v>
       </c>
       <c r="B55" s="38" t="inlineStr">
         <is>
-          <t>Anderson Jose de Santana</t>
+          <t>Juliana Patricia Goncalves</t>
         </is>
       </c>
       <c r="C55" s="38" t="inlineStr">
@@ -30869,17 +32174,17 @@
       </c>
       <c r="D55" s="38" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>20/08/2026</t>
         </is>
       </c>
       <c r="E55" s="38" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="F55" s="38" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G55" s="38" t="inlineStr">
@@ -30890,11 +32195,11 @@
     </row>
     <row r="56">
       <c r="A56" s="38" t="n">
-        <v>149</v>
+        <v>2789</v>
       </c>
       <c r="B56" s="38" t="inlineStr">
         <is>
-          <t>Kátia Cilene Silveira Machado</t>
+          <t>Kariele Jackeline Rodrigues Silva</t>
         </is>
       </c>
       <c r="C56" s="38" t="inlineStr">
@@ -30904,17 +32209,17 @@
       </c>
       <c r="D56" s="38" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>20/08/2026</t>
         </is>
       </c>
       <c r="E56" s="38" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="F56" s="38" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G56" s="38" t="inlineStr">
@@ -30925,11 +32230,11 @@
     </row>
     <row r="57">
       <c r="A57" s="38" t="n">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="B57" s="38" t="inlineStr">
         <is>
-          <t>Walquiria Araujo Flores</t>
+          <t>Kátia Cilene Silveira Machado</t>
         </is>
       </c>
       <c r="C57" s="38" t="inlineStr">
@@ -30939,17 +32244,17 @@
       </c>
       <c r="D57" s="38" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>20/08/2026</t>
         </is>
       </c>
       <c r="E57" s="38" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="F57" s="38" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G57" s="38" t="inlineStr">
@@ -30960,11 +32265,11 @@
     </row>
     <row r="58">
       <c r="A58" s="38" t="n">
-        <v>80</v>
+        <v>1942</v>
       </c>
       <c r="B58" s="38" t="inlineStr">
         <is>
-          <t>Gisele Lopes Justiniano</t>
+          <t>Rafael Ramos Recalde</t>
         </is>
       </c>
       <c r="C58" s="38" t="inlineStr">
@@ -30995,11 +32300,11 @@
     </row>
     <row r="59">
       <c r="A59" s="38" t="n">
-        <v>1943</v>
+        <v>1996</v>
       </c>
       <c r="B59" s="38" t="inlineStr">
         <is>
-          <t>Juliana Patricia Goncalves</t>
+          <t>Sara Eliane Talaveira de Oliveira</t>
         </is>
       </c>
       <c r="C59" s="38" t="inlineStr">
@@ -31030,11 +32335,11 @@
     </row>
     <row r="60">
       <c r="A60" s="38" t="n">
-        <v>2789</v>
+        <v>86</v>
       </c>
       <c r="B60" s="38" t="inlineStr">
         <is>
-          <t>Kariele Jackeline Rodrigues Silva</t>
+          <t>Silvina Regina de Souza Valiente</t>
         </is>
       </c>
       <c r="C60" s="38" t="inlineStr">
@@ -31065,11 +32370,11 @@
     </row>
     <row r="61">
       <c r="A61" s="38" t="n">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="B61" s="38" t="inlineStr">
         <is>
-          <t>Kátia Cilene Silveira Machado</t>
+          <t>Walquiria Araujo Flores</t>
         </is>
       </c>
       <c r="C61" s="38" t="inlineStr">
@@ -31100,11 +32405,11 @@
     </row>
     <row r="62">
       <c r="A62" s="38" t="n">
-        <v>1942</v>
+        <v>1996</v>
       </c>
       <c r="B62" s="38" t="inlineStr">
         <is>
-          <t>Rafael Ramos Recalde</t>
+          <t>Sara Eliane Talaveira de Oliveira</t>
         </is>
       </c>
       <c r="C62" s="38" t="inlineStr">
@@ -31124,7 +32429,7 @@
       </c>
       <c r="F62" s="38" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G62" s="38" t="inlineStr">
@@ -31135,11 +32440,11 @@
     </row>
     <row r="63">
       <c r="A63" s="38" t="n">
-        <v>1996</v>
+        <v>157</v>
       </c>
       <c r="B63" s="38" t="inlineStr">
         <is>
-          <t>Sara Eliane Talaveira de Oliveira</t>
+          <t>Walquiria Araujo Flores</t>
         </is>
       </c>
       <c r="C63" s="38" t="inlineStr">
@@ -31159,7 +32464,7 @@
       </c>
       <c r="F63" s="38" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G63" s="38" t="inlineStr">
@@ -31168,183 +32473,8 @@
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="38" t="n">
-        <v>86</v>
-      </c>
-      <c r="B64" s="38" t="inlineStr">
-        <is>
-          <t>Silvina Regina de Souza Valiente</t>
-        </is>
-      </c>
-      <c r="C64" s="38" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="D64" s="38" t="inlineStr">
-        <is>
-          <t>20/08/2026</t>
-        </is>
-      </c>
-      <c r="E64" s="38" t="inlineStr">
-        <is>
-          <t>Quinta</t>
-        </is>
-      </c>
-      <c r="F64" s="38" t="inlineStr">
-        <is>
-          <t>Manhã</t>
-        </is>
-      </c>
-      <c r="G64" s="38" t="inlineStr">
-        <is>
-          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="38" t="n">
-        <v>157</v>
-      </c>
-      <c r="B65" s="38" t="inlineStr">
-        <is>
-          <t>Walquiria Araujo Flores</t>
-        </is>
-      </c>
-      <c r="C65" s="38" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="D65" s="38" t="inlineStr">
-        <is>
-          <t>20/08/2026</t>
-        </is>
-      </c>
-      <c r="E65" s="38" t="inlineStr">
-        <is>
-          <t>Quinta</t>
-        </is>
-      </c>
-      <c r="F65" s="38" t="inlineStr">
-        <is>
-          <t>Manhã</t>
-        </is>
-      </c>
-      <c r="G65" s="38" t="inlineStr">
-        <is>
-          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="38" t="n">
-        <v>80</v>
-      </c>
-      <c r="B66" s="38" t="inlineStr">
-        <is>
-          <t>Gisele Lopes Justiniano</t>
-        </is>
-      </c>
-      <c r="C66" s="38" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="D66" s="38" t="inlineStr">
-        <is>
-          <t>20/08/2026</t>
-        </is>
-      </c>
-      <c r="E66" s="38" t="inlineStr">
-        <is>
-          <t>Quinta</t>
-        </is>
-      </c>
-      <c r="F66" s="38" t="inlineStr">
-        <is>
-          <t>Tarde</t>
-        </is>
-      </c>
-      <c r="G66" s="38" t="inlineStr">
-        <is>
-          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="38" t="n">
-        <v>1996</v>
-      </c>
-      <c r="B67" s="38" t="inlineStr">
-        <is>
-          <t>Sara Eliane Talaveira de Oliveira</t>
-        </is>
-      </c>
-      <c r="C67" s="38" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="D67" s="38" t="inlineStr">
-        <is>
-          <t>20/08/2026</t>
-        </is>
-      </c>
-      <c r="E67" s="38" t="inlineStr">
-        <is>
-          <t>Quinta</t>
-        </is>
-      </c>
-      <c r="F67" s="38" t="inlineStr">
-        <is>
-          <t>Tarde</t>
-        </is>
-      </c>
-      <c r="G67" s="38" t="inlineStr">
-        <is>
-          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="38" t="n">
-        <v>157</v>
-      </c>
-      <c r="B68" s="38" t="inlineStr">
-        <is>
-          <t>Walquiria Araujo Flores</t>
-        </is>
-      </c>
-      <c r="C68" s="38" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="D68" s="38" t="inlineStr">
-        <is>
-          <t>20/08/2026</t>
-        </is>
-      </c>
-      <c r="E68" s="38" t="inlineStr">
-        <is>
-          <t>Quinta</t>
-        </is>
-      </c>
-      <c r="F68" s="38" t="inlineStr">
-        <is>
-          <t>Tarde</t>
-        </is>
-      </c>
-      <c r="G68" s="38" t="inlineStr">
-        <is>
-          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A2:G68"/>
+  <autoFilter ref="A2:G63"/>
   <mergeCells count="1">
     <mergeCell ref="A1:G1"/>
   </mergeCells>

--- a/data/historico/semana_320.xlsx
+++ b/data/historico/semana_320.xlsx
@@ -32500,7 +32500,7 @@
       </c>
       <c r="C58" s="30" t="inlineStr">
         <is>
-          <t>17017079</t>
+          <t>17017093</t>
         </is>
       </c>
       <c r="D58" s="29" t="inlineStr">
@@ -32520,17 +32520,17 @@
       </c>
       <c r="G58" s="29" t="inlineStr">
         <is>
-          <t>57 - R</t>
+          <t>69 - R</t>
         </is>
       </c>
       <c r="H58" s="29" t="inlineStr">
         <is>
-          <t>17/08/2026 09:16</t>
+          <t>17/08/2026 15:44</t>
         </is>
       </c>
       <c r="I58" s="29" t="inlineStr">
         <is>
-          <t>17/08/2026 09:32</t>
+          <t>17/08/2026 16:00</t>
         </is>
       </c>
       <c r="J58" s="29" t="n">
@@ -32550,7 +32550,7 @@
       </c>
       <c r="C59" s="30" t="inlineStr">
         <is>
-          <t>17017093</t>
+          <t>17017079</t>
         </is>
       </c>
       <c r="D59" s="29" t="inlineStr">
@@ -32570,17 +32570,17 @@
       </c>
       <c r="G59" s="29" t="inlineStr">
         <is>
-          <t>69 - R</t>
+          <t>57 - R</t>
         </is>
       </c>
       <c r="H59" s="29" t="inlineStr">
         <is>
-          <t>17/08/2026 15:44</t>
+          <t>17/08/2026 09:16</t>
         </is>
       </c>
       <c r="I59" s="29" t="inlineStr">
         <is>
-          <t>17/08/2026 16:00</t>
+          <t>17/08/2026 09:32</t>
         </is>
       </c>
       <c r="J59" s="29" t="n">

--- a/data/historico/semana_320.xlsx
+++ b/data/historico/semana_320.xlsx
@@ -31,7 +31,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Fora do Expediente'!$A$2:$K$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Visitas no Almoço'!$A$2:$I$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Ausências'!$A$2:$G$54</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Cronograma'!$A$2:$D$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Cronograma'!$A$2:$D$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Ponto Estratégico'!$A$2:$AE$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Ranking'!$A$2:$H$40</definedName>
   </definedNames>
@@ -5100,7 +5100,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5112,7 +5112,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>CRONOGRAMA — CHUVA/FOLGA/ATESTADO/REUNIÃO/FÉRIAS (5 registros) — EXCLUÍDOS DA ABA 'AUSÊNCIAS'. Edite em data/cronograma_ausencias.json (use cronograma_editor.html).</t>
+          <t>CRONOGRAMA — CHUVA/FOLGA/ATESTADO/REUNIÃO/FÉRIAS (7 registros) — EXCLUÍDOS DA ABA 'AUSÊNCIAS'. Edite em data/cronograma_ausencias.json (use cronograma_editor.html).</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5215,7 +5215,7 @@
       </c>
       <c r="B6" s="38" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
       <c r="C6" s="38" t="inlineStr">
@@ -5230,29 +5230,73 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="39" t="inlineStr">
+      <c r="A7" s="38" t="inlineStr">
         <is>
           <t>17/08/2026</t>
         </is>
       </c>
-      <c r="B7" s="39" t="inlineStr">
+      <c r="B7" s="38" t="inlineStr">
+        <is>
+          <t>25/08/2026</t>
+        </is>
+      </c>
+      <c r="C7" s="38" t="inlineStr">
+        <is>
+          <t>Férias/Atestado (automático)</t>
+        </is>
+      </c>
+      <c r="D7" s="38" t="inlineStr">
+        <is>
+          <t>Mateus Falcao de Souza</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="38" t="inlineStr">
         <is>
           <t>17/08/2026</t>
         </is>
       </c>
-      <c r="C7" s="39" t="inlineStr">
+      <c r="B8" s="38" t="inlineStr">
+        <is>
+          <t>25/08/2026</t>
+        </is>
+      </c>
+      <c r="C8" s="38" t="inlineStr">
+        <is>
+          <t>Férias/Atestado (automático)</t>
+        </is>
+      </c>
+      <c r="D8" s="38" t="inlineStr">
+        <is>
+          <t>Tania Maria Montania</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="39" t="inlineStr">
+        <is>
+          <t>17/08/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="39" t="inlineStr">
+        <is>
+          <t>17/08/2026</t>
+        </is>
+      </c>
+      <c r="C9" s="39" t="inlineStr">
         <is>
           <t>Chuva (confirmada)</t>
         </is>
       </c>
-      <c r="D7" s="39" t="inlineStr">
+      <c r="D9" s="39" t="inlineStr">
         <is>
           <t>Equipe 4</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:D7"/>
+  <autoFilter ref="A2:D9"/>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>
   </mergeCells>

--- a/data/historico/semana_320.xlsx
+++ b/data/historico/semana_320.xlsx
@@ -24,8 +24,8 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Resumo Geral'!$A$2:$AC$40</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Por Área'!$A$2:$N$89</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Visitas Duplicadas'!$A$2:$J$26</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Visitas Suspeitas'!$A$2:$K$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Visitas Duplicadas'!$A$2:$J$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Visitas Suspeitas'!$A$2:$K$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Visitas Negativas'!$A$2:$K$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Visitas Acima de 15min'!$A$2:$J$65</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Fora do Expediente'!$A$2:$K$30</definedName>
@@ -3090,105 +3090,105 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="6" t="inlineStr">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>Claine Luisa Figueiredo Torraca</t>
         </is>
       </c>
-      <c r="B23" s="6" t="inlineStr">
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>Equipe 3</t>
         </is>
       </c>
-      <c r="C23" s="6" t="inlineStr">
-        <is>
-          <t>🟡 ATENÇÃO</t>
-        </is>
-      </c>
-      <c r="D23" s="6" t="n">
-        <v>136</v>
-      </c>
-      <c r="E23" s="6" t="n">
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>🟢 NORMAL</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="n">
+        <v>127</v>
+      </c>
+      <c r="E23" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="F23" s="6" t="n">
-        <v>27.2</v>
-      </c>
-      <c r="G23" s="6" t="n">
-        <v>4.93</v>
-      </c>
-      <c r="H23" s="6" t="n">
+      <c r="F23" s="4" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="G23" s="4" t="n">
+        <v>5.28</v>
+      </c>
+      <c r="H23" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="I23" s="6" t="n">
-        <v>14</v>
-      </c>
-      <c r="J23" s="6" t="n">
-        <v>10.29</v>
-      </c>
-      <c r="K23" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" s="6" t="n">
+      <c r="I23" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="N23" s="6" t="n">
-        <v>24</v>
-      </c>
-      <c r="O23" s="6" t="n">
-        <v>24</v>
-      </c>
-      <c r="P23" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R23" s="6" t="n">
-        <v>110</v>
-      </c>
-      <c r="S23" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T23" s="6" t="n">
-        <v>246</v>
-      </c>
-      <c r="U23" s="6" t="n">
-        <v>44.72</v>
-      </c>
-      <c r="V23" s="6" t="n">
+      <c r="J23" s="4" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="K23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="N23" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="O23" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="P23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" s="4" t="n">
+        <v>109</v>
+      </c>
+      <c r="S23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" s="4" t="n">
+        <v>236</v>
+      </c>
+      <c r="U23" s="4" t="n">
+        <v>46.19</v>
+      </c>
+      <c r="V23" s="4" t="n">
         <v>5.5</v>
       </c>
-      <c r="W23" s="6" t="n">
+      <c r="W23" s="4" t="n">
         <v>27.52</v>
       </c>
-      <c r="X23" s="6" t="n">
+      <c r="X23" s="4" t="n">
         <v>2.23</v>
       </c>
-      <c r="Y23" s="6" t="inlineStr">
+      <c r="Y23" s="4" t="inlineStr">
         <is>
           <t>R$ 98,98</t>
         </is>
       </c>
-      <c r="Z23" s="6" t="inlineStr">
+      <c r="Z23" s="4" t="inlineStr">
         <is>
           <t>08:45</t>
         </is>
       </c>
-      <c r="AA23" s="6" t="inlineStr">
+      <c r="AA23" s="4" t="inlineStr">
         <is>
           <t>10:27</t>
         </is>
       </c>
-      <c r="AB23" s="6" t="inlineStr">
+      <c r="AB23" s="4" t="inlineStr">
         <is>
           <t>13:46</t>
         </is>
       </c>
-      <c r="AC23" s="6" t="inlineStr">
+      <c r="AC23" s="4" t="inlineStr">
         <is>
           <t>16:21</t>
         </is>
@@ -5970,19 +5970,19 @@
         </is>
       </c>
       <c r="C23" s="27" t="n">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="D23" s="27" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E23" s="27" t="n">
         <v>0</v>
       </c>
       <c r="F23" s="27" t="n">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="G23" s="27" t="n">
-        <v>44.72</v>
+        <v>46.19</v>
       </c>
       <c r="H23" s="2" t="n"/>
       <c r="I23" s="2" t="n"/>
@@ -6492,19 +6492,19 @@
         </is>
       </c>
       <c r="C41" s="40" t="n">
-        <v>4789</v>
+        <v>4780</v>
       </c>
       <c r="D41" s="40" t="n">
-        <v>2051</v>
+        <v>2050</v>
       </c>
       <c r="E41" s="40" t="n">
         <v>6</v>
       </c>
       <c r="F41" s="40" t="n">
-        <v>6846</v>
+        <v>6836</v>
       </c>
       <c r="G41" s="40" t="n">
-        <v>30.05</v>
+        <v>30.08</v>
       </c>
       <c r="H41" s="2" t="n"/>
       <c r="I41" s="2" t="n"/>
@@ -8365,25 +8365,25 @@
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>Wagner Tarlei Gomes</t>
+          <t>Claine Luisa Figueiredo Torraca</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 3</t>
         </is>
       </c>
       <c r="D32" s="6" t="n">
         <v>5</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>78.40000000000001</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="H32" s="6" t="inlineStr">
         <is>
@@ -8397,25 +8397,25 @@
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>Emidio Rainer Vilhalba</t>
+          <t>Wagner Tarlei Gomes</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="D33" s="6" t="n">
         <v>5</v>
       </c>
       <c r="E33" s="6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>77.7</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="H33" s="6" t="inlineStr">
         <is>
@@ -8429,61 +8429,61 @@
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>Carlos Alberto Albiero</t>
+          <t>Emidio Rainer Vilhalba</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 3</t>
         </is>
       </c>
       <c r="D34" s="6" t="n">
         <v>5</v>
       </c>
       <c r="E34" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="F34" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="G34" s="6" t="n">
+        <v>77.7</v>
+      </c>
+      <c r="H34" s="6" t="inlineStr">
+        <is>
+          <t>🟡 BOM</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="n">
+        <v>33</v>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>Carlos Alberto Albiero</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>Equipe 1</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="E35" s="6" t="n">
         <v>15</v>
       </c>
-      <c r="F34" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G34" s="6" t="n">
+      <c r="F35" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" s="6" t="n">
         <v>76.40000000000001</v>
       </c>
-      <c r="H34" s="6" t="inlineStr">
+      <c r="H35" s="6" t="inlineStr">
         <is>
           <t>🟡 BOM</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="46" t="n">
-        <v>33</v>
-      </c>
-      <c r="B35" s="46" t="inlineStr">
-        <is>
-          <t>Kariele Jackeline Rodrigues Silva</t>
-        </is>
-      </c>
-      <c r="C35" s="46" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="D35" s="46" t="n">
-        <v>5</v>
-      </c>
-      <c r="E35" s="46" t="n">
-        <v>13</v>
-      </c>
-      <c r="F35" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="G35" s="46" t="n">
-        <v>68.2</v>
-      </c>
-      <c r="H35" s="46" t="inlineStr">
-        <is>
-          <t>🟠 ATENÇÃO</t>
         </is>
       </c>
     </row>
@@ -8493,25 +8493,25 @@
       </c>
       <c r="B36" s="46" t="inlineStr">
         <is>
-          <t>Raquel Ortiz dos Santos</t>
+          <t>Kariele Jackeline Rodrigues Silva</t>
         </is>
       </c>
       <c r="C36" s="46" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="D36" s="46" t="n">
         <v>5</v>
       </c>
       <c r="E36" s="46" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F36" s="46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G36" s="46" t="n">
-        <v>65.7</v>
+        <v>68.2</v>
       </c>
       <c r="H36" s="46" t="inlineStr">
         <is>
@@ -8525,25 +8525,25 @@
       </c>
       <c r="B37" s="46" t="inlineStr">
         <is>
-          <t>Anderson Jose de Santana</t>
+          <t>Raquel Ortiz dos Santos</t>
         </is>
       </c>
       <c r="C37" s="46" t="inlineStr">
         <is>
-          <t>Equipe 4</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="D37" s="46" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E37" s="46" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F37" s="46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G37" s="46" t="n">
-        <v>61.3</v>
+        <v>65.7</v>
       </c>
       <c r="H37" s="46" t="inlineStr">
         <is>
@@ -8557,7 +8557,7 @@
       </c>
       <c r="B38" s="46" t="inlineStr">
         <is>
-          <t>Kátia Cilene Silveira Machado</t>
+          <t>Anderson Jose de Santana</t>
         </is>
       </c>
       <c r="C38" s="46" t="inlineStr">
@@ -8566,52 +8566,52 @@
         </is>
       </c>
       <c r="D38" s="46" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E38" s="46" t="n">
         <v>13</v>
       </c>
       <c r="F38" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="G38" s="46" t="n">
+        <v>61.3</v>
+      </c>
+      <c r="H38" s="46" t="inlineStr">
+        <is>
+          <t>🟠 ATENÇÃO</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="46" t="n">
+        <v>37</v>
+      </c>
+      <c r="B39" s="46" t="inlineStr">
+        <is>
+          <t>Kátia Cilene Silveira Machado</t>
+        </is>
+      </c>
+      <c r="C39" s="46" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="D39" s="46" t="n">
+        <v>5</v>
+      </c>
+      <c r="E39" s="46" t="n">
+        <v>13</v>
+      </c>
+      <c r="F39" s="46" t="n">
         <v>2</v>
       </c>
-      <c r="G38" s="46" t="n">
+      <c r="G39" s="46" t="n">
         <v>60.2</v>
       </c>
-      <c r="H38" s="46" t="inlineStr">
+      <c r="H39" s="46" t="inlineStr">
         <is>
           <t>🟠 ATENÇÃO</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="5" t="n">
-        <v>37</v>
-      </c>
-      <c r="B39" s="5" t="inlineStr">
-        <is>
-          <t>Rafael Ramos Recalde</t>
-        </is>
-      </c>
-      <c r="C39" s="5" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="D39" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="E39" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="F39" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="G39" s="5" t="n">
-        <v>58</v>
-      </c>
-      <c r="H39" s="5" t="inlineStr">
-        <is>
-          <t>🔴 CRÍTICO</t>
         </is>
       </c>
     </row>
@@ -8621,25 +8621,25 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>Claine Luisa Figueiredo Torraca</t>
+          <t>Rafael Ramos Recalde</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="D40" s="5" t="n">
         <v>5</v>
       </c>
       <c r="E40" s="5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F40" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>31</v>
+        <v>58</v>
       </c>
       <c r="H40" s="5" t="inlineStr">
         <is>
@@ -10532,7 +10532,7 @@
         </is>
       </c>
       <c r="D101" s="49" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="E101" s="49" t="n">
         <v>0.3</v>
@@ -10544,7 +10544,7 @@
         <v>0.6</v>
       </c>
       <c r="H101" s="49" t="n">
-        <v>-14.4</v>
+        <v>-3.6</v>
       </c>
     </row>
     <row r="102">
@@ -10564,7 +10564,7 @@
         </is>
       </c>
       <c r="D102" s="49" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="E102" s="49" t="n">
         <v>1</v>
@@ -10576,7 +10576,7 @@
         <v>2</v>
       </c>
       <c r="H102" s="49" t="n">
-        <v>-48</v>
+        <v>-12</v>
       </c>
     </row>
     <row r="103">
@@ -10596,7 +10596,7 @@
         </is>
       </c>
       <c r="D103" s="49" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E103" s="49" t="n">
         <v>0.2</v>
@@ -10608,7 +10608,7 @@
         <v>0.4</v>
       </c>
       <c r="H103" s="49" t="n">
-        <v>-5.6</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="104">
@@ -19249,56 +19249,56 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="5" t="inlineStr">
+      <c r="A48" s="6" t="inlineStr">
         <is>
           <t>Claine Luisa Figueiredo Torraca</t>
         </is>
       </c>
-      <c r="B48" s="5" t="inlineStr">
+      <c r="B48" s="6" t="inlineStr">
         <is>
           <t>Equipe 3</t>
         </is>
       </c>
-      <c r="C48" s="5" t="inlineStr">
+      <c r="C48" s="6" t="inlineStr">
         <is>
           <t>449 - ÁREA C RESIDENCIAL PONTA PORÃ 1</t>
         </is>
       </c>
-      <c r="D48" s="5" t="n">
-        <v>26</v>
-      </c>
-      <c r="E48" s="5" t="n">
-        <v>3.92</v>
-      </c>
-      <c r="F48" s="5" t="n">
+      <c r="D48" s="6" t="n">
+        <v>21</v>
+      </c>
+      <c r="E48" s="6" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="F48" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="G48" s="5" t="n">
+      <c r="G48" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="H48" s="5" t="inlineStr">
+      <c r="H48" s="6" t="inlineStr">
         <is>
           <t>Q029, Q030</t>
         </is>
       </c>
-      <c r="I48" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="J48" s="5" t="n">
-        <v>30.77</v>
-      </c>
-      <c r="K48" s="5" t="n">
-        <v>26</v>
-      </c>
-      <c r="L48" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M48" s="5" t="n">
-        <v>50</v>
-      </c>
-      <c r="N48" s="5" t="inlineStr">
-        <is>
-          <t>🔴 CRÍTICO</t>
+      <c r="I48" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J48" s="6" t="n">
+        <v>14.29</v>
+      </c>
+      <c r="K48" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="L48" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" s="6" t="n">
+        <v>54.35</v>
+      </c>
+      <c r="N48" s="6" t="inlineStr">
+        <is>
+          <t>🟡 ATENÇÃO</t>
         </is>
       </c>
     </row>
@@ -19319,10 +19319,10 @@
         </is>
       </c>
       <c r="D49" s="4" t="n">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="E49" s="4" t="n">
-        <v>4.94</v>
+        <v>5.28</v>
       </c>
       <c r="F49" s="4" t="n">
         <v>5</v>
@@ -19336,10 +19336,10 @@
         </is>
       </c>
       <c r="I49" s="4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J49" s="4" t="n">
-        <v>8.06</v>
+        <v>1.72</v>
       </c>
       <c r="K49" s="4" t="n">
         <v>54</v>
@@ -19348,7 +19348,7 @@
         <v>0</v>
       </c>
       <c r="M49" s="4" t="n">
-        <v>46.55</v>
+        <v>48.21</v>
       </c>
       <c r="N49" s="4" t="inlineStr">
         <is>
@@ -21645,7 +21645,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J26"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
@@ -21663,7 +21663,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>VISITAS DUPLICADAS (24 registros) — CONFIRME E EXCLUA NO SISTEMA</t>
+          <t>VISITAS DUPLICADAS (6 registros) — CONFIRME E EXCLUA NO SISTEMA</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -21741,37 +21741,37 @@
       </c>
       <c r="C3" s="21" t="inlineStr">
         <is>
-          <t>17078217</t>
+          <t>17019173</t>
         </is>
       </c>
       <c r="D3" s="20" t="inlineStr">
         <is>
-          <t>429 - COOPHA FRONTEIRA</t>
+          <t>449 - ÁREA C RESIDENCIAL PONTA PORÃ 1</t>
         </is>
       </c>
       <c r="E3" s="20" t="inlineStr">
         <is>
-          <t>Q006</t>
+          <t>Q029</t>
         </is>
       </c>
       <c r="F3" s="20" t="inlineStr">
         <is>
-          <t>Rua XAVANTES</t>
+          <t>Rua CARAMBOLEIRA</t>
         </is>
       </c>
       <c r="G3" s="20" t="inlineStr">
         <is>
-          <t>567 - 2 - TB</t>
+          <t>105 - 1 - TB</t>
         </is>
       </c>
       <c r="H3" s="20" t="inlineStr">
         <is>
-          <t>21/08/2026 09:50</t>
+          <t>19/08/2026 09:36</t>
         </is>
       </c>
       <c r="I3" s="20" t="inlineStr">
         <is>
-          <t>21/08/2026 09:55</t>
+          <t>19/08/2026 09:36</t>
         </is>
       </c>
       <c r="J3" s="20" t="inlineStr">
@@ -21793,37 +21793,37 @@
       </c>
       <c r="C4" s="21" t="inlineStr">
         <is>
-          <t>17078216</t>
+          <t>17019174</t>
         </is>
       </c>
       <c r="D4" s="20" t="inlineStr">
         <is>
-          <t>429 - COOPHA FRONTEIRA</t>
+          <t>449 - ÁREA C RESIDENCIAL PONTA PORÃ 1</t>
         </is>
       </c>
       <c r="E4" s="20" t="inlineStr">
         <is>
-          <t>Q006</t>
+          <t>Q029</t>
         </is>
       </c>
       <c r="F4" s="20" t="inlineStr">
         <is>
-          <t>Rua XAVANTES</t>
+          <t>Rua CARAMBOLEIRA</t>
         </is>
       </c>
       <c r="G4" s="20" t="inlineStr">
         <is>
-          <t>567 - 2 - TB</t>
+          <t>105 - 1 - TB</t>
         </is>
       </c>
       <c r="H4" s="20" t="inlineStr">
         <is>
-          <t>21/08/2026 09:50</t>
+          <t>19/08/2026 09:36</t>
         </is>
       </c>
       <c r="I4" s="20" t="inlineStr">
         <is>
-          <t>21/08/2026 09:50</t>
+          <t>19/08/2026 09:42</t>
         </is>
       </c>
       <c r="J4" s="20" t="inlineStr">
@@ -21845,37 +21845,37 @@
       </c>
       <c r="C5" s="21" t="inlineStr">
         <is>
-          <t>17078208</t>
+          <t>17019195</t>
         </is>
       </c>
       <c r="D5" s="20" t="inlineStr">
         <is>
-          <t>429 - COOPHA FRONTEIRA</t>
+          <t>449 - ÁREA C RESIDENCIAL PONTA PORÃ 1</t>
         </is>
       </c>
       <c r="E5" s="20" t="inlineStr">
         <is>
-          <t>Q006</t>
+          <t>Q030</t>
         </is>
       </c>
       <c r="F5" s="20" t="inlineStr">
         <is>
-          <t>Rua GUARANTA</t>
+          <t>Rua AMEIXEIRA</t>
         </is>
       </c>
       <c r="G5" s="20" t="inlineStr">
         <is>
-          <t>617 - 1 - TB</t>
+          <t>106 - 2 - TB</t>
         </is>
       </c>
       <c r="H5" s="20" t="inlineStr">
         <is>
-          <t>21/08/2026 09:21</t>
+          <t>19/08/2026 14:18</t>
         </is>
       </c>
       <c r="I5" s="20" t="inlineStr">
         <is>
-          <t>21/08/2026 09:21</t>
+          <t>19/08/2026 14:18</t>
         </is>
       </c>
       <c r="J5" s="20" t="inlineStr">
@@ -21897,37 +21897,37 @@
       </c>
       <c r="C6" s="21" t="inlineStr">
         <is>
-          <t>17078209</t>
+          <t>17019196</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr">
         <is>
-          <t>429 - COOPHA FRONTEIRA</t>
+          <t>449 - ÁREA C RESIDENCIAL PONTA PORÃ 1</t>
         </is>
       </c>
       <c r="E6" s="20" t="inlineStr">
         <is>
-          <t>Q006</t>
+          <t>Q030</t>
         </is>
       </c>
       <c r="F6" s="20" t="inlineStr">
         <is>
-          <t>Rua GUARANTA</t>
+          <t>Rua AMEIXEIRA</t>
         </is>
       </c>
       <c r="G6" s="20" t="inlineStr">
         <is>
-          <t>617 - 1 - TB</t>
+          <t>106 - 2 - TB</t>
         </is>
       </c>
       <c r="H6" s="20" t="inlineStr">
         <is>
-          <t>21/08/2026 09:21</t>
+          <t>19/08/2026 14:18</t>
         </is>
       </c>
       <c r="I6" s="20" t="inlineStr">
         <is>
-          <t>21/08/2026 09:27</t>
+          <t>19/08/2026 14:24</t>
         </is>
       </c>
       <c r="J6" s="20" t="inlineStr">
@@ -21949,37 +21949,37 @@
       </c>
       <c r="C7" s="21" t="inlineStr">
         <is>
-          <t>17048102</t>
+          <t>17019200</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr">
         <is>
-          <t>429 - COOPHA FRONTEIRA</t>
+          <t>449 - ÁREA C RESIDENCIAL PONTA PORÃ 1</t>
         </is>
       </c>
       <c r="E7" s="20" t="inlineStr">
         <is>
-          <t>Q004</t>
+          <t>Q030</t>
         </is>
       </c>
       <c r="F7" s="20" t="inlineStr">
         <is>
-          <t>Rua NOGUEIRA</t>
+          <t>Rua AMEIXEIRA</t>
         </is>
       </c>
       <c r="G7" s="20" t="inlineStr">
         <is>
-          <t>669 - 3 - TB</t>
+          <t>55 - 1 - TB</t>
         </is>
       </c>
       <c r="H7" s="20" t="inlineStr">
         <is>
-          <t>20/08/2026 13:35</t>
+          <t>19/08/2026 14:33</t>
         </is>
       </c>
       <c r="I7" s="20" t="inlineStr">
         <is>
-          <t>20/08/2026 13:35</t>
+          <t>19/08/2026 14:33</t>
         </is>
       </c>
       <c r="J7" s="20" t="inlineStr">
@@ -22001,37 +22001,37 @@
       </c>
       <c r="C8" s="21" t="inlineStr">
         <is>
-          <t>17048103</t>
+          <t>17019201</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
         <is>
-          <t>429 - COOPHA FRONTEIRA</t>
+          <t>449 - ÁREA C RESIDENCIAL PONTA PORÃ 1</t>
         </is>
       </c>
       <c r="E8" s="20" t="inlineStr">
         <is>
-          <t>Q004</t>
+          <t>Q030</t>
         </is>
       </c>
       <c r="F8" s="20" t="inlineStr">
         <is>
-          <t>Rua NOGUEIRA</t>
+          <t>Rua AMEIXEIRA</t>
         </is>
       </c>
       <c r="G8" s="20" t="inlineStr">
         <is>
-          <t>669 - 3 - TB</t>
+          <t>55 - 1 - TB</t>
         </is>
       </c>
       <c r="H8" s="20" t="inlineStr">
         <is>
-          <t>20/08/2026 13:35</t>
+          <t>19/08/2026 14:33</t>
         </is>
       </c>
       <c r="I8" s="20" t="inlineStr">
         <is>
-          <t>20/08/2026 13:41</t>
+          <t>19/08/2026 14:38</t>
         </is>
       </c>
       <c r="J8" s="20" t="inlineStr">
@@ -22040,944 +22040,8 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="20" t="inlineStr">
-        <is>
-          <t>Claine Luisa Figueiredo Torraca</t>
-        </is>
-      </c>
-      <c r="B9" s="20" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C9" s="21" t="inlineStr">
-        <is>
-          <t>17078203</t>
-        </is>
-      </c>
-      <c r="D9" s="20" t="inlineStr">
-        <is>
-          <t>429 - COOPHA FRONTEIRA</t>
-        </is>
-      </c>
-      <c r="E9" s="20" t="inlineStr">
-        <is>
-          <t>Q006</t>
-        </is>
-      </c>
-      <c r="F9" s="20" t="inlineStr">
-        <is>
-          <t>Rua GUARANTA</t>
-        </is>
-      </c>
-      <c r="G9" s="20" t="inlineStr">
-        <is>
-          <t>677 - 1 - TB</t>
-        </is>
-      </c>
-      <c r="H9" s="20" t="inlineStr">
-        <is>
-          <t>21/08/2026 09:12</t>
-        </is>
-      </c>
-      <c r="I9" s="20" t="inlineStr">
-        <is>
-          <t>21/08/2026 09:12</t>
-        </is>
-      </c>
-      <c r="J9" s="20" t="inlineStr">
-        <is>
-          <t>Mesmo horário de chegada + imóvel</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="20" t="inlineStr">
-        <is>
-          <t>Claine Luisa Figueiredo Torraca</t>
-        </is>
-      </c>
-      <c r="B10" s="20" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C10" s="21" t="inlineStr">
-        <is>
-          <t>17078204</t>
-        </is>
-      </c>
-      <c r="D10" s="20" t="inlineStr">
-        <is>
-          <t>429 - COOPHA FRONTEIRA</t>
-        </is>
-      </c>
-      <c r="E10" s="20" t="inlineStr">
-        <is>
-          <t>Q006</t>
-        </is>
-      </c>
-      <c r="F10" s="20" t="inlineStr">
-        <is>
-          <t>Rua GUARANTA</t>
-        </is>
-      </c>
-      <c r="G10" s="20" t="inlineStr">
-        <is>
-          <t>677 - 1 - TB</t>
-        </is>
-      </c>
-      <c r="H10" s="20" t="inlineStr">
-        <is>
-          <t>21/08/2026 09:12</t>
-        </is>
-      </c>
-      <c r="I10" s="20" t="inlineStr">
-        <is>
-          <t>21/08/2026 09:18</t>
-        </is>
-      </c>
-      <c r="J10" s="20" t="inlineStr">
-        <is>
-          <t>Mesmo horário de chegada + imóvel</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="20" t="inlineStr">
-        <is>
-          <t>Claine Luisa Figueiredo Torraca</t>
-        </is>
-      </c>
-      <c r="B11" s="20" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C11" s="21" t="inlineStr">
-        <is>
-          <t>17019173</t>
-        </is>
-      </c>
-      <c r="D11" s="20" t="inlineStr">
-        <is>
-          <t>449 - ÁREA C RESIDENCIAL PONTA PORÃ 1</t>
-        </is>
-      </c>
-      <c r="E11" s="20" t="inlineStr">
-        <is>
-          <t>Q029</t>
-        </is>
-      </c>
-      <c r="F11" s="20" t="inlineStr">
-        <is>
-          <t>Rua CARAMBOLEIRA</t>
-        </is>
-      </c>
-      <c r="G11" s="20" t="inlineStr">
-        <is>
-          <t>105 - 1 - TB</t>
-        </is>
-      </c>
-      <c r="H11" s="20" t="inlineStr">
-        <is>
-          <t>19/08/2026 09:36</t>
-        </is>
-      </c>
-      <c r="I11" s="20" t="inlineStr">
-        <is>
-          <t>19/08/2026 09:36</t>
-        </is>
-      </c>
-      <c r="J11" s="20" t="inlineStr">
-        <is>
-          <t>Mesmo horário de chegada + imóvel</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="20" t="inlineStr">
-        <is>
-          <t>Claine Luisa Figueiredo Torraca</t>
-        </is>
-      </c>
-      <c r="B12" s="20" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C12" s="21" t="inlineStr">
-        <is>
-          <t>17019174</t>
-        </is>
-      </c>
-      <c r="D12" s="20" t="inlineStr">
-        <is>
-          <t>449 - ÁREA C RESIDENCIAL PONTA PORÃ 1</t>
-        </is>
-      </c>
-      <c r="E12" s="20" t="inlineStr">
-        <is>
-          <t>Q029</t>
-        </is>
-      </c>
-      <c r="F12" s="20" t="inlineStr">
-        <is>
-          <t>Rua CARAMBOLEIRA</t>
-        </is>
-      </c>
-      <c r="G12" s="20" t="inlineStr">
-        <is>
-          <t>105 - 1 - TB</t>
-        </is>
-      </c>
-      <c r="H12" s="20" t="inlineStr">
-        <is>
-          <t>19/08/2026 09:36</t>
-        </is>
-      </c>
-      <c r="I12" s="20" t="inlineStr">
-        <is>
-          <t>19/08/2026 09:42</t>
-        </is>
-      </c>
-      <c r="J12" s="20" t="inlineStr">
-        <is>
-          <t>Mesmo horário de chegada + imóvel</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="20" t="inlineStr">
-        <is>
-          <t>Claine Luisa Figueiredo Torraca</t>
-        </is>
-      </c>
-      <c r="B13" s="20" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C13" s="21" t="inlineStr">
-        <is>
-          <t>17019193</t>
-        </is>
-      </c>
-      <c r="D13" s="20" t="inlineStr">
-        <is>
-          <t>449 - ÁREA C RESIDENCIAL PONTA PORÃ 1</t>
-        </is>
-      </c>
-      <c r="E13" s="20" t="inlineStr">
-        <is>
-          <t>Q030</t>
-        </is>
-      </c>
-      <c r="F13" s="20" t="inlineStr">
-        <is>
-          <t>Rua CARAMBOLEIRA</t>
-        </is>
-      </c>
-      <c r="G13" s="20" t="inlineStr">
-        <is>
-          <t>106 - 1 - TB</t>
-        </is>
-      </c>
-      <c r="H13" s="20" t="inlineStr">
-        <is>
-          <t>19/08/2026 14:12</t>
-        </is>
-      </c>
-      <c r="I13" s="20" t="inlineStr">
-        <is>
-          <t>19/08/2026 14:12</t>
-        </is>
-      </c>
-      <c r="J13" s="20" t="inlineStr">
-        <is>
-          <t>Mesmo horário de chegada + imóvel</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="20" t="inlineStr">
-        <is>
-          <t>Claine Luisa Figueiredo Torraca</t>
-        </is>
-      </c>
-      <c r="B14" s="20" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C14" s="21" t="inlineStr">
-        <is>
-          <t>17019194</t>
-        </is>
-      </c>
-      <c r="D14" s="20" t="inlineStr">
-        <is>
-          <t>449 - ÁREA C RESIDENCIAL PONTA PORÃ 1</t>
-        </is>
-      </c>
-      <c r="E14" s="20" t="inlineStr">
-        <is>
-          <t>Q030</t>
-        </is>
-      </c>
-      <c r="F14" s="20" t="inlineStr">
-        <is>
-          <t>Rua CARAMBOLEIRA</t>
-        </is>
-      </c>
-      <c r="G14" s="20" t="inlineStr">
-        <is>
-          <t>106 - 1 - TB</t>
-        </is>
-      </c>
-      <c r="H14" s="20" t="inlineStr">
-        <is>
-          <t>19/08/2026 14:12</t>
-        </is>
-      </c>
-      <c r="I14" s="20" t="inlineStr">
-        <is>
-          <t>19/08/2026 14:18</t>
-        </is>
-      </c>
-      <c r="J14" s="20" t="inlineStr">
-        <is>
-          <t>Mesmo horário de chegada + imóvel</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="20" t="inlineStr">
-        <is>
-          <t>Claine Luisa Figueiredo Torraca</t>
-        </is>
-      </c>
-      <c r="B15" s="20" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C15" s="21" t="inlineStr">
-        <is>
-          <t>17019196</t>
-        </is>
-      </c>
-      <c r="D15" s="20" t="inlineStr">
-        <is>
-          <t>449 - ÁREA C RESIDENCIAL PONTA PORÃ 1</t>
-        </is>
-      </c>
-      <c r="E15" s="20" t="inlineStr">
-        <is>
-          <t>Q030</t>
-        </is>
-      </c>
-      <c r="F15" s="20" t="inlineStr">
-        <is>
-          <t>Rua AMEIXEIRA</t>
-        </is>
-      </c>
-      <c r="G15" s="20" t="inlineStr">
-        <is>
-          <t>106 - 2 - TB</t>
-        </is>
-      </c>
-      <c r="H15" s="20" t="inlineStr">
-        <is>
-          <t>19/08/2026 14:18</t>
-        </is>
-      </c>
-      <c r="I15" s="20" t="inlineStr">
-        <is>
-          <t>19/08/2026 14:24</t>
-        </is>
-      </c>
-      <c r="J15" s="20" t="inlineStr">
-        <is>
-          <t>Mesmo horário de chegada + imóvel</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="20" t="inlineStr">
-        <is>
-          <t>Claine Luisa Figueiredo Torraca</t>
-        </is>
-      </c>
-      <c r="B16" s="20" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C16" s="21" t="inlineStr">
-        <is>
-          <t>17019195</t>
-        </is>
-      </c>
-      <c r="D16" s="20" t="inlineStr">
-        <is>
-          <t>449 - ÁREA C RESIDENCIAL PONTA PORÃ 1</t>
-        </is>
-      </c>
-      <c r="E16" s="20" t="inlineStr">
-        <is>
-          <t>Q030</t>
-        </is>
-      </c>
-      <c r="F16" s="20" t="inlineStr">
-        <is>
-          <t>Rua AMEIXEIRA</t>
-        </is>
-      </c>
-      <c r="G16" s="20" t="inlineStr">
-        <is>
-          <t>106 - 2 - TB</t>
-        </is>
-      </c>
-      <c r="H16" s="20" t="inlineStr">
-        <is>
-          <t>19/08/2026 14:18</t>
-        </is>
-      </c>
-      <c r="I16" s="20" t="inlineStr">
-        <is>
-          <t>19/08/2026 14:18</t>
-        </is>
-      </c>
-      <c r="J16" s="20" t="inlineStr">
-        <is>
-          <t>Mesmo horário de chegada + imóvel</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="20" t="inlineStr">
-        <is>
-          <t>Claine Luisa Figueiredo Torraca</t>
-        </is>
-      </c>
-      <c r="B17" s="20" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C17" s="21" t="inlineStr">
-        <is>
-          <t>17019182</t>
-        </is>
-      </c>
-      <c r="D17" s="20" t="inlineStr">
-        <is>
-          <t>449 - ÁREA C RESIDENCIAL PONTA PORÃ 1</t>
-        </is>
-      </c>
-      <c r="E17" s="20" t="inlineStr">
-        <is>
-          <t>Q030</t>
-        </is>
-      </c>
-      <c r="F17" s="20" t="inlineStr">
-        <is>
-          <t>Rua CARAMBOLEIRA</t>
-        </is>
-      </c>
-      <c r="G17" s="20" t="inlineStr">
-        <is>
-          <t>18 - 1 - TB</t>
-        </is>
-      </c>
-      <c r="H17" s="20" t="inlineStr">
-        <is>
-          <t>19/08/2026 10:11</t>
-        </is>
-      </c>
-      <c r="I17" s="20" t="inlineStr">
-        <is>
-          <t>19/08/2026 10:11</t>
-        </is>
-      </c>
-      <c r="J17" s="20" t="inlineStr">
-        <is>
-          <t>Mesmo horário de chegada + imóvel</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="20" t="inlineStr">
-        <is>
-          <t>Claine Luisa Figueiredo Torraca</t>
-        </is>
-      </c>
-      <c r="B18" s="20" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C18" s="21" t="inlineStr">
-        <is>
-          <t>17019183</t>
-        </is>
-      </c>
-      <c r="D18" s="20" t="inlineStr">
-        <is>
-          <t>449 - ÁREA C RESIDENCIAL PONTA PORÃ 1</t>
-        </is>
-      </c>
-      <c r="E18" s="20" t="inlineStr">
-        <is>
-          <t>Q030</t>
-        </is>
-      </c>
-      <c r="F18" s="20" t="inlineStr">
-        <is>
-          <t>Rua CARAMBOLEIRA</t>
-        </is>
-      </c>
-      <c r="G18" s="20" t="inlineStr">
-        <is>
-          <t>18 - 1 - TB</t>
-        </is>
-      </c>
-      <c r="H18" s="20" t="inlineStr">
-        <is>
-          <t>19/08/2026 10:11</t>
-        </is>
-      </c>
-      <c r="I18" s="20" t="inlineStr">
-        <is>
-          <t>19/08/2026 10:16</t>
-        </is>
-      </c>
-      <c r="J18" s="20" t="inlineStr">
-        <is>
-          <t>Mesmo horário de chegada + imóvel</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="20" t="inlineStr">
-        <is>
-          <t>Claine Luisa Figueiredo Torraca</t>
-        </is>
-      </c>
-      <c r="B19" s="20" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C19" s="21" t="inlineStr">
-        <is>
-          <t>17019158</t>
-        </is>
-      </c>
-      <c r="D19" s="20" t="inlineStr">
-        <is>
-          <t>449 - ÁREA C RESIDENCIAL PONTA PORÃ 1</t>
-        </is>
-      </c>
-      <c r="E19" s="20" t="inlineStr">
-        <is>
-          <t>Q029</t>
-        </is>
-      </c>
-      <c r="F19" s="20" t="inlineStr">
-        <is>
-          <t>Rua CAJUEIRO</t>
-        </is>
-      </c>
-      <c r="G19" s="20" t="inlineStr">
-        <is>
-          <t>26 - 1 - TB</t>
-        </is>
-      </c>
-      <c r="H19" s="20" t="inlineStr">
-        <is>
-          <t>19/08/2026 08:45</t>
-        </is>
-      </c>
-      <c r="I19" s="20" t="inlineStr">
-        <is>
-          <t>19/08/2026 08:45</t>
-        </is>
-      </c>
-      <c r="J19" s="20" t="inlineStr">
-        <is>
-          <t>Mesmo horário de chegada + imóvel</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="20" t="inlineStr">
-        <is>
-          <t>Claine Luisa Figueiredo Torraca</t>
-        </is>
-      </c>
-      <c r="B20" s="20" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C20" s="21" t="inlineStr">
-        <is>
-          <t>17019159</t>
-        </is>
-      </c>
-      <c r="D20" s="20" t="inlineStr">
-        <is>
-          <t>449 - ÁREA C RESIDENCIAL PONTA PORÃ 1</t>
-        </is>
-      </c>
-      <c r="E20" s="20" t="inlineStr">
-        <is>
-          <t>Q029</t>
-        </is>
-      </c>
-      <c r="F20" s="20" t="inlineStr">
-        <is>
-          <t>Rua CAJUEIRO</t>
-        </is>
-      </c>
-      <c r="G20" s="20" t="inlineStr">
-        <is>
-          <t>26 - 1 - TB</t>
-        </is>
-      </c>
-      <c r="H20" s="20" t="inlineStr">
-        <is>
-          <t>19/08/2026 08:45</t>
-        </is>
-      </c>
-      <c r="I20" s="20" t="inlineStr">
-        <is>
-          <t>19/08/2026 08:51</t>
-        </is>
-      </c>
-      <c r="J20" s="20" t="inlineStr">
-        <is>
-          <t>Mesmo horário de chegada + imóvel</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="20" t="inlineStr">
-        <is>
-          <t>Claine Luisa Figueiredo Torraca</t>
-        </is>
-      </c>
-      <c r="B21" s="20" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C21" s="21" t="inlineStr">
-        <is>
-          <t>17019200</t>
-        </is>
-      </c>
-      <c r="D21" s="20" t="inlineStr">
-        <is>
-          <t>449 - ÁREA C RESIDENCIAL PONTA PORÃ 1</t>
-        </is>
-      </c>
-      <c r="E21" s="20" t="inlineStr">
-        <is>
-          <t>Q030</t>
-        </is>
-      </c>
-      <c r="F21" s="20" t="inlineStr">
-        <is>
-          <t>Rua AMEIXEIRA</t>
-        </is>
-      </c>
-      <c r="G21" s="20" t="inlineStr">
-        <is>
-          <t>55 - 1 - TB</t>
-        </is>
-      </c>
-      <c r="H21" s="20" t="inlineStr">
-        <is>
-          <t>19/08/2026 14:33</t>
-        </is>
-      </c>
-      <c r="I21" s="20" t="inlineStr">
-        <is>
-          <t>19/08/2026 14:33</t>
-        </is>
-      </c>
-      <c r="J21" s="20" t="inlineStr">
-        <is>
-          <t>Mesmo horário de chegada + imóvel</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="20" t="inlineStr">
-        <is>
-          <t>Claine Luisa Figueiredo Torraca</t>
-        </is>
-      </c>
-      <c r="B22" s="20" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C22" s="21" t="inlineStr">
-        <is>
-          <t>17019201</t>
-        </is>
-      </c>
-      <c r="D22" s="20" t="inlineStr">
-        <is>
-          <t>449 - ÁREA C RESIDENCIAL PONTA PORÃ 1</t>
-        </is>
-      </c>
-      <c r="E22" s="20" t="inlineStr">
-        <is>
-          <t>Q030</t>
-        </is>
-      </c>
-      <c r="F22" s="20" t="inlineStr">
-        <is>
-          <t>Rua AMEIXEIRA</t>
-        </is>
-      </c>
-      <c r="G22" s="20" t="inlineStr">
-        <is>
-          <t>55 - 1 - TB</t>
-        </is>
-      </c>
-      <c r="H22" s="20" t="inlineStr">
-        <is>
-          <t>19/08/2026 14:33</t>
-        </is>
-      </c>
-      <c r="I22" s="20" t="inlineStr">
-        <is>
-          <t>19/08/2026 14:38</t>
-        </is>
-      </c>
-      <c r="J22" s="20" t="inlineStr">
-        <is>
-          <t>Mesmo horário de chegada + imóvel</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="20" t="inlineStr">
-        <is>
-          <t>Claine Luisa Figueiredo Torraca</t>
-        </is>
-      </c>
-      <c r="B23" s="20" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C23" s="21" t="inlineStr">
-        <is>
-          <t>17019184</t>
-        </is>
-      </c>
-      <c r="D23" s="20" t="inlineStr">
-        <is>
-          <t>449 - ÁREA C RESIDENCIAL PONTA PORÃ 1</t>
-        </is>
-      </c>
-      <c r="E23" s="20" t="inlineStr">
-        <is>
-          <t>Q030</t>
-        </is>
-      </c>
-      <c r="F23" s="20" t="inlineStr">
-        <is>
-          <t>Rua CARAMBOLEIRA</t>
-        </is>
-      </c>
-      <c r="G23" s="20" t="inlineStr">
-        <is>
-          <t>84 - 1 - TB</t>
-        </is>
-      </c>
-      <c r="H23" s="20" t="inlineStr">
-        <is>
-          <t>19/08/2026 10:17</t>
-        </is>
-      </c>
-      <c r="I23" s="20" t="inlineStr">
-        <is>
-          <t>19/08/2026 10:17</t>
-        </is>
-      </c>
-      <c r="J23" s="20" t="inlineStr">
-        <is>
-          <t>Mesmo horário de chegada + imóvel</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="20" t="inlineStr">
-        <is>
-          <t>Claine Luisa Figueiredo Torraca</t>
-        </is>
-      </c>
-      <c r="B24" s="20" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C24" s="21" t="inlineStr">
-        <is>
-          <t>17019185</t>
-        </is>
-      </c>
-      <c r="D24" s="20" t="inlineStr">
-        <is>
-          <t>449 - ÁREA C RESIDENCIAL PONTA PORÃ 1</t>
-        </is>
-      </c>
-      <c r="E24" s="20" t="inlineStr">
-        <is>
-          <t>Q030</t>
-        </is>
-      </c>
-      <c r="F24" s="20" t="inlineStr">
-        <is>
-          <t>Rua CARAMBOLEIRA</t>
-        </is>
-      </c>
-      <c r="G24" s="20" t="inlineStr">
-        <is>
-          <t>84 - 1 - TB</t>
-        </is>
-      </c>
-      <c r="H24" s="20" t="inlineStr">
-        <is>
-          <t>19/08/2026 10:17</t>
-        </is>
-      </c>
-      <c r="I24" s="20" t="inlineStr">
-        <is>
-          <t>19/08/2026 10:23</t>
-        </is>
-      </c>
-      <c r="J24" s="20" t="inlineStr">
-        <is>
-          <t>Mesmo horário de chegada + imóvel</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="20" t="inlineStr">
-        <is>
-          <t>Claine Luisa Figueiredo Torraca</t>
-        </is>
-      </c>
-      <c r="B25" s="20" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C25" s="21" t="inlineStr">
-        <is>
-          <t>17019165</t>
-        </is>
-      </c>
-      <c r="D25" s="20" t="inlineStr">
-        <is>
-          <t>449 - ÁREA C RESIDENCIAL PONTA PORÃ 1</t>
-        </is>
-      </c>
-      <c r="E25" s="20" t="inlineStr">
-        <is>
-          <t>Q029</t>
-        </is>
-      </c>
-      <c r="F25" s="20" t="inlineStr">
-        <is>
-          <t>Rua CAJUEIRO</t>
-        </is>
-      </c>
-      <c r="G25" s="20" t="inlineStr">
-        <is>
-          <t>96 - 01 - TB</t>
-        </is>
-      </c>
-      <c r="H25" s="20" t="inlineStr">
-        <is>
-          <t>19/08/2026 09:08</t>
-        </is>
-      </c>
-      <c r="I25" s="20" t="inlineStr">
-        <is>
-          <t>19/08/2026 09:08</t>
-        </is>
-      </c>
-      <c r="J25" s="20" t="inlineStr">
-        <is>
-          <t>Mesmo horário de chegada + imóvel</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="20" t="inlineStr">
-        <is>
-          <t>Claine Luisa Figueiredo Torraca</t>
-        </is>
-      </c>
-      <c r="B26" s="20" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C26" s="21" t="inlineStr">
-        <is>
-          <t>17019166</t>
-        </is>
-      </c>
-      <c r="D26" s="20" t="inlineStr">
-        <is>
-          <t>449 - ÁREA C RESIDENCIAL PONTA PORÃ 1</t>
-        </is>
-      </c>
-      <c r="E26" s="20" t="inlineStr">
-        <is>
-          <t>Q029</t>
-        </is>
-      </c>
-      <c r="F26" s="20" t="inlineStr">
-        <is>
-          <t>Rua CAJUEIRO</t>
-        </is>
-      </c>
-      <c r="G26" s="20" t="inlineStr">
-        <is>
-          <t>96 - 01 - TB</t>
-        </is>
-      </c>
-      <c r="H26" s="20" t="inlineStr">
-        <is>
-          <t>19/08/2026 09:08</t>
-        </is>
-      </c>
-      <c r="I26" s="20" t="inlineStr">
-        <is>
-          <t>19/08/2026 09:16</t>
-        </is>
-      </c>
-      <c r="J26" s="20" t="inlineStr">
-        <is>
-          <t>Mesmo horário de chegada + imóvel</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A2:J26"/>
+  <autoFilter ref="A2:J8"/>
   <mergeCells count="1">
     <mergeCell ref="A1:J1"/>
   </mergeCells>
@@ -22988,24 +22052,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C17" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C18" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C19" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C20" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C21" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C22" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C23" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C24" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C25" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C26" r:id="rId24"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -23017,7 +22063,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K48"/>
+  <dimension ref="A1:K30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
@@ -23036,7 +22082,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>VISITAS EM SEQUÊNCIA SUSPEITA (28 registros) — CHEGADA NO MESMO MINUTO DA VISITA ANTERIOR</t>
+          <t>VISITAS EM SEQUÊNCIA SUSPEITA (10 registros) — CHEGADA NO MESMO MINUTO DA VISITA ANTERIOR</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -23227,7 +22273,7 @@
       </c>
       <c r="D5" s="24" t="inlineStr">
         <is>
-          <t>17019158</t>
+          <t>17019173</t>
         </is>
       </c>
       <c r="E5" s="23" t="inlineStr">
@@ -23242,22 +22288,22 @@
       </c>
       <c r="G5" s="23" t="inlineStr">
         <is>
-          <t>Rua CAJUEIRO</t>
+          <t>Rua CARAMBOLEIRA</t>
         </is>
       </c>
       <c r="H5" s="23" t="inlineStr">
         <is>
-          <t>26 - 1 - TB</t>
+          <t>105 - 1 - TB</t>
         </is>
       </c>
       <c r="I5" s="23" t="inlineStr">
         <is>
-          <t>19/08/2026 08:45</t>
+          <t>19/08/2026 09:36</t>
         </is>
       </c>
       <c r="J5" s="23" t="inlineStr">
         <is>
-          <t>19/08/2026 08:45</t>
+          <t>19/08/2026 09:36</t>
         </is>
       </c>
       <c r="K5" s="23" t="inlineStr"/>
@@ -23278,7 +22324,7 @@
       </c>
       <c r="D6" s="24" t="inlineStr">
         <is>
-          <t>17019159</t>
+          <t>17019174</t>
         </is>
       </c>
       <c r="E6" s="23" t="inlineStr">
@@ -23293,22 +22339,22 @@
       </c>
       <c r="G6" s="23" t="inlineStr">
         <is>
-          <t>Rua CAJUEIRO</t>
+          <t>Rua CARAMBOLEIRA</t>
         </is>
       </c>
       <c r="H6" s="23" t="inlineStr">
         <is>
-          <t>26 - 1 - TB</t>
+          <t>105 - 1 - TB</t>
         </is>
       </c>
       <c r="I6" s="23" t="inlineStr">
         <is>
-          <t>19/08/2026 08:45</t>
+          <t>19/08/2026 09:36</t>
         </is>
       </c>
       <c r="J6" s="23" t="inlineStr">
         <is>
-          <t>19/08/2026 08:51</t>
+          <t>19/08/2026 09:42</t>
         </is>
       </c>
       <c r="K6" s="23" t="n">
@@ -23331,7 +22377,7 @@
       </c>
       <c r="D7" s="24" t="inlineStr">
         <is>
-          <t>17019165</t>
+          <t>17019195</t>
         </is>
       </c>
       <c r="E7" s="23" t="inlineStr">
@@ -23341,27 +22387,27 @@
       </c>
       <c r="F7" s="23" t="inlineStr">
         <is>
-          <t>Q029</t>
+          <t>Q030</t>
         </is>
       </c>
       <c r="G7" s="23" t="inlineStr">
         <is>
-          <t>Rua CAJUEIRO</t>
+          <t>Rua AMEIXEIRA</t>
         </is>
       </c>
       <c r="H7" s="23" t="inlineStr">
         <is>
-          <t>96 - 01 - TB</t>
+          <t>106 - 2 - TB</t>
         </is>
       </c>
       <c r="I7" s="23" t="inlineStr">
         <is>
-          <t>19/08/2026 09:08</t>
+          <t>19/08/2026 14:18</t>
         </is>
       </c>
       <c r="J7" s="23" t="inlineStr">
         <is>
-          <t>19/08/2026 09:08</t>
+          <t>19/08/2026 14:18</t>
         </is>
       </c>
       <c r="K7" s="23" t="inlineStr"/>
@@ -23382,7 +22428,7 @@
       </c>
       <c r="D8" s="24" t="inlineStr">
         <is>
-          <t>17019166</t>
+          <t>17019196</t>
         </is>
       </c>
       <c r="E8" s="23" t="inlineStr">
@@ -23392,27 +22438,27 @@
       </c>
       <c r="F8" s="23" t="inlineStr">
         <is>
-          <t>Q029</t>
+          <t>Q030</t>
         </is>
       </c>
       <c r="G8" s="23" t="inlineStr">
         <is>
-          <t>Rua CAJUEIRO</t>
+          <t>Rua AMEIXEIRA</t>
         </is>
       </c>
       <c r="H8" s="23" t="inlineStr">
         <is>
-          <t>96 - 01 - TB</t>
+          <t>106 - 2 - TB</t>
         </is>
       </c>
       <c r="I8" s="23" t="inlineStr">
         <is>
-          <t>19/08/2026 09:08</t>
+          <t>19/08/2026 14:18</t>
         </is>
       </c>
       <c r="J8" s="23" t="inlineStr">
         <is>
-          <t>19/08/2026 09:16</t>
+          <t>19/08/2026 14:24</t>
         </is>
       </c>
       <c r="K8" s="23" t="n">
@@ -23435,7 +22481,7 @@
       </c>
       <c r="D9" s="24" t="inlineStr">
         <is>
-          <t>17019173</t>
+          <t>17019200</t>
         </is>
       </c>
       <c r="E9" s="23" t="inlineStr">
@@ -23445,27 +22491,27 @@
       </c>
       <c r="F9" s="23" t="inlineStr">
         <is>
-          <t>Q029</t>
+          <t>Q030</t>
         </is>
       </c>
       <c r="G9" s="23" t="inlineStr">
         <is>
-          <t>Rua CARAMBOLEIRA</t>
+          <t>Rua AMEIXEIRA</t>
         </is>
       </c>
       <c r="H9" s="23" t="inlineStr">
         <is>
-          <t>105 - 1 - TB</t>
+          <t>55 - 1 - TB</t>
         </is>
       </c>
       <c r="I9" s="23" t="inlineStr">
         <is>
-          <t>19/08/2026 09:36</t>
+          <t>19/08/2026 14:33</t>
         </is>
       </c>
       <c r="J9" s="23" t="inlineStr">
         <is>
-          <t>19/08/2026 09:36</t>
+          <t>19/08/2026 14:33</t>
         </is>
       </c>
       <c r="K9" s="23" t="inlineStr"/>
@@ -23486,7 +22532,7 @@
       </c>
       <c r="D10" s="24" t="inlineStr">
         <is>
-          <t>17019174</t>
+          <t>17019201</t>
         </is>
       </c>
       <c r="E10" s="23" t="inlineStr">
@@ -23496,27 +22542,27 @@
       </c>
       <c r="F10" s="23" t="inlineStr">
         <is>
-          <t>Q029</t>
+          <t>Q030</t>
         </is>
       </c>
       <c r="G10" s="23" t="inlineStr">
         <is>
-          <t>Rua CARAMBOLEIRA</t>
+          <t>Rua AMEIXEIRA</t>
         </is>
       </c>
       <c r="H10" s="23" t="inlineStr">
         <is>
-          <t>105 - 1 - TB</t>
+          <t>55 - 1 - TB</t>
         </is>
       </c>
       <c r="I10" s="23" t="inlineStr">
         <is>
-          <t>19/08/2026 09:36</t>
+          <t>19/08/2026 14:33</t>
         </is>
       </c>
       <c r="J10" s="23" t="inlineStr">
         <is>
-          <t>19/08/2026 09:42</t>
+          <t>19/08/2026 14:38</t>
         </is>
       </c>
       <c r="K10" s="23" t="n">
@@ -23526,7 +22572,7 @@
     <row r="11">
       <c r="A11" s="23" t="inlineStr">
         <is>
-          <t>Claine Luisa Figueiredo Torraca</t>
+          <t>Emidio Rainer Vilhalba</t>
         </is>
       </c>
       <c r="B11" s="23" t="inlineStr">
@@ -23535,41 +22581,41 @@
         </is>
       </c>
       <c r="C11" s="23" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D11" s="24" t="inlineStr">
         <is>
-          <t>17019182</t>
+          <t>16959229</t>
         </is>
       </c>
       <c r="E11" s="23" t="inlineStr">
         <is>
-          <t>449 - ÁREA C RESIDENCIAL PONTA PORÃ 1</t>
+          <t>430 - VILA RENÔ</t>
         </is>
       </c>
       <c r="F11" s="23" t="inlineStr">
         <is>
-          <t>Q030</t>
+          <t>Q034</t>
         </is>
       </c>
       <c r="G11" s="23" t="inlineStr">
         <is>
-          <t>Rua CARAMBOLEIRA</t>
+          <t>Avenida URUMBELA</t>
         </is>
       </c>
       <c r="H11" s="23" t="inlineStr">
         <is>
-          <t>18 - 1 - TB</t>
+          <t>890 - 10 - R</t>
         </is>
       </c>
       <c r="I11" s="23" t="inlineStr">
         <is>
-          <t>19/08/2026 10:11</t>
+          <t>18/08/2026 09:50</t>
         </is>
       </c>
       <c r="J11" s="23" t="inlineStr">
         <is>
-          <t>19/08/2026 10:11</t>
+          <t>18/08/2026 09:51</t>
         </is>
       </c>
       <c r="K11" s="23" t="inlineStr"/>
@@ -23577,7 +22623,7 @@
     <row r="12">
       <c r="A12" s="23" t="inlineStr">
         <is>
-          <t>Claine Luisa Figueiredo Torraca</t>
+          <t>Emidio Rainer Vilhalba</t>
         </is>
       </c>
       <c r="B12" s="23" t="inlineStr">
@@ -23586,1101 +22632,165 @@
         </is>
       </c>
       <c r="C12" s="23" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D12" s="24" t="inlineStr">
         <is>
-          <t>17019183</t>
+          <t>16959228</t>
         </is>
       </c>
       <c r="E12" s="23" t="inlineStr">
         <is>
-          <t>449 - ÁREA C RESIDENCIAL PONTA PORÃ 1</t>
+          <t>430 - VILA RENÔ</t>
         </is>
       </c>
       <c r="F12" s="23" t="inlineStr">
         <is>
-          <t>Q030</t>
+          <t>Q034</t>
         </is>
       </c>
       <c r="G12" s="23" t="inlineStr">
         <is>
-          <t>Rua CARAMBOLEIRA</t>
+          <t>Avenida URUMBELA</t>
         </is>
       </c>
       <c r="H12" s="23" t="inlineStr">
         <is>
-          <t>18 - 1 - TB</t>
+          <t>890 - 9 - C</t>
         </is>
       </c>
       <c r="I12" s="23" t="inlineStr">
         <is>
-          <t>19/08/2026 10:11</t>
+          <t>18/08/2026 09:50</t>
         </is>
       </c>
       <c r="J12" s="23" t="inlineStr">
         <is>
-          <t>19/08/2026 10:16</t>
+          <t>18/08/2026 09:50</t>
         </is>
       </c>
       <c r="K12" s="23" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="23" t="inlineStr">
-        <is>
-          <t>Claine Luisa Figueiredo Torraca</t>
-        </is>
-      </c>
-      <c r="B13" s="23" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C13" s="23" t="n">
-        <v>5</v>
-      </c>
-      <c r="D13" s="24" t="inlineStr">
-        <is>
-          <t>17019184</t>
-        </is>
-      </c>
-      <c r="E13" s="23" t="inlineStr">
-        <is>
-          <t>449 - ÁREA C RESIDENCIAL PONTA PORÃ 1</t>
-        </is>
-      </c>
-      <c r="F13" s="23" t="inlineStr">
-        <is>
-          <t>Q030</t>
-        </is>
-      </c>
-      <c r="G13" s="23" t="inlineStr">
-        <is>
-          <t>Rua CARAMBOLEIRA</t>
-        </is>
-      </c>
-      <c r="H13" s="23" t="inlineStr">
-        <is>
-          <t>84 - 1 - TB</t>
-        </is>
-      </c>
-      <c r="I13" s="23" t="inlineStr">
-        <is>
-          <t>19/08/2026 10:17</t>
-        </is>
-      </c>
-      <c r="J13" s="23" t="inlineStr">
-        <is>
-          <t>19/08/2026 10:17</t>
-        </is>
-      </c>
-      <c r="K13" s="23" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="23" t="inlineStr">
-        <is>
-          <t>Claine Luisa Figueiredo Torraca</t>
-        </is>
-      </c>
-      <c r="B14" s="23" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C14" s="23" t="n">
-        <v>5</v>
-      </c>
-      <c r="D14" s="24" t="inlineStr">
-        <is>
-          <t>17019185</t>
-        </is>
-      </c>
-      <c r="E14" s="23" t="inlineStr">
-        <is>
-          <t>449 - ÁREA C RESIDENCIAL PONTA PORÃ 1</t>
-        </is>
-      </c>
-      <c r="F14" s="23" t="inlineStr">
-        <is>
-          <t>Q030</t>
-        </is>
-      </c>
-      <c r="G14" s="23" t="inlineStr">
-        <is>
-          <t>Rua CARAMBOLEIRA</t>
-        </is>
-      </c>
-      <c r="H14" s="23" t="inlineStr">
-        <is>
-          <t>84 - 1 - TB</t>
-        </is>
-      </c>
-      <c r="I14" s="23" t="inlineStr">
-        <is>
-          <t>19/08/2026 10:17</t>
-        </is>
-      </c>
-      <c r="J14" s="23" t="inlineStr">
-        <is>
-          <t>19/08/2026 10:23</t>
-        </is>
-      </c>
-      <c r="K14" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
     <row r="15">
-      <c r="A15" s="23" t="inlineStr">
-        <is>
-          <t>Claine Luisa Figueiredo Torraca</t>
-        </is>
-      </c>
-      <c r="B15" s="23" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C15" s="23" t="n">
-        <v>6</v>
-      </c>
-      <c r="D15" s="24" t="inlineStr">
-        <is>
-          <t>17019193</t>
-        </is>
-      </c>
-      <c r="E15" s="23" t="inlineStr">
-        <is>
-          <t>449 - ÁREA C RESIDENCIAL PONTA PORÃ 1</t>
-        </is>
-      </c>
-      <c r="F15" s="23" t="inlineStr">
-        <is>
-          <t>Q030</t>
-        </is>
-      </c>
-      <c r="G15" s="23" t="inlineStr">
-        <is>
-          <t>Rua CARAMBOLEIRA</t>
-        </is>
-      </c>
-      <c r="H15" s="23" t="inlineStr">
-        <is>
-          <t>106 - 1 - TB</t>
-        </is>
-      </c>
-      <c r="I15" s="23" t="inlineStr">
-        <is>
-          <t>19/08/2026 14:12</t>
-        </is>
-      </c>
-      <c r="J15" s="23" t="inlineStr">
-        <is>
-          <t>19/08/2026 14:12</t>
-        </is>
-      </c>
-      <c r="K15" s="23" t="inlineStr"/>
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>LEGENDA — CLASSIFICAÇÃO (baseada em % de Visitas Rápidas)</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="23" t="inlineStr">
-        <is>
-          <t>Claine Luisa Figueiredo Torraca</t>
-        </is>
-      </c>
-      <c r="B16" s="23" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C16" s="23" t="n">
-        <v>6</v>
-      </c>
-      <c r="D16" s="24" t="inlineStr">
-        <is>
-          <t>17019194</t>
-        </is>
-      </c>
-      <c r="E16" s="23" t="inlineStr">
-        <is>
-          <t>449 - ÁREA C RESIDENCIAL PONTA PORÃ 1</t>
-        </is>
-      </c>
-      <c r="F16" s="23" t="inlineStr">
-        <is>
-          <t>Q030</t>
-        </is>
-      </c>
-      <c r="G16" s="23" t="inlineStr">
-        <is>
-          <t>Rua CARAMBOLEIRA</t>
-        </is>
-      </c>
-      <c r="H16" s="23" t="inlineStr">
-        <is>
-          <t>106 - 1 - TB</t>
-        </is>
-      </c>
-      <c r="I16" s="23" t="inlineStr">
-        <is>
-          <t>19/08/2026 14:12</t>
-        </is>
-      </c>
-      <c r="J16" s="23" t="inlineStr">
-        <is>
-          <t>19/08/2026 14:18</t>
-        </is>
-      </c>
-      <c r="K16" s="23" t="n">
-        <v>0</v>
-      </c>
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>🟢 NORMAL</t>
+        </is>
+      </c>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>% Rápidas até 10%</t>
+        </is>
+      </c>
+      <c r="C16" s="10" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="23" t="inlineStr">
-        <is>
-          <t>Claine Luisa Figueiredo Torraca</t>
-        </is>
-      </c>
-      <c r="B17" s="23" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C17" s="23" t="n">
-        <v>7</v>
-      </c>
-      <c r="D17" s="24" t="inlineStr">
-        <is>
-          <t>17019196</t>
-        </is>
-      </c>
-      <c r="E17" s="23" t="inlineStr">
-        <is>
-          <t>449 - ÁREA C RESIDENCIAL PONTA PORÃ 1</t>
-        </is>
-      </c>
-      <c r="F17" s="23" t="inlineStr">
-        <is>
-          <t>Q030</t>
-        </is>
-      </c>
-      <c r="G17" s="23" t="inlineStr">
-        <is>
-          <t>Rua AMEIXEIRA</t>
-        </is>
-      </c>
-      <c r="H17" s="23" t="inlineStr">
-        <is>
-          <t>106 - 2 - TB</t>
-        </is>
-      </c>
-      <c r="I17" s="23" t="inlineStr">
-        <is>
-          <t>19/08/2026 14:18</t>
-        </is>
-      </c>
-      <c r="J17" s="23" t="inlineStr">
-        <is>
-          <t>19/08/2026 14:24</t>
-        </is>
-      </c>
-      <c r="K17" s="23" t="inlineStr"/>
+      <c r="A17" s="11" t="inlineStr">
+        <is>
+          <t>🟡 ATENÇÃO</t>
+        </is>
+      </c>
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>% Rápidas entre 11% e 20%</t>
+        </is>
+      </c>
+      <c r="C17" s="10" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="23" t="inlineStr">
-        <is>
-          <t>Claine Luisa Figueiredo Torraca</t>
-        </is>
-      </c>
-      <c r="B18" s="23" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C18" s="23" t="n">
-        <v>7</v>
-      </c>
-      <c r="D18" s="24" t="inlineStr">
-        <is>
-          <t>17019195</t>
-        </is>
-      </c>
-      <c r="E18" s="23" t="inlineStr">
-        <is>
-          <t>449 - ÁREA C RESIDENCIAL PONTA PORÃ 1</t>
-        </is>
-      </c>
-      <c r="F18" s="23" t="inlineStr">
-        <is>
-          <t>Q030</t>
-        </is>
-      </c>
-      <c r="G18" s="23" t="inlineStr">
-        <is>
-          <t>Rua AMEIXEIRA</t>
-        </is>
-      </c>
-      <c r="H18" s="23" t="inlineStr">
-        <is>
-          <t>106 - 2 - TB</t>
-        </is>
-      </c>
-      <c r="I18" s="23" t="inlineStr">
-        <is>
-          <t>19/08/2026 14:18</t>
-        </is>
-      </c>
-      <c r="J18" s="23" t="inlineStr">
-        <is>
-          <t>19/08/2026 14:18</t>
-        </is>
-      </c>
-      <c r="K18" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="23" t="inlineStr">
-        <is>
-          <t>Claine Luisa Figueiredo Torraca</t>
-        </is>
-      </c>
-      <c r="B19" s="23" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C19" s="23" t="n">
-        <v>8</v>
-      </c>
-      <c r="D19" s="24" t="inlineStr">
-        <is>
-          <t>17019200</t>
-        </is>
-      </c>
-      <c r="E19" s="23" t="inlineStr">
-        <is>
-          <t>449 - ÁREA C RESIDENCIAL PONTA PORÃ 1</t>
-        </is>
-      </c>
-      <c r="F19" s="23" t="inlineStr">
-        <is>
-          <t>Q030</t>
-        </is>
-      </c>
-      <c r="G19" s="23" t="inlineStr">
-        <is>
-          <t>Rua AMEIXEIRA</t>
-        </is>
-      </c>
-      <c r="H19" s="23" t="inlineStr">
-        <is>
-          <t>55 - 1 - TB</t>
-        </is>
-      </c>
-      <c r="I19" s="23" t="inlineStr">
-        <is>
-          <t>19/08/2026 14:33</t>
-        </is>
-      </c>
-      <c r="J19" s="23" t="inlineStr">
-        <is>
-          <t>19/08/2026 14:33</t>
-        </is>
-      </c>
-      <c r="K19" s="23" t="inlineStr"/>
+      <c r="A18" s="12" t="inlineStr">
+        <is>
+          <t>🔴 CRÍTICO</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>% Rápidas acima de 20%</t>
+        </is>
+      </c>
+      <c r="C18" s="10" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="23" t="inlineStr">
-        <is>
-          <t>Claine Luisa Figueiredo Torraca</t>
-        </is>
-      </c>
-      <c r="B20" s="23" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C20" s="23" t="n">
-        <v>8</v>
-      </c>
-      <c r="D20" s="24" t="inlineStr">
-        <is>
-          <t>17019201</t>
-        </is>
-      </c>
-      <c r="E20" s="23" t="inlineStr">
-        <is>
-          <t>449 - ÁREA C RESIDENCIAL PONTA PORÃ 1</t>
-        </is>
-      </c>
-      <c r="F20" s="23" t="inlineStr">
-        <is>
-          <t>Q030</t>
-        </is>
-      </c>
-      <c r="G20" s="23" t="inlineStr">
-        <is>
-          <t>Rua AMEIXEIRA</t>
-        </is>
-      </c>
-      <c r="H20" s="23" t="inlineStr">
-        <is>
-          <t>55 - 1 - TB</t>
-        </is>
-      </c>
-      <c r="I20" s="23" t="inlineStr">
-        <is>
-          <t>19/08/2026 14:33</t>
-        </is>
-      </c>
-      <c r="J20" s="23" t="inlineStr">
-        <is>
-          <t>19/08/2026 14:38</t>
-        </is>
-      </c>
-      <c r="K20" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="23" t="inlineStr">
-        <is>
-          <t>Claine Luisa Figueiredo Torraca</t>
-        </is>
-      </c>
-      <c r="B21" s="23" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C21" s="23" t="n">
-        <v>9</v>
-      </c>
-      <c r="D21" s="24" t="inlineStr">
-        <is>
-          <t>17048102</t>
-        </is>
-      </c>
-      <c r="E21" s="23" t="inlineStr">
-        <is>
-          <t>429 - COOPHA FRONTEIRA</t>
-        </is>
-      </c>
-      <c r="F21" s="23" t="inlineStr">
-        <is>
-          <t>Q004</t>
-        </is>
-      </c>
-      <c r="G21" s="23" t="inlineStr">
-        <is>
-          <t>Rua NOGUEIRA</t>
-        </is>
-      </c>
-      <c r="H21" s="23" t="inlineStr">
-        <is>
-          <t>669 - 3 - TB</t>
-        </is>
-      </c>
-      <c r="I21" s="23" t="inlineStr">
-        <is>
-          <t>20/08/2026 13:35</t>
-        </is>
-      </c>
-      <c r="J21" s="23" t="inlineStr">
-        <is>
-          <t>20/08/2026 13:35</t>
-        </is>
-      </c>
-      <c r="K21" s="23" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="23" t="inlineStr">
-        <is>
-          <t>Claine Luisa Figueiredo Torraca</t>
-        </is>
-      </c>
-      <c r="B22" s="23" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C22" s="23" t="n">
-        <v>9</v>
-      </c>
-      <c r="D22" s="24" t="inlineStr">
-        <is>
-          <t>17048103</t>
-        </is>
-      </c>
-      <c r="E22" s="23" t="inlineStr">
-        <is>
-          <t>429 - COOPHA FRONTEIRA</t>
-        </is>
-      </c>
-      <c r="F22" s="23" t="inlineStr">
-        <is>
-          <t>Q004</t>
-        </is>
-      </c>
-      <c r="G22" s="23" t="inlineStr">
-        <is>
-          <t>Rua NOGUEIRA</t>
-        </is>
-      </c>
-      <c r="H22" s="23" t="inlineStr">
-        <is>
-          <t>669 - 3 - TB</t>
-        </is>
-      </c>
-      <c r="I22" s="23" t="inlineStr">
-        <is>
-          <t>20/08/2026 13:35</t>
-        </is>
-      </c>
-      <c r="J22" s="23" t="inlineStr">
-        <is>
-          <t>20/08/2026 13:41</t>
-        </is>
-      </c>
-      <c r="K22" s="23" t="n">
-        <v>0</v>
+      <c r="A20" s="13" t="inlineStr">
+        <is>
+          <t>⚠️ SEQUÊNCIA SUSPEITA</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="45" customHeight="1">
+      <c r="A21" s="14" t="inlineStr">
+        <is>
+          <t>Duas ou mais visitas consecutivas do mesmo agente registradas no MESMO MINUTO de chegada são marcadas como suspeitas (o e-Visita não registra segundos, então o critério de negócio de 50s de diferença equivale, na prática, a 'mesmo minuto') — sugere lançamento em lote no sistema, não visita real de campo. Colunas: 'Visitas em Sequência Suspeita' (total de visitas envolvidas) e 'Maior Sequência Suspeita' (maior número de visitas seguidas nessa condição). Na aba 'Visitas Suspeitas', a coluna 'Diferença p/ Anterior (s)*' fica em branco quando o alerta da linha veio do par com a visita SEGUINTE (não da anterior).</t>
+        </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="23" t="inlineStr">
-        <is>
-          <t>Claine Luisa Figueiredo Torraca</t>
-        </is>
-      </c>
-      <c r="B23" s="23" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C23" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="D23" s="24" t="inlineStr">
-        <is>
-          <t>17078203</t>
-        </is>
-      </c>
-      <c r="E23" s="23" t="inlineStr">
-        <is>
-          <t>429 - COOPHA FRONTEIRA</t>
-        </is>
-      </c>
-      <c r="F23" s="23" t="inlineStr">
-        <is>
-          <t>Q006</t>
-        </is>
-      </c>
-      <c r="G23" s="23" t="inlineStr">
-        <is>
-          <t>Rua GUARANTA</t>
-        </is>
-      </c>
-      <c r="H23" s="23" t="inlineStr">
-        <is>
-          <t>677 - 1 - TB</t>
-        </is>
-      </c>
-      <c r="I23" s="23" t="inlineStr">
-        <is>
-          <t>21/08/2026 09:12</t>
-        </is>
-      </c>
-      <c r="J23" s="23" t="inlineStr">
-        <is>
-          <t>21/08/2026 09:12</t>
-        </is>
-      </c>
-      <c r="K23" s="23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="23" t="inlineStr">
-        <is>
-          <t>Claine Luisa Figueiredo Torraca</t>
-        </is>
-      </c>
-      <c r="B24" s="23" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C24" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="D24" s="24" t="inlineStr">
-        <is>
-          <t>17078204</t>
-        </is>
-      </c>
-      <c r="E24" s="23" t="inlineStr">
-        <is>
-          <t>429 - COOPHA FRONTEIRA</t>
-        </is>
-      </c>
-      <c r="F24" s="23" t="inlineStr">
-        <is>
-          <t>Q006</t>
-        </is>
-      </c>
-      <c r="G24" s="23" t="inlineStr">
-        <is>
-          <t>Rua GUARANTA</t>
-        </is>
-      </c>
-      <c r="H24" s="23" t="inlineStr">
-        <is>
-          <t>677 - 1 - TB</t>
-        </is>
-      </c>
-      <c r="I24" s="23" t="inlineStr">
-        <is>
-          <t>21/08/2026 09:12</t>
-        </is>
-      </c>
-      <c r="J24" s="23" t="inlineStr">
-        <is>
-          <t>21/08/2026 09:18</t>
-        </is>
-      </c>
-      <c r="K24" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="23" t="inlineStr">
-        <is>
-          <t>Claine Luisa Figueiredo Torraca</t>
-        </is>
-      </c>
-      <c r="B25" s="23" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C25" s="23" t="n">
-        <v>11</v>
-      </c>
-      <c r="D25" s="24" t="inlineStr">
-        <is>
-          <t>17078208</t>
-        </is>
-      </c>
-      <c r="E25" s="23" t="inlineStr">
-        <is>
-          <t>429 - COOPHA FRONTEIRA</t>
-        </is>
-      </c>
-      <c r="F25" s="23" t="inlineStr">
-        <is>
-          <t>Q006</t>
-        </is>
-      </c>
-      <c r="G25" s="23" t="inlineStr">
-        <is>
-          <t>Rua GUARANTA</t>
-        </is>
-      </c>
-      <c r="H25" s="23" t="inlineStr">
-        <is>
-          <t>617 - 1 - TB</t>
-        </is>
-      </c>
-      <c r="I25" s="23" t="inlineStr">
-        <is>
-          <t>21/08/2026 09:21</t>
-        </is>
-      </c>
-      <c r="J25" s="23" t="inlineStr">
-        <is>
-          <t>21/08/2026 09:21</t>
-        </is>
-      </c>
-      <c r="K25" s="23" t="inlineStr"/>
+      <c r="A23" s="15" t="inlineStr">
+        <is>
+          <t>🍽️ VISITAS NO HORÁRIO DE ALMOÇO</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="70" customHeight="1">
+      <c r="A24" s="14" t="inlineStr">
+        <is>
+          <t>Coluna 'Visitas no Almoço (11h15-12h45)' conta as visitas com chegada registrada nesse intervalo — o horário oficial de almoço é 11h15 às 12h45, JÁ COM 15 MINUTOS DE TOLERÂNCIA em cada borda (visitas entre 11h-11h15 ou 12h45-13h não são tratadas como violação, só como 'fora do expediente' genérico) — use para checar se o agente está trabalhando no horário de almoço ou se há erro de lançamento. Essas visitas ficam de fora do cálculo de 'Início/Fim Manhã' e 'Início/Fim Tarde', que usam a primeira chegada e a última saída de cada dia (não a média de todos os horários), para refletir melhor o início e o fim reais do expediente.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" s="23" t="inlineStr">
-        <is>
-          <t>Claine Luisa Figueiredo Torraca</t>
-        </is>
-      </c>
-      <c r="B26" s="23" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C26" s="23" t="n">
-        <v>11</v>
-      </c>
-      <c r="D26" s="24" t="inlineStr">
-        <is>
-          <t>17078209</t>
-        </is>
-      </c>
-      <c r="E26" s="23" t="inlineStr">
-        <is>
-          <t>429 - COOPHA FRONTEIRA</t>
-        </is>
-      </c>
-      <c r="F26" s="23" t="inlineStr">
-        <is>
-          <t>Q006</t>
-        </is>
-      </c>
-      <c r="G26" s="23" t="inlineStr">
-        <is>
-          <t>Rua GUARANTA</t>
-        </is>
-      </c>
-      <c r="H26" s="23" t="inlineStr">
-        <is>
-          <t>617 - 1 - TB</t>
-        </is>
-      </c>
-      <c r="I26" s="23" t="inlineStr">
-        <is>
-          <t>21/08/2026 09:21</t>
-        </is>
-      </c>
-      <c r="J26" s="23" t="inlineStr">
-        <is>
-          <t>21/08/2026 09:27</t>
-        </is>
-      </c>
-      <c r="K26" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="23" t="inlineStr">
-        <is>
-          <t>Claine Luisa Figueiredo Torraca</t>
-        </is>
-      </c>
-      <c r="B27" s="23" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C27" s="23" t="n">
-        <v>12</v>
-      </c>
-      <c r="D27" s="24" t="inlineStr">
-        <is>
-          <t>17078217</t>
-        </is>
-      </c>
-      <c r="E27" s="23" t="inlineStr">
-        <is>
-          <t>429 - COOPHA FRONTEIRA</t>
-        </is>
-      </c>
-      <c r="F27" s="23" t="inlineStr">
-        <is>
-          <t>Q006</t>
-        </is>
-      </c>
-      <c r="G27" s="23" t="inlineStr">
-        <is>
-          <t>Rua XAVANTES</t>
-        </is>
-      </c>
-      <c r="H27" s="23" t="inlineStr">
-        <is>
-          <t>567 - 2 - TB</t>
-        </is>
-      </c>
-      <c r="I27" s="23" t="inlineStr">
-        <is>
-          <t>21/08/2026 09:50</t>
-        </is>
-      </c>
-      <c r="J27" s="23" t="inlineStr">
-        <is>
-          <t>21/08/2026 09:55</t>
-        </is>
-      </c>
-      <c r="K27" s="23" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="23" t="inlineStr">
-        <is>
-          <t>Claine Luisa Figueiredo Torraca</t>
-        </is>
-      </c>
-      <c r="B28" s="23" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C28" s="23" t="n">
-        <v>12</v>
-      </c>
-      <c r="D28" s="24" t="inlineStr">
-        <is>
-          <t>17078216</t>
-        </is>
-      </c>
-      <c r="E28" s="23" t="inlineStr">
-        <is>
-          <t>429 - COOPHA FRONTEIRA</t>
-        </is>
-      </c>
-      <c r="F28" s="23" t="inlineStr">
-        <is>
-          <t>Q006</t>
-        </is>
-      </c>
-      <c r="G28" s="23" t="inlineStr">
-        <is>
-          <t>Rua XAVANTES</t>
-        </is>
-      </c>
-      <c r="H28" s="23" t="inlineStr">
-        <is>
-          <t>567 - 2 - TB</t>
-        </is>
-      </c>
-      <c r="I28" s="23" t="inlineStr">
-        <is>
-          <t>21/08/2026 09:50</t>
-        </is>
-      </c>
-      <c r="J28" s="23" t="inlineStr">
-        <is>
-          <t>21/08/2026 09:50</t>
-        </is>
-      </c>
-      <c r="K28" s="23" t="n">
-        <v>0</v>
+      <c r="A26" s="16" t="inlineStr">
+        <is>
+          <t>💰 HORAS TRABALHADAS, HORAS ÚTEIS E CUSTO DA HORA ÚTIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="60" customHeight="1">
+      <c r="A27" s="14" t="inlineStr">
+        <is>
+          <t>'Horas Trabalhadas' = jornada total do dia (primeira chegada até a última saída), descontando a sobreposição com o horário de almoço — depois tira-se a média entre os dias/semanas trabalhados, 'Horas Úteis' = soma das durações de visita no dia (tempo realmente dentro de imóveis), sem contar deslocamento entre visitas, 'Custo Hora Útil' = salário mensal do agente (R$ 4863,00, equivalente a 3 salários mínimos federais) dividido pelas horas úteis mensais estimadas (Média Horas Úteis/Dia × 22 dias úteis/mês). Quanto menos tempo o agente passa efetivamente em visita por dia, mais caro fica o custo por hora útil.</t>
+        </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="23" t="inlineStr">
-        <is>
-          <t>Emidio Rainer Vilhalba</t>
-        </is>
-      </c>
-      <c r="B29" s="23" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C29" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="D29" s="24" t="inlineStr">
-        <is>
-          <t>16959229</t>
-        </is>
-      </c>
-      <c r="E29" s="23" t="inlineStr">
-        <is>
-          <t>430 - VILA RENÔ</t>
-        </is>
-      </c>
-      <c r="F29" s="23" t="inlineStr">
-        <is>
-          <t>Q034</t>
-        </is>
-      </c>
-      <c r="G29" s="23" t="inlineStr">
-        <is>
-          <t>Avenida URUMBELA</t>
-        </is>
-      </c>
-      <c r="H29" s="23" t="inlineStr">
-        <is>
-          <t>890 - 10 - R</t>
-        </is>
-      </c>
-      <c r="I29" s="23" t="inlineStr">
-        <is>
-          <t>18/08/2026 09:50</t>
-        </is>
-      </c>
-      <c r="J29" s="23" t="inlineStr">
-        <is>
-          <t>18/08/2026 09:51</t>
-        </is>
-      </c>
-      <c r="K29" s="23" t="inlineStr"/>
+      <c r="A29" s="17" t="inlineStr">
+        <is>
+          <t>ℹ️ A lista detalhada de visitas duplicadas (com endereço) está na aba 'Visitas Duplicadas' — use-a para localizar e excluir os registros repetidos.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" s="23" t="inlineStr">
-        <is>
-          <t>Emidio Rainer Vilhalba</t>
-        </is>
-      </c>
-      <c r="B30" s="23" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C30" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="D30" s="24" t="inlineStr">
-        <is>
-          <t>16959228</t>
-        </is>
-      </c>
-      <c r="E30" s="23" t="inlineStr">
-        <is>
-          <t>430 - VILA RENÔ</t>
-        </is>
-      </c>
-      <c r="F30" s="23" t="inlineStr">
-        <is>
-          <t>Q034</t>
-        </is>
-      </c>
-      <c r="G30" s="23" t="inlineStr">
-        <is>
-          <t>Avenida URUMBELA</t>
-        </is>
-      </c>
-      <c r="H30" s="23" t="inlineStr">
-        <is>
-          <t>890 - 9 - C</t>
-        </is>
-      </c>
-      <c r="I30" s="23" t="inlineStr">
-        <is>
-          <t>18/08/2026 09:50</t>
-        </is>
-      </c>
-      <c r="J30" s="23" t="inlineStr">
-        <is>
-          <t>18/08/2026 09:50</t>
-        </is>
-      </c>
-      <c r="K30" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="7" t="inlineStr">
-        <is>
-          <t>LEGENDA — CLASSIFICAÇÃO (baseada em % de Visitas Rápidas)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="8" t="inlineStr">
-        <is>
-          <t>🟢 NORMAL</t>
-        </is>
-      </c>
-      <c r="B34" s="9" t="inlineStr">
-        <is>
-          <t>% Rápidas até 10%</t>
-        </is>
-      </c>
-      <c r="C34" s="10" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="11" t="inlineStr">
-        <is>
-          <t>🟡 ATENÇÃO</t>
-        </is>
-      </c>
-      <c r="B35" s="9" t="inlineStr">
-        <is>
-          <t>% Rápidas entre 11% e 20%</t>
-        </is>
-      </c>
-      <c r="C35" s="10" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="12" t="inlineStr">
-        <is>
-          <t>🔴 CRÍTICO</t>
-        </is>
-      </c>
-      <c r="B36" s="9" t="inlineStr">
-        <is>
-          <t>% Rápidas acima de 20%</t>
-        </is>
-      </c>
-      <c r="C36" s="10" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="13" t="inlineStr">
-        <is>
-          <t>⚠️ SEQUÊNCIA SUSPEITA</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="45" customHeight="1">
-      <c r="A39" s="14" t="inlineStr">
-        <is>
-          <t>Duas ou mais visitas consecutivas do mesmo agente registradas no MESMO MINUTO de chegada são marcadas como suspeitas (o e-Visita não registra segundos, então o critério de negócio de 50s de diferença equivale, na prática, a 'mesmo minuto') — sugere lançamento em lote no sistema, não visita real de campo. Colunas: 'Visitas em Sequência Suspeita' (total de visitas envolvidas) e 'Maior Sequência Suspeita' (maior número de visitas seguidas nessa condição). Na aba 'Visitas Suspeitas', a coluna 'Diferença p/ Anterior (s)*' fica em branco quando o alerta da linha veio do par com a visita SEGUINTE (não da anterior).</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="15" t="inlineStr">
-        <is>
-          <t>🍽️ VISITAS NO HORÁRIO DE ALMOÇO</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="70" customHeight="1">
-      <c r="A42" s="14" t="inlineStr">
-        <is>
-          <t>Coluna 'Visitas no Almoço (11h15-12h45)' conta as visitas com chegada registrada nesse intervalo — o horário oficial de almoço é 11h15 às 12h45, JÁ COM 15 MINUTOS DE TOLERÂNCIA em cada borda (visitas entre 11h-11h15 ou 12h45-13h não são tratadas como violação, só como 'fora do expediente' genérico) — use para checar se o agente está trabalhando no horário de almoço ou se há erro de lançamento. Essas visitas ficam de fora do cálculo de 'Início/Fim Manhã' e 'Início/Fim Tarde', que usam a primeira chegada e a última saída de cada dia (não a média de todos os horários), para refletir melhor o início e o fim reais do expediente.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="16" t="inlineStr">
-        <is>
-          <t>💰 HORAS TRABALHADAS, HORAS ÚTEIS E CUSTO DA HORA ÚTIL</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="60" customHeight="1">
-      <c r="A45" s="14" t="inlineStr">
-        <is>
-          <t>'Horas Trabalhadas' = jornada total do dia (primeira chegada até a última saída), descontando a sobreposição com o horário de almoço — depois tira-se a média entre os dias/semanas trabalhados, 'Horas Úteis' = soma das durações de visita no dia (tempo realmente dentro de imóveis), sem contar deslocamento entre visitas, 'Custo Hora Útil' = salário mensal do agente (R$ 4863,00, equivalente a 3 salários mínimos federais) dividido pelas horas úteis mensais estimadas (Média Horas Úteis/Dia × 22 dias úteis/mês). Quanto menos tempo o agente passa efetivamente em visita por dia, mais caro fica o custo por hora útil.</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="17" t="inlineStr">
-        <is>
-          <t>ℹ️ A lista detalhada de visitas duplicadas (com endereço) está na aba 'Visitas Duplicadas' — use-a para localizar e excluir os registros repetidos.</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="17" t="inlineStr">
+      <c r="A30" s="17" t="inlineStr">
         <is>
           <t>ℹ️ Visitas com duração NEGATIVA (saída antes da chegada — provável bug do sistema) foram excluídas do cálculo de Média/Mediana e estão detalhadas na aba 'Visitas Negativas', para investigação junto ao suporte do e-Visita.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:K30"/>
+  <autoFilter ref="A2:K12"/>
   <mergeCells count="13">
-    <mergeCell ref="A42:C42"/>
-    <mergeCell ref="A41:C41"/>
-    <mergeCell ref="A33:C33"/>
-    <mergeCell ref="A44:C44"/>
-    <mergeCell ref="A47:C47"/>
-    <mergeCell ref="A45:C45"/>
-    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="A15:C15"/>
     <mergeCell ref="A1:K1"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="A39:C39"/>
-    <mergeCell ref="A48:C48"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="A38:C38"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="A29:C29"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId1"/>
@@ -24693,24 +22803,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D10" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D11" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D12" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D13" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D14" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D15" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D16" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D17" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D18" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D19" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D20" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D21" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D22" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D23" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D24" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D25" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D26" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D27" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D28" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D29" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D30" r:id="rId28"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/historico/semana_320.xlsx
+++ b/data/historico/semana_320.xlsx
@@ -5215,7 +5215,7 @@
       </c>
       <c r="B6" s="38" t="inlineStr">
         <is>
-          <t>25/08/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
       <c r="C6" s="38" t="inlineStr">
@@ -5237,7 +5237,7 @@
       </c>
       <c r="B7" s="38" t="inlineStr">
         <is>
-          <t>25/08/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
       <c r="C7" s="38" t="inlineStr">
@@ -5259,7 +5259,7 @@
       </c>
       <c r="B8" s="38" t="inlineStr">
         <is>
-          <t>25/08/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
       <c r="C8" s="38" t="inlineStr">

--- a/data/historico/semana_320.xlsx
+++ b/data/historico/semana_320.xlsx
@@ -23619,7 +23619,7 @@
     <row r="13">
       <c r="A13" s="27" t="inlineStr">
         <is>
-          <t>Wagner Tarlei Gomes</t>
+          <t>Gabriel Alan de Oliveira Martins</t>
         </is>
       </c>
       <c r="B13" s="27" t="inlineStr">
@@ -23629,37 +23629,37 @@
       </c>
       <c r="C13" s="28" t="inlineStr">
         <is>
-          <t>17076987</t>
+          <t>16990895</t>
         </is>
       </c>
       <c r="D13" s="27" t="inlineStr">
         <is>
-          <t>400 - JULIA CARDINAL</t>
+          <t>410 - SALGADO FILHO</t>
         </is>
       </c>
       <c r="E13" s="27" t="inlineStr">
         <is>
-          <t>Q012</t>
+          <t>Q008</t>
         </is>
       </c>
       <c r="F13" s="27" t="inlineStr">
         <is>
-          <t>Rua Anselmo Soares</t>
+          <t>Rua TIETE</t>
         </is>
       </c>
       <c r="G13" s="27" t="inlineStr">
         <is>
-          <t>700 - 9 - TB</t>
+          <t>513 - R</t>
         </is>
       </c>
       <c r="H13" s="27" t="inlineStr">
         <is>
-          <t>19/08/2026 14:12</t>
+          <t>17/08/2026 09:24</t>
         </is>
       </c>
       <c r="I13" s="27" t="inlineStr">
         <is>
-          <t>19/08/2026 14:39</t>
+          <t>17/08/2026 09:51</t>
         </is>
       </c>
       <c r="J13" s="27" t="n">
@@ -23669,7 +23669,7 @@
     <row r="14">
       <c r="A14" s="27" t="inlineStr">
         <is>
-          <t>Gabriel Alan de Oliveira Martins</t>
+          <t>Wagner Tarlei Gomes</t>
         </is>
       </c>
       <c r="B14" s="27" t="inlineStr">
@@ -23679,37 +23679,37 @@
       </c>
       <c r="C14" s="28" t="inlineStr">
         <is>
-          <t>16990895</t>
+          <t>17076987</t>
         </is>
       </c>
       <c r="D14" s="27" t="inlineStr">
         <is>
-          <t>410 - SALGADO FILHO</t>
+          <t>400 - JULIA CARDINAL</t>
         </is>
       </c>
       <c r="E14" s="27" t="inlineStr">
         <is>
-          <t>Q008</t>
+          <t>Q012</t>
         </is>
       </c>
       <c r="F14" s="27" t="inlineStr">
         <is>
-          <t>Rua TIETE</t>
+          <t>Rua Anselmo Soares</t>
         </is>
       </c>
       <c r="G14" s="27" t="inlineStr">
         <is>
-          <t>513 - R</t>
+          <t>700 - 9 - TB</t>
         </is>
       </c>
       <c r="H14" s="27" t="inlineStr">
         <is>
-          <t>17/08/2026 09:24</t>
+          <t>19/08/2026 14:12</t>
         </is>
       </c>
       <c r="I14" s="27" t="inlineStr">
         <is>
-          <t>17/08/2026 09:51</t>
+          <t>19/08/2026 14:39</t>
         </is>
       </c>
       <c r="J14" s="27" t="n">
@@ -23719,7 +23719,7 @@
     <row r="15">
       <c r="A15" s="27" t="inlineStr">
         <is>
-          <t>Gabriel Alan de Oliveira Martins</t>
+          <t>Wagner Tarlei Gomes</t>
         </is>
       </c>
       <c r="B15" s="27" t="inlineStr">
@@ -23729,37 +23729,37 @@
       </c>
       <c r="C15" s="28" t="inlineStr">
         <is>
-          <t>17026385</t>
+          <t>17076990</t>
         </is>
       </c>
       <c r="D15" s="27" t="inlineStr">
         <is>
-          <t>401 - EMÍLIO DIAS BRANDÃO</t>
+          <t>400 - JULIA CARDINAL</t>
         </is>
       </c>
       <c r="E15" s="27" t="inlineStr">
         <is>
-          <t>Q013</t>
+          <t>Q012</t>
         </is>
       </c>
       <c r="F15" s="27" t="inlineStr">
         <is>
-          <t>Rua JABAQUARA</t>
+          <t>Rua Anselmo Soares</t>
         </is>
       </c>
       <c r="G15" s="27" t="inlineStr">
         <is>
-          <t>26 - 2 - OU</t>
+          <t>28 - 2 - TB</t>
         </is>
       </c>
       <c r="H15" s="27" t="inlineStr">
         <is>
-          <t>19/08/2026 09:27</t>
+          <t>19/08/2026 15:03</t>
         </is>
       </c>
       <c r="I15" s="27" t="inlineStr">
         <is>
-          <t>19/08/2026 09:53</t>
+          <t>19/08/2026 15:29</t>
         </is>
       </c>
       <c r="J15" s="27" t="n">
@@ -23769,47 +23769,47 @@
     <row r="16">
       <c r="A16" s="27" t="inlineStr">
         <is>
-          <t>Wagner Tarlei Gomes</t>
+          <t>Fabiana de Figueredo Vieira</t>
         </is>
       </c>
       <c r="B16" s="27" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="C16" s="28" t="inlineStr">
         <is>
-          <t>17076990</t>
+          <t>17027677</t>
         </is>
       </c>
       <c r="D16" s="27" t="inlineStr">
         <is>
-          <t>400 - JULIA CARDINAL</t>
+          <t>411 - JARDIM AEROPORTO</t>
         </is>
       </c>
       <c r="E16" s="27" t="inlineStr">
         <is>
-          <t>Q012</t>
+          <t>Q023</t>
         </is>
       </c>
       <c r="F16" s="27" t="inlineStr">
         <is>
-          <t>Rua Anselmo Soares</t>
+          <t>Rua SÃO JOÃO DEL REI</t>
         </is>
       </c>
       <c r="G16" s="27" t="inlineStr">
         <is>
-          <t>28 - 2 - TB</t>
+          <t>20 - R</t>
         </is>
       </c>
       <c r="H16" s="27" t="inlineStr">
         <is>
-          <t>19/08/2026 15:03</t>
+          <t>18/08/2026 10:24</t>
         </is>
       </c>
       <c r="I16" s="27" t="inlineStr">
         <is>
-          <t>19/08/2026 15:29</t>
+          <t>18/08/2026 10:50</t>
         </is>
       </c>
       <c r="J16" s="27" t="n">
@@ -23819,47 +23819,47 @@
     <row r="17">
       <c r="A17" s="27" t="inlineStr">
         <is>
-          <t>Fabiana de Figueredo Vieira</t>
+          <t>Gabriel Alan de Oliveira Martins</t>
         </is>
       </c>
       <c r="B17" s="27" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="C17" s="28" t="inlineStr">
         <is>
-          <t>17027677</t>
+          <t>17026385</t>
         </is>
       </c>
       <c r="D17" s="27" t="inlineStr">
         <is>
-          <t>411 - JARDIM AEROPORTO</t>
+          <t>401 - EMÍLIO DIAS BRANDÃO</t>
         </is>
       </c>
       <c r="E17" s="27" t="inlineStr">
         <is>
-          <t>Q023</t>
+          <t>Q013</t>
         </is>
       </c>
       <c r="F17" s="27" t="inlineStr">
         <is>
-          <t>Rua SÃO JOÃO DEL REI</t>
+          <t>Rua JABAQUARA</t>
         </is>
       </c>
       <c r="G17" s="27" t="inlineStr">
         <is>
-          <t>20 - R</t>
+          <t>26 - 2 - OU</t>
         </is>
       </c>
       <c r="H17" s="27" t="inlineStr">
         <is>
-          <t>18/08/2026 10:24</t>
+          <t>19/08/2026 09:27</t>
         </is>
       </c>
       <c r="I17" s="27" t="inlineStr">
         <is>
-          <t>18/08/2026 10:50</t>
+          <t>19/08/2026 09:53</t>
         </is>
       </c>
       <c r="J17" s="27" t="n">
@@ -23919,47 +23919,47 @@
     <row r="19">
       <c r="A19" s="27" t="inlineStr">
         <is>
-          <t>Gabriel Alan de Oliveira Martins</t>
+          <t>Miglidiane Maciel Ajala</t>
         </is>
       </c>
       <c r="B19" s="27" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 3</t>
         </is>
       </c>
       <c r="C19" s="28" t="inlineStr">
         <is>
-          <t>17076414</t>
+          <t>16986159</t>
         </is>
       </c>
       <c r="D19" s="27" t="inlineStr">
         <is>
-          <t>402 - JARDIM MARAMBAIA</t>
+          <t>425 - JARDIM ESTORIL</t>
         </is>
       </c>
       <c r="E19" s="27" t="inlineStr">
         <is>
-          <t>Q024</t>
+          <t>Q036</t>
         </is>
       </c>
       <c r="F19" s="27" t="inlineStr">
         <is>
-          <t>Rua WEIMAR TORRES</t>
+          <t>Avenida ADJALMA SALDANHA</t>
         </is>
       </c>
       <c r="G19" s="27" t="inlineStr">
         <is>
-          <t>774 - R</t>
+          <t>873 - R</t>
         </is>
       </c>
       <c r="H19" s="27" t="inlineStr">
         <is>
-          <t>21/08/2026 15:30</t>
+          <t>18/08/2026 13:15</t>
         </is>
       </c>
       <c r="I19" s="27" t="inlineStr">
         <is>
-          <t>21/08/2026 15:53</t>
+          <t>18/08/2026 13:38</t>
         </is>
       </c>
       <c r="J19" s="27" t="n">
@@ -23979,7 +23979,7 @@
       </c>
       <c r="C20" s="28" t="inlineStr">
         <is>
-          <t>16986159</t>
+          <t>17071087</t>
         </is>
       </c>
       <c r="D20" s="27" t="inlineStr">
@@ -23989,27 +23989,27 @@
       </c>
       <c r="E20" s="27" t="inlineStr">
         <is>
-          <t>Q036</t>
+          <t>Q042</t>
         </is>
       </c>
       <c r="F20" s="27" t="inlineStr">
         <is>
-          <t>Avenida ADJALMA SALDANHA</t>
+          <t>Rua POLICARPO DAVILA</t>
         </is>
       </c>
       <c r="G20" s="27" t="inlineStr">
         <is>
-          <t>873 - R</t>
+          <t>769 - R</t>
         </is>
       </c>
       <c r="H20" s="27" t="inlineStr">
         <is>
-          <t>18/08/2026 13:15</t>
+          <t>21/08/2026 14:34</t>
         </is>
       </c>
       <c r="I20" s="27" t="inlineStr">
         <is>
-          <t>18/08/2026 13:38</t>
+          <t>21/08/2026 14:57</t>
         </is>
       </c>
       <c r="J20" s="27" t="n">
@@ -24019,47 +24019,47 @@
     <row r="21">
       <c r="A21" s="27" t="inlineStr">
         <is>
-          <t>Miglidiane Maciel Ajala</t>
+          <t>Wagner Tarlei Gomes</t>
         </is>
       </c>
       <c r="B21" s="27" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="C21" s="28" t="inlineStr">
         <is>
-          <t>17071087</t>
+          <t>17077037</t>
         </is>
       </c>
       <c r="D21" s="27" t="inlineStr">
         <is>
-          <t>425 - JARDIM ESTORIL</t>
+          <t>400 - JULIA CARDINAL</t>
         </is>
       </c>
       <c r="E21" s="27" t="inlineStr">
         <is>
-          <t>Q042</t>
+          <t>Q024</t>
         </is>
       </c>
       <c r="F21" s="27" t="inlineStr">
         <is>
-          <t>Rua POLICARPO DAVILA</t>
+          <t>Rua INÁCIO SUBTIL OLIVEIRA</t>
         </is>
       </c>
       <c r="G21" s="27" t="inlineStr">
         <is>
-          <t>769 - R</t>
+          <t>517 - R</t>
         </is>
       </c>
       <c r="H21" s="27" t="inlineStr">
         <is>
-          <t>21/08/2026 14:34</t>
+          <t>21/08/2026 08:51</t>
         </is>
       </c>
       <c r="I21" s="27" t="inlineStr">
         <is>
-          <t>21/08/2026 14:57</t>
+          <t>21/08/2026 09:14</t>
         </is>
       </c>
       <c r="J21" s="27" t="n">
@@ -24069,7 +24069,7 @@
     <row r="22">
       <c r="A22" s="27" t="inlineStr">
         <is>
-          <t>Ana Gabriela Silva Garcete</t>
+          <t>Gabriel Alan de Oliveira Martins</t>
         </is>
       </c>
       <c r="B22" s="27" t="inlineStr">
@@ -24079,37 +24079,37 @@
       </c>
       <c r="C22" s="28" t="inlineStr">
         <is>
-          <t>16997935</t>
+          <t>17076414</t>
         </is>
       </c>
       <c r="D22" s="27" t="inlineStr">
         <is>
-          <t>401 - EMÍLIO DIAS BRANDÃO</t>
+          <t>402 - JARDIM MARAMBAIA</t>
         </is>
       </c>
       <c r="E22" s="27" t="inlineStr">
         <is>
-          <t>Q015</t>
+          <t>Q024</t>
         </is>
       </c>
       <c r="F22" s="27" t="inlineStr">
         <is>
-          <t>Rua CARLOS DRUMOND DE ANDRADE</t>
+          <t>Rua WEIMAR TORRES</t>
         </is>
       </c>
       <c r="G22" s="27" t="inlineStr">
         <is>
-          <t>1157 - R</t>
+          <t>774 - R</t>
         </is>
       </c>
       <c r="H22" s="27" t="inlineStr">
         <is>
-          <t>19/08/2026 09:04</t>
+          <t>21/08/2026 15:30</t>
         </is>
       </c>
       <c r="I22" s="27" t="inlineStr">
         <is>
-          <t>19/08/2026 09:27</t>
+          <t>21/08/2026 15:53</t>
         </is>
       </c>
       <c r="J22" s="27" t="n">
@@ -24119,7 +24119,7 @@
     <row r="23">
       <c r="A23" s="27" t="inlineStr">
         <is>
-          <t>Wagner Tarlei Gomes</t>
+          <t>Ana Gabriela Silva Garcete</t>
         </is>
       </c>
       <c r="B23" s="27" t="inlineStr">
@@ -24129,37 +24129,37 @@
       </c>
       <c r="C23" s="28" t="inlineStr">
         <is>
-          <t>17077037</t>
+          <t>16997935</t>
         </is>
       </c>
       <c r="D23" s="27" t="inlineStr">
         <is>
-          <t>400 - JULIA CARDINAL</t>
+          <t>401 - EMÍLIO DIAS BRANDÃO</t>
         </is>
       </c>
       <c r="E23" s="27" t="inlineStr">
         <is>
-          <t>Q024</t>
+          <t>Q015</t>
         </is>
       </c>
       <c r="F23" s="27" t="inlineStr">
         <is>
-          <t>Rua INÁCIO SUBTIL OLIVEIRA</t>
+          <t>Rua CARLOS DRUMOND DE ANDRADE</t>
         </is>
       </c>
       <c r="G23" s="27" t="inlineStr">
         <is>
-          <t>517 - R</t>
+          <t>1157 - R</t>
         </is>
       </c>
       <c r="H23" s="27" t="inlineStr">
         <is>
-          <t>21/08/2026 08:51</t>
+          <t>19/08/2026 09:04</t>
         </is>
       </c>
       <c r="I23" s="27" t="inlineStr">
         <is>
-          <t>21/08/2026 09:14</t>
+          <t>19/08/2026 09:27</t>
         </is>
       </c>
       <c r="J23" s="27" t="n">
@@ -24169,47 +24169,47 @@
     <row r="24">
       <c r="A24" s="27" t="inlineStr">
         <is>
-          <t>Silvina Regina de Souza Valiente</t>
+          <t>Cris Milene Cardenas da Silva</t>
         </is>
       </c>
       <c r="B24" s="27" t="inlineStr">
         <is>
-          <t>Equipe 4</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="C24" s="28" t="inlineStr">
         <is>
-          <t>17011667</t>
+          <t>17018827</t>
         </is>
       </c>
       <c r="D24" s="27" t="inlineStr">
         <is>
-          <t>434 - VILA AUREA</t>
+          <t>403 - JARDIM UNIVERSITARIO</t>
         </is>
       </c>
       <c r="E24" s="27" t="inlineStr">
         <is>
-          <t>Q034</t>
+          <t>Q016</t>
         </is>
       </c>
       <c r="F24" s="27" t="inlineStr">
         <is>
-          <t>Rua HONOROPOLIS</t>
+          <t>Rua DR HELIO BRANDAO</t>
         </is>
       </c>
       <c r="G24" s="27" t="inlineStr">
         <is>
-          <t>541 - R</t>
+          <t>227 - C</t>
         </is>
       </c>
       <c r="H24" s="27" t="inlineStr">
         <is>
-          <t>19/08/2026 08:55</t>
+          <t>19/08/2026 08:44</t>
         </is>
       </c>
       <c r="I24" s="27" t="inlineStr">
         <is>
-          <t>19/08/2026 09:17</t>
+          <t>19/08/2026 09:06</t>
         </is>
       </c>
       <c r="J24" s="27" t="n">
@@ -24219,47 +24219,47 @@
     <row r="25">
       <c r="A25" s="27" t="inlineStr">
         <is>
-          <t>Cris Milene Cardenas da Silva</t>
+          <t>Silvina Regina de Souza Valiente</t>
         </is>
       </c>
       <c r="B25" s="27" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="C25" s="28" t="inlineStr">
         <is>
-          <t>17018827</t>
+          <t>17011667</t>
         </is>
       </c>
       <c r="D25" s="27" t="inlineStr">
         <is>
-          <t>403 - JARDIM UNIVERSITARIO</t>
+          <t>434 - VILA AUREA</t>
         </is>
       </c>
       <c r="E25" s="27" t="inlineStr">
         <is>
-          <t>Q016</t>
+          <t>Q034</t>
         </is>
       </c>
       <c r="F25" s="27" t="inlineStr">
         <is>
-          <t>Rua DR HELIO BRANDAO</t>
+          <t>Rua HONOROPOLIS</t>
         </is>
       </c>
       <c r="G25" s="27" t="inlineStr">
         <is>
-          <t>227 - C</t>
+          <t>541 - R</t>
         </is>
       </c>
       <c r="H25" s="27" t="inlineStr">
         <is>
-          <t>19/08/2026 08:44</t>
+          <t>19/08/2026 08:55</t>
         </is>
       </c>
       <c r="I25" s="27" t="inlineStr">
         <is>
-          <t>19/08/2026 09:06</t>
+          <t>19/08/2026 09:17</t>
         </is>
       </c>
       <c r="J25" s="27" t="n">
@@ -24269,47 +24269,47 @@
     <row r="26">
       <c r="A26" s="27" t="inlineStr">
         <is>
-          <t>Kátia Cilene Silveira Machado</t>
+          <t>Brauher Luiz Alvarenga Gonzalez</t>
         </is>
       </c>
       <c r="B26" s="27" t="inlineStr">
         <is>
-          <t>Equipe 4</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="C26" s="28" t="inlineStr">
         <is>
-          <t>16960082</t>
+          <t>17009505</t>
         </is>
       </c>
       <c r="D26" s="27" t="inlineStr">
         <is>
-          <t>434 - VILA AUREA</t>
+          <t>422 - VILA TORRES</t>
         </is>
       </c>
       <c r="E26" s="27" t="inlineStr">
         <is>
-          <t>Q023</t>
+          <t>Q027</t>
         </is>
       </c>
       <c r="F26" s="27" t="inlineStr">
         <is>
-          <t>Rua FORTALEZA</t>
+          <t>Rua MANOEL DIAS DE PINHO</t>
         </is>
       </c>
       <c r="G26" s="27" t="inlineStr">
         <is>
-          <t>622 - R</t>
+          <t>625 - 1 - C</t>
         </is>
       </c>
       <c r="H26" s="27" t="inlineStr">
         <is>
-          <t>18/08/2026 09:32</t>
+          <t>19/08/2026 15:31</t>
         </is>
       </c>
       <c r="I26" s="27" t="inlineStr">
         <is>
-          <t>18/08/2026 09:53</t>
+          <t>19/08/2026 15:52</t>
         </is>
       </c>
       <c r="J26" s="27" t="n">
@@ -24319,7 +24319,7 @@
     <row r="27">
       <c r="A27" s="27" t="inlineStr">
         <is>
-          <t>Brauher Luiz Alvarenga Gonzalez</t>
+          <t>Fabiana de Figueredo Vieira</t>
         </is>
       </c>
       <c r="B27" s="27" t="inlineStr">
@@ -24329,37 +24329,37 @@
       </c>
       <c r="C27" s="28" t="inlineStr">
         <is>
-          <t>17009505</t>
+          <t>17027695</t>
         </is>
       </c>
       <c r="D27" s="27" t="inlineStr">
         <is>
-          <t>422 - VILA TORRES</t>
+          <t>411 - JARDIM AEROPORTO</t>
         </is>
       </c>
       <c r="E27" s="27" t="inlineStr">
         <is>
-          <t>Q027</t>
+          <t>Q024</t>
         </is>
       </c>
       <c r="F27" s="27" t="inlineStr">
         <is>
-          <t>Rua MANOEL DIAS DE PINHO</t>
+          <t>Rua ROSA BRANCA</t>
         </is>
       </c>
       <c r="G27" s="27" t="inlineStr">
         <is>
-          <t>625 - 1 - C</t>
+          <t>140 - R</t>
         </is>
       </c>
       <c r="H27" s="27" t="inlineStr">
         <is>
-          <t>19/08/2026 15:31</t>
+          <t>19/08/2026 08:57</t>
         </is>
       </c>
       <c r="I27" s="27" t="inlineStr">
         <is>
-          <t>19/08/2026 15:52</t>
+          <t>19/08/2026 09:18</t>
         </is>
       </c>
       <c r="J27" s="27" t="n">
@@ -24369,47 +24369,47 @@
     <row r="28">
       <c r="A28" s="27" t="inlineStr">
         <is>
-          <t>Fabiana de Figueredo Vieira</t>
+          <t>Kátia Cilene Silveira Machado</t>
         </is>
       </c>
       <c r="B28" s="27" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="C28" s="28" t="inlineStr">
         <is>
-          <t>17027695</t>
+          <t>16960082</t>
         </is>
       </c>
       <c r="D28" s="27" t="inlineStr">
         <is>
-          <t>411 - JARDIM AEROPORTO</t>
+          <t>434 - VILA AUREA</t>
         </is>
       </c>
       <c r="E28" s="27" t="inlineStr">
         <is>
-          <t>Q024</t>
+          <t>Q023</t>
         </is>
       </c>
       <c r="F28" s="27" t="inlineStr">
         <is>
-          <t>Rua ROSA BRANCA</t>
+          <t>Rua FORTALEZA</t>
         </is>
       </c>
       <c r="G28" s="27" t="inlineStr">
         <is>
-          <t>140 - R</t>
+          <t>622 - R</t>
         </is>
       </c>
       <c r="H28" s="27" t="inlineStr">
         <is>
-          <t>19/08/2026 08:57</t>
+          <t>18/08/2026 09:32</t>
         </is>
       </c>
       <c r="I28" s="27" t="inlineStr">
         <is>
-          <t>19/08/2026 09:18</t>
+          <t>18/08/2026 09:53</t>
         </is>
       </c>
       <c r="J28" s="27" t="n">
@@ -24469,7 +24469,7 @@
     <row r="30">
       <c r="A30" s="27" t="inlineStr">
         <is>
-          <t>Rozentina Matos de Oliveira</t>
+          <t>Wagner Tarlei Gomes</t>
         </is>
       </c>
       <c r="B30" s="27" t="inlineStr">
@@ -24479,37 +24479,37 @@
       </c>
       <c r="C30" s="28" t="inlineStr">
         <is>
-          <t>17068744</t>
+          <t>17066233</t>
         </is>
       </c>
       <c r="D30" s="27" t="inlineStr">
         <is>
-          <t>408 - PARQUE DE EXPOSIÇÕES</t>
+          <t>401 - EMÍLIO DIAS BRANDÃO</t>
         </is>
       </c>
       <c r="E30" s="27" t="inlineStr">
         <is>
-          <t>Q037</t>
+          <t>Q005</t>
         </is>
       </c>
       <c r="F30" s="27" t="inlineStr">
         <is>
-          <t>Rua CORONEL PONCE</t>
+          <t>Rua CAPÃO BONITO</t>
         </is>
       </c>
       <c r="G30" s="27" t="inlineStr">
         <is>
-          <t>04 - OU</t>
+          <t>191 - R</t>
         </is>
       </c>
       <c r="H30" s="27" t="inlineStr">
         <is>
-          <t>21/08/2026 15:05</t>
+          <t>17/08/2026 09:01</t>
         </is>
       </c>
       <c r="I30" s="27" t="inlineStr">
         <is>
-          <t>21/08/2026 15:24</t>
+          <t>17/08/2026 09:20</t>
         </is>
       </c>
       <c r="J30" s="27" t="n">
@@ -24519,7 +24519,7 @@
     <row r="31">
       <c r="A31" s="27" t="inlineStr">
         <is>
-          <t>Wagner Tarlei Gomes</t>
+          <t>Ana Gabriela Silva Garcete</t>
         </is>
       </c>
       <c r="B31" s="27" t="inlineStr">
@@ -24529,7 +24529,7 @@
       </c>
       <c r="C31" s="28" t="inlineStr">
         <is>
-          <t>17066233</t>
+          <t>16971726</t>
         </is>
       </c>
       <c r="D31" s="27" t="inlineStr">
@@ -24539,27 +24539,27 @@
       </c>
       <c r="E31" s="27" t="inlineStr">
         <is>
-          <t>Q005</t>
+          <t>Q008</t>
         </is>
       </c>
       <c r="F31" s="27" t="inlineStr">
         <is>
-          <t>Rua CAPÃO BONITO</t>
+          <t>Rua VICENTE  AZAMBUJA</t>
         </is>
       </c>
       <c r="G31" s="27" t="inlineStr">
         <is>
-          <t>191 - R</t>
+          <t>15 - R</t>
         </is>
       </c>
       <c r="H31" s="27" t="inlineStr">
         <is>
-          <t>17/08/2026 09:01</t>
+          <t>18/08/2026 08:29</t>
         </is>
       </c>
       <c r="I31" s="27" t="inlineStr">
         <is>
-          <t>17/08/2026 09:20</t>
+          <t>18/08/2026 08:48</t>
         </is>
       </c>
       <c r="J31" s="27" t="n">
@@ -24569,7 +24569,7 @@
     <row r="32">
       <c r="A32" s="27" t="inlineStr">
         <is>
-          <t>Ana Gabriela Silva Garcete</t>
+          <t>Rozentina Matos de Oliveira</t>
         </is>
       </c>
       <c r="B32" s="27" t="inlineStr">
@@ -24579,37 +24579,37 @@
       </c>
       <c r="C32" s="28" t="inlineStr">
         <is>
-          <t>16971726</t>
+          <t>17068744</t>
         </is>
       </c>
       <c r="D32" s="27" t="inlineStr">
         <is>
-          <t>401 - EMÍLIO DIAS BRANDÃO</t>
+          <t>408 - PARQUE DE EXPOSIÇÕES</t>
         </is>
       </c>
       <c r="E32" s="27" t="inlineStr">
         <is>
-          <t>Q008</t>
+          <t>Q037</t>
         </is>
       </c>
       <c r="F32" s="27" t="inlineStr">
         <is>
-          <t>Rua VICENTE  AZAMBUJA</t>
+          <t>Rua CORONEL PONCE</t>
         </is>
       </c>
       <c r="G32" s="27" t="inlineStr">
         <is>
-          <t>15 - R</t>
+          <t>04 - OU</t>
         </is>
       </c>
       <c r="H32" s="27" t="inlineStr">
         <is>
-          <t>18/08/2026 08:29</t>
+          <t>21/08/2026 15:05</t>
         </is>
       </c>
       <c r="I32" s="27" t="inlineStr">
         <is>
-          <t>18/08/2026 08:48</t>
+          <t>21/08/2026 15:24</t>
         </is>
       </c>
       <c r="J32" s="27" t="n">
@@ -24619,7 +24619,7 @@
     <row r="33">
       <c r="A33" s="27" t="inlineStr">
         <is>
-          <t>Evelyn Santana Santos Oliveira</t>
+          <t>Ana Gabriela Silva Garcete</t>
         </is>
       </c>
       <c r="B33" s="27" t="inlineStr">
@@ -24629,7 +24629,7 @@
       </c>
       <c r="C33" s="28" t="inlineStr">
         <is>
-          <t>17034408</t>
+          <t>17051418</t>
         </is>
       </c>
       <c r="D33" s="27" t="inlineStr">
@@ -24639,27 +24639,27 @@
       </c>
       <c r="E33" s="27" t="inlineStr">
         <is>
-          <t>Q013</t>
+          <t>Q031</t>
         </is>
       </c>
       <c r="F33" s="27" t="inlineStr">
         <is>
-          <t>Rua JABAQUARA</t>
+          <t>Rua AFONSO DE ALBUQUERQUE</t>
         </is>
       </c>
       <c r="G33" s="27" t="inlineStr">
         <is>
-          <t>1370 - 4 - R</t>
+          <t>231 - 3 - R</t>
         </is>
       </c>
       <c r="H33" s="27" t="inlineStr">
         <is>
-          <t>19/08/2026 10:05</t>
+          <t>19/08/2026 14:18</t>
         </is>
       </c>
       <c r="I33" s="27" t="inlineStr">
         <is>
-          <t>19/08/2026 10:23</t>
+          <t>19/08/2026 14:36</t>
         </is>
       </c>
       <c r="J33" s="27" t="n">
@@ -24669,47 +24669,47 @@
     <row r="34">
       <c r="A34" s="27" t="inlineStr">
         <is>
-          <t>Gilmar Bitencourt Luiz</t>
+          <t>Evelyn Santana Santos Oliveira</t>
         </is>
       </c>
       <c r="B34" s="27" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="C34" s="28" t="inlineStr">
         <is>
-          <t>16986947</t>
+          <t>17034408</t>
         </is>
       </c>
       <c r="D34" s="27" t="inlineStr">
         <is>
-          <t>420 - FERROVIARIA</t>
+          <t>401 - EMÍLIO DIAS BRANDÃO</t>
         </is>
       </c>
       <c r="E34" s="27" t="inlineStr">
         <is>
-          <t>Q014</t>
+          <t>Q013</t>
         </is>
       </c>
       <c r="F34" s="27" t="inlineStr">
         <is>
-          <t>Beco PROJETADA 06 FERROVIARIA</t>
+          <t>Rua JABAQUARA</t>
         </is>
       </c>
       <c r="G34" s="27" t="inlineStr">
         <is>
-          <t>113 - R</t>
+          <t>1370 - 4 - R</t>
         </is>
       </c>
       <c r="H34" s="27" t="inlineStr">
         <is>
-          <t>18/08/2026 08:15</t>
+          <t>19/08/2026 10:05</t>
         </is>
       </c>
       <c r="I34" s="27" t="inlineStr">
         <is>
-          <t>18/08/2026 08:33</t>
+          <t>19/08/2026 10:23</t>
         </is>
       </c>
       <c r="J34" s="27" t="n">
@@ -24769,47 +24769,47 @@
     <row r="36">
       <c r="A36" s="27" t="inlineStr">
         <is>
-          <t>Ana Gabriela Silva Garcete</t>
+          <t>Gilmar Bitencourt Luiz</t>
         </is>
       </c>
       <c r="B36" s="27" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="C36" s="28" t="inlineStr">
         <is>
-          <t>17051418</t>
+          <t>16986947</t>
         </is>
       </c>
       <c r="D36" s="27" t="inlineStr">
         <is>
-          <t>401 - EMÍLIO DIAS BRANDÃO</t>
+          <t>420 - FERROVIARIA</t>
         </is>
       </c>
       <c r="E36" s="27" t="inlineStr">
         <is>
-          <t>Q031</t>
+          <t>Q014</t>
         </is>
       </c>
       <c r="F36" s="27" t="inlineStr">
         <is>
-          <t>Rua AFONSO DE ALBUQUERQUE</t>
+          <t>Beco PROJETADA 06 FERROVIARIA</t>
         </is>
       </c>
       <c r="G36" s="27" t="inlineStr">
         <is>
-          <t>231 - 3 - R</t>
+          <t>113 - R</t>
         </is>
       </c>
       <c r="H36" s="27" t="inlineStr">
         <is>
-          <t>19/08/2026 14:18</t>
+          <t>18/08/2026 08:15</t>
         </is>
       </c>
       <c r="I36" s="27" t="inlineStr">
         <is>
-          <t>19/08/2026 14:36</t>
+          <t>18/08/2026 08:33</t>
         </is>
       </c>
       <c r="J36" s="27" t="n">
@@ -24819,47 +24819,47 @@
     <row r="37">
       <c r="A37" s="27" t="inlineStr">
         <is>
-          <t>Walquiria Araujo Flores</t>
+          <t>Gilmar Bitencourt Luiz</t>
         </is>
       </c>
       <c r="B37" s="27" t="inlineStr">
         <is>
-          <t>Equipe 4</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="C37" s="28" t="inlineStr">
         <is>
-          <t>17100546</t>
+          <t>17073314</t>
         </is>
       </c>
       <c r="D37" s="27" t="inlineStr">
         <is>
-          <t>440 - JARDIM IBIRAPUERA</t>
+          <t>418 - CENTRO 4</t>
         </is>
       </c>
       <c r="E37" s="27" t="inlineStr">
         <is>
-          <t>Q031</t>
+          <t>Q011</t>
         </is>
       </c>
       <c r="F37" s="27" t="inlineStr">
         <is>
-          <t>Avenida BELMIRO DE ALBUQUERQUE</t>
+          <t>Avenida ANTONIO JOAO</t>
         </is>
       </c>
       <c r="G37" s="27" t="inlineStr">
         <is>
-          <t>3933 - R</t>
+          <t>1371 - OU</t>
         </is>
       </c>
       <c r="H37" s="27" t="inlineStr">
         <is>
-          <t>21/08/2026 14:04</t>
+          <t>20/08/2026 15:23</t>
         </is>
       </c>
       <c r="I37" s="27" t="inlineStr">
         <is>
-          <t>21/08/2026 14:21</t>
+          <t>20/08/2026 15:40</t>
         </is>
       </c>
       <c r="J37" s="27" t="n">
@@ -24869,7 +24869,7 @@
     <row r="38">
       <c r="A38" s="27" t="inlineStr">
         <is>
-          <t>Kátia Cilene Silveira Machado</t>
+          <t>Walquiria Araujo Flores</t>
         </is>
       </c>
       <c r="B38" s="27" t="inlineStr">
@@ -24879,37 +24879,37 @@
       </c>
       <c r="C38" s="28" t="inlineStr">
         <is>
-          <t>17072136</t>
+          <t>17100546</t>
         </is>
       </c>
       <c r="D38" s="27" t="inlineStr">
         <is>
-          <t>443 - KAMEL SAAD 1</t>
+          <t>440 - JARDIM IBIRAPUERA</t>
         </is>
       </c>
       <c r="E38" s="27" t="inlineStr">
         <is>
-          <t>Q017</t>
+          <t>Q031</t>
         </is>
       </c>
       <c r="F38" s="27" t="inlineStr">
         <is>
-          <t>Rua TOMBADOR</t>
+          <t>Avenida BELMIRO DE ALBUQUERQUE</t>
         </is>
       </c>
       <c r="G38" s="27" t="inlineStr">
         <is>
-          <t>684 - R</t>
+          <t>3933 - R</t>
         </is>
       </c>
       <c r="H38" s="27" t="inlineStr">
         <is>
-          <t>21/08/2026 10:12</t>
+          <t>21/08/2026 14:04</t>
         </is>
       </c>
       <c r="I38" s="27" t="inlineStr">
         <is>
-          <t>21/08/2026 10:29</t>
+          <t>21/08/2026 14:21</t>
         </is>
       </c>
       <c r="J38" s="27" t="n">
@@ -24929,7 +24929,7 @@
       </c>
       <c r="C39" s="28" t="inlineStr">
         <is>
-          <t>16960061</t>
+          <t>16960075</t>
         </is>
       </c>
       <c r="D39" s="27" t="inlineStr">
@@ -24949,17 +24949,17 @@
       </c>
       <c r="G39" s="27" t="inlineStr">
         <is>
-          <t>118 - R</t>
+          <t>58 - R</t>
         </is>
       </c>
       <c r="H39" s="27" t="inlineStr">
         <is>
-          <t>17/08/2026 10:37</t>
+          <t>17/08/2026 15:47</t>
         </is>
       </c>
       <c r="I39" s="27" t="inlineStr">
         <is>
-          <t>17/08/2026 10:54</t>
+          <t>17/08/2026 16:04</t>
         </is>
       </c>
       <c r="J39" s="27" t="n">
@@ -24969,47 +24969,47 @@
     <row r="40">
       <c r="A40" s="27" t="inlineStr">
         <is>
-          <t>Evelyn Santana Santos Oliveira</t>
+          <t>Kátia Cilene Silveira Machado</t>
         </is>
       </c>
       <c r="B40" s="27" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="C40" s="28" t="inlineStr">
         <is>
-          <t>17022532</t>
+          <t>16960061</t>
         </is>
       </c>
       <c r="D40" s="27" t="inlineStr">
         <is>
-          <t>410 - SALGADO FILHO</t>
+          <t>443 - KAMEL SAAD 1</t>
         </is>
       </c>
       <c r="E40" s="27" t="inlineStr">
         <is>
-          <t>Q023</t>
+          <t>Q016</t>
         </is>
       </c>
       <c r="F40" s="27" t="inlineStr">
         <is>
-          <t>Rua MARINGA</t>
+          <t>Rua SALIM DERZI</t>
         </is>
       </c>
       <c r="G40" s="27" t="inlineStr">
         <is>
-          <t>807 - R</t>
+          <t>118 - R</t>
         </is>
       </c>
       <c r="H40" s="27" t="inlineStr">
         <is>
-          <t>17/08/2026 09:53</t>
+          <t>17/08/2026 10:37</t>
         </is>
       </c>
       <c r="I40" s="27" t="inlineStr">
         <is>
-          <t>17/08/2026 10:10</t>
+          <t>17/08/2026 10:54</t>
         </is>
       </c>
       <c r="J40" s="27" t="n">
@@ -25019,7 +25019,7 @@
     <row r="41">
       <c r="A41" s="27" t="inlineStr">
         <is>
-          <t>Ana Gabriela Silva Garcete</t>
+          <t>Evelyn Santana Santos Oliveira</t>
         </is>
       </c>
       <c r="B41" s="27" t="inlineStr">
@@ -25029,37 +25029,37 @@
       </c>
       <c r="C41" s="28" t="inlineStr">
         <is>
-          <t>17070288</t>
+          <t>17022532</t>
         </is>
       </c>
       <c r="D41" s="27" t="inlineStr">
         <is>
-          <t>401 - EMÍLIO DIAS BRANDÃO</t>
+          <t>410 - SALGADO FILHO</t>
         </is>
       </c>
       <c r="E41" s="27" t="inlineStr">
         <is>
-          <t>Q019</t>
+          <t>Q023</t>
         </is>
       </c>
       <c r="F41" s="27" t="inlineStr">
         <is>
-          <t>Rua JABAQUARA</t>
+          <t>Rua MARINGA</t>
         </is>
       </c>
       <c r="G41" s="27" t="inlineStr">
         <is>
-          <t>1490 - C</t>
+          <t>807 - R</t>
         </is>
       </c>
       <c r="H41" s="27" t="inlineStr">
         <is>
-          <t>21/08/2026 15:07</t>
+          <t>17/08/2026 09:53</t>
         </is>
       </c>
       <c r="I41" s="27" t="inlineStr">
         <is>
-          <t>21/08/2026 15:24</t>
+          <t>17/08/2026 10:10</t>
         </is>
       </c>
       <c r="J41" s="27" t="n">
@@ -25079,7 +25079,7 @@
       </c>
       <c r="C42" s="28" t="inlineStr">
         <is>
-          <t>17070286</t>
+          <t>17070288</t>
         </is>
       </c>
       <c r="D42" s="27" t="inlineStr">
@@ -25089,27 +25089,27 @@
       </c>
       <c r="E42" s="27" t="inlineStr">
         <is>
-          <t>Q029</t>
+          <t>Q019</t>
         </is>
       </c>
       <c r="F42" s="27" t="inlineStr">
         <is>
-          <t>Rua GUAÍBA</t>
+          <t>Rua JABAQUARA</t>
         </is>
       </c>
       <c r="G42" s="27" t="inlineStr">
         <is>
-          <t>1262 - C</t>
+          <t>1490 - C</t>
         </is>
       </c>
       <c r="H42" s="27" t="inlineStr">
         <is>
-          <t>21/08/2026 14:40</t>
+          <t>21/08/2026 15:07</t>
         </is>
       </c>
       <c r="I42" s="27" t="inlineStr">
         <is>
-          <t>21/08/2026 14:57</t>
+          <t>21/08/2026 15:24</t>
         </is>
       </c>
       <c r="J42" s="27" t="n">
@@ -25119,7 +25119,7 @@
     <row r="43">
       <c r="A43" s="27" t="inlineStr">
         <is>
-          <t>Ana Gabriela Silva Garcete</t>
+          <t>Wagner Tarlei Gomes</t>
         </is>
       </c>
       <c r="B43" s="27" t="inlineStr">
@@ -25129,37 +25129,37 @@
       </c>
       <c r="C43" s="28" t="inlineStr">
         <is>
-          <t>16971696</t>
+          <t>17064916</t>
         </is>
       </c>
       <c r="D43" s="27" t="inlineStr">
         <is>
-          <t>410 - SALGADO FILHO</t>
+          <t>401 - EMÍLIO DIAS BRANDÃO</t>
         </is>
       </c>
       <c r="E43" s="27" t="inlineStr">
         <is>
-          <t>Q014</t>
+          <t>Q007</t>
         </is>
       </c>
       <c r="F43" s="27" t="inlineStr">
         <is>
-          <t>Rua TENENTE SAMUEL DE ALMEIDA</t>
+          <t>Rua RIACHO DOCE</t>
         </is>
       </c>
       <c r="G43" s="27" t="inlineStr">
         <is>
-          <t>630 - 1 - R</t>
+          <t>78 - R</t>
         </is>
       </c>
       <c r="H43" s="27" t="inlineStr">
         <is>
-          <t>17/08/2026 10:58</t>
+          <t>18/08/2026 14:00</t>
         </is>
       </c>
       <c r="I43" s="27" t="inlineStr">
         <is>
-          <t>17/08/2026 11:15</t>
+          <t>18/08/2026 14:17</t>
         </is>
       </c>
       <c r="J43" s="27" t="n">
@@ -25169,7 +25169,7 @@
     <row r="44">
       <c r="A44" s="27" t="inlineStr">
         <is>
-          <t>Wagner Tarlei Gomes</t>
+          <t>Ana Gabriela Silva Garcete</t>
         </is>
       </c>
       <c r="B44" s="27" t="inlineStr">
@@ -25179,7 +25179,7 @@
       </c>
       <c r="C44" s="28" t="inlineStr">
         <is>
-          <t>17064916</t>
+          <t>17070286</t>
         </is>
       </c>
       <c r="D44" s="27" t="inlineStr">
@@ -25189,27 +25189,27 @@
       </c>
       <c r="E44" s="27" t="inlineStr">
         <is>
-          <t>Q007</t>
+          <t>Q029</t>
         </is>
       </c>
       <c r="F44" s="27" t="inlineStr">
         <is>
-          <t>Rua RIACHO DOCE</t>
+          <t>Rua GUAÍBA</t>
         </is>
       </c>
       <c r="G44" s="27" t="inlineStr">
         <is>
-          <t>78 - R</t>
+          <t>1262 - C</t>
         </is>
       </c>
       <c r="H44" s="27" t="inlineStr">
         <is>
-          <t>18/08/2026 14:00</t>
+          <t>21/08/2026 14:40</t>
         </is>
       </c>
       <c r="I44" s="27" t="inlineStr">
         <is>
-          <t>18/08/2026 14:17</t>
+          <t>21/08/2026 14:57</t>
         </is>
       </c>
       <c r="J44" s="27" t="n">
@@ -25219,47 +25219,47 @@
     <row r="45">
       <c r="A45" s="27" t="inlineStr">
         <is>
-          <t>Miglidiane Maciel Ajala</t>
+          <t>Ana Gabriela Silva Garcete</t>
         </is>
       </c>
       <c r="B45" s="27" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="C45" s="28" t="inlineStr">
         <is>
-          <t>17041447</t>
+          <t>16971696</t>
         </is>
       </c>
       <c r="D45" s="27" t="inlineStr">
         <is>
-          <t>425 - JARDIM ESTORIL</t>
+          <t>410 - SALGADO FILHO</t>
         </is>
       </c>
       <c r="E45" s="27" t="inlineStr">
         <is>
-          <t>Q038</t>
+          <t>Q014</t>
         </is>
       </c>
       <c r="F45" s="27" t="inlineStr">
         <is>
-          <t>Rua DAS PEROBAS</t>
+          <t>Rua TENENTE SAMUEL DE ALMEIDA</t>
         </is>
       </c>
       <c r="G45" s="27" t="inlineStr">
         <is>
-          <t>1018 - R</t>
+          <t>630 - 1 - R</t>
         </is>
       </c>
       <c r="H45" s="27" t="inlineStr">
         <is>
-          <t>20/08/2026 14:48</t>
+          <t>17/08/2026 10:58</t>
         </is>
       </c>
       <c r="I45" s="27" t="inlineStr">
         <is>
-          <t>20/08/2026 15:05</t>
+          <t>17/08/2026 11:15</t>
         </is>
       </c>
       <c r="J45" s="27" t="n">
@@ -25369,7 +25369,7 @@
     <row r="48">
       <c r="A48" s="27" t="inlineStr">
         <is>
-          <t>Gilmar Bitencourt Luiz</t>
+          <t>William Anderson Chamorro Tavares</t>
         </is>
       </c>
       <c r="B48" s="27" t="inlineStr">
@@ -25379,37 +25379,37 @@
       </c>
       <c r="C48" s="28" t="inlineStr">
         <is>
-          <t>17073314</t>
+          <t>17043629</t>
         </is>
       </c>
       <c r="D48" s="27" t="inlineStr">
         <is>
-          <t>418 - CENTRO 4</t>
+          <t>413 - BAIRRO DA GRANJA</t>
         </is>
       </c>
       <c r="E48" s="27" t="inlineStr">
         <is>
-          <t>Q011</t>
+          <t>Q034</t>
         </is>
       </c>
       <c r="F48" s="27" t="inlineStr">
         <is>
-          <t>Avenida ANTONIO JOAO</t>
+          <t>Rua ARAPONGAS</t>
         </is>
       </c>
       <c r="G48" s="27" t="inlineStr">
         <is>
-          <t>1371 - OU</t>
+          <t>142 - R</t>
         </is>
       </c>
       <c r="H48" s="27" t="inlineStr">
         <is>
-          <t>20/08/2026 15:23</t>
+          <t>20/08/2026 15:52</t>
         </is>
       </c>
       <c r="I48" s="27" t="inlineStr">
         <is>
-          <t>20/08/2026 15:40</t>
+          <t>20/08/2026 16:09</t>
         </is>
       </c>
       <c r="J48" s="27" t="n">
@@ -25479,7 +25479,7 @@
       </c>
       <c r="C50" s="28" t="inlineStr">
         <is>
-          <t>16960075</t>
+          <t>17072136</t>
         </is>
       </c>
       <c r="D50" s="27" t="inlineStr">
@@ -25489,27 +25489,27 @@
       </c>
       <c r="E50" s="27" t="inlineStr">
         <is>
-          <t>Q016</t>
+          <t>Q017</t>
         </is>
       </c>
       <c r="F50" s="27" t="inlineStr">
         <is>
-          <t>Rua SALIM DERZI</t>
+          <t>Rua TOMBADOR</t>
         </is>
       </c>
       <c r="G50" s="27" t="inlineStr">
         <is>
-          <t>58 - R</t>
+          <t>684 - R</t>
         </is>
       </c>
       <c r="H50" s="27" t="inlineStr">
         <is>
-          <t>17/08/2026 15:47</t>
+          <t>21/08/2026 10:12</t>
         </is>
       </c>
       <c r="I50" s="27" t="inlineStr">
         <is>
-          <t>17/08/2026 16:04</t>
+          <t>21/08/2026 10:29</t>
         </is>
       </c>
       <c r="J50" s="27" t="n">
@@ -25519,7 +25519,7 @@
     <row r="51">
       <c r="A51" s="27" t="inlineStr">
         <is>
-          <t>Alana Amanda Fernandes Ovelar</t>
+          <t>Miglidiane Maciel Ajala</t>
         </is>
       </c>
       <c r="B51" s="27" t="inlineStr">
@@ -25529,37 +25529,37 @@
       </c>
       <c r="C51" s="28" t="inlineStr">
         <is>
-          <t>17014581</t>
+          <t>17041447</t>
         </is>
       </c>
       <c r="D51" s="27" t="inlineStr">
         <is>
-          <t>433 - ÁREA A - RESIDENCIAL PONTA PORÃ 1</t>
+          <t>425 - JARDIM ESTORIL</t>
         </is>
       </c>
       <c r="E51" s="27" t="inlineStr">
         <is>
-          <t>Q016</t>
+          <t>Q038</t>
         </is>
       </c>
       <c r="F51" s="27" t="inlineStr">
         <is>
-          <t>Rua GUARANTA</t>
+          <t>Rua DAS PEROBAS</t>
         </is>
       </c>
       <c r="G51" s="27" t="inlineStr">
         <is>
-          <t>295 - 1 - TB</t>
+          <t>1018 - R</t>
         </is>
       </c>
       <c r="H51" s="27" t="inlineStr">
         <is>
-          <t>19/08/2026 09:45</t>
+          <t>20/08/2026 14:48</t>
         </is>
       </c>
       <c r="I51" s="27" t="inlineStr">
         <is>
-          <t>19/08/2026 10:02</t>
+          <t>20/08/2026 15:05</t>
         </is>
       </c>
       <c r="J51" s="27" t="n">
@@ -25569,47 +25569,47 @@
     <row r="52">
       <c r="A52" s="27" t="inlineStr">
         <is>
-          <t>William Anderson Chamorro Tavares</t>
+          <t>Alana Amanda Fernandes Ovelar</t>
         </is>
       </c>
       <c r="B52" s="27" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 3</t>
         </is>
       </c>
       <c r="C52" s="28" t="inlineStr">
         <is>
-          <t>17043629</t>
+          <t>17014581</t>
         </is>
       </c>
       <c r="D52" s="27" t="inlineStr">
         <is>
-          <t>413 - BAIRRO DA GRANJA</t>
+          <t>433 - ÁREA A - RESIDENCIAL PONTA PORÃ 1</t>
         </is>
       </c>
       <c r="E52" s="27" t="inlineStr">
         <is>
-          <t>Q034</t>
+          <t>Q016</t>
         </is>
       </c>
       <c r="F52" s="27" t="inlineStr">
         <is>
-          <t>Rua ARAPONGAS</t>
+          <t>Rua GUARANTA</t>
         </is>
       </c>
       <c r="G52" s="27" t="inlineStr">
         <is>
-          <t>142 - R</t>
+          <t>295 - 1 - TB</t>
         </is>
       </c>
       <c r="H52" s="27" t="inlineStr">
         <is>
-          <t>20/08/2026 15:52</t>
+          <t>19/08/2026 09:45</t>
         </is>
       </c>
       <c r="I52" s="27" t="inlineStr">
         <is>
-          <t>20/08/2026 16:09</t>
+          <t>19/08/2026 10:02</t>
         </is>
       </c>
       <c r="J52" s="27" t="n">
@@ -25619,7 +25619,7 @@
     <row r="53">
       <c r="A53" s="27" t="inlineStr">
         <is>
-          <t>Evelyn Santana Santos Oliveira</t>
+          <t>Wagner Tarlei Gomes</t>
         </is>
       </c>
       <c r="B53" s="27" t="inlineStr">
@@ -25629,37 +25629,37 @@
       </c>
       <c r="C53" s="28" t="inlineStr">
         <is>
-          <t>17033729</t>
+          <t>17076991</t>
         </is>
       </c>
       <c r="D53" s="27" t="inlineStr">
         <is>
-          <t>401 - EMÍLIO DIAS BRANDÃO</t>
+          <t>400 - JULIA CARDINAL</t>
         </is>
       </c>
       <c r="E53" s="27" t="inlineStr">
         <is>
-          <t>Q013</t>
+          <t>Q012</t>
         </is>
       </c>
       <c r="F53" s="27" t="inlineStr">
         <is>
-          <t>Rua VICENTE  AZAMBUJA</t>
+          <t>Rua Anselmo Soares</t>
         </is>
       </c>
       <c r="G53" s="27" t="inlineStr">
         <is>
-          <t>1407 - R</t>
+          <t>700 - OU</t>
         </is>
       </c>
       <c r="H53" s="27" t="inlineStr">
         <is>
-          <t>19/08/2026 08:45</t>
+          <t>19/08/2026 15:29</t>
         </is>
       </c>
       <c r="I53" s="27" t="inlineStr">
         <is>
-          <t>19/08/2026 09:01</t>
+          <t>19/08/2026 15:45</t>
         </is>
       </c>
       <c r="J53" s="27" t="n">
@@ -25719,7 +25719,7 @@
     <row r="55">
       <c r="A55" s="27" t="inlineStr">
         <is>
-          <t>Wagner Tarlei Gomes</t>
+          <t>Ana Gabriela Silva Garcete</t>
         </is>
       </c>
       <c r="B55" s="27" t="inlineStr">
@@ -25729,37 +25729,37 @@
       </c>
       <c r="C55" s="28" t="inlineStr">
         <is>
-          <t>17076991</t>
+          <t>16971669</t>
         </is>
       </c>
       <c r="D55" s="27" t="inlineStr">
         <is>
-          <t>400 - JULIA CARDINAL</t>
+          <t>410 - SALGADO FILHO</t>
         </is>
       </c>
       <c r="E55" s="27" t="inlineStr">
         <is>
-          <t>Q012</t>
+          <t>Q014</t>
         </is>
       </c>
       <c r="F55" s="27" t="inlineStr">
         <is>
-          <t>Rua Anselmo Soares</t>
+          <t>Rua SAO CRISTOVAO</t>
         </is>
       </c>
       <c r="G55" s="27" t="inlineStr">
         <is>
-          <t>700 - OU</t>
+          <t>652 - R</t>
         </is>
       </c>
       <c r="H55" s="27" t="inlineStr">
         <is>
-          <t>19/08/2026 15:29</t>
+          <t>17/08/2026 09:08</t>
         </is>
       </c>
       <c r="I55" s="27" t="inlineStr">
         <is>
-          <t>19/08/2026 15:45</t>
+          <t>17/08/2026 09:24</t>
         </is>
       </c>
       <c r="J55" s="27" t="n">
@@ -25819,7 +25819,7 @@
     <row r="57">
       <c r="A57" s="27" t="inlineStr">
         <is>
-          <t>Ana Gabriela Silva Garcete</t>
+          <t>Evelyn Santana Santos Oliveira</t>
         </is>
       </c>
       <c r="B57" s="27" t="inlineStr">
@@ -25829,37 +25829,37 @@
       </c>
       <c r="C57" s="28" t="inlineStr">
         <is>
-          <t>16971669</t>
+          <t>17033729</t>
         </is>
       </c>
       <c r="D57" s="27" t="inlineStr">
         <is>
-          <t>410 - SALGADO FILHO</t>
+          <t>401 - EMÍLIO DIAS BRANDÃO</t>
         </is>
       </c>
       <c r="E57" s="27" t="inlineStr">
         <is>
-          <t>Q014</t>
+          <t>Q013</t>
         </is>
       </c>
       <c r="F57" s="27" t="inlineStr">
         <is>
-          <t>Rua SAO CRISTOVAO</t>
+          <t>Rua VICENTE  AZAMBUJA</t>
         </is>
       </c>
       <c r="G57" s="27" t="inlineStr">
         <is>
-          <t>652 - R</t>
+          <t>1407 - R</t>
         </is>
       </c>
       <c r="H57" s="27" t="inlineStr">
         <is>
-          <t>17/08/2026 09:08</t>
+          <t>19/08/2026 08:45</t>
         </is>
       </c>
       <c r="I57" s="27" t="inlineStr">
         <is>
-          <t>17/08/2026 09:24</t>
+          <t>19/08/2026 09:01</t>
         </is>
       </c>
       <c r="J57" s="27" t="n">
@@ -25869,7 +25869,7 @@
     <row r="58">
       <c r="A58" s="27" t="inlineStr">
         <is>
-          <t>Adriano Ricardo Thiel</t>
+          <t>Rozentina Matos de Oliveira</t>
         </is>
       </c>
       <c r="B58" s="27" t="inlineStr">
@@ -25879,37 +25879,37 @@
       </c>
       <c r="C58" s="28" t="inlineStr">
         <is>
-          <t>16957579</t>
+          <t>17055208</t>
         </is>
       </c>
       <c r="D58" s="27" t="inlineStr">
         <is>
-          <t>407 - MOOCA</t>
+          <t>408 - PARQUE DE EXPOSIÇÕES</t>
         </is>
       </c>
       <c r="E58" s="27" t="inlineStr">
         <is>
-          <t>Q041</t>
+          <t>Q036</t>
         </is>
       </c>
       <c r="F58" s="27" t="inlineStr">
         <is>
-          <t>Rua VALPARAISO</t>
+          <t>Rua DIGNO TORRES GIMENEZ</t>
         </is>
       </c>
       <c r="G58" s="27" t="inlineStr">
         <is>
-          <t>335 - R</t>
+          <t>590 - 2 - R</t>
         </is>
       </c>
       <c r="H58" s="27" t="inlineStr">
         <is>
-          <t>17/08/2026 08:59</t>
+          <t>21/08/2026 08:57</t>
         </is>
       </c>
       <c r="I58" s="27" t="inlineStr">
         <is>
-          <t>17/08/2026 09:15</t>
+          <t>21/08/2026 09:13</t>
         </is>
       </c>
       <c r="J58" s="27" t="n">
@@ -25919,47 +25919,47 @@
     <row r="59">
       <c r="A59" s="27" t="inlineStr">
         <is>
-          <t>Suely Aguiar Alves Luiz</t>
+          <t>Adriano Ricardo Thiel</t>
         </is>
       </c>
       <c r="B59" s="27" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="C59" s="28" t="inlineStr">
         <is>
-          <t>17017093</t>
+          <t>16957579</t>
         </is>
       </c>
       <c r="D59" s="27" t="inlineStr">
         <is>
-          <t>420 - FERROVIARIA</t>
+          <t>407 - MOOCA</t>
         </is>
       </c>
       <c r="E59" s="27" t="inlineStr">
         <is>
-          <t>Q013</t>
+          <t>Q041</t>
         </is>
       </c>
       <c r="F59" s="27" t="inlineStr">
         <is>
-          <t>Travessa PROJETADA 06 FERROVIARIA</t>
+          <t>Rua VALPARAISO</t>
         </is>
       </c>
       <c r="G59" s="27" t="inlineStr">
         <is>
-          <t>69 - R</t>
+          <t>335 - R</t>
         </is>
       </c>
       <c r="H59" s="27" t="inlineStr">
         <is>
-          <t>17/08/2026 15:44</t>
+          <t>17/08/2026 08:59</t>
         </is>
       </c>
       <c r="I59" s="27" t="inlineStr">
         <is>
-          <t>17/08/2026 16:00</t>
+          <t>17/08/2026 09:15</t>
         </is>
       </c>
       <c r="J59" s="27" t="n">
@@ -26019,47 +26019,47 @@
     <row r="61">
       <c r="A61" s="27" t="inlineStr">
         <is>
-          <t>Rozentina Matos de Oliveira</t>
+          <t>Suely Aguiar Alves Luiz</t>
         </is>
       </c>
       <c r="B61" s="27" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="C61" s="28" t="inlineStr">
         <is>
-          <t>17055208</t>
+          <t>17017093</t>
         </is>
       </c>
       <c r="D61" s="27" t="inlineStr">
         <is>
-          <t>408 - PARQUE DE EXPOSIÇÕES</t>
+          <t>420 - FERROVIARIA</t>
         </is>
       </c>
       <c r="E61" s="27" t="inlineStr">
         <is>
-          <t>Q036</t>
+          <t>Q013</t>
         </is>
       </c>
       <c r="F61" s="27" t="inlineStr">
         <is>
-          <t>Rua DIGNO TORRES GIMENEZ</t>
+          <t>Travessa PROJETADA 06 FERROVIARIA</t>
         </is>
       </c>
       <c r="G61" s="27" t="inlineStr">
         <is>
-          <t>590 - 2 - R</t>
+          <t>69 - R</t>
         </is>
       </c>
       <c r="H61" s="27" t="inlineStr">
         <is>
-          <t>21/08/2026 08:57</t>
+          <t>17/08/2026 15:44</t>
         </is>
       </c>
       <c r="I61" s="27" t="inlineStr">
         <is>
-          <t>21/08/2026 09:13</t>
+          <t>17/08/2026 16:00</t>
         </is>
       </c>
       <c r="J61" s="27" t="n">

--- a/data/historico/semana_320.xlsx
+++ b/data/historico/semana_320.xlsx
@@ -5215,7 +5215,7 @@
       </c>
       <c r="B6" s="38" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="C6" s="38" t="inlineStr">
@@ -5237,7 +5237,7 @@
       </c>
       <c r="B7" s="38" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="C7" s="38" t="inlineStr">
@@ -5259,7 +5259,7 @@
       </c>
       <c r="B8" s="38" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="C8" s="38" t="inlineStr">

--- a/data/historico/semana_320.xlsx
+++ b/data/historico/semana_320.xlsx
@@ -24,8 +24,8 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Resumo Geral'!$A$2:$AC$40</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Por Área'!$A$2:$N$89</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Visitas Duplicadas'!$A$2:$J$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Visitas Suspeitas'!$A$2:$K$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Visitas Duplicadas'!$A$2:$J$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Visitas Suspeitas'!$A$2:$K$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Visitas Negativas'!$A$2:$K$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Visitas Acima de 15min'!$A$2:$J$64</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Fora do Expediente'!$A$2:$K$30</definedName>
@@ -3106,25 +3106,25 @@
         </is>
       </c>
       <c r="D23" s="4" t="n">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E23" s="4" t="n">
         <v>5</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>25.4</v>
+        <v>25</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>5.28</v>
+        <v>5.36</v>
       </c>
       <c r="H23" s="4" t="n">
         <v>5</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>3.94</v>
+        <v>2.4</v>
       </c>
       <c r="K23" s="4" t="n">
         <v>0</v>
@@ -3136,10 +3136,10 @@
         <v>5</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="P23" s="4" t="n">
         <v>0</v>
@@ -3154,10 +3154,10 @@
         <v>0</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>46.19</v>
+        <v>46.58</v>
       </c>
       <c r="V23" s="4" t="n">
         <v>5.5</v>
@@ -5970,7 +5970,7 @@
         </is>
       </c>
       <c r="C23" s="27" t="n">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D23" s="27" t="n">
         <v>109</v>
@@ -5979,10 +5979,10 @@
         <v>0</v>
       </c>
       <c r="F23" s="27" t="n">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="G23" s="27" t="n">
-        <v>46.19</v>
+        <v>46.58</v>
       </c>
       <c r="H23" s="2" t="n"/>
       <c r="I23" s="2" t="n"/>
@@ -6492,7 +6492,7 @@
         </is>
       </c>
       <c r="C41" s="40" t="n">
-        <v>4779</v>
+        <v>4777</v>
       </c>
       <c r="D41" s="40" t="n">
         <v>2050</v>
@@ -6501,10 +6501,10 @@
         <v>6</v>
       </c>
       <c r="F41" s="40" t="n">
-        <v>6835</v>
+        <v>6833</v>
       </c>
       <c r="G41" s="40" t="n">
-        <v>30.08</v>
+        <v>30.09</v>
       </c>
       <c r="H41" s="2" t="n"/>
       <c r="I41" s="2" t="n"/>
@@ -8045,25 +8045,25 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>Evelyn Santana Santos Oliveira</t>
+          <t>Claine Luisa Figueiredo Torraca</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 3</t>
         </is>
       </c>
       <c r="D22" s="4" t="n">
         <v>5</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>92.3</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
@@ -8077,61 +8077,61 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Sara Eliane Talaveira de Oliveira</t>
+          <t>Evelyn Santana Santos Oliveira</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Equipe 4</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="D23" s="4" t="n">
         <v>5</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F23" s="4" t="n">
         <v>2</v>
       </c>
       <c r="G23" s="4" t="n">
+        <v>92.3</v>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>🟢 EXCELENTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>Sara Eliane Talaveira de Oliveira</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="E24" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="F24" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G24" s="4" t="n">
         <v>90.90000000000001</v>
       </c>
-      <c r="H23" s="4" t="inlineStr">
+      <c r="H24" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="6" t="n">
-        <v>22</v>
-      </c>
-      <c r="B24" s="6" t="inlineStr">
-        <is>
-          <t>Alana Amanda Fernandes Ovelar</t>
-        </is>
-      </c>
-      <c r="C24" s="6" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="D24" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="E24" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="F24" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="G24" s="6" t="n">
-        <v>89.90000000000001</v>
-      </c>
-      <c r="H24" s="6" t="inlineStr">
-        <is>
-          <t>🟡 BOM</t>
         </is>
       </c>
     </row>
@@ -8141,25 +8141,25 @@
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>Juliana Patricia Goncalves</t>
+          <t>Alana Amanda Fernandes Ovelar</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>Equipe 4</t>
+          <t>Equipe 3</t>
         </is>
       </c>
       <c r="D25" s="6" t="n">
         <v>2</v>
       </c>
       <c r="E25" s="6" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>89.7</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="H25" s="6" t="inlineStr">
         <is>
@@ -8173,7 +8173,7 @@
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>Rozana Reis da Silva</t>
+          <t>Juliana Patricia Goncalves</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
@@ -8182,16 +8182,16 @@
         </is>
       </c>
       <c r="D26" s="6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E26" s="6" t="n">
         <v>13</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>87.7</v>
+        <v>89.7</v>
       </c>
       <c r="H26" s="6" t="inlineStr">
         <is>
@@ -8205,25 +8205,25 @@
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>Gabriel Alan de Oliveira Martins</t>
+          <t>Rozana Reis da Silva</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="D27" s="6" t="n">
         <v>5</v>
       </c>
       <c r="E27" s="6" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>87.5</v>
+        <v>87.7</v>
       </c>
       <c r="H27" s="6" t="inlineStr">
         <is>
@@ -8237,25 +8237,25 @@
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>Teonilda Florentino Vieira</t>
+          <t>Gabriel Alan de Oliveira Martins</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="D28" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E28" s="6" t="n">
         <v>15</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>84.90000000000001</v>
+        <v>87.5</v>
       </c>
       <c r="H28" s="6" t="inlineStr">
         <is>
@@ -8269,25 +8269,25 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>Walquiria Araujo Flores</t>
+          <t>Teonilda Florentino Vieira</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>Equipe 4</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="D29" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E29" s="6" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>84.7</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="H29" s="6" t="inlineStr">
         <is>
@@ -8301,25 +8301,25 @@
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>Brauher Luiz Alvarenga Gonzalez</t>
+          <t>Walquiria Araujo Flores</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="D30" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E30" s="6" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>83.2</v>
+        <v>84.7</v>
       </c>
       <c r="H30" s="6" t="inlineStr">
         <is>
@@ -8333,7 +8333,7 @@
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>Gisele Olimpia Torres</t>
+          <t>Brauher Luiz Alvarenga Gonzalez</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
@@ -8342,16 +8342,16 @@
         </is>
       </c>
       <c r="D31" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E31" s="6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F31" s="6" t="n">
         <v>3</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>81.90000000000001</v>
+        <v>83.2</v>
       </c>
       <c r="H31" s="6" t="inlineStr">
         <is>
@@ -8365,12 +8365,12 @@
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>Claine Luisa Figueiredo Torraca</t>
+          <t>Gisele Olimpia Torres</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="D32" s="6" t="n">
@@ -8380,10 +8380,10 @@
         <v>14</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>81.40000000000001</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="H32" s="6" t="inlineStr">
         <is>
@@ -10500,7 +10500,7 @@
         </is>
       </c>
       <c r="D100" s="49" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E100" s="49" t="n">
         <v>0.3</v>
@@ -10512,7 +10512,7 @@
         <v>0.6</v>
       </c>
       <c r="H100" s="49" t="n">
-        <v>-3.6</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="101">
@@ -10532,7 +10532,7 @@
         </is>
       </c>
       <c r="D101" s="49" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E101" s="49" t="n">
         <v>1</v>
@@ -10544,7 +10544,7 @@
         <v>2</v>
       </c>
       <c r="H101" s="49" t="n">
-        <v>-12</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="102">
@@ -10564,7 +10564,7 @@
         </is>
       </c>
       <c r="D102" s="49" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E102" s="49" t="n">
         <v>0.2</v>
@@ -10576,7 +10576,7 @@
         <v>0.4</v>
       </c>
       <c r="H102" s="49" t="n">
-        <v>-2</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="103">
@@ -19217,56 +19217,56 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="6" t="inlineStr">
+      <c r="A48" s="4" t="inlineStr">
         <is>
           <t>Claine Luisa Figueiredo Torraca</t>
         </is>
       </c>
-      <c r="B48" s="6" t="inlineStr">
+      <c r="B48" s="4" t="inlineStr">
         <is>
           <t>Equipe 3</t>
         </is>
       </c>
-      <c r="C48" s="6" t="inlineStr">
-        <is>
-          <t>449 - ÁREA C RESIDENCIAL PONTA PORÃ 1</t>
-        </is>
-      </c>
-      <c r="D48" s="6" t="n">
-        <v>21</v>
-      </c>
-      <c r="E48" s="6" t="n">
-        <v>4.86</v>
-      </c>
-      <c r="F48" s="6" t="n">
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>429 - COOPHA FRONTEIRA</t>
+        </is>
+      </c>
+      <c r="D48" s="4" t="n">
+        <v>58</v>
+      </c>
+      <c r="E48" s="4" t="n">
+        <v>5.28</v>
+      </c>
+      <c r="F48" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="G48" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="H48" s="6" t="inlineStr">
-        <is>
-          <t>Q029, Q030</t>
-        </is>
-      </c>
-      <c r="I48" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="J48" s="6" t="n">
-        <v>14.29</v>
-      </c>
-      <c r="K48" s="6" t="n">
-        <v>25</v>
-      </c>
-      <c r="L48" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M48" s="6" t="n">
-        <v>54.35</v>
-      </c>
-      <c r="N48" s="6" t="inlineStr">
-        <is>
-          <t>🟡 ATENÇÃO</t>
+      <c r="G48" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="H48" s="4" t="inlineStr">
+        <is>
+          <t>Q004, Q005, Q006, Q012, Q013</t>
+        </is>
+      </c>
+      <c r="I48" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J48" s="4" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="K48" s="4" t="n">
+        <v>54</v>
+      </c>
+      <c r="L48" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" s="4" t="n">
+        <v>48.21</v>
+      </c>
+      <c r="N48" s="4" t="inlineStr">
+        <is>
+          <t>🟢 NORMAL</t>
         </is>
       </c>
     </row>
@@ -19283,40 +19283,40 @@
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>429 - COOPHA FRONTEIRA</t>
+          <t>449 - ÁREA C RESIDENCIAL PONTA PORÃ 1</t>
         </is>
       </c>
       <c r="D49" s="4" t="n">
-        <v>58</v>
+        <v>19</v>
       </c>
       <c r="E49" s="4" t="n">
-        <v>5.28</v>
+        <v>5.37</v>
       </c>
       <c r="F49" s="4" t="n">
         <v>5</v>
       </c>
       <c r="G49" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H49" s="4" t="inlineStr">
         <is>
-          <t>Q004, Q005, Q006, Q012, Q013</t>
+          <t>Q029, Q030</t>
         </is>
       </c>
       <c r="I49" s="4" t="n">
         <v>1</v>
       </c>
       <c r="J49" s="4" t="n">
-        <v>1.72</v>
+        <v>5.26</v>
       </c>
       <c r="K49" s="4" t="n">
-        <v>54</v>
+        <v>25</v>
       </c>
       <c r="L49" s="4" t="n">
         <v>0</v>
       </c>
       <c r="M49" s="4" t="n">
-        <v>48.21</v>
+        <v>56.82</v>
       </c>
       <c r="N49" s="4" t="inlineStr">
         <is>
@@ -21613,7 +21613,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
@@ -21621,7 +21621,7 @@
     <col width="11" customWidth="1" min="3" max="3"/>
     <col width="39" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
     <col width="18" customWidth="1" min="9" max="9"/>
@@ -21631,7 +21631,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>VISITAS DUPLICADAS (6 registros) — CONFIRME E EXCLUA NO SISTEMA</t>
+          <t>VISITAS DUPLICADAS (2 registros) — CONFIRME E EXCLUA NO SISTEMA</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -21709,7 +21709,7 @@
       </c>
       <c r="C3" s="21" t="inlineStr">
         <is>
-          <t>17019173</t>
+          <t>17019195</t>
         </is>
       </c>
       <c r="D3" s="20" t="inlineStr">
@@ -21719,27 +21719,27 @@
       </c>
       <c r="E3" s="20" t="inlineStr">
         <is>
-          <t>Q029</t>
+          <t>Q030</t>
         </is>
       </c>
       <c r="F3" s="20" t="inlineStr">
         <is>
-          <t>Rua CARAMBOLEIRA</t>
+          <t>Rua AMEIXEIRA</t>
         </is>
       </c>
       <c r="G3" s="20" t="inlineStr">
         <is>
-          <t>105 - 1 - TB</t>
+          <t>106 - 2 - TB</t>
         </is>
       </c>
       <c r="H3" s="20" t="inlineStr">
         <is>
-          <t>19/08/2026 09:36</t>
+          <t>19/08/2026 14:18</t>
         </is>
       </c>
       <c r="I3" s="20" t="inlineStr">
         <is>
-          <t>19/08/2026 09:36</t>
+          <t>19/08/2026 14:18</t>
         </is>
       </c>
       <c r="J3" s="20" t="inlineStr">
@@ -21761,7 +21761,7 @@
       </c>
       <c r="C4" s="21" t="inlineStr">
         <is>
-          <t>17019174</t>
+          <t>17019196</t>
         </is>
       </c>
       <c r="D4" s="20" t="inlineStr">
@@ -21771,27 +21771,27 @@
       </c>
       <c r="E4" s="20" t="inlineStr">
         <is>
-          <t>Q029</t>
+          <t>Q030</t>
         </is>
       </c>
       <c r="F4" s="20" t="inlineStr">
         <is>
-          <t>Rua CARAMBOLEIRA</t>
+          <t>Rua AMEIXEIRA</t>
         </is>
       </c>
       <c r="G4" s="20" t="inlineStr">
         <is>
-          <t>105 - 1 - TB</t>
+          <t>106 - 2 - TB</t>
         </is>
       </c>
       <c r="H4" s="20" t="inlineStr">
         <is>
-          <t>19/08/2026 09:36</t>
+          <t>19/08/2026 14:18</t>
         </is>
       </c>
       <c r="I4" s="20" t="inlineStr">
         <is>
-          <t>19/08/2026 09:42</t>
+          <t>19/08/2026 14:24</t>
         </is>
       </c>
       <c r="J4" s="20" t="inlineStr">
@@ -21800,226 +21800,14 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="20" t="inlineStr">
-        <is>
-          <t>Claine Luisa Figueiredo Torraca</t>
-        </is>
-      </c>
-      <c r="B5" s="20" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C5" s="21" t="inlineStr">
-        <is>
-          <t>17019195</t>
-        </is>
-      </c>
-      <c r="D5" s="20" t="inlineStr">
-        <is>
-          <t>449 - ÁREA C RESIDENCIAL PONTA PORÃ 1</t>
-        </is>
-      </c>
-      <c r="E5" s="20" t="inlineStr">
-        <is>
-          <t>Q030</t>
-        </is>
-      </c>
-      <c r="F5" s="20" t="inlineStr">
-        <is>
-          <t>Rua AMEIXEIRA</t>
-        </is>
-      </c>
-      <c r="G5" s="20" t="inlineStr">
-        <is>
-          <t>106 - 2 - TB</t>
-        </is>
-      </c>
-      <c r="H5" s="20" t="inlineStr">
-        <is>
-          <t>19/08/2026 14:18</t>
-        </is>
-      </c>
-      <c r="I5" s="20" t="inlineStr">
-        <is>
-          <t>19/08/2026 14:18</t>
-        </is>
-      </c>
-      <c r="J5" s="20" t="inlineStr">
-        <is>
-          <t>Mesmo horário de chegada + imóvel</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="20" t="inlineStr">
-        <is>
-          <t>Claine Luisa Figueiredo Torraca</t>
-        </is>
-      </c>
-      <c r="B6" s="20" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C6" s="21" t="inlineStr">
-        <is>
-          <t>17019196</t>
-        </is>
-      </c>
-      <c r="D6" s="20" t="inlineStr">
-        <is>
-          <t>449 - ÁREA C RESIDENCIAL PONTA PORÃ 1</t>
-        </is>
-      </c>
-      <c r="E6" s="20" t="inlineStr">
-        <is>
-          <t>Q030</t>
-        </is>
-      </c>
-      <c r="F6" s="20" t="inlineStr">
-        <is>
-          <t>Rua AMEIXEIRA</t>
-        </is>
-      </c>
-      <c r="G6" s="20" t="inlineStr">
-        <is>
-          <t>106 - 2 - TB</t>
-        </is>
-      </c>
-      <c r="H6" s="20" t="inlineStr">
-        <is>
-          <t>19/08/2026 14:18</t>
-        </is>
-      </c>
-      <c r="I6" s="20" t="inlineStr">
-        <is>
-          <t>19/08/2026 14:24</t>
-        </is>
-      </c>
-      <c r="J6" s="20" t="inlineStr">
-        <is>
-          <t>Mesmo horário de chegada + imóvel</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="20" t="inlineStr">
-        <is>
-          <t>Claine Luisa Figueiredo Torraca</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C7" s="21" t="inlineStr">
-        <is>
-          <t>17019200</t>
-        </is>
-      </c>
-      <c r="D7" s="20" t="inlineStr">
-        <is>
-          <t>449 - ÁREA C RESIDENCIAL PONTA PORÃ 1</t>
-        </is>
-      </c>
-      <c r="E7" s="20" t="inlineStr">
-        <is>
-          <t>Q030</t>
-        </is>
-      </c>
-      <c r="F7" s="20" t="inlineStr">
-        <is>
-          <t>Rua AMEIXEIRA</t>
-        </is>
-      </c>
-      <c r="G7" s="20" t="inlineStr">
-        <is>
-          <t>55 - 1 - TB</t>
-        </is>
-      </c>
-      <c r="H7" s="20" t="inlineStr">
-        <is>
-          <t>19/08/2026 14:33</t>
-        </is>
-      </c>
-      <c r="I7" s="20" t="inlineStr">
-        <is>
-          <t>19/08/2026 14:33</t>
-        </is>
-      </c>
-      <c r="J7" s="20" t="inlineStr">
-        <is>
-          <t>Mesmo horário de chegada + imóvel</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="20" t="inlineStr">
-        <is>
-          <t>Claine Luisa Figueiredo Torraca</t>
-        </is>
-      </c>
-      <c r="B8" s="20" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C8" s="21" t="inlineStr">
-        <is>
-          <t>17019201</t>
-        </is>
-      </c>
-      <c r="D8" s="20" t="inlineStr">
-        <is>
-          <t>449 - ÁREA C RESIDENCIAL PONTA PORÃ 1</t>
-        </is>
-      </c>
-      <c r="E8" s="20" t="inlineStr">
-        <is>
-          <t>Q030</t>
-        </is>
-      </c>
-      <c r="F8" s="20" t="inlineStr">
-        <is>
-          <t>Rua AMEIXEIRA</t>
-        </is>
-      </c>
-      <c r="G8" s="20" t="inlineStr">
-        <is>
-          <t>55 - 1 - TB</t>
-        </is>
-      </c>
-      <c r="H8" s="20" t="inlineStr">
-        <is>
-          <t>19/08/2026 14:33</t>
-        </is>
-      </c>
-      <c r="I8" s="20" t="inlineStr">
-        <is>
-          <t>19/08/2026 14:38</t>
-        </is>
-      </c>
-      <c r="J8" s="20" t="inlineStr">
-        <is>
-          <t>Mesmo horário de chegada + imóvel</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A2:J8"/>
+  <autoFilter ref="A2:J4"/>
   <mergeCells count="1">
     <mergeCell ref="A1:J1"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId6"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -22031,7 +21819,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K30"/>
+  <dimension ref="A1:K26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
@@ -22050,7 +21838,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>VISITAS EM SEQUÊNCIA SUSPEITA (10 registros) — CHEGADA NO MESMO MINUTO DA VISITA ANTERIOR</t>
+          <t>VISITAS EM SEQUÊNCIA SUSPEITA (6 registros) — CHEGADA NO MESMO MINUTO DA VISITA ANTERIOR</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -22241,7 +22029,7 @@
       </c>
       <c r="D5" s="24" t="inlineStr">
         <is>
-          <t>17019173</t>
+          <t>17019195</t>
         </is>
       </c>
       <c r="E5" s="23" t="inlineStr">
@@ -22251,27 +22039,27 @@
       </c>
       <c r="F5" s="23" t="inlineStr">
         <is>
-          <t>Q029</t>
+          <t>Q030</t>
         </is>
       </c>
       <c r="G5" s="23" t="inlineStr">
         <is>
-          <t>Rua CARAMBOLEIRA</t>
+          <t>Rua AMEIXEIRA</t>
         </is>
       </c>
       <c r="H5" s="23" t="inlineStr">
         <is>
-          <t>105 - 1 - TB</t>
+          <t>106 - 2 - TB</t>
         </is>
       </c>
       <c r="I5" s="23" t="inlineStr">
         <is>
-          <t>19/08/2026 09:36</t>
+          <t>19/08/2026 14:18</t>
         </is>
       </c>
       <c r="J5" s="23" t="inlineStr">
         <is>
-          <t>19/08/2026 09:36</t>
+          <t>19/08/2026 14:18</t>
         </is>
       </c>
       <c r="K5" s="23" t="inlineStr"/>
@@ -22292,7 +22080,7 @@
       </c>
       <c r="D6" s="24" t="inlineStr">
         <is>
-          <t>17019174</t>
+          <t>17019196</t>
         </is>
       </c>
       <c r="E6" s="23" t="inlineStr">
@@ -22302,27 +22090,27 @@
       </c>
       <c r="F6" s="23" t="inlineStr">
         <is>
-          <t>Q029</t>
+          <t>Q030</t>
         </is>
       </c>
       <c r="G6" s="23" t="inlineStr">
         <is>
-          <t>Rua CARAMBOLEIRA</t>
+          <t>Rua AMEIXEIRA</t>
         </is>
       </c>
       <c r="H6" s="23" t="inlineStr">
         <is>
-          <t>105 - 1 - TB</t>
+          <t>106 - 2 - TB</t>
         </is>
       </c>
       <c r="I6" s="23" t="inlineStr">
         <is>
-          <t>19/08/2026 09:36</t>
+          <t>19/08/2026 14:18</t>
         </is>
       </c>
       <c r="J6" s="23" t="inlineStr">
         <is>
-          <t>19/08/2026 09:42</t>
+          <t>19/08/2026 14:24</t>
         </is>
       </c>
       <c r="K6" s="23" t="n">
@@ -22332,7 +22120,7 @@
     <row r="7">
       <c r="A7" s="23" t="inlineStr">
         <is>
-          <t>Claine Luisa Figueiredo Torraca</t>
+          <t>Emidio Rainer Vilhalba</t>
         </is>
       </c>
       <c r="B7" s="23" t="inlineStr">
@@ -22341,41 +22129,41 @@
         </is>
       </c>
       <c r="C7" s="23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D7" s="24" t="inlineStr">
         <is>
-          <t>17019195</t>
+          <t>16959229</t>
         </is>
       </c>
       <c r="E7" s="23" t="inlineStr">
         <is>
-          <t>449 - ÁREA C RESIDENCIAL PONTA PORÃ 1</t>
+          <t>430 - VILA RENÔ</t>
         </is>
       </c>
       <c r="F7" s="23" t="inlineStr">
         <is>
-          <t>Q030</t>
+          <t>Q034</t>
         </is>
       </c>
       <c r="G7" s="23" t="inlineStr">
         <is>
-          <t>Rua AMEIXEIRA</t>
+          <t>Avenida URUMBELA</t>
         </is>
       </c>
       <c r="H7" s="23" t="inlineStr">
         <is>
-          <t>106 - 2 - TB</t>
+          <t>890 - 10 - R</t>
         </is>
       </c>
       <c r="I7" s="23" t="inlineStr">
         <is>
-          <t>19/08/2026 14:18</t>
+          <t>18/08/2026 09:50</t>
         </is>
       </c>
       <c r="J7" s="23" t="inlineStr">
         <is>
-          <t>19/08/2026 14:18</t>
+          <t>18/08/2026 09:51</t>
         </is>
       </c>
       <c r="K7" s="23" t="inlineStr"/>
@@ -22383,7 +22171,7 @@
     <row r="8">
       <c r="A8" s="23" t="inlineStr">
         <is>
-          <t>Claine Luisa Figueiredo Torraca</t>
+          <t>Emidio Rainer Vilhalba</t>
         </is>
       </c>
       <c r="B8" s="23" t="inlineStr">
@@ -22392,373 +22180,165 @@
         </is>
       </c>
       <c r="C8" s="23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D8" s="24" t="inlineStr">
         <is>
-          <t>17019196</t>
+          <t>16959228</t>
         </is>
       </c>
       <c r="E8" s="23" t="inlineStr">
         <is>
-          <t>449 - ÁREA C RESIDENCIAL PONTA PORÃ 1</t>
+          <t>430 - VILA RENÔ</t>
         </is>
       </c>
       <c r="F8" s="23" t="inlineStr">
         <is>
-          <t>Q030</t>
+          <t>Q034</t>
         </is>
       </c>
       <c r="G8" s="23" t="inlineStr">
         <is>
-          <t>Rua AMEIXEIRA</t>
+          <t>Avenida URUMBELA</t>
         </is>
       </c>
       <c r="H8" s="23" t="inlineStr">
         <is>
-          <t>106 - 2 - TB</t>
+          <t>890 - 9 - C</t>
         </is>
       </c>
       <c r="I8" s="23" t="inlineStr">
         <is>
-          <t>19/08/2026 14:18</t>
+          <t>18/08/2026 09:50</t>
         </is>
       </c>
       <c r="J8" s="23" t="inlineStr">
         <is>
-          <t>19/08/2026 14:24</t>
+          <t>18/08/2026 09:50</t>
         </is>
       </c>
       <c r="K8" s="23" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="23" t="inlineStr">
-        <is>
-          <t>Claine Luisa Figueiredo Torraca</t>
-        </is>
-      </c>
-      <c r="B9" s="23" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C9" s="23" t="n">
-        <v>3</v>
-      </c>
-      <c r="D9" s="24" t="inlineStr">
-        <is>
-          <t>17019200</t>
-        </is>
-      </c>
-      <c r="E9" s="23" t="inlineStr">
-        <is>
-          <t>449 - ÁREA C RESIDENCIAL PONTA PORÃ 1</t>
-        </is>
-      </c>
-      <c r="F9" s="23" t="inlineStr">
-        <is>
-          <t>Q030</t>
-        </is>
-      </c>
-      <c r="G9" s="23" t="inlineStr">
-        <is>
-          <t>Rua AMEIXEIRA</t>
-        </is>
-      </c>
-      <c r="H9" s="23" t="inlineStr">
-        <is>
-          <t>55 - 1 - TB</t>
-        </is>
-      </c>
-      <c r="I9" s="23" t="inlineStr">
-        <is>
-          <t>19/08/2026 14:33</t>
-        </is>
-      </c>
-      <c r="J9" s="23" t="inlineStr">
-        <is>
-          <t>19/08/2026 14:33</t>
-        </is>
-      </c>
-      <c r="K9" s="23" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="23" t="inlineStr">
-        <is>
-          <t>Claine Luisa Figueiredo Torraca</t>
-        </is>
-      </c>
-      <c r="B10" s="23" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C10" s="23" t="n">
-        <v>3</v>
-      </c>
-      <c r="D10" s="24" t="inlineStr">
-        <is>
-          <t>17019201</t>
-        </is>
-      </c>
-      <c r="E10" s="23" t="inlineStr">
-        <is>
-          <t>449 - ÁREA C RESIDENCIAL PONTA PORÃ 1</t>
-        </is>
-      </c>
-      <c r="F10" s="23" t="inlineStr">
-        <is>
-          <t>Q030</t>
-        </is>
-      </c>
-      <c r="G10" s="23" t="inlineStr">
-        <is>
-          <t>Rua AMEIXEIRA</t>
-        </is>
-      </c>
-      <c r="H10" s="23" t="inlineStr">
-        <is>
-          <t>55 - 1 - TB</t>
-        </is>
-      </c>
-      <c r="I10" s="23" t="inlineStr">
-        <is>
-          <t>19/08/2026 14:33</t>
-        </is>
-      </c>
-      <c r="J10" s="23" t="inlineStr">
-        <is>
-          <t>19/08/2026 14:38</t>
-        </is>
-      </c>
-      <c r="K10" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
     <row r="11">
-      <c r="A11" s="23" t="inlineStr">
-        <is>
-          <t>Emidio Rainer Vilhalba</t>
-        </is>
-      </c>
-      <c r="B11" s="23" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C11" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="D11" s="24" t="inlineStr">
-        <is>
-          <t>16959229</t>
-        </is>
-      </c>
-      <c r="E11" s="23" t="inlineStr">
-        <is>
-          <t>430 - VILA RENÔ</t>
-        </is>
-      </c>
-      <c r="F11" s="23" t="inlineStr">
-        <is>
-          <t>Q034</t>
-        </is>
-      </c>
-      <c r="G11" s="23" t="inlineStr">
-        <is>
-          <t>Avenida URUMBELA</t>
-        </is>
-      </c>
-      <c r="H11" s="23" t="inlineStr">
-        <is>
-          <t>890 - 10 - R</t>
-        </is>
-      </c>
-      <c r="I11" s="23" t="inlineStr">
-        <is>
-          <t>18/08/2026 09:50</t>
-        </is>
-      </c>
-      <c r="J11" s="23" t="inlineStr">
-        <is>
-          <t>18/08/2026 09:51</t>
-        </is>
-      </c>
-      <c r="K11" s="23" t="inlineStr"/>
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>LEGENDA — CLASSIFICAÇÃO (baseada em % de Visitas Rápidas)</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="23" t="inlineStr">
-        <is>
-          <t>Emidio Rainer Vilhalba</t>
-        </is>
-      </c>
-      <c r="B12" s="23" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C12" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="D12" s="24" t="inlineStr">
-        <is>
-          <t>16959228</t>
-        </is>
-      </c>
-      <c r="E12" s="23" t="inlineStr">
-        <is>
-          <t>430 - VILA RENÔ</t>
-        </is>
-      </c>
-      <c r="F12" s="23" t="inlineStr">
-        <is>
-          <t>Q034</t>
-        </is>
-      </c>
-      <c r="G12" s="23" t="inlineStr">
-        <is>
-          <t>Avenida URUMBELA</t>
-        </is>
-      </c>
-      <c r="H12" s="23" t="inlineStr">
-        <is>
-          <t>890 - 9 - C</t>
-        </is>
-      </c>
-      <c r="I12" s="23" t="inlineStr">
-        <is>
-          <t>18/08/2026 09:50</t>
-        </is>
-      </c>
-      <c r="J12" s="23" t="inlineStr">
-        <is>
-          <t>18/08/2026 09:50</t>
-        </is>
-      </c>
-      <c r="K12" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>LEGENDA — CLASSIFICAÇÃO (baseada em % de Visitas Rápidas)</t>
-        </is>
-      </c>
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>🟢 NORMAL</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>% Rápidas até 10%</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="11" t="inlineStr">
+        <is>
+          <t>🟡 ATENÇÃO</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>% Rápidas entre 11% e 20%</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>🔴 CRÍTICO</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>% Rápidas acima de 20%</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="inlineStr">
-        <is>
-          <t>🟢 NORMAL</t>
-        </is>
-      </c>
-      <c r="B16" s="9" t="inlineStr">
-        <is>
-          <t>% Rápidas até 10%</t>
-        </is>
-      </c>
-      <c r="C16" s="10" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="11" t="inlineStr">
-        <is>
-          <t>🟡 ATENÇÃO</t>
-        </is>
-      </c>
-      <c r="B17" s="9" t="inlineStr">
-        <is>
-          <t>% Rápidas entre 11% e 20%</t>
-        </is>
-      </c>
-      <c r="C17" s="10" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="12" t="inlineStr">
-        <is>
-          <t>🔴 CRÍTICO</t>
-        </is>
-      </c>
-      <c r="B18" s="9" t="inlineStr">
-        <is>
-          <t>% Rápidas acima de 20%</t>
-        </is>
-      </c>
-      <c r="C18" s="10" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="13" t="inlineStr">
+      <c r="A16" s="13" t="inlineStr">
         <is>
           <t>⚠️ SEQUÊNCIA SUSPEITA</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="45" customHeight="1">
-      <c r="A21" s="14" t="inlineStr">
+    <row r="17" ht="45" customHeight="1">
+      <c r="A17" s="14" t="inlineStr">
         <is>
           <t>Duas ou mais visitas consecutivas do mesmo agente registradas no MESMO MINUTO de chegada são marcadas como suspeitas (o e-Visita não registra segundos, então o critério de negócio de 50s de diferença equivale, na prática, a 'mesmo minuto') — sugere lançamento em lote no sistema, não visita real de campo. Colunas: 'Visitas em Sequência Suspeita' (total de visitas envolvidas) e 'Maior Sequência Suspeita' (maior número de visitas seguidas nessa condição). Na aba 'Visitas Suspeitas', a coluna 'Diferença p/ Anterior (s)*' fica em branco quando o alerta da linha veio do par com a visita SEGUINTE (não da anterior).</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="15" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="15" t="inlineStr">
         <is>
           <t>🍽️ VISITAS NO HORÁRIO DE ALMOÇO</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="70" customHeight="1">
-      <c r="A24" s="14" t="inlineStr">
+    <row r="20" ht="70" customHeight="1">
+      <c r="A20" s="14" t="inlineStr">
         <is>
           <t>Coluna 'Visitas no Almoço (11h15-12h45)' conta as visitas com chegada registrada nesse intervalo — o horário oficial de almoço é 11h15 às 12h45, JÁ COM 15 MINUTOS DE TOLERÂNCIA em cada borda (visitas entre 11h-11h15 ou 12h45-13h não são tratadas como violação, só como 'fora do expediente' genérico) — use para checar se o agente está trabalhando no horário de almoço ou se há erro de lançamento. Essas visitas ficam de fora do cálculo de 'Início/Fim Manhã' e 'Início/Fim Tarde', que usam a primeira chegada e a última saída de cada dia (não a média de todos os horários), para refletir melhor o início e o fim reais do expediente.</t>
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" s="16" t="inlineStr">
+        <is>
+          <t>💰 HORAS TRABALHADAS, HORAS ÚTEIS E CUSTO DA HORA ÚTIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="60" customHeight="1">
+      <c r="A23" s="14" t="inlineStr">
+        <is>
+          <t>'Horas Trabalhadas' = jornada total do dia (primeira chegada até a última saída), descontando a sobreposição com o horário de almoço — depois tira-se a média entre os dias/semanas trabalhados, 'Horas Úteis' = soma das durações de visita no dia (tempo realmente dentro de imóveis), sem contar deslocamento entre visitas, 'Custo Hora Útil' = salário mensal do agente (R$ 4863,00, equivalente a 3 salários mínimos federais) dividido pelas horas úteis mensais estimadas (Média Horas Úteis/Dia × 22 dias úteis/mês). Quanto menos tempo o agente passa efetivamente em visita por dia, mais caro fica o custo por hora útil.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="17" t="inlineStr">
+        <is>
+          <t>ℹ️ A lista detalhada de visitas duplicadas (com endereço) está na aba 'Visitas Duplicadas' — use-a para localizar e excluir os registros repetidos.</t>
+        </is>
+      </c>
+    </row>
     <row r="26">
-      <c r="A26" s="16" t="inlineStr">
-        <is>
-          <t>💰 HORAS TRABALHADAS, HORAS ÚTEIS E CUSTO DA HORA ÚTIL</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="60" customHeight="1">
-      <c r="A27" s="14" t="inlineStr">
-        <is>
-          <t>'Horas Trabalhadas' = jornada total do dia (primeira chegada até a última saída), descontando a sobreposição com o horário de almoço — depois tira-se a média entre os dias/semanas trabalhados, 'Horas Úteis' = soma das durações de visita no dia (tempo realmente dentro de imóveis), sem contar deslocamento entre visitas, 'Custo Hora Útil' = salário mensal do agente (R$ 4863,00, equivalente a 3 salários mínimos federais) dividido pelas horas úteis mensais estimadas (Média Horas Úteis/Dia × 22 dias úteis/mês). Quanto menos tempo o agente passa efetivamente em visita por dia, mais caro fica o custo por hora útil.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="17" t="inlineStr">
-        <is>
-          <t>ℹ️ A lista detalhada de visitas duplicadas (com endereço) está na aba 'Visitas Duplicadas' — use-a para localizar e excluir os registros repetidos.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="17" t="inlineStr">
+      <c r="A26" s="17" t="inlineStr">
         <is>
           <t>ℹ️ Visitas com duração NEGATIVA (saída antes da chegada — provável bug do sistema) foram excluídas do cálculo de Média/Mediana e estão detalhadas na aba 'Visitas Negativas', para investigação junto ao suporte do e-Visita.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:K12"/>
+  <autoFilter ref="A2:K8"/>
   <mergeCells count="13">
+    <mergeCell ref="B13:C13"/>
     <mergeCell ref="A20:C20"/>
-    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="B14:C14"/>
     <mergeCell ref="A26:C26"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A30:C30"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="A15:C15"/>
     <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="B12:C12"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId1"/>
@@ -22767,10 +22347,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D6" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D7" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D8" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D9" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D10" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D11" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D12" r:id="rId10"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -23467,7 +23043,7 @@
       </c>
       <c r="G10" s="27" t="inlineStr">
         <is>
-          <t>76 - 1 - TB</t>
+          <t>76 - 1 - OU</t>
         </is>
       </c>
       <c r="H10" s="27" t="inlineStr">
@@ -23637,7 +23213,7 @@
     <row r="14">
       <c r="A14" s="27" t="inlineStr">
         <is>
-          <t>Gabriel Alan de Oliveira Martins</t>
+          <t>Wagner Tarlei Gomes</t>
         </is>
       </c>
       <c r="B14" s="27" t="inlineStr">
@@ -23647,37 +23223,37 @@
       </c>
       <c r="C14" s="28" t="inlineStr">
         <is>
-          <t>17026385</t>
+          <t>17076990</t>
         </is>
       </c>
       <c r="D14" s="27" t="inlineStr">
         <is>
-          <t>401 - EMÍLIO DIAS BRANDÃO</t>
+          <t>400 - JULIA CARDINAL</t>
         </is>
       </c>
       <c r="E14" s="27" t="inlineStr">
         <is>
-          <t>Q013</t>
+          <t>Q012</t>
         </is>
       </c>
       <c r="F14" s="27" t="inlineStr">
         <is>
-          <t>Rua JABAQUARA</t>
+          <t>Rua Anselmo Soares</t>
         </is>
       </c>
       <c r="G14" s="27" t="inlineStr">
         <is>
-          <t>26 - 2 - OU</t>
+          <t>28 - 2 - TB</t>
         </is>
       </c>
       <c r="H14" s="27" t="inlineStr">
         <is>
-          <t>19/08/2026 09:27</t>
+          <t>19/08/2026 15:03</t>
         </is>
       </c>
       <c r="I14" s="27" t="inlineStr">
         <is>
-          <t>19/08/2026 09:53</t>
+          <t>19/08/2026 15:29</t>
         </is>
       </c>
       <c r="J14" s="27" t="n">
@@ -23687,7 +23263,7 @@
     <row r="15">
       <c r="A15" s="27" t="inlineStr">
         <is>
-          <t>Wagner Tarlei Gomes</t>
+          <t>Gabriel Alan de Oliveira Martins</t>
         </is>
       </c>
       <c r="B15" s="27" t="inlineStr">
@@ -23697,37 +23273,37 @@
       </c>
       <c r="C15" s="28" t="inlineStr">
         <is>
-          <t>17076990</t>
+          <t>17026385</t>
         </is>
       </c>
       <c r="D15" s="27" t="inlineStr">
         <is>
-          <t>400 - JULIA CARDINAL</t>
+          <t>401 - EMÍLIO DIAS BRANDÃO</t>
         </is>
       </c>
       <c r="E15" s="27" t="inlineStr">
         <is>
-          <t>Q012</t>
+          <t>Q013</t>
         </is>
       </c>
       <c r="F15" s="27" t="inlineStr">
         <is>
-          <t>Rua Anselmo Soares</t>
+          <t>Rua JABAQUARA</t>
         </is>
       </c>
       <c r="G15" s="27" t="inlineStr">
         <is>
-          <t>28 - 2 - TB</t>
+          <t>26 - 2 - OU</t>
         </is>
       </c>
       <c r="H15" s="27" t="inlineStr">
         <is>
-          <t>19/08/2026 15:03</t>
+          <t>19/08/2026 09:27</t>
         </is>
       </c>
       <c r="I15" s="27" t="inlineStr">
         <is>
-          <t>19/08/2026 15:29</t>
+          <t>19/08/2026 09:53</t>
         </is>
       </c>
       <c r="J15" s="27" t="n">
@@ -24537,7 +24113,7 @@
     <row r="32">
       <c r="A32" s="27" t="inlineStr">
         <is>
-          <t>Ana Gabriela Silva Garcete</t>
+          <t>Evelyn Santana Santos Oliveira</t>
         </is>
       </c>
       <c r="B32" s="27" t="inlineStr">
@@ -24547,7 +24123,7 @@
       </c>
       <c r="C32" s="28" t="inlineStr">
         <is>
-          <t>17051418</t>
+          <t>17034408</t>
         </is>
       </c>
       <c r="D32" s="27" t="inlineStr">
@@ -24557,27 +24133,27 @@
       </c>
       <c r="E32" s="27" t="inlineStr">
         <is>
-          <t>Q031</t>
+          <t>Q013</t>
         </is>
       </c>
       <c r="F32" s="27" t="inlineStr">
         <is>
-          <t>Rua AFONSO DE ALBUQUERQUE</t>
+          <t>Rua JABAQUARA</t>
         </is>
       </c>
       <c r="G32" s="27" t="inlineStr">
         <is>
-          <t>231 - 3 - R</t>
+          <t>1370 - 4 - R</t>
         </is>
       </c>
       <c r="H32" s="27" t="inlineStr">
         <is>
-          <t>19/08/2026 14:18</t>
+          <t>19/08/2026 10:05</t>
         </is>
       </c>
       <c r="I32" s="27" t="inlineStr">
         <is>
-          <t>19/08/2026 14:36</t>
+          <t>19/08/2026 10:23</t>
         </is>
       </c>
       <c r="J32" s="27" t="n">
@@ -24687,7 +24263,7 @@
     <row r="35">
       <c r="A35" s="27" t="inlineStr">
         <is>
-          <t>Evelyn Santana Santos Oliveira</t>
+          <t>Ana Gabriela Silva Garcete</t>
         </is>
       </c>
       <c r="B35" s="27" t="inlineStr">
@@ -24697,7 +24273,7 @@
       </c>
       <c r="C35" s="28" t="inlineStr">
         <is>
-          <t>17034408</t>
+          <t>17051418</t>
         </is>
       </c>
       <c r="D35" s="27" t="inlineStr">
@@ -24707,27 +24283,27 @@
       </c>
       <c r="E35" s="27" t="inlineStr">
         <is>
-          <t>Q013</t>
+          <t>Q031</t>
         </is>
       </c>
       <c r="F35" s="27" t="inlineStr">
         <is>
-          <t>Rua JABAQUARA</t>
+          <t>Rua AFONSO DE ALBUQUERQUE</t>
         </is>
       </c>
       <c r="G35" s="27" t="inlineStr">
         <is>
-          <t>1370 - 4 - R</t>
+          <t>231 - 3 - R</t>
         </is>
       </c>
       <c r="H35" s="27" t="inlineStr">
         <is>
-          <t>19/08/2026 10:05</t>
+          <t>19/08/2026 14:18</t>
         </is>
       </c>
       <c r="I35" s="27" t="inlineStr">
         <is>
-          <t>19/08/2026 10:23</t>
+          <t>19/08/2026 14:36</t>
         </is>
       </c>
       <c r="J35" s="27" t="n">
@@ -24847,7 +24423,7 @@
       </c>
       <c r="C38" s="28" t="inlineStr">
         <is>
-          <t>16960075</t>
+          <t>16960061</t>
         </is>
       </c>
       <c r="D38" s="27" t="inlineStr">
@@ -24867,17 +24443,17 @@
       </c>
       <c r="G38" s="27" t="inlineStr">
         <is>
-          <t>58 - R</t>
+          <t>118 - R</t>
         </is>
       </c>
       <c r="H38" s="27" t="inlineStr">
         <is>
-          <t>17/08/2026 15:47</t>
+          <t>17/08/2026 10:37</t>
         </is>
       </c>
       <c r="I38" s="27" t="inlineStr">
         <is>
-          <t>17/08/2026 16:04</t>
+          <t>17/08/2026 10:54</t>
         </is>
       </c>
       <c r="J38" s="27" t="n">
@@ -24887,7 +24463,7 @@
     <row r="39">
       <c r="A39" s="27" t="inlineStr">
         <is>
-          <t>Ana Gabriela Silva Garcete</t>
+          <t>Evelyn Santana Santos Oliveira</t>
         </is>
       </c>
       <c r="B39" s="27" t="inlineStr">
@@ -24897,37 +24473,37 @@
       </c>
       <c r="C39" s="28" t="inlineStr">
         <is>
-          <t>17070286</t>
+          <t>17022532</t>
         </is>
       </c>
       <c r="D39" s="27" t="inlineStr">
         <is>
-          <t>401 - EMÍLIO DIAS BRANDÃO</t>
+          <t>410 - SALGADO FILHO</t>
         </is>
       </c>
       <c r="E39" s="27" t="inlineStr">
         <is>
-          <t>Q029</t>
+          <t>Q023</t>
         </is>
       </c>
       <c r="F39" s="27" t="inlineStr">
         <is>
-          <t>Rua GUAÍBA</t>
+          <t>Rua MARINGA</t>
         </is>
       </c>
       <c r="G39" s="27" t="inlineStr">
         <is>
-          <t>1262 - C</t>
+          <t>807 - R</t>
         </is>
       </c>
       <c r="H39" s="27" t="inlineStr">
         <is>
-          <t>21/08/2026 14:40</t>
+          <t>17/08/2026 09:53</t>
         </is>
       </c>
       <c r="I39" s="27" t="inlineStr">
         <is>
-          <t>21/08/2026 14:57</t>
+          <t>17/08/2026 10:10</t>
         </is>
       </c>
       <c r="J39" s="27" t="n">
@@ -24937,7 +24513,7 @@
     <row r="40">
       <c r="A40" s="27" t="inlineStr">
         <is>
-          <t>Ana Gabriela Silva Garcete</t>
+          <t>Wagner Tarlei Gomes</t>
         </is>
       </c>
       <c r="B40" s="27" t="inlineStr">
@@ -24947,7 +24523,7 @@
       </c>
       <c r="C40" s="28" t="inlineStr">
         <is>
-          <t>17070288</t>
+          <t>17064916</t>
         </is>
       </c>
       <c r="D40" s="27" t="inlineStr">
@@ -24957,27 +24533,27 @@
       </c>
       <c r="E40" s="27" t="inlineStr">
         <is>
-          <t>Q019</t>
+          <t>Q007</t>
         </is>
       </c>
       <c r="F40" s="27" t="inlineStr">
         <is>
-          <t>Rua JABAQUARA</t>
+          <t>Rua RIACHO DOCE</t>
         </is>
       </c>
       <c r="G40" s="27" t="inlineStr">
         <is>
-          <t>1490 - C</t>
+          <t>78 - R</t>
         </is>
       </c>
       <c r="H40" s="27" t="inlineStr">
         <is>
-          <t>21/08/2026 15:07</t>
+          <t>18/08/2026 14:00</t>
         </is>
       </c>
       <c r="I40" s="27" t="inlineStr">
         <is>
-          <t>21/08/2026 15:24</t>
+          <t>18/08/2026 14:17</t>
         </is>
       </c>
       <c r="J40" s="27" t="n">
@@ -24987,7 +24563,7 @@
     <row r="41">
       <c r="A41" s="27" t="inlineStr">
         <is>
-          <t>Wagner Tarlei Gomes</t>
+          <t>Ana Gabriela Silva Garcete</t>
         </is>
       </c>
       <c r="B41" s="27" t="inlineStr">
@@ -24997,7 +24573,7 @@
       </c>
       <c r="C41" s="28" t="inlineStr">
         <is>
-          <t>17064916</t>
+          <t>17070286</t>
         </is>
       </c>
       <c r="D41" s="27" t="inlineStr">
@@ -25007,27 +24583,27 @@
       </c>
       <c r="E41" s="27" t="inlineStr">
         <is>
-          <t>Q007</t>
+          <t>Q029</t>
         </is>
       </c>
       <c r="F41" s="27" t="inlineStr">
         <is>
-          <t>Rua RIACHO DOCE</t>
+          <t>Rua GUAÍBA</t>
         </is>
       </c>
       <c r="G41" s="27" t="inlineStr">
         <is>
-          <t>78 - R</t>
+          <t>1262 - C</t>
         </is>
       </c>
       <c r="H41" s="27" t="inlineStr">
         <is>
-          <t>18/08/2026 14:00</t>
+          <t>21/08/2026 14:40</t>
         </is>
       </c>
       <c r="I41" s="27" t="inlineStr">
         <is>
-          <t>18/08/2026 14:17</t>
+          <t>21/08/2026 14:57</t>
         </is>
       </c>
       <c r="J41" s="27" t="n">
@@ -25047,37 +24623,37 @@
       </c>
       <c r="C42" s="28" t="inlineStr">
         <is>
-          <t>16971696</t>
+          <t>17070288</t>
         </is>
       </c>
       <c r="D42" s="27" t="inlineStr">
         <is>
-          <t>410 - SALGADO FILHO</t>
+          <t>401 - EMÍLIO DIAS BRANDÃO</t>
         </is>
       </c>
       <c r="E42" s="27" t="inlineStr">
         <is>
-          <t>Q014</t>
+          <t>Q019</t>
         </is>
       </c>
       <c r="F42" s="27" t="inlineStr">
         <is>
-          <t>Rua TENENTE SAMUEL DE ALMEIDA</t>
+          <t>Rua JABAQUARA</t>
         </is>
       </c>
       <c r="G42" s="27" t="inlineStr">
         <is>
-          <t>630 - 1 - R</t>
+          <t>1490 - C</t>
         </is>
       </c>
       <c r="H42" s="27" t="inlineStr">
         <is>
-          <t>17/08/2026 10:58</t>
+          <t>21/08/2026 15:07</t>
         </is>
       </c>
       <c r="I42" s="27" t="inlineStr">
         <is>
-          <t>17/08/2026 11:15</t>
+          <t>21/08/2026 15:24</t>
         </is>
       </c>
       <c r="J42" s="27" t="n">
@@ -25087,7 +24663,7 @@
     <row r="43">
       <c r="A43" s="27" t="inlineStr">
         <is>
-          <t>Evelyn Santana Santos Oliveira</t>
+          <t>Ana Gabriela Silva Garcete</t>
         </is>
       </c>
       <c r="B43" s="27" t="inlineStr">
@@ -25097,7 +24673,7 @@
       </c>
       <c r="C43" s="28" t="inlineStr">
         <is>
-          <t>17022532</t>
+          <t>16971696</t>
         </is>
       </c>
       <c r="D43" s="27" t="inlineStr">
@@ -25107,27 +24683,27 @@
       </c>
       <c r="E43" s="27" t="inlineStr">
         <is>
-          <t>Q023</t>
+          <t>Q014</t>
         </is>
       </c>
       <c r="F43" s="27" t="inlineStr">
         <is>
-          <t>Rua MARINGA</t>
+          <t>Rua TENENTE SAMUEL DE ALMEIDA</t>
         </is>
       </c>
       <c r="G43" s="27" t="inlineStr">
         <is>
-          <t>807 - R</t>
+          <t>630 - 1 - R</t>
         </is>
       </c>
       <c r="H43" s="27" t="inlineStr">
         <is>
-          <t>17/08/2026 09:53</t>
+          <t>17/08/2026 10:58</t>
         </is>
       </c>
       <c r="I43" s="27" t="inlineStr">
         <is>
-          <t>17/08/2026 10:10</t>
+          <t>17/08/2026 11:15</t>
         </is>
       </c>
       <c r="J43" s="27" t="n">
@@ -25137,47 +24713,47 @@
     <row r="44">
       <c r="A44" s="27" t="inlineStr">
         <is>
-          <t>Gilmar Bitencourt Luiz</t>
+          <t>Miglidiane Maciel Ajala</t>
         </is>
       </c>
       <c r="B44" s="27" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 3</t>
         </is>
       </c>
       <c r="C44" s="28" t="inlineStr">
         <is>
-          <t>17073314</t>
+          <t>17041447</t>
         </is>
       </c>
       <c r="D44" s="27" t="inlineStr">
         <is>
-          <t>418 - CENTRO 4</t>
+          <t>425 - JARDIM ESTORIL</t>
         </is>
       </c>
       <c r="E44" s="27" t="inlineStr">
         <is>
-          <t>Q011</t>
+          <t>Q038</t>
         </is>
       </c>
       <c r="F44" s="27" t="inlineStr">
         <is>
-          <t>Avenida ANTONIO JOAO</t>
+          <t>Rua DAS PEROBAS</t>
         </is>
       </c>
       <c r="G44" s="27" t="inlineStr">
         <is>
-          <t>1371 - OU</t>
+          <t>1018 - R</t>
         </is>
       </c>
       <c r="H44" s="27" t="inlineStr">
         <is>
-          <t>20/08/2026 15:23</t>
+          <t>20/08/2026 14:48</t>
         </is>
       </c>
       <c r="I44" s="27" t="inlineStr">
         <is>
-          <t>20/08/2026 15:40</t>
+          <t>20/08/2026 15:05</t>
         </is>
       </c>
       <c r="J44" s="27" t="n">
@@ -25187,7 +24763,7 @@
     <row r="45">
       <c r="A45" s="27" t="inlineStr">
         <is>
-          <t>Gilmar Bitencourt Luiz</t>
+          <t>William Anderson Chamorro Tavares</t>
         </is>
       </c>
       <c r="B45" s="27" t="inlineStr">
@@ -25197,37 +24773,37 @@
       </c>
       <c r="C45" s="28" t="inlineStr">
         <is>
-          <t>17073307</t>
+          <t>17043629</t>
         </is>
       </c>
       <c r="D45" s="27" t="inlineStr">
         <is>
-          <t>418 - CENTRO 4</t>
+          <t>413 - BAIRRO DA GRANJA</t>
         </is>
       </c>
       <c r="E45" s="27" t="inlineStr">
         <is>
-          <t>Q011</t>
+          <t>Q034</t>
         </is>
       </c>
       <c r="F45" s="27" t="inlineStr">
         <is>
-          <t>Avenida ANTONIO JOAO</t>
+          <t>Rua ARAPONGAS</t>
         </is>
       </c>
       <c r="G45" s="27" t="inlineStr">
         <is>
-          <t>1477 - R</t>
+          <t>142 - R</t>
         </is>
       </c>
       <c r="H45" s="27" t="inlineStr">
         <is>
-          <t>20/08/2026 13:54</t>
+          <t>20/08/2026 15:52</t>
         </is>
       </c>
       <c r="I45" s="27" t="inlineStr">
         <is>
-          <t>20/08/2026 14:11</t>
+          <t>20/08/2026 16:09</t>
         </is>
       </c>
       <c r="J45" s="27" t="n">
@@ -25247,7 +24823,7 @@
       </c>
       <c r="C46" s="28" t="inlineStr">
         <is>
-          <t>17073270</t>
+          <t>17073314</t>
         </is>
       </c>
       <c r="D46" s="27" t="inlineStr">
@@ -25262,22 +24838,22 @@
       </c>
       <c r="F46" s="27" t="inlineStr">
         <is>
-          <t>Avenida BRASIL</t>
+          <t>Avenida ANTONIO JOAO</t>
         </is>
       </c>
       <c r="G46" s="27" t="inlineStr">
         <is>
-          <t>3974 - 33 - R - 30</t>
+          <t>1371 - OU</t>
         </is>
       </c>
       <c r="H46" s="27" t="inlineStr">
         <is>
-          <t>19/08/2026 09:22</t>
+          <t>20/08/2026 15:23</t>
         </is>
       </c>
       <c r="I46" s="27" t="inlineStr">
         <is>
-          <t>19/08/2026 09:39</t>
+          <t>20/08/2026 15:40</t>
         </is>
       </c>
       <c r="J46" s="27" t="n">
@@ -25287,47 +24863,47 @@
     <row r="47">
       <c r="A47" s="27" t="inlineStr">
         <is>
-          <t>Alana Amanda Fernandes Ovelar</t>
+          <t>Gilmar Bitencourt Luiz</t>
         </is>
       </c>
       <c r="B47" s="27" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="C47" s="28" t="inlineStr">
         <is>
-          <t>17014581</t>
+          <t>17073270</t>
         </is>
       </c>
       <c r="D47" s="27" t="inlineStr">
         <is>
-          <t>433 - ÁREA A - RESIDENCIAL PONTA PORÃ 1</t>
+          <t>418 - CENTRO 4</t>
         </is>
       </c>
       <c r="E47" s="27" t="inlineStr">
         <is>
-          <t>Q016</t>
+          <t>Q011</t>
         </is>
       </c>
       <c r="F47" s="27" t="inlineStr">
         <is>
-          <t>Rua GUARANTA</t>
+          <t>Avenida BRASIL</t>
         </is>
       </c>
       <c r="G47" s="27" t="inlineStr">
         <is>
-          <t>295 - 1 - TB</t>
+          <t>3974 - 33 - R - 30</t>
         </is>
       </c>
       <c r="H47" s="27" t="inlineStr">
         <is>
-          <t>19/08/2026 09:45</t>
+          <t>19/08/2026 09:22</t>
         </is>
       </c>
       <c r="I47" s="27" t="inlineStr">
         <is>
-          <t>19/08/2026 10:02</t>
+          <t>19/08/2026 09:39</t>
         </is>
       </c>
       <c r="J47" s="27" t="n">
@@ -25397,7 +24973,7 @@
       </c>
       <c r="C49" s="28" t="inlineStr">
         <is>
-          <t>16960061</t>
+          <t>16960075</t>
         </is>
       </c>
       <c r="D49" s="27" t="inlineStr">
@@ -25417,17 +24993,17 @@
       </c>
       <c r="G49" s="27" t="inlineStr">
         <is>
-          <t>118 - R</t>
+          <t>58 - R</t>
         </is>
       </c>
       <c r="H49" s="27" t="inlineStr">
         <is>
-          <t>17/08/2026 10:37</t>
+          <t>17/08/2026 15:47</t>
         </is>
       </c>
       <c r="I49" s="27" t="inlineStr">
         <is>
-          <t>17/08/2026 10:54</t>
+          <t>17/08/2026 16:04</t>
         </is>
       </c>
       <c r="J49" s="27" t="n">
@@ -25437,7 +25013,7 @@
     <row r="50">
       <c r="A50" s="27" t="inlineStr">
         <is>
-          <t>Miglidiane Maciel Ajala</t>
+          <t>Alana Amanda Fernandes Ovelar</t>
         </is>
       </c>
       <c r="B50" s="27" t="inlineStr">
@@ -25447,37 +25023,37 @@
       </c>
       <c r="C50" s="28" t="inlineStr">
         <is>
-          <t>17041447</t>
+          <t>17014581</t>
         </is>
       </c>
       <c r="D50" s="27" t="inlineStr">
         <is>
-          <t>425 - JARDIM ESTORIL</t>
+          <t>433 - ÁREA A - RESIDENCIAL PONTA PORÃ 1</t>
         </is>
       </c>
       <c r="E50" s="27" t="inlineStr">
         <is>
-          <t>Q038</t>
+          <t>Q016</t>
         </is>
       </c>
       <c r="F50" s="27" t="inlineStr">
         <is>
-          <t>Rua DAS PEROBAS</t>
+          <t>Rua GUARANTA</t>
         </is>
       </c>
       <c r="G50" s="27" t="inlineStr">
         <is>
-          <t>1018 - R</t>
+          <t>295 - 1 - TB</t>
         </is>
       </c>
       <c r="H50" s="27" t="inlineStr">
         <is>
-          <t>20/08/2026 14:48</t>
+          <t>19/08/2026 09:45</t>
         </is>
       </c>
       <c r="I50" s="27" t="inlineStr">
         <is>
-          <t>20/08/2026 15:05</t>
+          <t>19/08/2026 10:02</t>
         </is>
       </c>
       <c r="J50" s="27" t="n">
@@ -25487,7 +25063,7 @@
     <row r="51">
       <c r="A51" s="27" t="inlineStr">
         <is>
-          <t>William Anderson Chamorro Tavares</t>
+          <t>Gilmar Bitencourt Luiz</t>
         </is>
       </c>
       <c r="B51" s="27" t="inlineStr">
@@ -25497,37 +25073,37 @@
       </c>
       <c r="C51" s="28" t="inlineStr">
         <is>
-          <t>17043629</t>
+          <t>17073307</t>
         </is>
       </c>
       <c r="D51" s="27" t="inlineStr">
         <is>
-          <t>413 - BAIRRO DA GRANJA</t>
+          <t>418 - CENTRO 4</t>
         </is>
       </c>
       <c r="E51" s="27" t="inlineStr">
         <is>
-          <t>Q034</t>
+          <t>Q011</t>
         </is>
       </c>
       <c r="F51" s="27" t="inlineStr">
         <is>
-          <t>Rua ARAPONGAS</t>
+          <t>Avenida ANTONIO JOAO</t>
         </is>
       </c>
       <c r="G51" s="27" t="inlineStr">
         <is>
-          <t>142 - R</t>
+          <t>1477 - R</t>
         </is>
       </c>
       <c r="H51" s="27" t="inlineStr">
         <is>
-          <t>20/08/2026 15:52</t>
+          <t>20/08/2026 13:54</t>
         </is>
       </c>
       <c r="I51" s="27" t="inlineStr">
         <is>
-          <t>20/08/2026 16:09</t>
+          <t>20/08/2026 14:11</t>
         </is>
       </c>
       <c r="J51" s="27" t="n">
@@ -25537,7 +25113,7 @@
     <row r="52">
       <c r="A52" s="27" t="inlineStr">
         <is>
-          <t>Evelyn Santana Santos Oliveira</t>
+          <t>Wagner Tarlei Gomes</t>
         </is>
       </c>
       <c r="B52" s="27" t="inlineStr">
@@ -25547,37 +25123,37 @@
       </c>
       <c r="C52" s="28" t="inlineStr">
         <is>
-          <t>17033729</t>
+          <t>17076991</t>
         </is>
       </c>
       <c r="D52" s="27" t="inlineStr">
         <is>
-          <t>401 - EMÍLIO DIAS BRANDÃO</t>
+          <t>400 - JULIA CARDINAL</t>
         </is>
       </c>
       <c r="E52" s="27" t="inlineStr">
         <is>
-          <t>Q013</t>
+          <t>Q012</t>
         </is>
       </c>
       <c r="F52" s="27" t="inlineStr">
         <is>
-          <t>Rua VICENTE  AZAMBUJA</t>
+          <t>Rua Anselmo Soares</t>
         </is>
       </c>
       <c r="G52" s="27" t="inlineStr">
         <is>
-          <t>1407 - R</t>
+          <t>700 - OU</t>
         </is>
       </c>
       <c r="H52" s="27" t="inlineStr">
         <is>
-          <t>19/08/2026 08:45</t>
+          <t>19/08/2026 15:29</t>
         </is>
       </c>
       <c r="I52" s="27" t="inlineStr">
         <is>
-          <t>19/08/2026 09:01</t>
+          <t>19/08/2026 15:45</t>
         </is>
       </c>
       <c r="J52" s="27" t="n">
@@ -25587,7 +25163,7 @@
     <row r="53">
       <c r="A53" s="27" t="inlineStr">
         <is>
-          <t>Wagner Tarlei Gomes</t>
+          <t>Ana Gabriela Silva Garcete</t>
         </is>
       </c>
       <c r="B53" s="27" t="inlineStr">
@@ -25597,37 +25173,37 @@
       </c>
       <c r="C53" s="28" t="inlineStr">
         <is>
-          <t>17076991</t>
+          <t>16971668</t>
         </is>
       </c>
       <c r="D53" s="27" t="inlineStr">
         <is>
-          <t>400 - JULIA CARDINAL</t>
+          <t>410 - SALGADO FILHO</t>
         </is>
       </c>
       <c r="E53" s="27" t="inlineStr">
         <is>
-          <t>Q012</t>
+          <t>Q014</t>
         </is>
       </c>
       <c r="F53" s="27" t="inlineStr">
         <is>
-          <t>Rua Anselmo Soares</t>
+          <t>Rua SAO CRISTOVAO</t>
         </is>
       </c>
       <c r="G53" s="27" t="inlineStr">
         <is>
-          <t>700 - OU</t>
+          <t>917 - 8 - R</t>
         </is>
       </c>
       <c r="H53" s="27" t="inlineStr">
         <is>
-          <t>19/08/2026 15:29</t>
+          <t>17/08/2026 08:51</t>
         </is>
       </c>
       <c r="I53" s="27" t="inlineStr">
         <is>
-          <t>19/08/2026 15:45</t>
+          <t>17/08/2026 09:07</t>
         </is>
       </c>
       <c r="J53" s="27" t="n">
@@ -25687,7 +25263,7 @@
     <row r="55">
       <c r="A55" s="27" t="inlineStr">
         <is>
-          <t>Ana Gabriela Silva Garcete</t>
+          <t>Evelyn Santana Santos Oliveira</t>
         </is>
       </c>
       <c r="B55" s="27" t="inlineStr">
@@ -25697,37 +25273,37 @@
       </c>
       <c r="C55" s="28" t="inlineStr">
         <is>
-          <t>16971669</t>
+          <t>17033729</t>
         </is>
       </c>
       <c r="D55" s="27" t="inlineStr">
         <is>
-          <t>410 - SALGADO FILHO</t>
+          <t>401 - EMÍLIO DIAS BRANDÃO</t>
         </is>
       </c>
       <c r="E55" s="27" t="inlineStr">
         <is>
-          <t>Q014</t>
+          <t>Q013</t>
         </is>
       </c>
       <c r="F55" s="27" t="inlineStr">
         <is>
-          <t>Rua SAO CRISTOVAO</t>
+          <t>Rua VICENTE  AZAMBUJA</t>
         </is>
       </c>
       <c r="G55" s="27" t="inlineStr">
         <is>
-          <t>652 - R</t>
+          <t>1407 - R</t>
         </is>
       </c>
       <c r="H55" s="27" t="inlineStr">
         <is>
-          <t>17/08/2026 09:08</t>
+          <t>19/08/2026 08:45</t>
         </is>
       </c>
       <c r="I55" s="27" t="inlineStr">
         <is>
-          <t>17/08/2026 09:24</t>
+          <t>19/08/2026 09:01</t>
         </is>
       </c>
       <c r="J55" s="27" t="n">
@@ -25747,7 +25323,7 @@
       </c>
       <c r="C56" s="28" t="inlineStr">
         <is>
-          <t>16971668</t>
+          <t>16971669</t>
         </is>
       </c>
       <c r="D56" s="27" t="inlineStr">
@@ -25767,17 +25343,17 @@
       </c>
       <c r="G56" s="27" t="inlineStr">
         <is>
-          <t>917 - 8 - R</t>
+          <t>652 - R</t>
         </is>
       </c>
       <c r="H56" s="27" t="inlineStr">
         <is>
-          <t>17/08/2026 08:51</t>
+          <t>17/08/2026 09:08</t>
         </is>
       </c>
       <c r="I56" s="27" t="inlineStr">
         <is>
-          <t>17/08/2026 09:07</t>
+          <t>17/08/2026 09:24</t>
         </is>
       </c>
       <c r="J56" s="27" t="n">
@@ -25837,47 +25413,47 @@
     <row r="58">
       <c r="A58" s="27" t="inlineStr">
         <is>
-          <t>Suely Aguiar Alves Luiz</t>
+          <t>Rozentina Matos de Oliveira</t>
         </is>
       </c>
       <c r="B58" s="27" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="C58" s="28" t="inlineStr">
         <is>
-          <t>17017079</t>
+          <t>17055208</t>
         </is>
       </c>
       <c r="D58" s="27" t="inlineStr">
         <is>
-          <t>420 - FERROVIARIA</t>
+          <t>408 - PARQUE DE EXPOSIÇÕES</t>
         </is>
       </c>
       <c r="E58" s="27" t="inlineStr">
         <is>
-          <t>Q013</t>
+          <t>Q036</t>
         </is>
       </c>
       <c r="F58" s="27" t="inlineStr">
         <is>
-          <t>Travessa PROJETADA 06 FERROVIARIA</t>
+          <t>Rua DIGNO TORRES GIMENEZ</t>
         </is>
       </c>
       <c r="G58" s="27" t="inlineStr">
         <is>
-          <t>57 - R</t>
+          <t>590 - 2 - R</t>
         </is>
       </c>
       <c r="H58" s="27" t="inlineStr">
         <is>
-          <t>17/08/2026 09:16</t>
+          <t>21/08/2026 08:57</t>
         </is>
       </c>
       <c r="I58" s="27" t="inlineStr">
         <is>
-          <t>17/08/2026 09:32</t>
+          <t>21/08/2026 09:13</t>
         </is>
       </c>
       <c r="J58" s="27" t="n">
@@ -25887,47 +25463,47 @@
     <row r="59">
       <c r="A59" s="27" t="inlineStr">
         <is>
-          <t>Rozentina Matos de Oliveira</t>
+          <t>Suely Aguiar Alves Luiz</t>
         </is>
       </c>
       <c r="B59" s="27" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="C59" s="28" t="inlineStr">
         <is>
-          <t>17055208</t>
+          <t>17017079</t>
         </is>
       </c>
       <c r="D59" s="27" t="inlineStr">
         <is>
-          <t>408 - PARQUE DE EXPOSIÇÕES</t>
+          <t>420 - FERROVIARIA</t>
         </is>
       </c>
       <c r="E59" s="27" t="inlineStr">
         <is>
-          <t>Q036</t>
+          <t>Q013</t>
         </is>
       </c>
       <c r="F59" s="27" t="inlineStr">
         <is>
-          <t>Rua DIGNO TORRES GIMENEZ</t>
+          <t>Travessa PROJETADA 06 FERROVIARIA</t>
         </is>
       </c>
       <c r="G59" s="27" t="inlineStr">
         <is>
-          <t>590 - 2 - R</t>
+          <t>57 - R</t>
         </is>
       </c>
       <c r="H59" s="27" t="inlineStr">
         <is>
-          <t>21/08/2026 08:57</t>
+          <t>17/08/2026 09:16</t>
         </is>
       </c>
       <c r="I59" s="27" t="inlineStr">
         <is>
-          <t>21/08/2026 09:13</t>
+          <t>17/08/2026 09:32</t>
         </is>
       </c>
       <c r="J59" s="27" t="n">
@@ -25937,7 +25513,7 @@
     <row r="60">
       <c r="A60" s="27" t="inlineStr">
         <is>
-          <t>Gilmar Bitencourt Luiz</t>
+          <t>Suely Aguiar Alves Luiz</t>
         </is>
       </c>
       <c r="B60" s="27" t="inlineStr">
@@ -25947,37 +25523,37 @@
       </c>
       <c r="C60" s="28" t="inlineStr">
         <is>
-          <t>17073275</t>
+          <t>17017093</t>
         </is>
       </c>
       <c r="D60" s="27" t="inlineStr">
         <is>
-          <t>418 - CENTRO 4</t>
+          <t>420 - FERROVIARIA</t>
         </is>
       </c>
       <c r="E60" s="27" t="inlineStr">
         <is>
-          <t>Q011</t>
+          <t>Q013</t>
         </is>
       </c>
       <c r="F60" s="27" t="inlineStr">
         <is>
-          <t>Avenida BRASIL</t>
+          <t>Travessa PROJETADA 06 FERROVIARIA</t>
         </is>
       </c>
       <c r="G60" s="27" t="inlineStr">
         <is>
-          <t>3986 - R</t>
+          <t>69 - R</t>
         </is>
       </c>
       <c r="H60" s="27" t="inlineStr">
         <is>
-          <t>19/08/2026 10:19</t>
+          <t>17/08/2026 15:44</t>
         </is>
       </c>
       <c r="I60" s="27" t="inlineStr">
         <is>
-          <t>19/08/2026 10:35</t>
+          <t>17/08/2026 16:00</t>
         </is>
       </c>
       <c r="J60" s="27" t="n">
@@ -25987,47 +25563,47 @@
     <row r="61">
       <c r="A61" s="27" t="inlineStr">
         <is>
-          <t>Gisele Lopes Justiniano</t>
+          <t>Gilmar Bitencourt Luiz</t>
         </is>
       </c>
       <c r="B61" s="27" t="inlineStr">
         <is>
-          <t>Equipe 4</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="C61" s="28" t="inlineStr">
         <is>
-          <t>16988946</t>
+          <t>17073275</t>
         </is>
       </c>
       <c r="D61" s="27" t="inlineStr">
         <is>
-          <t>435 - JARDIM PRIMOR</t>
+          <t>418 - CENTRO 4</t>
         </is>
       </c>
       <c r="E61" s="27" t="inlineStr">
         <is>
-          <t>Q022</t>
+          <t>Q011</t>
         </is>
       </c>
       <c r="F61" s="27" t="inlineStr">
         <is>
-          <t>Rua PIRACICABA</t>
+          <t>Avenida BRASIL</t>
         </is>
       </c>
       <c r="G61" s="27" t="inlineStr">
         <is>
-          <t>32 - R</t>
+          <t>3986 - R</t>
         </is>
       </c>
       <c r="H61" s="27" t="inlineStr">
         <is>
-          <t>17/08/2026 08:50</t>
+          <t>19/08/2026 10:19</t>
         </is>
       </c>
       <c r="I61" s="27" t="inlineStr">
         <is>
-          <t>17/08/2026 09:06</t>
+          <t>19/08/2026 10:35</t>
         </is>
       </c>
       <c r="J61" s="27" t="n">
@@ -26037,47 +25613,47 @@
     <row r="62">
       <c r="A62" s="27" t="inlineStr">
         <is>
-          <t>Suely Aguiar Alves Luiz</t>
+          <t>Gisele Lopes Justiniano</t>
         </is>
       </c>
       <c r="B62" s="27" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="C62" s="28" t="inlineStr">
         <is>
-          <t>17017093</t>
+          <t>16988946</t>
         </is>
       </c>
       <c r="D62" s="27" t="inlineStr">
         <is>
-          <t>420 - FERROVIARIA</t>
+          <t>435 - JARDIM PRIMOR</t>
         </is>
       </c>
       <c r="E62" s="27" t="inlineStr">
         <is>
-          <t>Q013</t>
+          <t>Q022</t>
         </is>
       </c>
       <c r="F62" s="27" t="inlineStr">
         <is>
-          <t>Travessa PROJETADA 06 FERROVIARIA</t>
+          <t>Rua PIRACICABA</t>
         </is>
       </c>
       <c r="G62" s="27" t="inlineStr">
         <is>
-          <t>69 - R</t>
+          <t>32 - R</t>
         </is>
       </c>
       <c r="H62" s="27" t="inlineStr">
         <is>
-          <t>17/08/2026 15:44</t>
+          <t>17/08/2026 08:50</t>
         </is>
       </c>
       <c r="I62" s="27" t="inlineStr">
         <is>
-          <t>17/08/2026 16:00</t>
+          <t>17/08/2026 09:06</t>
         </is>
       </c>
       <c r="J62" s="27" t="n">

--- a/data/historico/semana_320.xlsx
+++ b/data/historico/semana_320.xlsx
@@ -30,8 +30,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Visitas Acima de 15min'!$A$2:$J$64</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Fora do Expediente'!$A$2:$K$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Visitas no Almoço'!$A$2:$I$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Ausências'!$A$2:$G$56</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Cronograma'!$A$2:$D$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Ausências'!$A$2:$G$52</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Cronograma'!$A$2:$D$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Ponto Estratégico'!$A$2:$AE$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Ranking'!$A$2:$H$40</definedName>
   </definedNames>
@@ -5100,7 +5100,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5112,7 +5112,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>CRONOGRAMA — CHUVA/FOLGA/ATESTADO/REUNIÃO/FÉRIAS (7 registros) — EXCLUÍDOS DA ABA 'AUSÊNCIAS'. Edite em data/cronograma_ausencias.json (use cronograma_editor.html).</t>
+          <t>CRONOGRAMA — CHUVA/FOLGA/ATESTADO/REUNIÃO/FÉRIAS (8 registros) — EXCLUÍDOS DA ABA 'AUSÊNCIAS'. Edite em data/cronograma_ausencias.json (use cronograma_editor.html).</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5215,7 +5215,7 @@
       </c>
       <c r="B6" s="38" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="C6" s="38" t="inlineStr">
@@ -5237,7 +5237,7 @@
       </c>
       <c r="B7" s="38" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="C7" s="38" t="inlineStr">
@@ -5259,7 +5259,7 @@
       </c>
       <c r="B8" s="38" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="C8" s="38" t="inlineStr">
@@ -5295,8 +5295,30 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" s="38" t="inlineStr">
+        <is>
+          <t>20/08/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="38" t="inlineStr">
+        <is>
+          <t>28/08/2026</t>
+        </is>
+      </c>
+      <c r="C10" s="38" t="inlineStr">
+        <is>
+          <t>Férias/Atestado (automático)</t>
+        </is>
+      </c>
+      <c r="D10" s="38" t="inlineStr">
+        <is>
+          <t>Alana Amanda Fernandes Ovelar</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:D9"/>
+  <autoFilter ref="A2:D10"/>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>
   </mergeCells>
@@ -7661,7 +7683,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Geancarlos Ferreira Barrios</t>
+          <t>Alana Amanda Fernandes Ovelar</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -7670,13 +7692,13 @@
         </is>
       </c>
       <c r="D10" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G10" s="4" t="n">
         <v>100</v>
@@ -7693,7 +7715,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Naime Cristina Freitas</t>
+          <t>Geancarlos Ferreira Barrios</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -7708,7 +7730,7 @@
         <v>14</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G11" s="4" t="n">
         <v>100</v>
@@ -7725,7 +7747,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Rosalina Beniel Vargas</t>
+          <t>Naime Cristina Freitas</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -7757,7 +7779,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Selba Ramona Afonso</t>
+          <t>Rosalina Beniel Vargas</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -7772,7 +7794,7 @@
         <v>14</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G13" s="4" t="n">
         <v>100</v>
@@ -7789,25 +7811,25 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Adriana de Jesus Saraiva</t>
+          <t>Selba Ramona Afonso</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 3</t>
         </is>
       </c>
       <c r="D14" s="4" t="n">
         <v>5</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>99.2</v>
+        <v>100</v>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
@@ -7821,25 +7843,25 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Marco Antonio Ayala de Matos Freitas</t>
+          <t>Adriana de Jesus Saraiva</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="D15" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F15" s="4" t="n">
         <v>1</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>98.7</v>
+        <v>99.2</v>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
@@ -7853,25 +7875,25 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Fabiana de Figueredo Vieira</t>
+          <t>Marco Antonio Ayala de Matos Freitas</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 3</t>
         </is>
       </c>
       <c r="D16" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E16" s="4" t="n">
         <v>14</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>98.5</v>
+        <v>98.7</v>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
@@ -7885,25 +7907,25 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Miglidiane Maciel Ajala</t>
+          <t>Fabiana de Figueredo Vieira</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="D17" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E17" s="4" t="n">
         <v>14</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>98.2</v>
+        <v>98.5</v>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
@@ -7917,25 +7939,25 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Cris Milene Cardenas da Silva</t>
+          <t>Miglidiane Maciel Ajala</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 3</t>
         </is>
       </c>
       <c r="D18" s="4" t="n">
         <v>5</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>97.90000000000001</v>
+        <v>98.2</v>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
@@ -7949,7 +7971,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Ana Gabriela Silva Garcete</t>
+          <t>Cris Milene Cardenas da Silva</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -7967,7 +7989,7 @@
         <v>1</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>97.09999999999999</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
@@ -7981,25 +8003,25 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>Silvina Regina de Souza Valiente</t>
+          <t>Ana Gabriela Silva Garcete</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>Equipe 4</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="D20" s="4" t="n">
         <v>5</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F20" s="4" t="n">
         <v>1</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>95.5</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
@@ -8013,7 +8035,7 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Gisele Lopes Justiniano</t>
+          <t>Silvina Regina de Souza Valiente</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -8028,10 +8050,10 @@
         <v>13</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>93.8</v>
+        <v>95.5</v>
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
@@ -8045,25 +8067,25 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>Claine Luisa Figueiredo Torraca</t>
+          <t>Gisele Lopes Justiniano</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="D22" s="4" t="n">
         <v>5</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>92.59999999999999</v>
+        <v>93.8</v>
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
@@ -8077,25 +8099,25 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Evelyn Santana Santos Oliveira</t>
+          <t>Claine Luisa Figueiredo Torraca</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 3</t>
         </is>
       </c>
       <c r="D23" s="4" t="n">
         <v>5</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>92.3</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
@@ -8109,61 +8131,61 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>Sara Eliane Talaveira de Oliveira</t>
+          <t>Evelyn Santana Santos Oliveira</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>Equipe 4</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="D24" s="4" t="n">
         <v>5</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F24" s="4" t="n">
         <v>2</v>
       </c>
       <c r="G24" s="4" t="n">
+        <v>92.3</v>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>🟢 EXCELENTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>Sara Eliane Talaveira de Oliveira</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="E25" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="F25" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G25" s="4" t="n">
         <v>90.90000000000001</v>
       </c>
-      <c r="H24" s="4" t="inlineStr">
+      <c r="H25" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="6" t="n">
-        <v>23</v>
-      </c>
-      <c r="B25" s="6" t="inlineStr">
-        <is>
-          <t>Alana Amanda Fernandes Ovelar</t>
-        </is>
-      </c>
-      <c r="C25" s="6" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="D25" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="E25" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="F25" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="G25" s="6" t="n">
-        <v>89.90000000000001</v>
-      </c>
-      <c r="H25" s="6" t="inlineStr">
-        <is>
-          <t>🟡 BOM</t>
         </is>
       </c>
     </row>
@@ -9220,7 +9242,7 @@
         </is>
       </c>
       <c r="D60" s="49" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E60" s="49" t="n">
         <v>1.5</v>
@@ -9232,7 +9254,7 @@
         <v>3</v>
       </c>
       <c r="H60" s="49" t="n">
-        <v>-15</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="61">
@@ -28143,7 +28165,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G56"/>
+  <dimension ref="A1:G52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -28158,7 +28180,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>POSSÍVEIS AUSÊNCIAS POR DIA/TURNO (54 registros) — CONFIRMAR COM A ESCALA (FOLGA/ATESTADO/FALTA)</t>
+          <t>POSSÍVEIS AUSÊNCIAS POR DIA/TURNO (50 registros) — CONFIRMAR COM A ESCALA (FOLGA/ATESTADO/FALTA)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -29362,11 +29384,11 @@
     </row>
     <row r="36">
       <c r="A36" s="36" t="n">
-        <v>2951</v>
+        <v>2918</v>
       </c>
       <c r="B36" s="36" t="inlineStr">
         <is>
-          <t>Alana Amanda Fernandes Ovelar</t>
+          <t>Claine Luisa Figueiredo Torraca</t>
         </is>
       </c>
       <c r="C36" s="36" t="inlineStr">
@@ -29397,11 +29419,11 @@
     </row>
     <row r="37">
       <c r="A37" s="36" t="n">
-        <v>2918</v>
+        <v>3038</v>
       </c>
       <c r="B37" s="36" t="inlineStr">
         <is>
-          <t>Claine Luisa Figueiredo Torraca</t>
+          <t>Naime Cristina Freitas</t>
         </is>
       </c>
       <c r="C37" s="36" t="inlineStr">
@@ -29432,11 +29454,11 @@
     </row>
     <row r="38">
       <c r="A38" s="36" t="n">
-        <v>3038</v>
+        <v>3128</v>
       </c>
       <c r="B38" s="36" t="inlineStr">
         <is>
-          <t>Naime Cristina Freitas</t>
+          <t>Rosalina Beniel Vargas</t>
         </is>
       </c>
       <c r="C38" s="36" t="inlineStr">
@@ -29467,11 +29489,11 @@
     </row>
     <row r="39">
       <c r="A39" s="36" t="n">
-        <v>3128</v>
+        <v>1938</v>
       </c>
       <c r="B39" s="36" t="inlineStr">
         <is>
-          <t>Rosalina Beniel Vargas</t>
+          <t>Marco Antonio Ayala de Matos Freitas</t>
         </is>
       </c>
       <c r="C39" s="36" t="inlineStr">
@@ -29481,17 +29503,17 @@
       </c>
       <c r="D39" s="36" t="inlineStr">
         <is>
-          <t>20/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
       <c r="E39" s="36" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="F39" s="36" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G39" s="36" t="inlineStr">
@@ -29502,26 +29524,26 @@
     </row>
     <row r="40">
       <c r="A40" s="36" t="n">
-        <v>2951</v>
+        <v>110</v>
       </c>
       <c r="B40" s="36" t="inlineStr">
         <is>
-          <t>Alana Amanda Fernandes Ovelar</t>
+          <t>Anderson Jose de Santana</t>
         </is>
       </c>
       <c r="C40" s="36" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="D40" s="36" t="inlineStr">
         <is>
-          <t>20/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
       <c r="E40" s="36" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="F40" s="36" t="inlineStr">
@@ -29537,31 +29559,31 @@
     </row>
     <row r="41">
       <c r="A41" s="36" t="n">
-        <v>2951</v>
+        <v>149</v>
       </c>
       <c r="B41" s="36" t="inlineStr">
         <is>
-          <t>Alana Amanda Fernandes Ovelar</t>
+          <t>Kátia Cilene Silveira Machado</t>
         </is>
       </c>
       <c r="C41" s="36" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="D41" s="36" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
       <c r="E41" s="36" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="F41" s="36" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G41" s="36" t="inlineStr">
@@ -29572,31 +29594,31 @@
     </row>
     <row r="42">
       <c r="A42" s="36" t="n">
-        <v>2951</v>
+        <v>80</v>
       </c>
       <c r="B42" s="36" t="inlineStr">
         <is>
-          <t>Alana Amanda Fernandes Ovelar</t>
+          <t>Gisele Lopes Justiniano</t>
         </is>
       </c>
       <c r="C42" s="36" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="D42" s="36" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>20/08/2026</t>
         </is>
       </c>
       <c r="E42" s="36" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="F42" s="36" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G42" s="36" t="inlineStr">
@@ -29607,31 +29629,31 @@
     </row>
     <row r="43">
       <c r="A43" s="36" t="n">
-        <v>1938</v>
+        <v>1943</v>
       </c>
       <c r="B43" s="36" t="inlineStr">
         <is>
-          <t>Marco Antonio Ayala de Matos Freitas</t>
+          <t>Juliana Patricia Goncalves</t>
         </is>
       </c>
       <c r="C43" s="36" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="D43" s="36" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>20/08/2026</t>
         </is>
       </c>
       <c r="E43" s="36" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="F43" s="36" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G43" s="36" t="inlineStr">
@@ -29642,11 +29664,11 @@
     </row>
     <row r="44">
       <c r="A44" s="36" t="n">
-        <v>110</v>
+        <v>2789</v>
       </c>
       <c r="B44" s="36" t="inlineStr">
         <is>
-          <t>Anderson Jose de Santana</t>
+          <t>Kariele Jackeline Rodrigues Silva</t>
         </is>
       </c>
       <c r="C44" s="36" t="inlineStr">
@@ -29656,17 +29678,17 @@
       </c>
       <c r="D44" s="36" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>20/08/2026</t>
         </is>
       </c>
       <c r="E44" s="36" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="F44" s="36" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G44" s="36" t="inlineStr">
@@ -29691,17 +29713,17 @@
       </c>
       <c r="D45" s="36" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>20/08/2026</t>
         </is>
       </c>
       <c r="E45" s="36" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="F45" s="36" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G45" s="36" t="inlineStr">
@@ -29712,11 +29734,11 @@
     </row>
     <row r="46">
       <c r="A46" s="36" t="n">
-        <v>80</v>
+        <v>1942</v>
       </c>
       <c r="B46" s="36" t="inlineStr">
         <is>
-          <t>Gisele Lopes Justiniano</t>
+          <t>Rafael Ramos Recalde</t>
         </is>
       </c>
       <c r="C46" s="36" t="inlineStr">
@@ -29747,11 +29769,11 @@
     </row>
     <row r="47">
       <c r="A47" s="36" t="n">
-        <v>1943</v>
+        <v>1996</v>
       </c>
       <c r="B47" s="36" t="inlineStr">
         <is>
-          <t>Juliana Patricia Goncalves</t>
+          <t>Sara Eliane Talaveira de Oliveira</t>
         </is>
       </c>
       <c r="C47" s="36" t="inlineStr">
@@ -29782,11 +29804,11 @@
     </row>
     <row r="48">
       <c r="A48" s="36" t="n">
-        <v>2789</v>
+        <v>86</v>
       </c>
       <c r="B48" s="36" t="inlineStr">
         <is>
-          <t>Kariele Jackeline Rodrigues Silva</t>
+          <t>Silvina Regina de Souza Valiente</t>
         </is>
       </c>
       <c r="C48" s="36" t="inlineStr">
@@ -29817,11 +29839,11 @@
     </row>
     <row r="49">
       <c r="A49" s="36" t="n">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="B49" s="36" t="inlineStr">
         <is>
-          <t>Kátia Cilene Silveira Machado</t>
+          <t>Walquiria Araujo Flores</t>
         </is>
       </c>
       <c r="C49" s="36" t="inlineStr">
@@ -29852,11 +29874,11 @@
     </row>
     <row r="50">
       <c r="A50" s="36" t="n">
-        <v>1942</v>
+        <v>80</v>
       </c>
       <c r="B50" s="36" t="inlineStr">
         <is>
-          <t>Rafael Ramos Recalde</t>
+          <t>Gisele Lopes Justiniano</t>
         </is>
       </c>
       <c r="C50" s="36" t="inlineStr">
@@ -29866,12 +29888,12 @@
       </c>
       <c r="D50" s="36" t="inlineStr">
         <is>
-          <t>20/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
       <c r="E50" s="36" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="F50" s="36" t="inlineStr">
@@ -29887,11 +29909,11 @@
     </row>
     <row r="51">
       <c r="A51" s="36" t="n">
-        <v>1996</v>
+        <v>1942</v>
       </c>
       <c r="B51" s="36" t="inlineStr">
         <is>
-          <t>Sara Eliane Talaveira de Oliveira</t>
+          <t>Rafael Ramos Recalde</t>
         </is>
       </c>
       <c r="C51" s="36" t="inlineStr">
@@ -29901,12 +29923,12 @@
       </c>
       <c r="D51" s="36" t="inlineStr">
         <is>
-          <t>20/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
       <c r="E51" s="36" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="F51" s="36" t="inlineStr">
@@ -29922,11 +29944,11 @@
     </row>
     <row r="52">
       <c r="A52" s="36" t="n">
-        <v>86</v>
+        <v>1996</v>
       </c>
       <c r="B52" s="36" t="inlineStr">
         <is>
-          <t>Silvina Regina de Souza Valiente</t>
+          <t>Sara Eliane Talaveira de Oliveira</t>
         </is>
       </c>
       <c r="C52" s="36" t="inlineStr">
@@ -29936,12 +29958,12 @@
       </c>
       <c r="D52" s="36" t="inlineStr">
         <is>
-          <t>20/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
       <c r="E52" s="36" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="F52" s="36" t="inlineStr">
@@ -29955,148 +29977,8 @@
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="36" t="n">
-        <v>157</v>
-      </c>
-      <c r="B53" s="36" t="inlineStr">
-        <is>
-          <t>Walquiria Araujo Flores</t>
-        </is>
-      </c>
-      <c r="C53" s="36" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="D53" s="36" t="inlineStr">
-        <is>
-          <t>20/08/2026</t>
-        </is>
-      </c>
-      <c r="E53" s="36" t="inlineStr">
-        <is>
-          <t>Quinta</t>
-        </is>
-      </c>
-      <c r="F53" s="36" t="inlineStr">
-        <is>
-          <t>Manhã</t>
-        </is>
-      </c>
-      <c r="G53" s="36" t="inlineStr">
-        <is>
-          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="36" t="n">
-        <v>80</v>
-      </c>
-      <c r="B54" s="36" t="inlineStr">
-        <is>
-          <t>Gisele Lopes Justiniano</t>
-        </is>
-      </c>
-      <c r="C54" s="36" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="D54" s="36" t="inlineStr">
-        <is>
-          <t>21/08/2026</t>
-        </is>
-      </c>
-      <c r="E54" s="36" t="inlineStr">
-        <is>
-          <t>Sexta</t>
-        </is>
-      </c>
-      <c r="F54" s="36" t="inlineStr">
-        <is>
-          <t>Manhã</t>
-        </is>
-      </c>
-      <c r="G54" s="36" t="inlineStr">
-        <is>
-          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="36" t="n">
-        <v>1942</v>
-      </c>
-      <c r="B55" s="36" t="inlineStr">
-        <is>
-          <t>Rafael Ramos Recalde</t>
-        </is>
-      </c>
-      <c r="C55" s="36" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="D55" s="36" t="inlineStr">
-        <is>
-          <t>21/08/2026</t>
-        </is>
-      </c>
-      <c r="E55" s="36" t="inlineStr">
-        <is>
-          <t>Sexta</t>
-        </is>
-      </c>
-      <c r="F55" s="36" t="inlineStr">
-        <is>
-          <t>Manhã</t>
-        </is>
-      </c>
-      <c r="G55" s="36" t="inlineStr">
-        <is>
-          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="36" t="n">
-        <v>1996</v>
-      </c>
-      <c r="B56" s="36" t="inlineStr">
-        <is>
-          <t>Sara Eliane Talaveira de Oliveira</t>
-        </is>
-      </c>
-      <c r="C56" s="36" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="D56" s="36" t="inlineStr">
-        <is>
-          <t>21/08/2026</t>
-        </is>
-      </c>
-      <c r="E56" s="36" t="inlineStr">
-        <is>
-          <t>Sexta</t>
-        </is>
-      </c>
-      <c r="F56" s="36" t="inlineStr">
-        <is>
-          <t>Manhã</t>
-        </is>
-      </c>
-      <c r="G56" s="36" t="inlineStr">
-        <is>
-          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A2:G56"/>
+  <autoFilter ref="A2:G52"/>
   <mergeCells count="1">
     <mergeCell ref="A1:G1"/>
   </mergeCells>

--- a/data/historico/semana_320.xlsx
+++ b/data/historico/semana_320.xlsx
@@ -30,7 +30,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Visitas Acima de 15min'!$A$2:$J$64</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Fora do Expediente'!$A$2:$K$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Visitas no Almoço'!$A$2:$I$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Ausências'!$A$2:$G$52</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Ausências'!$A$2:$G$51</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Cronograma'!$A$2:$D$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Ponto Estratégico'!$A$2:$AE$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Ranking'!$A$2:$H$40</definedName>
@@ -5171,7 +5171,7 @@
       </c>
       <c r="B4" s="38" t="inlineStr">
         <is>
-          <t>17/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="C4" s="38" t="inlineStr">
@@ -7698,7 +7698,7 @@
         <v>15</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G10" s="4" t="n">
         <v>100</v>
@@ -9110,7 +9110,7 @@
       </c>
       <c r="C56" s="48" t="inlineStr">
         <is>
-          <t>Bônus: nenhuma visita rápida no período</t>
+          <t>Bônus: nenhum turno sem lançamento no período</t>
         </is>
       </c>
       <c r="D56" s="48" t="n">
@@ -9142,55 +9142,55 @@
       </c>
       <c r="C57" s="48" t="inlineStr">
         <is>
+          <t>Bônus: nenhuma visita rápida no período</t>
+        </is>
+      </c>
+      <c r="D57" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="E57" s="48" t="n">
+        <v>5</v>
+      </c>
+      <c r="F57" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="G57" s="48" t="n">
+        <v>5</v>
+      </c>
+      <c r="H57" s="48" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="48" t="inlineStr">
+        <is>
+          <t>Alana Amanda Fernandes Ovelar</t>
+        </is>
+      </c>
+      <c r="B58" s="48" t="inlineStr">
+        <is>
+          <t>Equipe 3</t>
+        </is>
+      </c>
+      <c r="C58" s="48" t="inlineStr">
+        <is>
           <t>Dia com meta diária batida</t>
         </is>
       </c>
-      <c r="D57" s="48" t="n">
-        <v>1</v>
-      </c>
-      <c r="E57" s="48" t="n">
-        <v>1</v>
-      </c>
-      <c r="F57" s="48" t="n">
-        <v>1</v>
-      </c>
-      <c r="G57" s="48" t="n">
-        <v>1</v>
-      </c>
-      <c r="H57" s="48" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="49" t="inlineStr">
-        <is>
-          <t>Alana Amanda Fernandes Ovelar</t>
-        </is>
-      </c>
-      <c r="B58" s="49" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C58" s="49" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D58" s="49" t="n">
-        <v>1</v>
-      </c>
-      <c r="E58" s="49" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F58" s="49" t="n">
-        <v>1</v>
-      </c>
-      <c r="G58" s="49" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H58" s="49" t="n">
-        <v>-0.5</v>
+      <c r="D58" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="E58" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="F58" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="G58" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="H58" s="48" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -9206,23 +9206,23 @@
       </c>
       <c r="C59" s="49" t="inlineStr">
         <is>
-          <t>Início manhã após 08h30</t>
+          <t>Dia sem bater a meta diária</t>
         </is>
       </c>
       <c r="D59" s="49" t="n">
         <v>1</v>
       </c>
       <c r="E59" s="49" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F59" s="49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G59" s="49" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="H59" s="49" t="n">
-        <v>-0.6</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="60">
@@ -9238,23 +9238,23 @@
       </c>
       <c r="C60" s="49" t="inlineStr">
         <is>
-          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
+          <t>Início manhã após 08h30</t>
         </is>
       </c>
       <c r="D60" s="49" t="n">
         <v>1</v>
       </c>
       <c r="E60" s="49" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="F60" s="49" t="n">
         <v>2</v>
       </c>
       <c r="G60" s="49" t="n">
-        <v>3</v>
+        <v>0.6</v>
       </c>
       <c r="H60" s="49" t="n">
-        <v>-3</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="61">
@@ -28165,7 +28165,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G52"/>
+  <dimension ref="A1:G51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -28180,7 +28180,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>POSSÍVEIS AUSÊNCIAS POR DIA/TURNO (50 registros) — CONFIRMAR COM A ESCALA (FOLGA/ATESTADO/FALTA)</t>
+          <t>POSSÍVEIS AUSÊNCIAS POR DIA/TURNO (49 registros) — CONFIRMAR COM A ESCALA (FOLGA/ATESTADO/FALTA)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -29279,11 +29279,11 @@
     </row>
     <row r="33">
       <c r="A33" s="36" t="n">
-        <v>2951</v>
+        <v>120</v>
       </c>
       <c r="B33" s="36" t="inlineStr">
         <is>
-          <t>Alana Amanda Fernandes Ovelar</t>
+          <t>Emidio Rainer Vilhalba</t>
         </is>
       </c>
       <c r="C33" s="36" t="inlineStr">
@@ -29303,7 +29303,7 @@
       </c>
       <c r="F33" s="36" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G33" s="36" t="inlineStr">
@@ -29328,17 +29328,17 @@
       </c>
       <c r="D34" s="36" t="inlineStr">
         <is>
-          <t>18/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
       <c r="E34" s="36" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="F34" s="36" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G34" s="36" t="inlineStr">
@@ -29349,11 +29349,11 @@
     </row>
     <row r="35">
       <c r="A35" s="36" t="n">
-        <v>120</v>
+        <v>2918</v>
       </c>
       <c r="B35" s="36" t="inlineStr">
         <is>
-          <t>Emidio Rainer Vilhalba</t>
+          <t>Claine Luisa Figueiredo Torraca</t>
         </is>
       </c>
       <c r="C35" s="36" t="inlineStr">
@@ -29363,12 +29363,12 @@
       </c>
       <c r="D35" s="36" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>20/08/2026</t>
         </is>
       </c>
       <c r="E35" s="36" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="F35" s="36" t="inlineStr">
@@ -29384,11 +29384,11 @@
     </row>
     <row r="36">
       <c r="A36" s="36" t="n">
-        <v>2918</v>
+        <v>3038</v>
       </c>
       <c r="B36" s="36" t="inlineStr">
         <is>
-          <t>Claine Luisa Figueiredo Torraca</t>
+          <t>Naime Cristina Freitas</t>
         </is>
       </c>
       <c r="C36" s="36" t="inlineStr">
@@ -29419,11 +29419,11 @@
     </row>
     <row r="37">
       <c r="A37" s="36" t="n">
-        <v>3038</v>
+        <v>3128</v>
       </c>
       <c r="B37" s="36" t="inlineStr">
         <is>
-          <t>Naime Cristina Freitas</t>
+          <t>Rosalina Beniel Vargas</t>
         </is>
       </c>
       <c r="C37" s="36" t="inlineStr">
@@ -29454,11 +29454,11 @@
     </row>
     <row r="38">
       <c r="A38" s="36" t="n">
-        <v>3128</v>
+        <v>1938</v>
       </c>
       <c r="B38" s="36" t="inlineStr">
         <is>
-          <t>Rosalina Beniel Vargas</t>
+          <t>Marco Antonio Ayala de Matos Freitas</t>
         </is>
       </c>
       <c r="C38" s="36" t="inlineStr">
@@ -29468,17 +29468,17 @@
       </c>
       <c r="D38" s="36" t="inlineStr">
         <is>
-          <t>20/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
       <c r="E38" s="36" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="F38" s="36" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G38" s="36" t="inlineStr">
@@ -29489,26 +29489,26 @@
     </row>
     <row r="39">
       <c r="A39" s="36" t="n">
-        <v>1938</v>
+        <v>110</v>
       </c>
       <c r="B39" s="36" t="inlineStr">
         <is>
-          <t>Marco Antonio Ayala de Matos Freitas</t>
+          <t>Anderson Jose de Santana</t>
         </is>
       </c>
       <c r="C39" s="36" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="D39" s="36" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
       <c r="E39" s="36" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="F39" s="36" t="inlineStr">
@@ -29524,11 +29524,11 @@
     </row>
     <row r="40">
       <c r="A40" s="36" t="n">
-        <v>110</v>
+        <v>149</v>
       </c>
       <c r="B40" s="36" t="inlineStr">
         <is>
-          <t>Anderson Jose de Santana</t>
+          <t>Kátia Cilene Silveira Machado</t>
         </is>
       </c>
       <c r="C40" s="36" t="inlineStr">
@@ -29559,11 +29559,11 @@
     </row>
     <row r="41">
       <c r="A41" s="36" t="n">
-        <v>149</v>
+        <v>80</v>
       </c>
       <c r="B41" s="36" t="inlineStr">
         <is>
-          <t>Kátia Cilene Silveira Machado</t>
+          <t>Gisele Lopes Justiniano</t>
         </is>
       </c>
       <c r="C41" s="36" t="inlineStr">
@@ -29573,17 +29573,17 @@
       </c>
       <c r="D41" s="36" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>20/08/2026</t>
         </is>
       </c>
       <c r="E41" s="36" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="F41" s="36" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G41" s="36" t="inlineStr">
@@ -29594,11 +29594,11 @@
     </row>
     <row r="42">
       <c r="A42" s="36" t="n">
-        <v>80</v>
+        <v>1943</v>
       </c>
       <c r="B42" s="36" t="inlineStr">
         <is>
-          <t>Gisele Lopes Justiniano</t>
+          <t>Juliana Patricia Goncalves</t>
         </is>
       </c>
       <c r="C42" s="36" t="inlineStr">
@@ -29629,11 +29629,11 @@
     </row>
     <row r="43">
       <c r="A43" s="36" t="n">
-        <v>1943</v>
+        <v>2789</v>
       </c>
       <c r="B43" s="36" t="inlineStr">
         <is>
-          <t>Juliana Patricia Goncalves</t>
+          <t>Kariele Jackeline Rodrigues Silva</t>
         </is>
       </c>
       <c r="C43" s="36" t="inlineStr">
@@ -29664,11 +29664,11 @@
     </row>
     <row r="44">
       <c r="A44" s="36" t="n">
-        <v>2789</v>
+        <v>149</v>
       </c>
       <c r="B44" s="36" t="inlineStr">
         <is>
-          <t>Kariele Jackeline Rodrigues Silva</t>
+          <t>Kátia Cilene Silveira Machado</t>
         </is>
       </c>
       <c r="C44" s="36" t="inlineStr">
@@ -29699,11 +29699,11 @@
     </row>
     <row r="45">
       <c r="A45" s="36" t="n">
-        <v>149</v>
+        <v>1942</v>
       </c>
       <c r="B45" s="36" t="inlineStr">
         <is>
-          <t>Kátia Cilene Silveira Machado</t>
+          <t>Rafael Ramos Recalde</t>
         </is>
       </c>
       <c r="C45" s="36" t="inlineStr">
@@ -29734,11 +29734,11 @@
     </row>
     <row r="46">
       <c r="A46" s="36" t="n">
-        <v>1942</v>
+        <v>1996</v>
       </c>
       <c r="B46" s="36" t="inlineStr">
         <is>
-          <t>Rafael Ramos Recalde</t>
+          <t>Sara Eliane Talaveira de Oliveira</t>
         </is>
       </c>
       <c r="C46" s="36" t="inlineStr">
@@ -29769,11 +29769,11 @@
     </row>
     <row r="47">
       <c r="A47" s="36" t="n">
-        <v>1996</v>
+        <v>86</v>
       </c>
       <c r="B47" s="36" t="inlineStr">
         <is>
-          <t>Sara Eliane Talaveira de Oliveira</t>
+          <t>Silvina Regina de Souza Valiente</t>
         </is>
       </c>
       <c r="C47" s="36" t="inlineStr">
@@ -29804,11 +29804,11 @@
     </row>
     <row r="48">
       <c r="A48" s="36" t="n">
-        <v>86</v>
+        <v>157</v>
       </c>
       <c r="B48" s="36" t="inlineStr">
         <is>
-          <t>Silvina Regina de Souza Valiente</t>
+          <t>Walquiria Araujo Flores</t>
         </is>
       </c>
       <c r="C48" s="36" t="inlineStr">
@@ -29839,11 +29839,11 @@
     </row>
     <row r="49">
       <c r="A49" s="36" t="n">
-        <v>157</v>
+        <v>80</v>
       </c>
       <c r="B49" s="36" t="inlineStr">
         <is>
-          <t>Walquiria Araujo Flores</t>
+          <t>Gisele Lopes Justiniano</t>
         </is>
       </c>
       <c r="C49" s="36" t="inlineStr">
@@ -29853,12 +29853,12 @@
       </c>
       <c r="D49" s="36" t="inlineStr">
         <is>
-          <t>20/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
       <c r="E49" s="36" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="F49" s="36" t="inlineStr">
@@ -29874,11 +29874,11 @@
     </row>
     <row r="50">
       <c r="A50" s="36" t="n">
-        <v>80</v>
+        <v>1942</v>
       </c>
       <c r="B50" s="36" t="inlineStr">
         <is>
-          <t>Gisele Lopes Justiniano</t>
+          <t>Rafael Ramos Recalde</t>
         </is>
       </c>
       <c r="C50" s="36" t="inlineStr">
@@ -29909,11 +29909,11 @@
     </row>
     <row r="51">
       <c r="A51" s="36" t="n">
-        <v>1942</v>
+        <v>1996</v>
       </c>
       <c r="B51" s="36" t="inlineStr">
         <is>
-          <t>Rafael Ramos Recalde</t>
+          <t>Sara Eliane Talaveira de Oliveira</t>
         </is>
       </c>
       <c r="C51" s="36" t="inlineStr">
@@ -29942,43 +29942,8 @@
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="36" t="n">
-        <v>1996</v>
-      </c>
-      <c r="B52" s="36" t="inlineStr">
-        <is>
-          <t>Sara Eliane Talaveira de Oliveira</t>
-        </is>
-      </c>
-      <c r="C52" s="36" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="D52" s="36" t="inlineStr">
-        <is>
-          <t>21/08/2026</t>
-        </is>
-      </c>
-      <c r="E52" s="36" t="inlineStr">
-        <is>
-          <t>Sexta</t>
-        </is>
-      </c>
-      <c r="F52" s="36" t="inlineStr">
-        <is>
-          <t>Manhã</t>
-        </is>
-      </c>
-      <c r="G52" s="36" t="inlineStr">
-        <is>
-          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A2:G52"/>
+  <autoFilter ref="A2:G51"/>
   <mergeCells count="1">
     <mergeCell ref="A1:G1"/>
   </mergeCells>
